--- a/Financial Analysis/FB.xlsx
+++ b/Financial Analysis/FB.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A0074C8-80E1-4032-80C1-A410EDB54FCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E97858FA-9D77-41FB-8DA1-14A10289ED72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{BFE532A1-2353-49AA-A72E-D2C0AD0DD88D}"/>
   </bookViews>
@@ -1024,14 +1024,14 @@
         <v>0</v>
       </c>
       <c r="D3" s="5">
-        <v>597.02</v>
+        <v>640.84</v>
       </c>
       <c r="E3" s="2">
-        <v>45781</v>
+        <v>45804</v>
       </c>
       <c r="F3" s="2">
         <f ca="1">TODAY()</f>
-        <v>45781</v>
+        <v>45804</v>
       </c>
       <c r="G3" s="2">
         <v>45868</v>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="D5" s="4">
         <f>D3*D4</f>
-        <v>1508669.54</v>
+        <v>1619402.6800000002</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D9" s="4">
         <f>D5-D8</f>
-        <v>1461100.54</v>
+        <v>1571833.6800000002</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
@@ -5993,7 +5993,7 @@
       </c>
       <c r="BI24" s="5">
         <f>Main!D3</f>
-        <v>597.02</v>
+        <v>640.84</v>
       </c>
     </row>
     <row r="25" spans="2:61" x14ac:dyDescent="0.3">
@@ -6005,7 +6005,7 @@
       </c>
       <c r="BI25" s="10">
         <f>BI23/BI24-1</f>
-        <v>7.9710547986230784E-2</v>
+        <v>5.8810176623484978E-3</v>
       </c>
     </row>
     <row r="26" spans="2:61" x14ac:dyDescent="0.3">

--- a/Financial Analysis/FB.xlsx
+++ b/Financial Analysis/FB.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E97858FA-9D77-41FB-8DA1-14A10289ED72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C17C0067-D4CA-49B3-8642-FDB2D2CAB839}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{BFE532A1-2353-49AA-A72E-D2C0AD0DD88D}"/>
   </bookViews>
@@ -363,10 +363,10 @@
     <t>META</t>
   </si>
   <si>
-    <t>Q125 8K</t>
-  </si>
-  <si>
     <t>Fairly valued</t>
+  </si>
+  <si>
+    <t>Q225 8K</t>
   </si>
 </sst>
 </file>
@@ -588,14 +588,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>35</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
@@ -612,7 +612,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21191220" y="0"/>
+          <a:off x="22395180" y="0"/>
           <a:ext cx="0" cy="6477000"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1024,17 +1024,17 @@
         <v>0</v>
       </c>
       <c r="D3" s="5">
-        <v>640.84</v>
+        <v>782.98</v>
       </c>
       <c r="E3" s="2">
-        <v>45804</v>
+        <v>45887</v>
       </c>
       <c r="F3" s="2">
         <f ca="1">TODAY()</f>
-        <v>45804</v>
+        <v>45887</v>
       </c>
       <c r="G3" s="2">
-        <v>45868</v>
+        <v>45960</v>
       </c>
       <c r="I3" s="14" t="s">
         <v>51</v>
@@ -1051,10 +1051,10 @@
         <v>1</v>
       </c>
       <c r="D4" s="4">
-        <v>2527</v>
+        <v>2518</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F4" s="1"/>
       <c r="I4" s="14" t="s">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="D5" s="4">
         <f>D3*D4</f>
-        <v>1619402.6800000002</v>
+        <v>1971543.6400000001</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -1092,11 +1092,11 @@
         <v>3</v>
       </c>
       <c r="D6" s="4">
-        <f>28750+41480+6168</f>
-        <v>76398</v>
+        <f>12005+35066+21988</f>
+        <v>69059</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F6" s="1"/>
       <c r="I6" s="14" t="s">
@@ -1114,11 +1114,11 @@
         <v>4</v>
       </c>
       <c r="D7" s="4">
-        <f>28829</f>
-        <v>28829</v>
+        <f>28832</f>
+        <v>28832</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F7" s="1"/>
       <c r="I7" s="17" t="s">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="D8" s="4">
         <f>D6-D7</f>
-        <v>47569</v>
+        <v>40227</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D9" s="4">
         <f>D5-D8</f>
-        <v>1571833.6800000002</v>
+        <v>1931316.6400000001</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
@@ -1441,16 +1441,15 @@
         <v>42314</v>
       </c>
       <c r="AJ3" s="8">
-        <f>AF3*1.12</f>
-        <v>43759.520000000004</v>
+        <v>47516</v>
       </c>
       <c r="AK3" s="8">
-        <f>AG3*1.1</f>
-        <v>44647.9</v>
+        <f>AG3*1.18</f>
+        <v>47895.02</v>
       </c>
       <c r="AL3" s="8">
-        <f>AH3*1.05</f>
-        <v>50804.25</v>
+        <f>AH3*1.1</f>
+        <v>53223.500000000007</v>
       </c>
       <c r="AN3" s="8">
         <f>SUM(C3:F3)</f>
@@ -1486,47 +1485,47 @@
       </c>
       <c r="AV3" s="8">
         <f>SUM(AI3:AL3)</f>
-        <v>181525.67</v>
+        <v>190948.52</v>
       </c>
       <c r="AW3" s="8">
-        <f>AV3*1.08</f>
-        <v>196047.72360000003</v>
+        <f>AV3*1.12</f>
+        <v>213862.34239999999</v>
       </c>
       <c r="AX3" s="8">
-        <f>AW3*1.05</f>
-        <v>205850.10978000003</v>
+        <f>AW3*1.08</f>
+        <v>230971.329792</v>
       </c>
       <c r="AY3" s="8">
-        <f>AX3*1.04</f>
-        <v>214084.11417120002</v>
+        <f>AX3*1.06</f>
+        <v>244829.60957952001</v>
       </c>
       <c r="AZ3" s="8">
-        <f>AY3*1.03</f>
-        <v>220506.63759633602</v>
+        <f>AY3*1.04</f>
+        <v>254622.79396270082</v>
       </c>
       <c r="BA3" s="8">
-        <f t="shared" ref="BA3" si="0">AZ3*1.02</f>
-        <v>224916.77034826274</v>
+        <f>AZ3*1.03</f>
+        <v>262261.47778158187</v>
       </c>
       <c r="BB3" s="8">
-        <f t="shared" ref="BB3" si="1">BA3*1.02</f>
-        <v>229415.105755228</v>
+        <f t="shared" ref="BB3" si="0">BA3*1.02</f>
+        <v>267506.70733721351</v>
       </c>
       <c r="BC3" s="8">
-        <f t="shared" ref="BC3" si="2">BB3*1.02</f>
-        <v>234003.40787033256</v>
+        <f t="shared" ref="BC3" si="1">BB3*1.02</f>
+        <v>272856.84148395777</v>
       </c>
       <c r="BD3" s="8">
-        <f t="shared" ref="BD3:BF3" si="3">BC3*1.01</f>
-        <v>236343.44194903589</v>
+        <f t="shared" ref="BD3" si="2">BC3*1.02</f>
+        <v>278313.97831363691</v>
       </c>
       <c r="BE3" s="8">
-        <f t="shared" si="3"/>
-        <v>238706.87636852625</v>
+        <f t="shared" ref="BE3" si="3">BD3*1.02</f>
+        <v>283880.25787990965</v>
       </c>
       <c r="BF3" s="8">
-        <f t="shared" si="3"/>
-        <v>241093.94513221152</v>
+        <f t="shared" ref="BF3" si="4">BE3*1.02</f>
+        <v>289557.86303750786</v>
       </c>
     </row>
     <row r="4" spans="2:165" x14ac:dyDescent="0.3">
@@ -1633,16 +1632,15 @@
         <v>7572</v>
       </c>
       <c r="AJ4" s="4">
-        <f t="shared" ref="AJ4:AL4" si="4">AJ3-AJ5</f>
-        <v>7876.7136000000028</v>
+        <v>8491</v>
       </c>
       <c r="AK4" s="4">
-        <f t="shared" si="4"/>
-        <v>8036.622000000003</v>
+        <f t="shared" ref="AK4:AL4" si="5">AK3-AK5</f>
+        <v>8621.1036000000022</v>
       </c>
       <c r="AL4" s="4">
-        <f t="shared" si="4"/>
-        <v>9144.7649999999994</v>
+        <f t="shared" si="5"/>
+        <v>9580.2300000000032</v>
       </c>
       <c r="AN4" s="4">
         <f>SUM(C4:F4)</f>
@@ -1678,47 +1676,47 @@
       </c>
       <c r="AV4" s="4">
         <f>SUM(AI4:AL4)</f>
-        <v>32630.100600000005</v>
+        <v>34264.333600000005</v>
       </c>
       <c r="AW4" s="4">
-        <f t="shared" ref="AW4:BA4" si="5">AW3-AW5</f>
-        <v>35288.590248000022</v>
+        <f t="shared" ref="AW4:BA4" si="6">AW3-AW5</f>
+        <v>38495.221632000001</v>
       </c>
       <c r="AX4" s="4">
-        <f t="shared" si="5"/>
-        <v>37053.019760400028</v>
+        <f t="shared" si="6"/>
+        <v>41574.839362560015</v>
       </c>
       <c r="AY4" s="4">
-        <f t="shared" si="5"/>
-        <v>38535.140550816024</v>
+        <f t="shared" si="6"/>
+        <v>44069.329724313604</v>
       </c>
       <c r="AZ4" s="4">
-        <f t="shared" si="5"/>
-        <v>39691.194767340494</v>
+        <f t="shared" si="6"/>
+        <v>45832.102913286159</v>
       </c>
       <c r="BA4" s="4">
-        <f t="shared" si="5"/>
-        <v>40485.018662687304</v>
+        <f t="shared" si="6"/>
+        <v>47207.066000684747</v>
       </c>
       <c r="BB4" s="4">
-        <f t="shared" ref="BB4:BF4" si="6">BB3-BB5</f>
-        <v>41294.71903594106</v>
+        <f t="shared" ref="BB4:BF4" si="7">BB3-BB5</f>
+        <v>48151.20732069845</v>
       </c>
       <c r="BC4" s="4">
-        <f t="shared" si="6"/>
-        <v>42120.613416659879</v>
+        <f t="shared" si="7"/>
+        <v>49114.231467112404</v>
       </c>
       <c r="BD4" s="4">
-        <f t="shared" si="6"/>
-        <v>42541.819550826476</v>
+        <f t="shared" si="7"/>
+        <v>50096.516096454667</v>
       </c>
       <c r="BE4" s="4">
-        <f t="shared" si="6"/>
-        <v>42967.237746334751</v>
+        <f t="shared" si="7"/>
+        <v>51098.446418383741</v>
       </c>
       <c r="BF4" s="4">
-        <f t="shared" si="6"/>
-        <v>43396.910123798094</v>
+        <f t="shared" si="7"/>
+        <v>52120.415346751426</v>
       </c>
     </row>
     <row r="5" spans="2:165" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -1726,224 +1724,224 @@
         <v>30</v>
       </c>
       <c r="C5" s="8">
-        <f t="shared" ref="C5:S5" si="7">C3-C4</f>
+        <f t="shared" ref="C5:S5" si="8">C3-C4</f>
         <v>6873</v>
       </c>
       <c r="D5" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>8084</v>
       </c>
       <c r="E5" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>8880</v>
       </c>
       <c r="F5" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>11361</v>
       </c>
       <c r="G5" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>10039</v>
       </c>
       <c r="H5" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>11017</v>
       </c>
       <c r="I5" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>11309</v>
       </c>
       <c r="J5" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>14118</v>
       </c>
       <c r="K5" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>12261</v>
       </c>
       <c r="L5" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>13559</v>
       </c>
       <c r="M5" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>14497</v>
       </c>
       <c r="N5" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>17590</v>
       </c>
       <c r="O5" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>14278</v>
       </c>
       <c r="P5" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>14858</v>
       </c>
       <c r="Q5" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>17276</v>
       </c>
       <c r="R5" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>22862</v>
       </c>
       <c r="S5" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>21040</v>
       </c>
       <c r="T5" s="8">
-        <f t="shared" ref="T5:U5" si="8">T3-T4</f>
+        <f t="shared" ref="T5:U5" si="9">T3-T4</f>
         <v>23678</v>
       </c>
       <c r="U5" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>23239</v>
       </c>
       <c r="V5" s="8">
-        <f t="shared" ref="V5" si="9">V3-V4</f>
+        <f t="shared" ref="V5" si="10">V3-V4</f>
         <v>27323</v>
       </c>
       <c r="W5" s="8">
-        <f t="shared" ref="W5:X5" si="10">W3-W4</f>
+        <f t="shared" ref="W5:X5" si="11">W3-W4</f>
         <v>21903</v>
       </c>
       <c r="X5" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>23630</v>
       </c>
       <c r="Y5" s="8">
-        <f t="shared" ref="Y5" si="11">Y3-Y4</f>
+        <f t="shared" ref="Y5" si="12">Y3-Y4</f>
         <v>21998</v>
       </c>
       <c r="Z5" s="8">
-        <f t="shared" ref="Z5" si="12">Z3-Z4</f>
+        <f t="shared" ref="Z5" si="13">Z3-Z4</f>
         <v>23829</v>
       </c>
       <c r="AA5" s="8">
-        <f t="shared" ref="AA5:AC5" si="13">AA3-AA4</f>
+        <f t="shared" ref="AA5:AC5" si="14">AA3-AA4</f>
         <v>22537</v>
       </c>
       <c r="AB5" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>26054</v>
       </c>
       <c r="AC5" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>28206</v>
       </c>
       <c r="AD5" s="8">
-        <f t="shared" ref="AD5" si="14">AD3-AD4</f>
+        <f t="shared" ref="AD5" si="15">AD3-AD4</f>
         <v>32416</v>
       </c>
       <c r="AE5" s="8">
-        <f t="shared" ref="AE5:AI5" si="15">AE3-AE4</f>
+        <f t="shared" ref="AE5:AJ5" si="16">AE3-AE4</f>
         <v>29815</v>
       </c>
       <c r="AF5" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>31763</v>
       </c>
       <c r="AG5" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>33214</v>
       </c>
       <c r="AH5" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>39546</v>
       </c>
       <c r="AI5" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>34742</v>
       </c>
       <c r="AJ5" s="8">
-        <f t="shared" ref="AJ5:AL5" si="16">AJ3*0.82</f>
-        <v>35882.806400000001</v>
+        <f t="shared" si="16"/>
+        <v>39025</v>
       </c>
       <c r="AK5" s="8">
-        <f t="shared" si="16"/>
-        <v>36611.277999999998</v>
+        <f t="shared" ref="AK5:AL5" si="17">AK3*0.82</f>
+        <v>39273.916399999995</v>
       </c>
       <c r="AL5" s="8">
-        <f t="shared" si="16"/>
-        <v>41659.485000000001</v>
+        <f t="shared" si="17"/>
+        <v>43643.270000000004</v>
       </c>
       <c r="AN5" s="8">
-        <f t="shared" ref="AN5:AU5" si="17">AN3-AN4</f>
+        <f t="shared" ref="AN5:AU5" si="18">AN3-AN4</f>
         <v>35198</v>
       </c>
       <c r="AO5" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>46483</v>
       </c>
       <c r="AP5" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>57907</v>
       </c>
       <c r="AQ5" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>69274</v>
       </c>
       <c r="AR5" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>95280</v>
       </c>
       <c r="AS5" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>91360</v>
       </c>
       <c r="AT5" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>109213</v>
       </c>
       <c r="AU5" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>134338</v>
       </c>
       <c r="AV5" s="8">
         <f>AV3*0.82</f>
-        <v>148851.04939999999</v>
+        <v>156577.78639999998</v>
       </c>
       <c r="AW5" s="8">
-        <f t="shared" ref="AW5:BF5" si="18">AW3*0.82</f>
-        <v>160759.133352</v>
+        <f t="shared" ref="AW5:BF5" si="19">AW3*0.82</f>
+        <v>175367.12076799999</v>
       </c>
       <c r="AX5" s="8">
-        <f t="shared" si="18"/>
-        <v>168797.0900196</v>
+        <f t="shared" si="19"/>
+        <v>189396.49042943999</v>
       </c>
       <c r="AY5" s="8">
-        <f t="shared" si="18"/>
-        <v>175548.973620384</v>
+        <f t="shared" si="19"/>
+        <v>200760.27985520641</v>
       </c>
       <c r="AZ5" s="8">
-        <f t="shared" si="18"/>
-        <v>180815.44282899552</v>
+        <f t="shared" si="19"/>
+        <v>208790.69104941466</v>
       </c>
       <c r="BA5" s="8">
-        <f t="shared" si="18"/>
-        <v>184431.75168557544</v>
+        <f t="shared" si="19"/>
+        <v>215054.41178089712</v>
       </c>
       <c r="BB5" s="8">
-        <f t="shared" si="18"/>
-        <v>188120.38671928694</v>
+        <f t="shared" si="19"/>
+        <v>219355.50001651506</v>
       </c>
       <c r="BC5" s="8">
-        <f t="shared" si="18"/>
-        <v>191882.79445367269</v>
+        <f t="shared" si="19"/>
+        <v>223742.61001684537</v>
       </c>
       <c r="BD5" s="8">
-        <f t="shared" si="18"/>
-        <v>193801.62239820941</v>
+        <f t="shared" si="19"/>
+        <v>228217.46221718224</v>
       </c>
       <c r="BE5" s="8">
-        <f t="shared" si="18"/>
-        <v>195739.6386221915</v>
+        <f t="shared" si="19"/>
+        <v>232781.81146152591</v>
       </c>
       <c r="BF5" s="8">
-        <f t="shared" si="18"/>
-        <v>197697.03500841343</v>
+        <f t="shared" si="19"/>
+        <v>237437.44769075644</v>
       </c>
     </row>
     <row r="6" spans="2:165" x14ac:dyDescent="0.3">
@@ -2050,8 +2048,7 @@
         <v>12150</v>
       </c>
       <c r="AJ6" s="4">
-        <f>AF6*1.18</f>
-        <v>12433.66</v>
+        <v>12942</v>
       </c>
       <c r="AK6" s="4">
         <f>AG6*1.13</f>
@@ -2095,47 +2092,47 @@
       </c>
       <c r="AV6" s="4">
         <f>SUM(AI6:AL6)</f>
-        <v>50246.27</v>
+        <v>50754.609999999993</v>
       </c>
       <c r="AW6" s="4">
         <f>AV6*1.06</f>
-        <v>53261.046199999997</v>
+        <v>53799.886599999998</v>
       </c>
       <c r="AX6" s="4">
         <f>AW6*1.04</f>
-        <v>55391.488047999999</v>
+        <v>55951.882063999998</v>
       </c>
       <c r="AY6" s="4">
         <f>AX6*1.03</f>
-        <v>57053.232689440003</v>
+        <v>57630.438525919999</v>
       </c>
       <c r="AZ6" s="4">
-        <f t="shared" ref="AZ6:BA6" si="19">AY6*1.03</f>
-        <v>58764.829670123203</v>
+        <f t="shared" ref="AZ6:BA6" si="20">AY6*1.03</f>
+        <v>59359.351681697597</v>
       </c>
       <c r="BA6" s="4">
-        <f t="shared" si="19"/>
-        <v>60527.774560226899</v>
+        <f t="shared" si="20"/>
+        <v>61140.132232148528</v>
       </c>
       <c r="BB6" s="4">
         <f>BA6*1.02</f>
-        <v>61738.33005143144</v>
+        <v>62362.9348767915</v>
       </c>
       <c r="BC6" s="4">
-        <f t="shared" ref="BC6:BF6" si="20">BB6*1.02</f>
-        <v>62973.096652460066</v>
+        <f t="shared" ref="BC6:BF6" si="21">BB6*1.02</f>
+        <v>63610.193574327328</v>
       </c>
       <c r="BD6" s="4">
-        <f t="shared" si="20"/>
-        <v>64232.558585509272</v>
+        <f t="shared" si="21"/>
+        <v>64882.397445813876</v>
       </c>
       <c r="BE6" s="4">
-        <f t="shared" si="20"/>
-        <v>65517.209757219462</v>
+        <f t="shared" si="21"/>
+        <v>66180.045394730158</v>
       </c>
       <c r="BF6" s="4">
-        <f t="shared" si="20"/>
-        <v>66827.553952363858</v>
+        <f t="shared" si="21"/>
+        <v>67503.646302624766</v>
       </c>
     </row>
     <row r="7" spans="2:165" x14ac:dyDescent="0.3">
@@ -2242,16 +2239,15 @@
         <v>2757</v>
       </c>
       <c r="AJ7" s="4">
-        <f t="shared" ref="AJ7:AL7" si="21">AJ3*0.065</f>
-        <v>2844.3688000000002</v>
+        <v>2979</v>
       </c>
       <c r="AK7" s="4">
-        <f t="shared" si="21"/>
-        <v>2902.1135000000004</v>
+        <f t="shared" ref="AK7:AL7" si="22">AK3*0.065</f>
+        <v>3113.1763000000001</v>
       </c>
       <c r="AL7" s="4">
-        <f t="shared" si="21"/>
-        <v>3302.2762499999999</v>
+        <f t="shared" si="22"/>
+        <v>3459.5275000000006</v>
       </c>
       <c r="AN7" s="4">
         <f>SUM(C7:F7)</f>
@@ -2287,47 +2283,47 @@
       </c>
       <c r="AV7" s="4">
         <f>SUM(AI7:AL7)</f>
-        <v>11805.758549999999</v>
+        <v>12308.703799999999</v>
       </c>
       <c r="AW7" s="4">
         <f>AW3*0.065</f>
-        <v>12743.102034000001</v>
+        <v>13901.052256000001</v>
       </c>
       <c r="AX7" s="4">
-        <f t="shared" ref="AX7:BF7" si="22">AX3*0.065</f>
-        <v>13380.257135700002</v>
+        <f t="shared" ref="AX7:BF7" si="23">AX3*0.065</f>
+        <v>15013.136436480001</v>
       </c>
       <c r="AY7" s="4">
-        <f t="shared" si="22"/>
-        <v>13915.467421128002</v>
+        <f t="shared" si="23"/>
+        <v>15913.924622668801</v>
       </c>
       <c r="AZ7" s="4">
-        <f t="shared" si="22"/>
-        <v>14332.931443761841</v>
+        <f t="shared" si="23"/>
+        <v>16550.481607575555</v>
       </c>
       <c r="BA7" s="4">
-        <f t="shared" si="22"/>
-        <v>14619.590072637078</v>
+        <f t="shared" si="23"/>
+        <v>17046.996055802822</v>
       </c>
       <c r="BB7" s="4">
-        <f t="shared" si="22"/>
-        <v>14911.981874089821</v>
+        <f t="shared" si="23"/>
+        <v>17387.935976918878</v>
       </c>
       <c r="BC7" s="4">
-        <f t="shared" si="22"/>
-        <v>15210.221511571617</v>
+        <f t="shared" si="23"/>
+        <v>17735.694696457256</v>
       </c>
       <c r="BD7" s="4">
-        <f t="shared" si="22"/>
-        <v>15362.323726687333</v>
+        <f t="shared" si="23"/>
+        <v>18090.4085903864</v>
       </c>
       <c r="BE7" s="4">
-        <f t="shared" si="22"/>
-        <v>15515.946963954208</v>
+        <f t="shared" si="23"/>
+        <v>18452.216762194126</v>
       </c>
       <c r="BF7" s="4">
-        <f t="shared" si="22"/>
-        <v>15671.10643359375</v>
+        <f t="shared" si="23"/>
+        <v>18821.261097438011</v>
       </c>
     </row>
     <row r="8" spans="2:165" x14ac:dyDescent="0.3">
@@ -2435,15 +2431,14 @@
         <v>2280</v>
       </c>
       <c r="AJ8" s="4">
-        <f t="shared" ref="AJ8:AL8" si="23">AF8*1.02</f>
-        <v>3731.16</v>
+        <v>2663</v>
       </c>
       <c r="AK8" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" ref="AK8:AL8" si="24">AG8*1.02</f>
         <v>1902.3</v>
       </c>
       <c r="AL8" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>2357.2200000000003</v>
       </c>
       <c r="AN8" s="4">
@@ -2480,47 +2475,47 @@
       </c>
       <c r="AV8" s="4">
         <f>SUM(AI8:AL8)</f>
-        <v>10270.68</v>
+        <v>9202.52</v>
       </c>
       <c r="AW8" s="4">
-        <f t="shared" ref="AW8:BF8" si="24">AV8*1.01</f>
-        <v>10373.3868</v>
+        <f t="shared" ref="AW8:BF8" si="25">AV8*1.01</f>
+        <v>9294.5452000000005</v>
       </c>
       <c r="AX8" s="4">
-        <f t="shared" si="24"/>
-        <v>10477.120668</v>
+        <f t="shared" si="25"/>
+        <v>9387.4906520000004</v>
       </c>
       <c r="AY8" s="4">
-        <f t="shared" si="24"/>
-        <v>10581.891874679999</v>
+        <f t="shared" si="25"/>
+        <v>9481.3655585200013</v>
       </c>
       <c r="AZ8" s="4">
-        <f t="shared" si="24"/>
-        <v>10687.710793426799</v>
+        <f t="shared" si="25"/>
+        <v>9576.179214105201</v>
       </c>
       <c r="BA8" s="4">
-        <f t="shared" si="24"/>
-        <v>10794.587901361067</v>
+        <f t="shared" si="25"/>
+        <v>9671.9410062462539</v>
       </c>
       <c r="BB8" s="4">
-        <f t="shared" si="24"/>
-        <v>10902.533780374677</v>
+        <f t="shared" si="25"/>
+        <v>9768.6604163087159</v>
       </c>
       <c r="BC8" s="4">
-        <f t="shared" si="24"/>
-        <v>11011.559118178424</v>
+        <f t="shared" si="25"/>
+        <v>9866.3470204718033</v>
       </c>
       <c r="BD8" s="4">
-        <f t="shared" si="24"/>
-        <v>11121.674709360208</v>
+        <f t="shared" si="25"/>
+        <v>9965.0104906765209</v>
       </c>
       <c r="BE8" s="4">
-        <f t="shared" si="24"/>
-        <v>11232.89145645381</v>
+        <f t="shared" si="25"/>
+        <v>10064.660595583286</v>
       </c>
       <c r="BF8" s="4">
-        <f t="shared" si="24"/>
-        <v>11345.220371018348</v>
+        <f t="shared" si="25"/>
+        <v>10165.307201539119</v>
       </c>
     </row>
     <row r="9" spans="2:165" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2528,148 +2523,148 @@
         <v>31</v>
       </c>
       <c r="C9" s="8">
-        <f t="shared" ref="C9:V9" si="25">C5-C6-C7-C8</f>
+        <f t="shared" ref="C9:V9" si="26">C5-C6-C7-C8</f>
         <v>3327</v>
       </c>
       <c r="D9" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>4401</v>
       </c>
       <c r="E9" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>5122</v>
       </c>
       <c r="F9" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>7352</v>
       </c>
       <c r="G9" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>5449</v>
       </c>
       <c r="H9" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>5863</v>
       </c>
       <c r="I9" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>5781</v>
       </c>
       <c r="J9" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>7820</v>
       </c>
       <c r="K9" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>3317</v>
       </c>
       <c r="L9" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>4606</v>
       </c>
       <c r="M9" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>7185</v>
       </c>
       <c r="N9" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>8858</v>
       </c>
       <c r="O9" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>5893</v>
       </c>
       <c r="P9" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>5963</v>
       </c>
       <c r="Q9" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>8040</v>
       </c>
       <c r="R9" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>12775</v>
       </c>
       <c r="S9" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>11378</v>
       </c>
       <c r="T9" s="8">
-        <f t="shared" ref="T9:U9" si="26">T5-T6-T7-T8</f>
+        <f t="shared" ref="T9:U9" si="27">T5-T6-T7-T8</f>
         <v>12367</v>
       </c>
       <c r="U9" s="8">
+        <f t="shared" si="27"/>
+        <v>10423</v>
+      </c>
+      <c r="V9" s="8">
         <f t="shared" si="26"/>
-        <v>10423</v>
-      </c>
-      <c r="V9" s="8">
-        <f t="shared" si="25"/>
         <v>12585</v>
       </c>
       <c r="W9" s="8">
-        <f t="shared" ref="W9:X9" si="27">W5-W6-W7-W8</f>
+        <f t="shared" ref="W9:X9" si="28">W5-W6-W7-W8</f>
         <v>8524</v>
       </c>
       <c r="X9" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>8358</v>
       </c>
       <c r="Y9" s="8">
-        <f t="shared" ref="Y9" si="28">Y5-Y6-Y7-Y8</f>
+        <f t="shared" ref="Y9" si="29">Y5-Y6-Y7-Y8</f>
         <v>5664</v>
       </c>
       <c r="Z9" s="8">
-        <f t="shared" ref="Z9" si="29">Z5-Z6-Z7-Z8</f>
+        <f t="shared" ref="Z9" si="30">Z5-Z6-Z7-Z8</f>
         <v>6399</v>
       </c>
       <c r="AA9" s="8">
-        <f t="shared" ref="AA9:AC9" si="30">AA5-AA6-AA7-AA8</f>
+        <f t="shared" ref="AA9:AC9" si="31">AA5-AA6-AA7-AA8</f>
         <v>7227</v>
       </c>
       <c r="AB9" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>9392</v>
       </c>
       <c r="AC9" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>14018</v>
       </c>
       <c r="AD9" s="8">
-        <f t="shared" ref="AD9" si="31">AD5-AD6-AD7-AD8</f>
+        <f t="shared" ref="AD9" si="32">AD5-AD6-AD7-AD8</f>
         <v>16384</v>
       </c>
       <c r="AE9" s="8">
-        <f t="shared" ref="AE9:AL9" si="32">AE5-AE6-AE7-AE8</f>
+        <f t="shared" ref="AE9:AL9" si="33">AE5-AE6-AE7-AE8</f>
         <v>13818</v>
       </c>
       <c r="AF9" s="8">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>14847</v>
       </c>
       <c r="AG9" s="8">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>17350</v>
       </c>
       <c r="AH9" s="8">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>21815</v>
       </c>
       <c r="AI9" s="8">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>17555</v>
       </c>
       <c r="AJ9" s="8">
-        <f t="shared" si="32"/>
-        <v>16873.617600000001</v>
+        <f t="shared" si="33"/>
+        <v>20441</v>
       </c>
       <c r="AK9" s="8">
-        <f t="shared" si="32"/>
-        <v>19176.854500000001</v>
+        <f t="shared" si="33"/>
+        <v>21628.430099999998</v>
       </c>
       <c r="AL9" s="8">
-        <f t="shared" si="32"/>
-        <v>22967.388750000002</v>
+        <f t="shared" si="33"/>
+        <v>24793.922500000004</v>
       </c>
       <c r="AN9" s="8">
         <f>AN5-AN6-AN7-AN8</f>
@@ -2688,64 +2683,64 @@
         <v>32671</v>
       </c>
       <c r="AR9" s="8">
-        <f t="shared" ref="AR9:BA9" si="33">AR5-AR6-AR7-AR8</f>
+        <f t="shared" ref="AR9:BA9" si="34">AR5-AR6-AR7-AR8</f>
         <v>46753</v>
       </c>
       <c r="AS9" s="8">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>28945</v>
       </c>
       <c r="AT9" s="8">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>47021</v>
       </c>
       <c r="AU9" s="8">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>67830</v>
       </c>
       <c r="AV9" s="8">
-        <f t="shared" si="33"/>
-        <v>76528.340850000008</v>
+        <f t="shared" si="34"/>
+        <v>84311.95259999999</v>
       </c>
       <c r="AW9" s="8">
-        <f t="shared" si="33"/>
-        <v>84381.598318000004</v>
+        <f t="shared" si="34"/>
+        <v>98371.636712000007</v>
       </c>
       <c r="AX9" s="8">
-        <f t="shared" si="33"/>
-        <v>89548.2241679</v>
+        <f t="shared" si="34"/>
+        <v>109043.98127696</v>
       </c>
       <c r="AY9" s="8">
-        <f t="shared" si="33"/>
-        <v>93998.381635135986</v>
+        <f t="shared" si="34"/>
+        <v>117734.5511480976</v>
       </c>
       <c r="AZ9" s="8">
-        <f t="shared" si="33"/>
-        <v>97029.970921683678</v>
+        <f t="shared" si="34"/>
+        <v>123304.67854603632</v>
       </c>
       <c r="BA9" s="8">
-        <f t="shared" si="33"/>
-        <v>98489.799151350395</v>
+        <f t="shared" si="34"/>
+        <v>127195.34248669952</v>
       </c>
       <c r="BB9" s="8">
-        <f t="shared" ref="BB9:BF9" si="34">BB5-BB6-BB7-BB8</f>
-        <v>100567.541013391</v>
+        <f t="shared" ref="BB9:BF9" si="35">BB5-BB6-BB7-BB8</f>
+        <v>129835.96874649597</v>
       </c>
       <c r="BC9" s="8">
-        <f t="shared" si="34"/>
-        <v>102687.91717146257</v>
+        <f t="shared" si="35"/>
+        <v>132530.37472558895</v>
       </c>
       <c r="BD9" s="8">
-        <f t="shared" si="34"/>
-        <v>103085.06537665259</v>
+        <f t="shared" si="35"/>
+        <v>135279.64569030545</v>
       </c>
       <c r="BE9" s="8">
-        <f t="shared" si="34"/>
-        <v>103473.59044456402</v>
+        <f t="shared" si="35"/>
+        <v>138084.88870901833</v>
       </c>
       <c r="BF9" s="8">
-        <f t="shared" si="34"/>
-        <v>103853.15425143746</v>
+        <f t="shared" si="35"/>
+        <v>140947.23308915456</v>
       </c>
     </row>
     <row r="10" spans="2:165" x14ac:dyDescent="0.3">
@@ -2852,15 +2847,14 @@
         <v>-827</v>
       </c>
       <c r="AJ10" s="4">
-        <f t="shared" ref="AJ10:AL10" si="35">AF10*1.02</f>
-        <v>-264.18</v>
+        <v>-93</v>
       </c>
       <c r="AK10" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" ref="AK10:AL10" si="36">AG10*1.02</f>
         <v>-481.44</v>
       </c>
       <c r="AL10" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>-191.76</v>
       </c>
       <c r="AN10" s="4">
@@ -2897,47 +2891,47 @@
       </c>
       <c r="AV10" s="4">
         <f>SUM(AI10:AL10)</f>
-        <v>-1764.38</v>
+        <v>-1593.2</v>
       </c>
       <c r="AW10" s="4">
-        <f t="shared" ref="AW10:BA10" si="36">-AV13*0.02</f>
-        <v>-1387.2018389600003</v>
+        <f t="shared" ref="AW10:BA10" si="37">-AV13*0.02</f>
+        <v>-1526.3737257599996</v>
       </c>
       <c r="AX10" s="4">
-        <f t="shared" si="36"/>
-        <v>-1509.5308827624958</v>
+        <f t="shared" si="37"/>
+        <v>-1758.2049837045761</v>
       </c>
       <c r="AY10" s="4">
-        <f t="shared" si="36"/>
-        <v>-1602.6164888916601</v>
+        <f t="shared" si="37"/>
+        <v>-1950.1184781876966</v>
       </c>
       <c r="AZ10" s="4">
-        <f t="shared" si="36"/>
-        <v>-1682.5775669828863</v>
+        <f t="shared" si="37"/>
+        <v>-2106.450185422621</v>
       </c>
       <c r="BA10" s="4">
-        <f t="shared" si="36"/>
-        <v>-1737.3408534005316</v>
+        <f t="shared" si="37"/>
+        <v>-2207.2358656736774</v>
       </c>
       <c r="BB10" s="4">
-        <f t="shared" ref="BB10" si="37">-BA13*0.02</f>
-        <v>-1763.9976640836162</v>
+        <f t="shared" ref="BB10" si="38">-BA13*0.02</f>
+        <v>-2277.4853790017683</v>
       </c>
       <c r="BC10" s="4">
-        <f t="shared" ref="BC10" si="38">-BB13*0.02</f>
-        <v>-1801.0350807235534</v>
+        <f t="shared" ref="BC10" si="39">-BB13*0.02</f>
+        <v>-2325.1967926087605</v>
       </c>
       <c r="BD10" s="4">
-        <f t="shared" ref="BD10" si="39">-BC13*0.02</f>
-        <v>-1839.0055596384759</v>
+        <f t="shared" ref="BD10" si="40">-BC13*0.02</f>
+        <v>-2373.4580587202795</v>
       </c>
       <c r="BE10" s="4">
-        <f t="shared" ref="BE10" si="40">-BD13*0.02</f>
-        <v>-1846.663648478723</v>
+        <f t="shared" ref="BE10" si="41">-BD13*0.02</f>
+        <v>-2422.6946259828528</v>
       </c>
       <c r="BF10" s="4">
-        <f t="shared" ref="BF10" si="41">-BE13*0.02</f>
-        <v>-1853.6364720375523</v>
+        <f t="shared" ref="BF10" si="42">-BE13*0.02</f>
+        <v>-2472.9334666960208</v>
       </c>
     </row>
     <row r="11" spans="2:165" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2945,148 +2939,148 @@
         <v>33</v>
       </c>
       <c r="C11" s="8">
-        <f t="shared" ref="C11:P11" si="42">C9-C10</f>
+        <f t="shared" ref="C11:P11" si="43">C9-C10</f>
         <v>3408</v>
       </c>
       <c r="D11" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>4488</v>
       </c>
       <c r="E11" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>5236</v>
       </c>
       <c r="F11" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>7462</v>
       </c>
       <c r="G11" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>5610</v>
       </c>
       <c r="H11" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>5868</v>
       </c>
       <c r="I11" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>5912</v>
       </c>
       <c r="J11" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>7971</v>
       </c>
       <c r="K11" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>3482</v>
       </c>
       <c r="L11" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>4812</v>
       </c>
       <c r="M11" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>7329</v>
       </c>
       <c r="N11" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>9169</v>
       </c>
       <c r="O11" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>5861</v>
       </c>
       <c r="P11" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>6131</v>
       </c>
       <c r="Q11" s="8">
-        <f t="shared" ref="Q11:V11" si="43">Q9-Q10</f>
+        <f t="shared" ref="Q11:V11" si="44">Q9-Q10</f>
         <v>8133</v>
       </c>
       <c r="R11" s="8">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>13055</v>
       </c>
       <c r="S11" s="8">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>11503</v>
       </c>
       <c r="T11" s="8">
-        <f t="shared" ref="T11:U11" si="44">T9-T10</f>
+        <f t="shared" ref="T11:U11" si="45">T9-T10</f>
         <v>12513</v>
       </c>
       <c r="U11" s="8">
+        <f t="shared" si="45"/>
+        <v>10565</v>
+      </c>
+      <c r="V11" s="8">
         <f t="shared" si="44"/>
-        <v>10565</v>
-      </c>
-      <c r="V11" s="8">
-        <f t="shared" si="43"/>
         <v>12702</v>
       </c>
       <c r="W11" s="8">
-        <f t="shared" ref="W11:X11" si="45">W9-W10</f>
+        <f t="shared" ref="W11:X11" si="46">W9-W10</f>
         <v>8908</v>
       </c>
       <c r="X11" s="8">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>8186</v>
       </c>
       <c r="Y11" s="8">
-        <f t="shared" ref="Y11" si="46">Y9-Y10</f>
+        <f t="shared" ref="Y11" si="47">Y9-Y10</f>
         <v>5576</v>
       </c>
       <c r="Z11" s="8">
-        <f t="shared" ref="Z11" si="47">Z9-Z10</f>
+        <f t="shared" ref="Z11" si="48">Z9-Z10</f>
         <v>6149</v>
       </c>
       <c r="AA11" s="8">
-        <f t="shared" ref="AA11:AC11" si="48">AA9-AA10</f>
+        <f t="shared" ref="AA11:AC11" si="49">AA9-AA10</f>
         <v>7307</v>
       </c>
       <c r="AB11" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>9293</v>
       </c>
       <c r="AC11" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>14290</v>
       </c>
       <c r="AD11" s="8">
-        <f t="shared" ref="AD11" si="49">AD9-AD10</f>
+        <f t="shared" ref="AD11" si="50">AD9-AD10</f>
         <v>16808</v>
       </c>
       <c r="AE11" s="8">
-        <f t="shared" ref="AE11:AL11" si="50">AE9-AE10</f>
+        <f t="shared" ref="AE11:AL11" si="51">AE9-AE10</f>
         <v>14183</v>
       </c>
       <c r="AF11" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>15106</v>
       </c>
       <c r="AG11" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>17822</v>
       </c>
       <c r="AH11" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>22003</v>
       </c>
       <c r="AI11" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>18382</v>
       </c>
       <c r="AJ11" s="8">
-        <f t="shared" si="50"/>
-        <v>17137.797600000002</v>
+        <f t="shared" si="51"/>
+        <v>20534</v>
       </c>
       <c r="AK11" s="8">
-        <f t="shared" si="50"/>
-        <v>19658.2945</v>
+        <f t="shared" si="51"/>
+        <v>22109.870099999996</v>
       </c>
       <c r="AL11" s="8">
-        <f t="shared" si="50"/>
-        <v>23159.14875</v>
+        <f t="shared" si="51"/>
+        <v>24985.682500000003</v>
       </c>
       <c r="AN11" s="8">
         <f>AN9-AN10</f>
@@ -3105,64 +3099,64 @@
         <v>33180</v>
       </c>
       <c r="AR11" s="8">
-        <f t="shared" ref="AR11:BA11" si="51">AR9-AR10</f>
+        <f t="shared" ref="AR11:BA11" si="52">AR9-AR10</f>
         <v>47283</v>
       </c>
       <c r="AS11" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>28819</v>
       </c>
       <c r="AT11" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>47698</v>
       </c>
       <c r="AU11" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>69114</v>
       </c>
       <c r="AV11" s="8">
-        <f t="shared" si="51"/>
-        <v>78292.720850000012</v>
+        <f t="shared" si="52"/>
+        <v>85905.152599999987</v>
       </c>
       <c r="AW11" s="8">
-        <f t="shared" si="51"/>
-        <v>85768.800156960002</v>
+        <f t="shared" si="52"/>
+        <v>99898.010437760007</v>
       </c>
       <c r="AX11" s="8">
-        <f t="shared" si="51"/>
-        <v>91057.755050662498</v>
+        <f t="shared" si="52"/>
+        <v>110802.18626066457</v>
       </c>
       <c r="AY11" s="8">
-        <f t="shared" si="51"/>
-        <v>95600.998124027639</v>
+        <f t="shared" si="52"/>
+        <v>119684.66962628529</v>
       </c>
       <c r="AZ11" s="8">
-        <f t="shared" si="51"/>
-        <v>98712.548488666565</v>
+        <f t="shared" si="52"/>
+        <v>125411.12873145894</v>
       </c>
       <c r="BA11" s="8">
-        <f t="shared" si="51"/>
-        <v>100227.14000475092</v>
+        <f t="shared" si="52"/>
+        <v>129402.5783523732</v>
       </c>
       <c r="BB11" s="8">
-        <f t="shared" ref="BB11:BF11" si="52">BB9-BB10</f>
-        <v>102331.53867747461</v>
+        <f t="shared" ref="BB11:BF11" si="53">BB9-BB10</f>
+        <v>132113.45412549775</v>
       </c>
       <c r="BC11" s="8">
-        <f t="shared" si="52"/>
-        <v>104488.95225218612</v>
+        <f t="shared" si="53"/>
+        <v>134855.57151819771</v>
       </c>
       <c r="BD11" s="8">
-        <f t="shared" si="52"/>
-        <v>104924.07093629107</v>
+        <f t="shared" si="53"/>
+        <v>137653.10374902573</v>
       </c>
       <c r="BE11" s="8">
-        <f t="shared" si="52"/>
-        <v>105320.25409304273</v>
+        <f t="shared" si="53"/>
+        <v>140507.58333500117</v>
       </c>
       <c r="BF11" s="8">
-        <f t="shared" si="52"/>
-        <v>105706.79072347502</v>
+        <f t="shared" si="53"/>
+        <v>143420.16655585059</v>
       </c>
     </row>
     <row r="12" spans="2:165" x14ac:dyDescent="0.3">
@@ -3273,16 +3267,15 @@
         <v>1738</v>
       </c>
       <c r="AJ12" s="4">
-        <f t="shared" ref="AJ12:AL12" si="53">AJ11*0.12</f>
-        <v>2056.5357120000003</v>
+        <v>2197</v>
       </c>
       <c r="AK12" s="4">
-        <f t="shared" si="53"/>
-        <v>2358.9953399999999</v>
+        <f t="shared" ref="AK12:AL12" si="54">AK11*0.12</f>
+        <v>2653.1844119999996</v>
       </c>
       <c r="AL12" s="4">
-        <f t="shared" si="53"/>
-        <v>2779.0978500000001</v>
+        <f t="shared" si="54"/>
+        <v>2998.2819000000004</v>
       </c>
       <c r="AN12" s="4">
         <f>SUM(C12:F12)</f>
@@ -3318,47 +3311,47 @@
       </c>
       <c r="AV12" s="4">
         <f>SUM(AI12:AL12)</f>
-        <v>8932.6289020000004</v>
+        <v>9586.4663120000005</v>
       </c>
       <c r="AW12" s="4">
         <f>AW11*0.12</f>
-        <v>10292.2560188352</v>
+        <v>11987.7612525312</v>
       </c>
       <c r="AX12" s="4">
-        <f t="shared" ref="AX12:BF12" si="54">AX11*0.12</f>
-        <v>10926.930606079499</v>
+        <f t="shared" ref="AX12:BF12" si="55">AX11*0.12</f>
+        <v>13296.262351279749</v>
       </c>
       <c r="AY12" s="4">
-        <f t="shared" si="54"/>
-        <v>11472.119774883316</v>
+        <f t="shared" si="55"/>
+        <v>14362.160355154234</v>
       </c>
       <c r="AZ12" s="4">
-        <f t="shared" si="54"/>
-        <v>11845.505818639987</v>
+        <f t="shared" si="55"/>
+        <v>15049.335447775073</v>
       </c>
       <c r="BA12" s="4">
-        <f t="shared" si="54"/>
-        <v>12027.25680057011</v>
+        <f t="shared" si="55"/>
+        <v>15528.309402284784</v>
       </c>
       <c r="BB12" s="4">
-        <f t="shared" si="54"/>
-        <v>12279.784641296954</v>
+        <f t="shared" si="55"/>
+        <v>15853.61449505973</v>
       </c>
       <c r="BC12" s="4">
-        <f t="shared" si="54"/>
-        <v>12538.674270262334</v>
+        <f t="shared" si="55"/>
+        <v>16182.668582183725</v>
       </c>
       <c r="BD12" s="4">
-        <f t="shared" si="54"/>
-        <v>12590.888512354928</v>
+        <f t="shared" si="55"/>
+        <v>16518.372449883085</v>
       </c>
       <c r="BE12" s="4">
-        <f t="shared" si="54"/>
-        <v>12638.430491165127</v>
+        <f t="shared" si="55"/>
+        <v>16860.91000020014</v>
       </c>
       <c r="BF12" s="4">
-        <f t="shared" si="54"/>
-        <v>12684.814886817001</v>
+        <f t="shared" si="55"/>
+        <v>17210.419986702069</v>
       </c>
     </row>
     <row r="13" spans="2:165" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -3366,148 +3359,148 @@
         <v>35</v>
       </c>
       <c r="C13" s="8">
-        <f t="shared" ref="C13:P13" si="55">C11-C12</f>
+        <f t="shared" ref="C13:P13" si="56">C11-C12</f>
         <v>3059</v>
       </c>
       <c r="D13" s="8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>3890</v>
       </c>
       <c r="E13" s="8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>4707</v>
       </c>
       <c r="F13" s="8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>3548</v>
       </c>
       <c r="G13" s="8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>4987</v>
       </c>
       <c r="H13" s="8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>5106</v>
       </c>
       <c r="I13" s="8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>5137</v>
       </c>
       <c r="J13" s="8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>6882</v>
       </c>
       <c r="K13" s="8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>2429</v>
       </c>
       <c r="L13" s="8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>2596</v>
       </c>
       <c r="M13" s="8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>6091</v>
       </c>
       <c r="N13" s="8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>7349</v>
       </c>
       <c r="O13" s="8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>4902</v>
       </c>
       <c r="P13" s="8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>5178</v>
       </c>
       <c r="Q13" s="8">
-        <f t="shared" ref="Q13:R13" si="56">Q11-Q12</f>
+        <f t="shared" ref="Q13:R13" si="57">Q11-Q12</f>
         <v>7846</v>
       </c>
       <c r="R13" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>11219</v>
       </c>
       <c r="S13" s="8">
-        <f t="shared" ref="S13:V13" si="57">S11-S12</f>
+        <f t="shared" ref="S13:V13" si="58">S11-S12</f>
         <v>9497</v>
       </c>
       <c r="T13" s="8">
-        <f t="shared" ref="T13:U13" si="58">T11-T12</f>
+        <f t="shared" ref="T13:U13" si="59">T11-T12</f>
         <v>10394</v>
       </c>
       <c r="U13" s="8">
+        <f t="shared" si="59"/>
+        <v>9194</v>
+      </c>
+      <c r="V13" s="8">
         <f t="shared" si="58"/>
-        <v>9194</v>
-      </c>
-      <c r="V13" s="8">
-        <f t="shared" si="57"/>
         <v>10285</v>
       </c>
       <c r="W13" s="8">
-        <f t="shared" ref="W13:X13" si="59">W11-W12</f>
+        <f t="shared" ref="W13:X13" si="60">W11-W12</f>
         <v>7465</v>
       </c>
       <c r="X13" s="8">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>6687</v>
       </c>
       <c r="Y13" s="8">
-        <f t="shared" ref="Y13" si="60">Y11-Y12</f>
+        <f t="shared" ref="Y13" si="61">Y11-Y12</f>
         <v>4395</v>
       </c>
       <c r="Z13" s="8">
-        <f t="shared" ref="Z13" si="61">Z11-Z12</f>
+        <f t="shared" ref="Z13" si="62">Z11-Z12</f>
         <v>4652</v>
       </c>
       <c r="AA13" s="8">
-        <f t="shared" ref="AA13:AC13" si="62">AA11-AA12</f>
+        <f t="shared" ref="AA13:AC13" si="63">AA11-AA12</f>
         <v>5709</v>
       </c>
       <c r="AB13" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>7788</v>
       </c>
       <c r="AC13" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>11853</v>
       </c>
       <c r="AD13" s="8">
-        <f t="shared" ref="AD13" si="63">AD11-AD12</f>
+        <f t="shared" ref="AD13" si="64">AD11-AD12</f>
         <v>14017</v>
       </c>
       <c r="AE13" s="8">
-        <f t="shared" ref="AE13" si="64">AE11-AE12</f>
+        <f t="shared" ref="AE13" si="65">AE11-AE12</f>
         <v>12369</v>
       </c>
       <c r="AF13" s="8">
-        <f t="shared" ref="AF13:AH13" si="65">AF11-AF12</f>
+        <f t="shared" ref="AF13:AH13" si="66">AF11-AF12</f>
         <v>13465</v>
       </c>
       <c r="AG13" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>15688</v>
       </c>
       <c r="AH13" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>19288</v>
       </c>
       <c r="AI13" s="8">
-        <f t="shared" ref="AI13:AL13" si="66">AI11-AI12</f>
+        <f t="shared" ref="AI13:AL13" si="67">AI11-AI12</f>
         <v>16644</v>
       </c>
       <c r="AJ13" s="8">
-        <f t="shared" si="66"/>
-        <v>15081.261888000001</v>
+        <f t="shared" si="67"/>
+        <v>18337</v>
       </c>
       <c r="AK13" s="8">
-        <f t="shared" si="66"/>
-        <v>17299.299159999999</v>
+        <f t="shared" si="67"/>
+        <v>19456.685687999998</v>
       </c>
       <c r="AL13" s="8">
-        <f t="shared" si="66"/>
-        <v>20380.050900000002</v>
+        <f t="shared" si="67"/>
+        <v>21987.400600000001</v>
       </c>
       <c r="AN13" s="8">
         <f>AN11-AN12</f>
@@ -3526,492 +3519,492 @@
         <v>29145</v>
       </c>
       <c r="AR13" s="8">
-        <f t="shared" ref="AR13:BA13" si="67">AR11-AR12</f>
+        <f t="shared" ref="AR13:BA13" si="68">AR11-AR12</f>
         <v>39370</v>
       </c>
       <c r="AS13" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>23199</v>
       </c>
       <c r="AT13" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>39367</v>
       </c>
       <c r="AU13" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>60810</v>
       </c>
       <c r="AV13" s="8">
-        <f t="shared" si="67"/>
-        <v>69360.091948000016</v>
+        <f t="shared" si="68"/>
+        <v>76318.686287999983</v>
       </c>
       <c r="AW13" s="8">
-        <f t="shared" si="67"/>
-        <v>75476.544138124795</v>
+        <f t="shared" si="68"/>
+        <v>87910.249185228808</v>
       </c>
       <c r="AX13" s="8">
-        <f t="shared" si="67"/>
-        <v>80130.824444583006</v>
+        <f t="shared" si="68"/>
+        <v>97505.92390938483</v>
       </c>
       <c r="AY13" s="8">
-        <f t="shared" si="67"/>
-        <v>84128.878349144317</v>
+        <f t="shared" si="68"/>
+        <v>105322.50927113106</v>
       </c>
       <c r="AZ13" s="8">
-        <f t="shared" si="67"/>
-        <v>86867.042670026582</v>
+        <f t="shared" si="68"/>
+        <v>110361.79328368387</v>
       </c>
       <c r="BA13" s="8">
-        <f t="shared" si="67"/>
-        <v>88199.883204180805</v>
+        <f t="shared" si="68"/>
+        <v>113874.26895008842</v>
       </c>
       <c r="BB13" s="8">
-        <f t="shared" ref="BB13:BF13" si="68">BB11-BB12</f>
-        <v>90051.754036177663</v>
+        <f t="shared" ref="BB13:BF13" si="69">BB11-BB12</f>
+        <v>116259.83963043801</v>
       </c>
       <c r="BC13" s="8">
-        <f t="shared" si="68"/>
-        <v>91950.277981923791</v>
+        <f t="shared" si="69"/>
+        <v>118672.90293601398</v>
       </c>
       <c r="BD13" s="8">
-        <f t="shared" si="68"/>
-        <v>92333.182423936145</v>
+        <f t="shared" si="69"/>
+        <v>121134.73129914264</v>
       </c>
       <c r="BE13" s="8">
-        <f t="shared" si="68"/>
-        <v>92681.823601877608</v>
+        <f t="shared" si="69"/>
+        <v>123646.67333480103</v>
       </c>
       <c r="BF13" s="8">
-        <f t="shared" si="68"/>
-        <v>93021.975836658021</v>
+        <f t="shared" si="69"/>
+        <v>126209.74656914853</v>
       </c>
       <c r="BG13" s="6">
         <f>BF13*(1+$BI$18)</f>
-        <v>92091.756078291437</v>
+        <v>124947.64910345704</v>
       </c>
       <c r="BH13" s="6">
-        <f t="shared" ref="BH13:DS13" si="69">BG13*(1+$BI$18)</f>
-        <v>91170.838517508528</v>
+        <f t="shared" ref="BH13:DS13" si="70">BG13*(1+$BI$18)</f>
+        <v>123698.17261242247</v>
       </c>
       <c r="BI13" s="6">
-        <f t="shared" si="69"/>
-        <v>90259.130132333448</v>
+        <f t="shared" si="70"/>
+        <v>122461.19088629824</v>
       </c>
       <c r="BJ13" s="6">
-        <f t="shared" si="69"/>
-        <v>89356.538831010112</v>
+        <f t="shared" si="70"/>
+        <v>121236.57897743526</v>
       </c>
       <c r="BK13" s="6">
-        <f t="shared" si="69"/>
-        <v>88462.973442700008</v>
+        <f t="shared" si="70"/>
+        <v>120024.21318766091</v>
       </c>
       <c r="BL13" s="6">
-        <f t="shared" si="69"/>
-        <v>87578.343708273009</v>
+        <f t="shared" si="70"/>
+        <v>118823.97105578429</v>
       </c>
       <c r="BM13" s="6">
-        <f t="shared" si="69"/>
-        <v>86702.560271190276</v>
+        <f t="shared" si="70"/>
+        <v>117635.73134522645</v>
       </c>
       <c r="BN13" s="6">
-        <f t="shared" si="69"/>
-        <v>85835.534668478373</v>
+        <f t="shared" si="70"/>
+        <v>116459.37403177419</v>
       </c>
       <c r="BO13" s="6">
-        <f t="shared" si="69"/>
-        <v>84977.179321793592</v>
+        <f t="shared" si="70"/>
+        <v>115294.78029145645</v>
       </c>
       <c r="BP13" s="6">
-        <f t="shared" si="69"/>
-        <v>84127.407528575655</v>
+        <f t="shared" si="70"/>
+        <v>114141.83248854188</v>
       </c>
       <c r="BQ13" s="6">
-        <f t="shared" si="69"/>
-        <v>83286.133453289891</v>
+        <f t="shared" si="70"/>
+        <v>113000.41416365646</v>
       </c>
       <c r="BR13" s="6">
-        <f t="shared" si="69"/>
-        <v>82453.272118756984</v>
+        <f t="shared" si="70"/>
+        <v>111870.41002201989</v>
       </c>
       <c r="BS13" s="6">
-        <f t="shared" si="69"/>
-        <v>81628.739397569414</v>
+        <f t="shared" si="70"/>
+        <v>110751.70592179969</v>
       </c>
       <c r="BT13" s="6">
-        <f t="shared" si="69"/>
-        <v>80812.452003593717</v>
+        <f t="shared" si="70"/>
+        <v>109644.18886258169</v>
       </c>
       <c r="BU13" s="6">
-        <f t="shared" si="69"/>
-        <v>80004.327483557776</v>
+        <f t="shared" si="70"/>
+        <v>108547.74697395587</v>
       </c>
       <c r="BV13" s="6">
-        <f t="shared" si="69"/>
-        <v>79204.284208722194</v>
+        <f t="shared" si="70"/>
+        <v>107462.26950421631</v>
       </c>
       <c r="BW13" s="6">
-        <f t="shared" si="69"/>
-        <v>78412.241366634975</v>
+        <f t="shared" si="70"/>
+        <v>106387.64680917414</v>
       </c>
       <c r="BX13" s="6">
-        <f t="shared" si="69"/>
-        <v>77628.118952968623</v>
+        <f t="shared" si="70"/>
+        <v>105323.7703410824</v>
       </c>
       <c r="BY13" s="6">
-        <f t="shared" si="69"/>
-        <v>76851.837763438933</v>
+        <f t="shared" si="70"/>
+        <v>104270.53263767158</v>
       </c>
       <c r="BZ13" s="6">
-        <f t="shared" si="69"/>
-        <v>76083.319385804542</v>
+        <f t="shared" si="70"/>
+        <v>103227.82731129487</v>
       </c>
       <c r="CA13" s="6">
-        <f t="shared" si="69"/>
-        <v>75322.486191946489</v>
+        <f t="shared" si="70"/>
+        <v>102195.54903818191</v>
       </c>
       <c r="CB13" s="6">
-        <f t="shared" si="69"/>
-        <v>74569.261330027017</v>
+        <f t="shared" si="70"/>
+        <v>101173.59354780009</v>
       </c>
       <c r="CC13" s="6">
-        <f t="shared" si="69"/>
-        <v>73823.568716726746</v>
+        <f t="shared" si="70"/>
+        <v>100161.85761232208</v>
       </c>
       <c r="CD13" s="6">
-        <f t="shared" si="69"/>
-        <v>73085.333029559479</v>
+        <f t="shared" si="70"/>
+        <v>99160.239036198866</v>
       </c>
       <c r="CE13" s="6">
-        <f t="shared" si="69"/>
-        <v>72354.479699263888</v>
+        <f t="shared" si="70"/>
+        <v>98168.636645836872</v>
       </c>
       <c r="CF13" s="6">
-        <f t="shared" si="69"/>
-        <v>71630.934902271241</v>
+        <f t="shared" si="70"/>
+        <v>97186.950279378507</v>
       </c>
       <c r="CG13" s="6">
-        <f t="shared" si="69"/>
-        <v>70914.625553248523</v>
+        <f t="shared" si="70"/>
+        <v>96215.080776584728</v>
       </c>
       <c r="CH13" s="6">
-        <f t="shared" si="69"/>
-        <v>70205.47929771604</v>
+        <f t="shared" si="70"/>
+        <v>95252.929968818877</v>
       </c>
       <c r="CI13" s="6">
-        <f t="shared" si="69"/>
-        <v>69503.424504738883</v>
+        <f t="shared" si="70"/>
+        <v>94300.400669130686</v>
       </c>
       <c r="CJ13" s="6">
-        <f t="shared" si="69"/>
-        <v>68808.3902596915</v>
+        <f t="shared" si="70"/>
+        <v>93357.39666243938</v>
       </c>
       <c r="CK13" s="6">
-        <f t="shared" si="69"/>
-        <v>68120.306357094581</v>
+        <f t="shared" si="70"/>
+        <v>92423.82269581499</v>
       </c>
       <c r="CL13" s="6">
-        <f t="shared" si="69"/>
-        <v>67439.103293523629</v>
+        <f t="shared" si="70"/>
+        <v>91499.584468856832</v>
       </c>
       <c r="CM13" s="6">
-        <f t="shared" si="69"/>
-        <v>66764.712260588392</v>
+        <f t="shared" si="70"/>
+        <v>90584.58862416826</v>
       </c>
       <c r="CN13" s="6">
-        <f t="shared" si="69"/>
-        <v>66097.065137982514</v>
+        <f t="shared" si="70"/>
+        <v>89678.742737926572</v>
       </c>
       <c r="CO13" s="6">
-        <f t="shared" si="69"/>
-        <v>65436.094486602691</v>
+        <f t="shared" si="70"/>
+        <v>88781.955310547302</v>
       </c>
       <c r="CP13" s="6">
-        <f t="shared" si="69"/>
-        <v>64781.733541736663</v>
+        <f t="shared" si="70"/>
+        <v>87894.135757441822</v>
       </c>
       <c r="CQ13" s="6">
-        <f t="shared" si="69"/>
-        <v>64133.916206319293</v>
+        <f t="shared" si="70"/>
+        <v>87015.194399867396</v>
       </c>
       <c r="CR13" s="6">
-        <f t="shared" si="69"/>
-        <v>63492.577044256097</v>
+        <f t="shared" si="70"/>
+        <v>86145.042455868723</v>
       </c>
       <c r="CS13" s="6">
-        <f t="shared" si="69"/>
-        <v>62857.651273813535</v>
+        <f t="shared" si="70"/>
+        <v>85283.592031310036</v>
       </c>
       <c r="CT13" s="6">
-        <f t="shared" si="69"/>
-        <v>62229.074761075397</v>
+        <f t="shared" si="70"/>
+        <v>84430.756110996939</v>
       </c>
       <c r="CU13" s="6">
-        <f t="shared" si="69"/>
-        <v>61606.784013464639</v>
+        <f t="shared" si="70"/>
+        <v>83586.448549886976</v>
       </c>
       <c r="CV13" s="6">
-        <f t="shared" si="69"/>
-        <v>60990.716173329994</v>
+        <f t="shared" si="70"/>
+        <v>82750.584064388109</v>
       </c>
       <c r="CW13" s="6">
-        <f t="shared" si="69"/>
-        <v>60380.809011596692</v>
+        <f t="shared" si="70"/>
+        <v>81923.078223744233</v>
       </c>
       <c r="CX13" s="6">
-        <f t="shared" si="69"/>
-        <v>59777.000921480721</v>
+        <f t="shared" si="70"/>
+        <v>81103.84744150679</v>
       </c>
       <c r="CY13" s="6">
-        <f t="shared" si="69"/>
-        <v>59179.230912265914</v>
+        <f t="shared" si="70"/>
+        <v>80292.808967091725</v>
       </c>
       <c r="CZ13" s="6">
-        <f t="shared" si="69"/>
-        <v>58587.438603143251</v>
+        <f t="shared" si="70"/>
+        <v>79489.880877420801</v>
       </c>
       <c r="DA13" s="6">
-        <f t="shared" si="69"/>
-        <v>58001.564217111816</v>
+        <f t="shared" si="70"/>
+        <v>78694.982068646597</v>
       </c>
       <c r="DB13" s="6">
-        <f t="shared" si="69"/>
-        <v>57421.548574940694</v>
+        <f t="shared" si="70"/>
+        <v>77908.032247960131</v>
       </c>
       <c r="DC13" s="6">
-        <f t="shared" si="69"/>
-        <v>56847.333089191285</v>
+        <f t="shared" si="70"/>
+        <v>77128.951925480535</v>
       </c>
       <c r="DD13" s="6">
-        <f t="shared" si="69"/>
-        <v>56278.859758299368</v>
+        <f t="shared" si="70"/>
+        <v>76357.662406225732</v>
       </c>
       <c r="DE13" s="6">
-        <f t="shared" si="69"/>
-        <v>55716.071160716376</v>
+        <f t="shared" si="70"/>
+        <v>75594.085782163471</v>
       </c>
       <c r="DF13" s="6">
-        <f t="shared" si="69"/>
-        <v>55158.910449109215</v>
+        <f t="shared" si="70"/>
+        <v>74838.144924341832</v>
       </c>
       <c r="DG13" s="6">
-        <f t="shared" si="69"/>
-        <v>54607.321344618125</v>
+        <f t="shared" si="70"/>
+        <v>74089.763475098414</v>
       </c>
       <c r="DH13" s="6">
-        <f t="shared" si="69"/>
-        <v>54061.248131171946</v>
+        <f t="shared" si="70"/>
+        <v>73348.865840347426</v>
       </c>
       <c r="DI13" s="6">
-        <f t="shared" si="69"/>
-        <v>53520.635649860225</v>
+        <f t="shared" si="70"/>
+        <v>72615.377181943957</v>
       </c>
       <c r="DJ13" s="6">
-        <f t="shared" si="69"/>
-        <v>52985.429293361623</v>
+        <f t="shared" si="70"/>
+        <v>71889.223410124512</v>
       </c>
       <c r="DK13" s="6">
-        <f t="shared" si="69"/>
-        <v>52455.575000428005</v>
+        <f t="shared" si="70"/>
+        <v>71170.331176023261</v>
       </c>
       <c r="DL13" s="6">
-        <f t="shared" si="69"/>
-        <v>51931.019250423727</v>
+        <f t="shared" si="70"/>
+        <v>70458.62786426302</v>
       </c>
       <c r="DM13" s="6">
-        <f t="shared" si="69"/>
-        <v>51411.709057919492</v>
+        <f t="shared" si="70"/>
+        <v>69754.041585620391</v>
       </c>
       <c r="DN13" s="6">
-        <f t="shared" si="69"/>
-        <v>50897.591967340297</v>
+        <f t="shared" si="70"/>
+        <v>69056.501169764189</v>
       </c>
       <c r="DO13" s="6">
-        <f t="shared" si="69"/>
-        <v>50388.616047666896</v>
+        <f t="shared" si="70"/>
+        <v>68365.936158066543</v>
       </c>
       <c r="DP13" s="6">
-        <f t="shared" si="69"/>
-        <v>49884.729887190224</v>
+        <f t="shared" si="70"/>
+        <v>67682.276796485879</v>
       </c>
       <c r="DQ13" s="6">
-        <f t="shared" si="69"/>
-        <v>49385.882588318324</v>
+        <f t="shared" si="70"/>
+        <v>67005.454028521024</v>
       </c>
       <c r="DR13" s="6">
-        <f t="shared" si="69"/>
-        <v>48892.023762435143</v>
+        <f t="shared" si="70"/>
+        <v>66335.399488235809</v>
       </c>
       <c r="DS13" s="6">
-        <f t="shared" si="69"/>
-        <v>48403.103524810795</v>
+        <f t="shared" si="70"/>
+        <v>65672.045493353449</v>
       </c>
       <c r="DT13" s="6">
-        <f t="shared" ref="DT13:FI13" si="70">DS13*(1+$BI$18)</f>
-        <v>47919.072489562684</v>
+        <f t="shared" ref="DT13:FI13" si="71">DS13*(1+$BI$18)</f>
+        <v>65015.325038419913</v>
       </c>
       <c r="DU13" s="6">
-        <f t="shared" si="70"/>
-        <v>47439.881764667058</v>
+        <f t="shared" si="71"/>
+        <v>64365.17178803571</v>
       </c>
       <c r="DV13" s="6">
-        <f t="shared" si="70"/>
-        <v>46965.482947020384</v>
+        <f t="shared" si="71"/>
+        <v>63721.520070155355</v>
       </c>
       <c r="DW13" s="6">
-        <f t="shared" si="70"/>
-        <v>46495.828117550183</v>
+        <f t="shared" si="71"/>
+        <v>63084.304869453801</v>
       </c>
       <c r="DX13" s="6">
-        <f t="shared" si="70"/>
-        <v>46030.869836374681</v>
+        <f t="shared" si="71"/>
+        <v>62453.461820759265</v>
       </c>
       <c r="DY13" s="6">
-        <f t="shared" si="70"/>
-        <v>45570.561138010933</v>
+        <f t="shared" si="71"/>
+        <v>61828.927202551669</v>
       </c>
       <c r="DZ13" s="6">
-        <f t="shared" si="70"/>
-        <v>45114.855526630825</v>
+        <f t="shared" si="71"/>
+        <v>61210.637930526151</v>
       </c>
       <c r="EA13" s="6">
-        <f t="shared" si="70"/>
-        <v>44663.706971364518</v>
+        <f t="shared" si="71"/>
+        <v>60598.531551220891</v>
       </c>
       <c r="EB13" s="6">
-        <f t="shared" si="70"/>
-        <v>44217.069901650873</v>
+        <f t="shared" si="71"/>
+        <v>59992.54623570868</v>
       </c>
       <c r="EC13" s="6">
-        <f t="shared" si="70"/>
-        <v>43774.899202634362</v>
+        <f t="shared" si="71"/>
+        <v>59392.620773351591</v>
       </c>
       <c r="ED13" s="6">
-        <f t="shared" si="70"/>
-        <v>43337.150210608015</v>
+        <f t="shared" si="71"/>
+        <v>58798.694565618076</v>
       </c>
       <c r="EE13" s="6">
-        <f t="shared" si="70"/>
-        <v>42903.778708501937</v>
+        <f t="shared" si="71"/>
+        <v>58210.707619961897</v>
       </c>
       <c r="EF13" s="6">
-        <f t="shared" si="70"/>
-        <v>42474.740921416917</v>
+        <f t="shared" si="71"/>
+        <v>57628.600543762281</v>
       </c>
       <c r="EG13" s="6">
-        <f t="shared" si="70"/>
-        <v>42049.993512202745</v>
+        <f t="shared" si="71"/>
+        <v>57052.314538324659</v>
       </c>
       <c r="EH13" s="6">
-        <f t="shared" si="70"/>
-        <v>41629.493577080721</v>
+        <f t="shared" si="71"/>
+        <v>56481.791392941414</v>
       </c>
       <c r="EI13" s="6">
-        <f t="shared" si="70"/>
-        <v>41213.198641309915</v>
+        <f t="shared" si="71"/>
+        <v>55916.973479011998</v>
       </c>
       <c r="EJ13" s="6">
-        <f t="shared" si="70"/>
-        <v>40801.066654896815</v>
+        <f t="shared" si="71"/>
+        <v>55357.803744221877</v>
       </c>
       <c r="EK13" s="6">
-        <f t="shared" si="70"/>
-        <v>40393.055988347849</v>
+        <f t="shared" si="71"/>
+        <v>54804.22570677966</v>
       </c>
       <c r="EL13" s="6">
-        <f t="shared" si="70"/>
-        <v>39989.125428464373</v>
+        <f t="shared" si="71"/>
+        <v>54256.183449711862</v>
       </c>
       <c r="EM13" s="6">
-        <f t="shared" si="70"/>
-        <v>39589.234174179728</v>
+        <f t="shared" si="71"/>
+        <v>53713.621615214739</v>
       </c>
       <c r="EN13" s="6">
-        <f t="shared" si="70"/>
-        <v>39193.341832437931</v>
+        <f t="shared" si="71"/>
+        <v>53176.485399062592</v>
       </c>
       <c r="EO13" s="6">
-        <f t="shared" si="70"/>
-        <v>38801.408414113554</v>
+        <f t="shared" si="71"/>
+        <v>52644.720545071963</v>
       </c>
       <c r="EP13" s="6">
-        <f t="shared" si="70"/>
-        <v>38413.39432997242</v>
+        <f t="shared" si="71"/>
+        <v>52118.273339621242</v>
       </c>
       <c r="EQ13" s="6">
-        <f t="shared" si="70"/>
-        <v>38029.260386672693</v>
+        <f t="shared" si="71"/>
+        <v>51597.090606225029</v>
       </c>
       <c r="ER13" s="6">
-        <f t="shared" si="70"/>
-        <v>37648.967782805965</v>
+        <f t="shared" si="71"/>
+        <v>51081.119700162781</v>
       </c>
       <c r="ES13" s="6">
-        <f t="shared" si="70"/>
-        <v>37272.478104977905</v>
+        <f t="shared" si="71"/>
+        <v>50570.308503161155</v>
       </c>
       <c r="ET13" s="6">
-        <f t="shared" si="70"/>
-        <v>36899.753323928126</v>
+        <f t="shared" si="71"/>
+        <v>50064.60541812954</v>
       </c>
       <c r="EU13" s="6">
-        <f t="shared" si="70"/>
-        <v>36530.755790688847</v>
+        <f t="shared" si="71"/>
+        <v>49563.959363948241</v>
       </c>
       <c r="EV13" s="6">
-        <f t="shared" si="70"/>
-        <v>36165.448232781957</v>
+        <f t="shared" si="71"/>
+        <v>49068.319770308757</v>
       </c>
       <c r="EW13" s="6">
-        <f t="shared" si="70"/>
-        <v>35803.793750454141</v>
+        <f t="shared" si="71"/>
+        <v>48577.636572605668</v>
       </c>
       <c r="EX13" s="6">
-        <f t="shared" si="70"/>
-        <v>35445.755812949596</v>
+        <f t="shared" si="71"/>
+        <v>48091.86020687961</v>
       </c>
       <c r="EY13" s="6">
-        <f t="shared" si="70"/>
-        <v>35091.298254820096</v>
+        <f t="shared" si="71"/>
+        <v>47610.941604810811</v>
       </c>
       <c r="EZ13" s="6">
-        <f t="shared" si="70"/>
-        <v>34740.385272271895</v>
+        <f t="shared" si="71"/>
+        <v>47134.832188762703</v>
       </c>
       <c r="FA13" s="6">
-        <f t="shared" si="70"/>
-        <v>34392.981419549178</v>
+        <f t="shared" si="71"/>
+        <v>46663.483866875074</v>
       </c>
       <c r="FB13" s="6">
-        <f t="shared" si="70"/>
-        <v>34049.051605353685</v>
+        <f t="shared" si="71"/>
+        <v>46196.849028206321</v>
       </c>
       <c r="FC13" s="6">
-        <f t="shared" si="70"/>
-        <v>33708.56108930015</v>
+        <f t="shared" si="71"/>
+        <v>45734.880537924255</v>
       </c>
       <c r="FD13" s="6">
-        <f t="shared" si="70"/>
-        <v>33371.475478407148</v>
+        <f t="shared" si="71"/>
+        <v>45277.531732545009</v>
       </c>
       <c r="FE13" s="6">
-        <f t="shared" si="70"/>
-        <v>33037.760723623076</v>
+        <f t="shared" si="71"/>
+        <v>44824.756415219555</v>
       </c>
       <c r="FF13" s="6">
-        <f t="shared" si="70"/>
-        <v>32707.383116386845</v>
+        <f t="shared" si="71"/>
+        <v>44376.50885106736</v>
       </c>
       <c r="FG13" s="6">
-        <f t="shared" si="70"/>
-        <v>32380.309285222978</v>
+        <f t="shared" si="71"/>
+        <v>43932.743762556689</v>
       </c>
       <c r="FH13" s="6">
-        <f t="shared" si="70"/>
-        <v>32056.506192370747</v>
+        <f t="shared" si="71"/>
+        <v>43493.416324931124</v>
       </c>
       <c r="FI13" s="6">
-        <f t="shared" si="70"/>
-        <v>31735.941130447038</v>
+        <f t="shared" si="71"/>
+        <v>43058.482161681815</v>
       </c>
     </row>
     <row r="14" spans="2:165" x14ac:dyDescent="0.3">
@@ -4059,7 +4052,7 @@
       </c>
       <c r="P14" s="4">
         <f>Main!D4</f>
-        <v>2527</v>
+        <v>2518</v>
       </c>
       <c r="Q14" s="4">
         <v>2848.8</v>
@@ -4122,78 +4115,78 @@
         <v>2527</v>
       </c>
       <c r="AJ14" s="4">
-        <v>2527</v>
+        <v>2518</v>
       </c>
       <c r="AK14" s="4">
-        <v>2527</v>
+        <v>2518</v>
       </c>
       <c r="AL14" s="4">
-        <v>2527</v>
+        <v>2518</v>
       </c>
       <c r="AN14" s="4">
         <f>P14</f>
-        <v>2527</v>
+        <v>2518</v>
       </c>
       <c r="AO14" s="4">
         <f>AN14</f>
-        <v>2527</v>
+        <v>2518</v>
       </c>
       <c r="AP14" s="4">
         <f>AO14</f>
-        <v>2527</v>
+        <v>2518</v>
       </c>
       <c r="AQ14" s="4">
         <f>AP14</f>
-        <v>2527</v>
+        <v>2518</v>
       </c>
       <c r="AR14" s="4">
-        <f t="shared" ref="AR14" si="71">AQ14</f>
-        <v>2527</v>
+        <f t="shared" ref="AR14" si="72">AQ14</f>
+        <v>2518</v>
       </c>
       <c r="AS14" s="4">
-        <f t="shared" ref="AS14:AT14" si="72">2396+439.4</f>
+        <f t="shared" ref="AS14:AT14" si="73">2396+439.4</f>
         <v>2835.4</v>
       </c>
       <c r="AT14" s="4">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>2835.4</v>
       </c>
       <c r="AU14" s="4">
-        <f t="shared" ref="AU14" si="73">2189.9+343.8</f>
+        <f t="shared" ref="AU14" si="74">2189.9+343.8</f>
         <v>2533.7000000000003</v>
       </c>
       <c r="AV14" s="4">
-        <v>2527</v>
+        <v>2518</v>
       </c>
       <c r="AW14" s="4">
-        <v>2527</v>
+        <v>2518</v>
       </c>
       <c r="AX14" s="4">
-        <v>2527</v>
+        <v>2518</v>
       </c>
       <c r="AY14" s="4">
-        <v>2527</v>
+        <v>2518</v>
       </c>
       <c r="AZ14" s="4">
-        <v>2527</v>
+        <v>2518</v>
       </c>
       <c r="BA14" s="4">
-        <v>2527</v>
+        <v>2518</v>
       </c>
       <c r="BB14" s="4">
-        <v>2527</v>
+        <v>2518</v>
       </c>
       <c r="BC14" s="4">
-        <v>2527</v>
+        <v>2518</v>
       </c>
       <c r="BD14" s="4">
-        <v>2527</v>
+        <v>2518</v>
       </c>
       <c r="BE14" s="4">
-        <v>2527</v>
+        <v>2518</v>
       </c>
       <c r="BF14" s="4">
-        <v>2527</v>
+        <v>2518</v>
       </c>
     </row>
     <row r="15" spans="2:165" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -4201,224 +4194,224 @@
         <v>36</v>
       </c>
       <c r="C15" s="7">
-        <f t="shared" ref="C15:P15" si="74">C13/C14</f>
+        <f t="shared" ref="C15:P15" si="75">C13/C14</f>
         <v>1.0737854535242908</v>
       </c>
       <c r="D15" s="7">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>1.3654872226902555</v>
       </c>
       <c r="E15" s="7">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>1.6522746419545071</v>
       </c>
       <c r="F15" s="7">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>1.2454366750912664</v>
       </c>
       <c r="G15" s="7">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>1.7505616399887671</v>
       </c>
       <c r="H15" s="7">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>1.7923336141533277</v>
       </c>
       <c r="I15" s="7">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>1.8032153889356921</v>
       </c>
       <c r="J15" s="7">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>2.4157540016849199</v>
       </c>
       <c r="K15" s="7">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0.85263970794720578</v>
       </c>
       <c r="L15" s="7">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0.91126088177478226</v>
       </c>
       <c r="M15" s="7">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>2.1380932322381354</v>
       </c>
       <c r="N15" s="7">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>2.5796826734063463</v>
       </c>
       <c r="O15" s="7">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>1.7207245155855095</v>
       </c>
       <c r="P15" s="7">
-        <f t="shared" si="74"/>
-        <v>2.0490700435298774</v>
+        <f t="shared" si="75"/>
+        <v>2.0563939634630661</v>
       </c>
       <c r="Q15" s="7">
-        <f t="shared" ref="Q15:R15" si="75">Q13/Q14</f>
+        <f t="shared" ref="Q15:R15" si="76">Q13/Q14</f>
         <v>2.754142094917158</v>
       </c>
       <c r="R15" s="7">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>3.9381493962370118</v>
       </c>
       <c r="S15" s="7">
-        <f t="shared" ref="S15:V15" si="76">S13/S14</f>
+        <f t="shared" ref="S15:V15" si="77">S13/S14</f>
         <v>3.3494392325597797</v>
       </c>
       <c r="T15" s="7">
-        <f t="shared" ref="T15:U15" si="77">T13/T14</f>
+        <f t="shared" ref="T15:U15" si="78">T13/T14</f>
         <v>3.667607621736062</v>
       </c>
       <c r="U15" s="7">
+        <f t="shared" si="78"/>
+        <v>3.2672352523098791</v>
+      </c>
+      <c r="V15" s="7">
         <f t="shared" si="77"/>
-        <v>3.2672352523098791</v>
-      </c>
-      <c r="V15" s="7">
-        <f t="shared" si="76"/>
         <v>3.7197106690777577</v>
       </c>
       <c r="W15" s="7">
-        <f t="shared" ref="W15:X15" si="78">W13/W14</f>
+        <f t="shared" ref="W15:X15" si="79">W13/W14</f>
         <v>2.7394495412844035</v>
       </c>
       <c r="X15" s="7">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>2.4730029585798818</v>
       </c>
       <c r="Y15" s="7">
-        <f t="shared" ref="Y15" si="79">Y13/Y14</f>
+        <f t="shared" ref="Y15" si="80">Y13/Y14</f>
         <v>1.638702460850112</v>
       </c>
       <c r="Z15" s="7">
-        <f t="shared" ref="Z15" si="80">Z13/Z14</f>
+        <f t="shared" ref="Z15" si="81">Z13/Z14</f>
         <v>1.7634571645185746</v>
       </c>
       <c r="AA15" s="7">
-        <f t="shared" ref="AA15:AC15" si="81">AA13/AA14</f>
+        <f t="shared" ref="AA15:AC15" si="82">AA13/AA14</f>
         <v>2.206803247004252</v>
       </c>
       <c r="AB15" s="7">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>3.0327102803738319</v>
       </c>
       <c r="AC15" s="7">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>4.6013198757763973</v>
       </c>
       <c r="AD15" s="7">
-        <f t="shared" ref="AD15" si="82">AD13/AD14</f>
+        <f t="shared" ref="AD15" si="83">AD13/AD14</f>
         <v>5.4625876851130162</v>
       </c>
       <c r="AE15" s="7">
-        <f t="shared" ref="AE15" si="83">AE13/AE14</f>
+        <f t="shared" ref="AE15" si="84">AE13/AE14</f>
         <v>4.8601178781925345</v>
       </c>
       <c r="AF15" s="7">
-        <f t="shared" ref="AF15:AH15" si="84">AF13/AF14</f>
+        <f t="shared" ref="AF15:AH15" si="85">AF13/AF14</f>
         <v>5.2907662082514735</v>
       </c>
       <c r="AG15" s="7">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>6.2142998613586853</v>
       </c>
       <c r="AH15" s="7">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>7.6125823893910081</v>
       </c>
       <c r="AI15" s="7">
-        <f t="shared" ref="AI15:AL15" si="85">AI13/AI14</f>
+        <f t="shared" ref="AI15:AL15" si="86">AI13/AI14</f>
         <v>6.5864661654135341</v>
       </c>
       <c r="AJ15" s="7">
-        <f t="shared" si="85"/>
-        <v>5.9680498171745153</v>
+        <f t="shared" si="86"/>
+        <v>7.2823669579030978</v>
       </c>
       <c r="AK15" s="7">
-        <f t="shared" si="85"/>
-        <v>6.8457851840126631</v>
+        <f t="shared" si="86"/>
+        <v>7.7270395901509126</v>
       </c>
       <c r="AL15" s="7">
-        <f t="shared" si="85"/>
-        <v>8.0649192322912544</v>
+        <f t="shared" si="86"/>
+        <v>8.7320891977760127</v>
       </c>
       <c r="AN15" s="7">
         <f>AN13/AN14</f>
-        <v>6.0166204986149587</v>
+        <v>6.0381254964257352</v>
       </c>
       <c r="AO15" s="7">
         <f>AO13/AO14</f>
-        <v>8.7502967946181247</v>
+        <v>8.7815726767275617</v>
       </c>
       <c r="AP15" s="7">
         <f>AP13/AP14</f>
-        <v>7.3070834982192325</v>
+        <v>7.3332009531374105</v>
       </c>
       <c r="AQ15" s="7">
         <f>AQ13/AQ14</f>
-        <v>11.533438860308667</v>
+        <v>11.574662430500398</v>
       </c>
       <c r="AR15" s="7">
-        <f t="shared" ref="AR15:BA15" si="86">AR13/AR14</f>
-        <v>15.579738820736051</v>
+        <f t="shared" ref="AR15:BA15" si="87">AR13/AR14</f>
+        <v>15.635424940428912</v>
       </c>
       <c r="AS15" s="7">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>8.1819143683430902</v>
       </c>
       <c r="AT15" s="7">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>13.884108062354517</v>
       </c>
       <c r="AU15" s="7">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>24.000473615660887</v>
       </c>
       <c r="AV15" s="7">
-        <f t="shared" si="86"/>
-        <v>27.447602670360116</v>
+        <f t="shared" si="87"/>
+        <v>30.30924793010325</v>
       </c>
       <c r="AW15" s="7">
-        <f t="shared" si="86"/>
-        <v>29.868042793084605</v>
+        <f t="shared" si="87"/>
+        <v>34.91272803225926</v>
       </c>
       <c r="AX15" s="7">
-        <f t="shared" si="86"/>
-        <v>31.709863254682631</v>
+        <f t="shared" si="87"/>
+        <v>38.723559932241791</v>
       </c>
       <c r="AY15" s="7">
-        <f t="shared" si="86"/>
-        <v>33.291997763808595</v>
+        <f t="shared" si="87"/>
+        <v>41.827843237144982</v>
       </c>
       <c r="AZ15" s="7">
-        <f t="shared" si="86"/>
-        <v>34.375561009112218</v>
+        <f t="shared" si="87"/>
+        <v>43.82914745182044</v>
       </c>
       <c r="BA15" s="7">
-        <f t="shared" si="86"/>
-        <v>34.903000872252001</v>
+        <f t="shared" si="87"/>
+        <v>45.224094102497382</v>
       </c>
       <c r="BB15" s="7">
-        <f t="shared" ref="BB15:BF15" si="87">BB13/BB14</f>
-        <v>35.635834600782616</v>
+        <f t="shared" ref="BB15:BF15" si="88">BB13/BB14</f>
+        <v>46.171501044653702</v>
       </c>
       <c r="BC15" s="7">
-        <f t="shared" si="87"/>
-        <v>36.387130186752586</v>
+        <f t="shared" si="88"/>
+        <v>47.129826424151702</v>
       </c>
       <c r="BD15" s="7">
-        <f t="shared" si="87"/>
-        <v>36.538655490279439</v>
+        <f t="shared" si="88"/>
+        <v>48.107518387268726</v>
       </c>
       <c r="BE15" s="7">
-        <f t="shared" si="87"/>
-        <v>36.676621923972142</v>
+        <f t="shared" si="88"/>
+        <v>49.105112523749419</v>
       </c>
       <c r="BF15" s="7">
-        <f t="shared" si="87"/>
-        <v>36.811229060806497</v>
+        <f t="shared" si="88"/>
+        <v>50.123012934530792</v>
       </c>
     </row>
     <row r="17" spans="2:61" x14ac:dyDescent="0.3">
@@ -4430,128 +4423,128 @@
         <v>0.48979083665338652</v>
       </c>
       <c r="H17" s="9">
-        <f t="shared" ref="H17:R17" si="88">H3/D3-1</f>
+        <f t="shared" ref="H17:R17" si="89">H3/D3-1</f>
         <v>0.41948288810213485</v>
       </c>
       <c r="I17" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.32910534469403574</v>
       </c>
       <c r="J17" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.30388529139685483</v>
       </c>
       <c r="K17" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.25998662878154777</v>
       </c>
       <c r="L17" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.27473358022825178</v>
       </c>
       <c r="M17" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.2859328331026445</v>
       </c>
       <c r="N17" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.2464230814709707</v>
       </c>
       <c r="O17" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.17642767128739134</v>
       </c>
       <c r="P17" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.10796869441479906</v>
       </c>
       <c r="Q17" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.21629277135735325</v>
       </c>
       <c r="R17" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.33156247035385644</v>
       </c>
       <c r="S17" s="9">
-        <f t="shared" ref="S17" si="89">S3/O3-1</f>
+        <f t="shared" ref="S17" si="90">S3/O3-1</f>
         <v>0.47550318543158365</v>
       </c>
       <c r="T17" s="9">
-        <f t="shared" ref="T17" si="90">T3/P3-1</f>
+        <f t="shared" ref="T17" si="91">T3/P3-1</f>
         <v>0.5560014983678494</v>
       </c>
       <c r="U17" s="9">
-        <f t="shared" ref="U17" si="91">U3/Q3-1</f>
+        <f t="shared" ref="U17" si="92">U3/Q3-1</f>
         <v>0.35118770377270603</v>
       </c>
       <c r="V17" s="9">
-        <f t="shared" ref="V17" si="92">V3/R3-1</f>
+        <f t="shared" ref="V17" si="93">V3/R3-1</f>
         <v>0.19945141065830718</v>
       </c>
       <c r="W17" s="9">
-        <f t="shared" ref="W17" si="93">W3/S3-1</f>
+        <f t="shared" ref="W17" si="94">W3/S3-1</f>
         <v>6.6371174200450911E-2</v>
       </c>
       <c r="X17" s="9">
-        <f t="shared" ref="X17" si="94">X3/T3-1</f>
+        <f t="shared" ref="X17" si="95">X3/T3-1</f>
         <v>-8.7698180692643568E-3</v>
       </c>
       <c r="Y17" s="9">
-        <f t="shared" ref="Y17" si="95">Y3/U3-1</f>
+        <f t="shared" ref="Y17" si="96">Y3/U3-1</f>
         <v>-4.4674250258531556E-2</v>
       </c>
       <c r="Z17" s="9">
-        <f t="shared" ref="Z17" si="96">Z3/V3-1</f>
+        <f t="shared" ref="Z17" si="97">Z3/V3-1</f>
         <v>-4.4726916337501144E-2</v>
       </c>
       <c r="AA17" s="9">
-        <f t="shared" ref="AA17" si="97">AA3/W3-1</f>
+        <f t="shared" ref="AA17" si="98">AA3/W3-1</f>
         <v>2.6408198366060009E-2</v>
       </c>
       <c r="AB17" s="9">
-        <f t="shared" ref="AB17" si="98">AB3/X3-1</f>
+        <f t="shared" ref="AB17" si="99">AB3/X3-1</f>
         <v>0.11022829782804799</v>
       </c>
       <c r="AC17" s="9">
-        <f t="shared" ref="AC17" si="99">AC3/Y3-1</f>
+        <f t="shared" ref="AC17" si="100">AC3/Y3-1</f>
         <v>0.24182723533232298</v>
       </c>
       <c r="AD17" s="9">
-        <f t="shared" ref="AD17" si="100">AD3/Z3-1</f>
+        <f t="shared" ref="AD17" si="101">AD3/Z3-1</f>
         <v>0.24703870666873939</v>
       </c>
       <c r="AE17" s="9">
-        <f t="shared" ref="AE17" si="101">AE3/AA3-1</f>
+        <f t="shared" ref="AE17" si="102">AE3/AA3-1</f>
         <v>0.27264793157619138</v>
       </c>
       <c r="AF17" s="9">
-        <f t="shared" ref="AF17" si="102">AF3/AB3-1</f>
+        <f t="shared" ref="AF17" si="103">AF3/AB3-1</f>
         <v>0.2210069064658271</v>
       </c>
       <c r="AG17" s="9">
-        <f t="shared" ref="AG17" si="103">AG3/AC3-1</f>
+        <f t="shared" ref="AG17" si="104">AG3/AC3-1</f>
         <v>0.17936424918642491</v>
       </c>
       <c r="AH17" s="9">
-        <f t="shared" ref="AH17" si="104">AH3/AD3-1</f>
+        <f t="shared" ref="AH17" si="105">AH3/AD3-1</f>
         <v>0.20627757971628724</v>
       </c>
       <c r="AI17" s="9">
-        <f t="shared" ref="AI17" si="105">AI3/AE3-1</f>
+        <f t="shared" ref="AI17" si="106">AI3/AE3-1</f>
         <v>0.16071869428062002</v>
       </c>
       <c r="AJ17" s="9">
-        <f t="shared" ref="AJ17" si="106">AJ3/AF3-1</f>
-        <v>0.12000000000000011</v>
+        <f t="shared" ref="AJ17" si="107">AJ3/AF3-1</f>
+        <v>0.21614496685521223</v>
       </c>
       <c r="AK17" s="9">
-        <f t="shared" ref="AK17" si="107">AK3/AG3-1</f>
+        <f t="shared" ref="AK17" si="108">AK3/AG3-1</f>
+        <v>0.17999999999999994</v>
+      </c>
+      <c r="AL17" s="9">
+        <f t="shared" ref="AL17" si="109">AL3/AH3-1</f>
         <v>0.10000000000000009</v>
-      </c>
-      <c r="AL17" s="9">
-        <f t="shared" ref="AL17" si="108">AL3/AH3-1</f>
-        <v>5.0000000000000044E-2</v>
       </c>
       <c r="AN17" s="9"/>
       <c r="AO17" s="9">
@@ -4559,72 +4552,72 @@
         <v>0.37352716896661997</v>
       </c>
       <c r="AP17" s="9">
-        <f t="shared" ref="AP17:BA17" si="109">AP3/AO3-1</f>
+        <f t="shared" ref="AP17:BA17" si="110">AP3/AO3-1</f>
         <v>0.26575092231097108</v>
       </c>
       <c r="AQ17" s="9">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>0.21632214157363783</v>
       </c>
       <c r="AR17" s="9">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>0.37180978526394148</v>
       </c>
       <c r="AS17" s="9">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>-1.1193175554782941E-2</v>
       </c>
       <c r="AT17" s="9">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>0.15918153830321846</v>
       </c>
       <c r="AU17" s="9">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>0.21697701430040461</v>
       </c>
       <c r="AV17" s="9">
-        <f t="shared" si="109"/>
-        <v>0.10349951367781163</v>
+        <f t="shared" si="110"/>
+        <v>0.16078127659574459</v>
       </c>
       <c r="AW17" s="9">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
+        <v>0.12000000000000011</v>
+      </c>
+      <c r="AX17" s="9">
+        <f t="shared" si="110"/>
         <v>8.0000000000000071E-2</v>
       </c>
-      <c r="AX17" s="9">
-        <f t="shared" si="109"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
       <c r="AY17" s="9">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
+        <v>6.0000000000000053E-2</v>
+      </c>
+      <c r="AZ17" s="9">
+        <f t="shared" si="110"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AZ17" s="9">
-        <f t="shared" si="109"/>
+      <c r="BA17" s="9">
+        <f t="shared" si="110"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="BA17" s="9">
-        <f t="shared" si="109"/>
+      <c r="BB17" s="9">
+        <f t="shared" ref="BB17" si="111">BB3/BA3-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BB17" s="9">
-        <f t="shared" ref="BB17" si="110">BB3/BA3-1</f>
+      <c r="BC17" s="9">
+        <f t="shared" ref="BC17" si="112">BC3/BB3-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BC17" s="9">
-        <f t="shared" ref="BC17" si="111">BC3/BB3-1</f>
+      <c r="BD17" s="9">
+        <f t="shared" ref="BD17" si="113">BD3/BC3-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BD17" s="9">
-        <f t="shared" ref="BD17" si="112">BD3/BC3-1</f>
-        <v>1.0000000000000009E-2</v>
-      </c>
       <c r="BE17" s="9">
-        <f t="shared" ref="BE17" si="113">BE3/BD3-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="BE17" si="114">BE3/BD3-1</f>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="BF17" s="9">
-        <f t="shared" ref="BF17" si="114">BF3/BE3-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="BF17" si="115">BF3/BE3-1</f>
+        <v>2.0000000000000018E-2</v>
       </c>
     </row>
     <row r="18" spans="2:61" x14ac:dyDescent="0.3">
@@ -4636,219 +4629,219 @@
         <v>0.85570219123505975</v>
       </c>
       <c r="D18" s="9">
-        <f t="shared" ref="D18:R18" si="115">D5/D3</f>
+        <f t="shared" ref="D18:R18" si="116">D5/D3</f>
         <v>0.86728891749812254</v>
       </c>
       <c r="E18" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>0.85979860573199074</v>
       </c>
       <c r="F18" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>0.87580943570767811</v>
       </c>
       <c r="G18" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>0.8389603877653351</v>
       </c>
       <c r="H18" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>0.83266570931902351</v>
       </c>
       <c r="I18" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>0.82385080498288044</v>
       </c>
       <c r="J18" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>0.83469315360056762</v>
       </c>
       <c r="K18" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>0.81322544272733299</v>
       </c>
       <c r="L18" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>0.80392505632633704</v>
       </c>
       <c r="M18" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>0.82126671198731027</v>
       </c>
       <c r="N18" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>0.83436106631249407</v>
       </c>
       <c r="O18" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>0.80498393189378137</v>
       </c>
       <c r="P18" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>0.7950981966072671</v>
       </c>
       <c r="Q18" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>0.80465766185374943</v>
       </c>
       <c r="R18" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>0.81440581362211462</v>
       </c>
       <c r="S18" s="9">
-        <f t="shared" ref="S18:V18" si="116">S5/S3</f>
+        <f t="shared" ref="S18:V18" si="117">S5/S3</f>
         <v>0.80394329601467274</v>
       </c>
       <c r="T18" s="9">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>0.81432059703545756</v>
       </c>
       <c r="U18" s="9">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>0.80106859703550504</v>
       </c>
       <c r="V18" s="9">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>0.81146981081642955</v>
       </c>
       <c r="W18" s="9">
-        <f t="shared" ref="W18:AE18" si="117">W5/W3</f>
+        <f t="shared" ref="W18:AE18" si="118">W5/W3</f>
         <v>0.78482872294682526</v>
       </c>
       <c r="X18" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>0.81985982929706469</v>
       </c>
       <c r="Y18" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>0.79375045103557773</v>
       </c>
       <c r="Z18" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>0.74083631276231932</v>
       </c>
       <c r="AA18" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>0.7867690696456624</v>
       </c>
       <c r="AB18" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>0.81421294415450485</v>
       </c>
       <c r="AC18" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>0.81956066945606698</v>
       </c>
       <c r="AD18" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>0.80815736331679588</v>
       </c>
       <c r="AE18" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>0.81785763269784661</v>
       </c>
       <c r="AF18" s="9">
-        <f t="shared" ref="AF18:AH18" si="118">AF5/AF3</f>
+        <f t="shared" ref="AF18:AH18" si="119">AF5/AF3</f>
         <v>0.81295590079598679</v>
       </c>
       <c r="AG18" s="9">
-        <f t="shared" si="118"/>
+        <f t="shared" si="119"/>
         <v>0.81830052477272164</v>
       </c>
       <c r="AH18" s="9">
-        <f t="shared" si="118"/>
+        <f t="shared" si="119"/>
         <v>0.81731941717474421</v>
       </c>
       <c r="AI18" s="9">
-        <f t="shared" ref="AI18:AL18" si="119">AI5/AI3</f>
+        <f t="shared" ref="AI18:AL18" si="120">AI5/AI3</f>
         <v>0.82105213404546962</v>
       </c>
       <c r="AJ18" s="9">
-        <f t="shared" si="119"/>
+        <f t="shared" si="120"/>
+        <v>0.82130229817324696</v>
+      </c>
+      <c r="AK18" s="9">
+        <f t="shared" si="120"/>
         <v>0.82</v>
       </c>
-      <c r="AK18" s="9">
-        <f t="shared" si="119"/>
+      <c r="AL18" s="9">
+        <f t="shared" si="120"/>
         <v>0.82</v>
       </c>
-      <c r="AL18" s="9">
-        <f t="shared" si="119"/>
-        <v>0.82000000000000006</v>
-      </c>
       <c r="AN18" s="9">
-        <f t="shared" ref="AN18" si="120">AN5/AN3</f>
+        <f t="shared" ref="AN18" si="121">AN5/AN3</f>
         <v>0.86581556096721024</v>
       </c>
       <c r="AO18" s="9">
-        <f t="shared" ref="AO18:BA18" si="121">AO5/AO3</f>
+        <f t="shared" ref="AO18:BA18" si="122">AO5/AO3</f>
         <v>0.8324617643898421</v>
       </c>
       <c r="AP18" s="9">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>0.81931887318363827</v>
       </c>
       <c r="AQ18" s="9">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>0.80583021194425708</v>
       </c>
       <c r="AR18" s="9">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>0.80794376277251567</v>
       </c>
       <c r="AS18" s="9">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>0.78347297378418479</v>
       </c>
       <c r="AT18" s="9">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>0.80796176694705224</v>
       </c>
       <c r="AU18" s="9">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>0.81664437689969605</v>
       </c>
       <c r="AV18" s="9">
-        <f t="shared" si="121"/>
-        <v>0.81999999999999984</v>
-      </c>
-      <c r="AW18" s="9">
-        <f t="shared" si="121"/>
-        <v>0.82</v>
-      </c>
-      <c r="AX18" s="9">
-        <f t="shared" si="121"/>
-        <v>0.81999999999999984</v>
-      </c>
-      <c r="AY18" s="9">
-        <f t="shared" si="121"/>
-        <v>0.82</v>
-      </c>
-      <c r="AZ18" s="9">
-        <f t="shared" si="121"/>
-        <v>0.82</v>
-      </c>
-      <c r="BA18" s="9">
-        <f t="shared" si="121"/>
-        <v>0.82</v>
-      </c>
-      <c r="BB18" s="9">
-        <f t="shared" ref="BB18:BF18" si="122">BB5/BB3</f>
-        <v>0.82</v>
-      </c>
-      <c r="BC18" s="9">
         <f t="shared" si="122"/>
         <v>0.82</v>
       </c>
-      <c r="BD18" s="9">
+      <c r="AW18" s="9">
         <f t="shared" si="122"/>
         <v>0.82</v>
       </c>
+      <c r="AX18" s="9">
+        <f t="shared" si="122"/>
+        <v>0.82</v>
+      </c>
+      <c r="AY18" s="9">
+        <f t="shared" si="122"/>
+        <v>0.82</v>
+      </c>
+      <c r="AZ18" s="9">
+        <f t="shared" si="122"/>
+        <v>0.82</v>
+      </c>
+      <c r="BA18" s="9">
+        <f t="shared" si="122"/>
+        <v>0.82</v>
+      </c>
+      <c r="BB18" s="9">
+        <f t="shared" ref="BB18:BF18" si="123">BB5/BB3</f>
+        <v>0.82</v>
+      </c>
+      <c r="BC18" s="9">
+        <f t="shared" si="123"/>
+        <v>0.82</v>
+      </c>
+      <c r="BD18" s="9">
+        <f t="shared" si="123"/>
+        <v>0.82</v>
+      </c>
       <c r="BE18" s="9">
-        <f t="shared" si="122"/>
-        <v>0.81999999999999984</v>
+        <f t="shared" si="123"/>
+        <v>0.82</v>
       </c>
       <c r="BF18" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>0.82</v>
       </c>
       <c r="BH18" t="s">
@@ -4867,220 +4860,220 @@
         <v>0.41421812749003983</v>
       </c>
       <c r="D19" s="9">
-        <f t="shared" ref="D19:R19" si="123">D9/D3</f>
+        <f t="shared" ref="D19:R19" si="124">D9/D3</f>
         <v>0.47215963952365625</v>
       </c>
       <c r="E19" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>0.49593338497288925</v>
       </c>
       <c r="F19" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>0.56675917360468697</v>
       </c>
       <c r="G19" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>0.45537355841551064</v>
       </c>
       <c r="H19" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>0.44312599198851182</v>
       </c>
       <c r="I19" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>0.42114081736723247</v>
       </c>
       <c r="J19" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>0.46233889085964291</v>
       </c>
       <c r="K19" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>0.22000397957153281</v>
       </c>
       <c r="L19" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>0.27309379817384088</v>
       </c>
       <c r="M19" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>0.40703602991162474</v>
       </c>
       <c r="N19" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>0.42016886443411439</v>
       </c>
       <c r="O19" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>0.33224333314540228</v>
       </c>
       <c r="P19" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>0.31909883876491679</v>
       </c>
       <c r="Q19" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>0.37447601304145317</v>
       </c>
       <c r="R19" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>0.45507979481333716</v>
       </c>
       <c r="S19" s="9">
-        <f t="shared" ref="S19:V19" si="124">S9/S3</f>
+        <f t="shared" ref="S19:V19" si="125">S9/S3</f>
         <v>0.43475602766420846</v>
       </c>
       <c r="T19" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="125"/>
         <v>0.42531898063761736</v>
       </c>
       <c r="U19" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="125"/>
         <v>0.35928990003447087</v>
       </c>
       <c r="V19" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="125"/>
         <v>0.37376377297971547</v>
       </c>
       <c r="W19" s="9">
-        <f t="shared" ref="W19:AE19" si="125">W9/W3</f>
+        <f t="shared" ref="W19:AE19" si="126">W9/W3</f>
         <v>0.30543213415508097</v>
       </c>
       <c r="X19" s="9">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>0.28998681562695161</v>
       </c>
       <c r="Y19" s="9">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>0.20437324096124701</v>
       </c>
       <c r="Z19" s="9">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>0.19894295041193844</v>
       </c>
       <c r="AA19" s="9">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>0.25229533950078548</v>
       </c>
       <c r="AB19" s="9">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>0.29350917216163003</v>
       </c>
       <c r="AC19" s="9">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>0.40731055323105531</v>
       </c>
       <c r="AD19" s="9">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>0.4084665054473835</v>
       </c>
       <c r="AE19" s="9">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>0.37904265532848719</v>
       </c>
       <c r="AF19" s="9">
-        <f t="shared" ref="AF19:AH19" si="126">AF9/AF3</f>
+        <f t="shared" ref="AF19:AH19" si="127">AF9/AF3</f>
         <v>0.38000051188861306</v>
       </c>
       <c r="AG19" s="9">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>0.4274557146024785</v>
       </c>
       <c r="AH19" s="9">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>0.45086287072439807</v>
       </c>
       <c r="AI19" s="9">
-        <f t="shared" ref="AI19:AL19" si="127">AI9/AI3</f>
+        <f t="shared" ref="AI19:AL19" si="128">AI9/AI3</f>
         <v>0.41487450961856598</v>
       </c>
       <c r="AJ19" s="9">
-        <f t="shared" si="127"/>
-        <v>0.38559878170510098</v>
+        <f t="shared" si="128"/>
+        <v>0.43019193534809325</v>
       </c>
       <c r="AK19" s="9">
-        <f t="shared" si="127"/>
-        <v>0.42951302300892091</v>
+        <f t="shared" si="128"/>
+        <v>0.45157993670323132</v>
       </c>
       <c r="AL19" s="9">
-        <f t="shared" si="127"/>
-        <v>0.45207613044184297</v>
+        <f t="shared" si="128"/>
+        <v>0.46584539723994101</v>
       </c>
       <c r="AN19" s="9">
-        <f t="shared" ref="AN19" si="128">AN9/AN3</f>
+        <f t="shared" ref="AN19" si="129">AN9/AN3</f>
         <v>0.49693749538779425</v>
       </c>
       <c r="AO19" s="9">
-        <f t="shared" ref="AO19:BA19" si="129">AO9/AO3</f>
+        <f t="shared" ref="AO19:BA19" si="130">AO9/AO3</f>
         <v>0.44616569361366809</v>
       </c>
       <c r="AP19" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="130"/>
         <v>0.33909192523734738</v>
       </c>
       <c r="AQ19" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="130"/>
         <v>0.38004559942302774</v>
       </c>
       <c r="AR19" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="130"/>
         <v>0.39645040660058173</v>
       </c>
       <c r="AS19" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="130"/>
         <v>0.24822269293107735</v>
       </c>
       <c r="AT19" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="130"/>
         <v>0.34786307713932724</v>
       </c>
       <c r="AU19" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="130"/>
         <v>0.41234042553191491</v>
       </c>
       <c r="AV19" s="9">
-        <f t="shared" si="129"/>
-        <v>0.42158412553993052</v>
+        <f t="shared" si="130"/>
+        <v>0.44154284411316724</v>
       </c>
       <c r="AW19" s="9">
-        <f t="shared" si="129"/>
-        <v>0.43041355833422179</v>
+        <f t="shared" si="130"/>
+        <v>0.45997642973539232</v>
       </c>
       <c r="AX19" s="9">
-        <f t="shared" si="129"/>
-        <v>0.43501664518713956</v>
+        <f t="shared" si="130"/>
+        <v>0.47211046226022496</v>
       </c>
       <c r="AY19" s="9">
-        <f t="shared" si="129"/>
-        <v>0.43907219365172895</v>
+        <f t="shared" si="130"/>
+        <v>0.48088362902795762</v>
       </c>
       <c r="AZ19" s="9">
-        <f t="shared" si="129"/>
-        <v>0.44003197354679519</v>
+        <f t="shared" si="130"/>
+        <v>0.48426410152462224</v>
       </c>
       <c r="BA19" s="9">
-        <f t="shared" si="129"/>
-        <v>0.43789442200707435</v>
+        <f t="shared" si="130"/>
+        <v>0.48499437874986384</v>
       </c>
       <c r="BB19" s="9">
-        <f t="shared" ref="BB19:BF19" si="130">BB9/BB3</f>
-        <v>0.43836494847331664</v>
+        <f t="shared" ref="BB19:BF19" si="131">BB9/BB3</f>
+        <v>0.48535593757216483</v>
       </c>
       <c r="BC19" s="9">
-        <f t="shared" si="130"/>
-        <v>0.43883086193498788</v>
+        <f t="shared" si="131"/>
+        <v>0.48571395170012943</v>
       </c>
       <c r="BD19" s="9">
-        <f t="shared" si="130"/>
-        <v>0.43616638789106504</v>
+        <f t="shared" si="131"/>
+        <v>0.48606845588566322</v>
       </c>
       <c r="BE19" s="9">
-        <f t="shared" si="130"/>
-        <v>0.43347553291601415</v>
+        <f t="shared" si="131"/>
+        <v>0.4864194845399662</v>
       </c>
       <c r="BF19" s="9">
-        <f t="shared" si="130"/>
-        <v>0.43075803581249744</v>
+        <f t="shared" si="131"/>
+        <v>0.48676707173687411</v>
       </c>
       <c r="BH19" t="s">
         <v>44</v>
@@ -5098,204 +5091,204 @@
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
       <c r="G20" s="9">
-        <f t="shared" ref="G20:R20" si="131">G6/C6-1</f>
+        <f t="shared" ref="G20:R20" si="132">G6/C6-1</f>
         <v>0.22028353326063255</v>
       </c>
       <c r="H20" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>0.31474726420010413</v>
       </c>
       <c r="I20" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>0.29483430799220267</v>
       </c>
       <c r="J20" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>0.46485377116469984</v>
       </c>
       <c r="K20" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>0.27792672028596965</v>
       </c>
       <c r="L20" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>0.31391200951248521</v>
       </c>
       <c r="M20" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>0.33534060971019941</v>
       </c>
       <c r="N20" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>0.35796847635726792</v>
       </c>
       <c r="O20" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>0.40384615384615374</v>
       </c>
       <c r="P20" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>0.34600301659125199</v>
       </c>
       <c r="Q20" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>0.34244644870349483</v>
       </c>
       <c r="R20" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>0.34330668042300738</v>
       </c>
       <c r="S20" s="9">
-        <f t="shared" ref="S20" si="132">S6/O6-1</f>
+        <f t="shared" ref="S20" si="133">S6/O6-1</f>
         <v>0.29439601494396017</v>
       </c>
       <c r="T20" s="9">
-        <f t="shared" ref="T20" si="133">T6/P6-1</f>
+        <f t="shared" ref="T20" si="134">T6/P6-1</f>
         <v>0.36620349619004933</v>
       </c>
       <c r="U20" s="9">
-        <f t="shared" ref="U20" si="134">U6/Q6-1</f>
+        <f t="shared" ref="U20" si="135">U6/Q6-1</f>
         <v>0.32605500734830994</v>
       </c>
       <c r="V20" s="9">
-        <f t="shared" ref="V20" si="135">V6/R6-1</f>
+        <f t="shared" ref="V20" si="136">V6/R6-1</f>
         <v>0.35291858678955457</v>
       </c>
       <c r="W20" s="9">
-        <f t="shared" ref="W20" si="136">W6/S6-1</f>
+        <f t="shared" ref="W20" si="137">W6/S6-1</f>
         <v>0.48297094477583213</v>
       </c>
       <c r="X20" s="9">
-        <f t="shared" ref="X20" si="137">X6/T6-1</f>
+        <f t="shared" ref="X20" si="138">X6/T6-1</f>
         <v>0.42552493438320216</v>
       </c>
       <c r="Y20" s="9">
-        <f t="shared" ref="Y20" si="138">Y6/U6-1</f>
+        <f t="shared" ref="Y20" si="139">Y6/U6-1</f>
         <v>0.45186827105763139</v>
       </c>
       <c r="Z20" s="9">
-        <f t="shared" ref="Z20" si="139">Z6/V6-1</f>
+        <f t="shared" ref="Z20" si="140">Z6/V6-1</f>
         <v>0.38674425205790519</v>
       </c>
       <c r="AA20" s="9">
-        <f t="shared" ref="AA20" si="140">AA6/W6-1</f>
+        <f t="shared" ref="AA20" si="141">AA6/W6-1</f>
         <v>0.21720513818606468</v>
       </c>
       <c r="AB20" s="9">
-        <f t="shared" ref="AB20" si="141">AB6/X6-1</f>
+        <f t="shared" ref="AB20" si="142">AB6/X6-1</f>
         <v>7.5258918296893018E-2</v>
       </c>
       <c r="AC20" s="9">
-        <f t="shared" ref="AC20" si="142">AC6/Y6-1</f>
+        <f t="shared" ref="AC20" si="143">AC6/Y6-1</f>
         <v>7.7426390403489975E-3</v>
       </c>
       <c r="AD20" s="9">
-        <f t="shared" ref="AD20" si="143">AD6/Z6-1</f>
+        <f t="shared" ref="AD20" si="144">AD6/Z6-1</f>
         <v>7.6348377852829774E-2</v>
       </c>
       <c r="AE20" s="9">
-        <f t="shared" ref="AE20" si="144">AE6/AA6-1</f>
+        <f t="shared" ref="AE20" si="145">AE6/AA6-1</f>
         <v>6.3639270866645337E-2</v>
       </c>
       <c r="AF20" s="9">
-        <f t="shared" ref="AF20" si="145">AF6/AB6-1</f>
+        <f t="shared" ref="AF20" si="146">AF6/AB6-1</f>
         <v>0.12767551369863006</v>
       </c>
       <c r="AG20" s="9">
-        <f t="shared" ref="AG20" si="146">AG6/AC6-1</f>
+        <f t="shared" ref="AG20" si="147">AG6/AC6-1</f>
         <v>0.20950113624066669</v>
       </c>
       <c r="AH20" s="9">
-        <f t="shared" ref="AH20" si="147">AH6/AD6-1</f>
+        <f t="shared" ref="AH20" si="148">AH6/AD6-1</f>
         <v>0.15812494057240656</v>
       </c>
       <c r="AI20" s="9">
-        <f t="shared" ref="AI20" si="148">AI6/AE6-1</f>
+        <f t="shared" ref="AI20" si="149">AI6/AE6-1</f>
         <v>0.21767889356584491</v>
       </c>
       <c r="AJ20" s="9">
-        <f t="shared" ref="AJ20" si="149">AJ6/AF6-1</f>
-        <v>0.17999999999999994</v>
+        <f t="shared" ref="AJ20" si="150">AJ6/AF6-1</f>
+        <v>0.22824333301698774</v>
       </c>
       <c r="AK20" s="9">
-        <f t="shared" ref="AK20" si="150">AK6/AG6-1</f>
+        <f t="shared" ref="AK20" si="151">AK6/AG6-1</f>
         <v>0.12999999999999989</v>
       </c>
       <c r="AL20" s="9">
-        <f t="shared" ref="AL20" si="151">AL6/AH6-1</f>
+        <f t="shared" ref="AL20" si="152">AL6/AH6-1</f>
         <v>7.0000000000000062E-2</v>
       </c>
       <c r="AN20" s="9"/>
       <c r="AO20" s="9">
-        <f t="shared" ref="AO20:BA20" si="152">AO6/AN6-1</f>
+        <f t="shared" ref="AO20:BA20" si="153">AO6/AN6-1</f>
         <v>0.3248645860201187</v>
       </c>
       <c r="AP20" s="9">
-        <f t="shared" si="152"/>
+        <f t="shared" si="153"/>
         <v>0.32385865861968277</v>
       </c>
       <c r="AQ20" s="9">
-        <f t="shared" si="152"/>
+        <f t="shared" si="153"/>
         <v>0.35647058823529409</v>
       </c>
       <c r="AR20" s="9">
-        <f t="shared" si="152"/>
+        <f t="shared" si="153"/>
         <v>0.3364592367736341</v>
       </c>
       <c r="AS20" s="9">
-        <f t="shared" si="152"/>
+        <f t="shared" si="153"/>
         <v>0.43329953356317175</v>
       </c>
       <c r="AT20" s="9">
-        <f t="shared" si="152"/>
+        <f t="shared" si="153"/>
         <v>8.8997679551757303E-2</v>
       </c>
       <c r="AU20" s="9">
-        <f t="shared" si="152"/>
+        <f t="shared" si="153"/>
         <v>0.14003585999012547</v>
       </c>
       <c r="AV20" s="9">
-        <f t="shared" si="152"/>
-        <v>0.1452924416484318</v>
+        <f t="shared" si="153"/>
+        <v>0.15687933078045213</v>
       </c>
       <c r="AW20" s="9">
-        <f t="shared" si="152"/>
+        <f t="shared" si="153"/>
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="AX20" s="9">
-        <f t="shared" si="152"/>
+        <f t="shared" si="153"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AY20" s="9">
-        <f t="shared" si="152"/>
+        <f t="shared" si="153"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AZ20" s="9">
-        <f t="shared" si="152"/>
+        <f t="shared" si="153"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="BA20" s="9">
-        <f t="shared" si="152"/>
+        <f t="shared" si="153"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="BB20" s="9">
-        <f t="shared" ref="BB20" si="153">BB6/BA6-1</f>
+        <f t="shared" ref="BB20" si="154">BB6/BA6-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BC20" s="9">
-        <f t="shared" ref="BC20" si="154">BC6/BB6-1</f>
+        <f t="shared" ref="BC20" si="155">BC6/BB6-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BD20" s="9">
-        <f t="shared" ref="BD20" si="155">BD6/BC6-1</f>
+        <f t="shared" ref="BD20" si="156">BD6/BC6-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BE20" s="9">
-        <f t="shared" ref="BE20" si="156">BE6/BD6-1</f>
+        <f t="shared" ref="BE20" si="157">BE6/BD6-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BF20" s="9">
-        <f t="shared" ref="BF20" si="157">BF6/BE6-1</f>
+        <f t="shared" ref="BF20" si="158">BF6/BE6-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BH20" t="s">
@@ -5303,7 +5296,7 @@
       </c>
       <c r="BI20" s="20">
         <f>NPV(BI19,AU13:FI13)</f>
-        <v>1581357.4157635346</v>
+        <v>2058680.1424818356</v>
       </c>
     </row>
     <row r="21" spans="2:61" x14ac:dyDescent="0.3">
@@ -5315,227 +5308,227 @@
         <v>0.13159860557768924</v>
       </c>
       <c r="D21" s="9">
-        <f t="shared" ref="D21:R21" si="158">D7/D3</f>
+        <f t="shared" ref="D21:R21" si="159">D7/D3</f>
         <v>0.12058791975109967</v>
       </c>
       <c r="E21" s="9">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>0.11328427575522851</v>
       </c>
       <c r="F21" s="9">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>0.1059204440333025</v>
       </c>
       <c r="G21" s="9">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>0.13329433394618084</v>
       </c>
       <c r="H21" s="9">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>0.14020104300506386</v>
       </c>
       <c r="I21" s="9">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>0.14045312158519704</v>
       </c>
       <c r="J21" s="9">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>0.14585550431595129</v>
       </c>
       <c r="K21" s="9">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>0.13397890827087616</v>
       </c>
       <c r="L21" s="9">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>0.14312818688485712</v>
       </c>
       <c r="M21" s="9">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>0.13686834353047814</v>
       </c>
       <c r="N21" s="9">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>0.14353476899724885</v>
       </c>
       <c r="O21" s="9">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>0.15712916502226984</v>
       </c>
       <c r="P21" s="9">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>0.15197731042971049</v>
       </c>
       <c r="Q21" s="9">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>0.12496506753609687</v>
       </c>
       <c r="R21" s="9">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>0.11684240524365916</v>
       </c>
       <c r="S21" s="9">
-        <f t="shared" ref="S21:V21" si="159">S7/S3</f>
+        <f t="shared" ref="S21:V21" si="160">S7/S3</f>
         <v>0.10863169156700164</v>
       </c>
       <c r="T21" s="9">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>0.1120817140695395</v>
       </c>
       <c r="U21" s="9">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>0.1225094794898311</v>
       </c>
       <c r="V21" s="9">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>0.13029016067238872</v>
       </c>
       <c r="W21" s="9">
-        <f t="shared" ref="W21:AE21" si="160">W7/W3</f>
+        <f t="shared" ref="W21:AE21" si="161">W7/W3</f>
         <v>0.11867564855955282</v>
       </c>
       <c r="X21" s="9">
-        <f t="shared" si="160"/>
+        <f t="shared" si="161"/>
         <v>0.12473110818125044</v>
       </c>
       <c r="Y21" s="9">
-        <f t="shared" si="160"/>
+        <f t="shared" si="161"/>
         <v>0.13639315869235766</v>
       </c>
       <c r="Z21" s="9">
-        <f t="shared" si="160"/>
+        <f t="shared" si="161"/>
         <v>0.142204259288046</v>
       </c>
       <c r="AA21" s="9">
-        <f t="shared" si="160"/>
+        <f t="shared" si="161"/>
         <v>0.10626636411241054</v>
       </c>
       <c r="AB21" s="9">
-        <f t="shared" si="160"/>
+        <f t="shared" si="161"/>
         <v>9.8565580174380454E-2</v>
       </c>
       <c r="AC21" s="9">
-        <f t="shared" si="160"/>
+        <f t="shared" si="161"/>
         <v>8.3594839609483967E-2</v>
       </c>
       <c r="AD21" s="9">
-        <f t="shared" si="160"/>
+        <f t="shared" si="161"/>
         <v>8.0426815586746775E-2</v>
       </c>
       <c r="AE21" s="9">
-        <f t="shared" si="160"/>
+        <f t="shared" si="161"/>
         <v>7.0333287614867651E-2</v>
       </c>
       <c r="AF21" s="9">
-        <f t="shared" ref="AF21:AH21" si="161">AF7/AF3</f>
+        <f t="shared" ref="AF21:AH21" si="162">AF7/AF3</f>
         <v>6.9642445803793099E-2</v>
       </c>
       <c r="AG21" s="9">
-        <f t="shared" si="161"/>
+        <f t="shared" si="162"/>
         <v>6.9526226317475182E-2</v>
       </c>
       <c r="AH21" s="9">
-        <f t="shared" si="161"/>
+        <f t="shared" si="162"/>
         <v>6.6962901725741444E-2</v>
       </c>
       <c r="AI21" s="9">
-        <f t="shared" ref="AI21:AL21" si="162">AI7/AI3</f>
+        <f t="shared" ref="AI21:AL21" si="163">AI7/AI3</f>
         <v>6.5155740416883295E-2</v>
       </c>
       <c r="AJ21" s="9">
-        <f t="shared" si="162"/>
+        <f t="shared" si="163"/>
+        <v>6.269467126862531E-2</v>
+      </c>
+      <c r="AK21" s="9">
+        <f t="shared" si="163"/>
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="AK21" s="9">
-        <f t="shared" si="162"/>
+      <c r="AL21" s="9">
+        <f t="shared" si="163"/>
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="AL21" s="9">
-        <f t="shared" si="162"/>
-        <v>6.5000000000000002E-2</v>
-      </c>
       <c r="AN21" s="9">
-        <f t="shared" ref="AN21" si="163">AN7/AN3</f>
+        <f t="shared" ref="AN21" si="164">AN7/AN3</f>
         <v>0.1162275846800974</v>
       </c>
       <c r="AO21" s="9">
-        <f t="shared" ref="AO21:BA21" si="164">AO7/AO3</f>
+        <f t="shared" ref="AO21:BA21" si="165">AO7/AO3</f>
         <v>0.14049571976073641</v>
       </c>
       <c r="AP21" s="9">
-        <f t="shared" si="164"/>
+        <f t="shared" si="165"/>
         <v>0.13973428413769684</v>
       </c>
       <c r="AQ21" s="9">
-        <f t="shared" si="164"/>
+        <f t="shared" si="165"/>
         <v>0.13482074308447525</v>
       </c>
       <c r="AR21" s="9">
-        <f t="shared" si="164"/>
+        <f t="shared" si="165"/>
         <v>0.11908012448167965</v>
       </c>
       <c r="AS21" s="9">
-        <f t="shared" si="164"/>
+        <f t="shared" si="165"/>
         <v>0.13087326021147597</v>
       </c>
       <c r="AT21" s="9">
-        <f t="shared" si="164"/>
+        <f t="shared" si="165"/>
         <v>9.1003247738050325E-2</v>
       </c>
       <c r="AU21" s="9">
-        <f t="shared" si="164"/>
+        <f t="shared" si="165"/>
         <v>6.8978723404255315E-2</v>
       </c>
       <c r="AV21" s="9">
-        <f t="shared" si="164"/>
-        <v>6.503630340546325E-2</v>
+        <f t="shared" si="165"/>
+        <v>6.4460849447798813E-2</v>
       </c>
       <c r="AW21" s="9">
-        <f t="shared" si="164"/>
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="AX21" s="9">
-        <f t="shared" si="164"/>
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="AY21" s="9">
-        <f t="shared" si="164"/>
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="AZ21" s="9">
-        <f t="shared" si="164"/>
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="BA21" s="9">
-        <f t="shared" si="164"/>
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="BB21" s="9">
-        <f t="shared" ref="BB21:BF21" si="165">BB7/BB3</f>
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="BC21" s="9">
         <f t="shared" si="165"/>
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="BD21" s="9">
+      <c r="AX21" s="9">
         <f t="shared" si="165"/>
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="BE21" s="9">
+      <c r="AY21" s="9">
         <f t="shared" si="165"/>
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="BF21" s="9">
+      <c r="AZ21" s="9">
         <f t="shared" si="165"/>
         <v>6.5000000000000002E-2</v>
       </c>
+      <c r="BA21" s="9">
+        <f t="shared" si="165"/>
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="BB21" s="9">
+        <f t="shared" ref="BB21:BF21" si="166">BB7/BB3</f>
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="BC21" s="9">
+        <f t="shared" si="166"/>
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="BD21" s="9">
+        <f t="shared" si="166"/>
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="BE21" s="9">
+        <f t="shared" si="166"/>
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="BF21" s="9">
+        <f t="shared" si="166"/>
+        <v>6.5000000000000002E-2</v>
+      </c>
       <c r="BH21" t="s">
         <v>46</v>
       </c>
       <c r="BI21" s="20">
         <f>Main!D8</f>
-        <v>47569</v>
+        <v>40227</v>
       </c>
     </row>
     <row r="22" spans="2:61" x14ac:dyDescent="0.3">
@@ -5547,204 +5540,204 @@
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
       <c r="G22" s="9">
-        <f t="shared" ref="G22" si="166">G8/C8-1</f>
+        <f t="shared" ref="G22" si="167">G8/C8-1</f>
         <v>0.1557251908396946</v>
       </c>
       <c r="H22" s="9">
-        <f t="shared" ref="H22" si="167">H8/D8-1</f>
+        <f t="shared" ref="H22" si="168">H8/D8-1</f>
         <v>0.21249999999999991</v>
       </c>
       <c r="I22" s="9">
-        <f t="shared" ref="I22" si="168">I8/E8-1</f>
+        <f t="shared" ref="I22" si="169">I8/E8-1</f>
         <v>0.75932835820895517</v>
       </c>
       <c r="J22" s="9">
-        <f t="shared" ref="J22" si="169">J8/F8-1</f>
+        <f t="shared" ref="J22" si="170">J8/F8-1</f>
         <v>0.42274052478134116</v>
       </c>
       <c r="K22" s="9">
-        <f t="shared" ref="K22" si="170">K8/G8-1</f>
+        <f t="shared" ref="K22" si="171">K8/G8-1</f>
         <v>4.3685601056803174</v>
       </c>
       <c r="L22" s="9">
-        <f t="shared" ref="L22" si="171">L8/H8-1</f>
+        <f t="shared" ref="L22" si="172">L8/H8-1</f>
         <v>3.1546391752577323</v>
       </c>
       <c r="M22" s="9">
-        <f t="shared" ref="M22" si="172">M8/I8-1</f>
+        <f t="shared" ref="M22" si="173">M8/I8-1</f>
         <v>0.42948038176033942</v>
       </c>
       <c r="N22" s="9">
-        <f t="shared" ref="N22" si="173">N8/J8-1</f>
+        <f t="shared" ref="N22" si="174">N8/J8-1</f>
         <v>0.87397540983606548</v>
       </c>
       <c r="O22" s="9">
-        <f t="shared" ref="O22" si="174">O8/K8-1</f>
+        <f t="shared" ref="O22" si="175">O8/K8-1</f>
         <v>-0.6104822834645669</v>
       </c>
       <c r="P22" s="9">
-        <f t="shared" ref="P22" si="175">P8/L8-1</f>
+        <f t="shared" ref="P22" si="176">P8/L8-1</f>
         <v>-0.50589330024813894</v>
       </c>
       <c r="Q22" s="9">
-        <f t="shared" ref="Q22" si="176">Q8/M8-1</f>
+        <f t="shared" ref="Q22" si="177">Q8/M8-1</f>
         <v>0.32789317507418403</v>
       </c>
       <c r="R22" s="9">
-        <f t="shared" ref="R22" si="177">R8/N8-1</f>
+        <f t="shared" ref="R22" si="178">R8/N8-1</f>
         <v>-0.12575177692728268</v>
       </c>
       <c r="S22" s="9">
-        <f t="shared" ref="S22" si="178">S8/O8-1</f>
+        <f t="shared" ref="S22" si="179">S8/O8-1</f>
         <v>2.4636765634870494E-2</v>
       </c>
       <c r="T22" s="9">
-        <f t="shared" ref="T22" si="179">T8/P8-1</f>
+        <f t="shared" ref="T22" si="180">T8/P8-1</f>
         <v>0.22787193973634645</v>
       </c>
       <c r="U22" s="9">
-        <f t="shared" ref="U22" si="180">U8/Q8-1</f>
+        <f t="shared" ref="U22" si="181">U8/Q8-1</f>
         <v>0.64581005586592188</v>
       </c>
       <c r="V22" s="9">
-        <f t="shared" ref="V22" si="181">V8/R8-1</f>
+        <f t="shared" ref="V22" si="182">V8/R8-1</f>
         <v>1.0669168230143842</v>
       </c>
       <c r="W22" s="9">
-        <f t="shared" ref="W22" si="182">W8/S8-1</f>
+        <f t="shared" ref="W22" si="183">W8/S8-1</f>
         <v>0.45499383477188649</v>
       </c>
       <c r="X22" s="9">
-        <f t="shared" ref="X22" si="183">X8/T8-1</f>
+        <f t="shared" ref="X22" si="184">X8/T8-1</f>
         <v>0.52709611451942751</v>
       </c>
       <c r="Y22" s="9">
-        <f t="shared" ref="Y22" si="184">Y8/U8-1</f>
+        <f t="shared" ref="Y22" si="185">Y8/U8-1</f>
         <v>0.14867617107942976</v>
       </c>
       <c r="Z22" s="9">
-        <f t="shared" ref="Z22" si="185">Z8/V8-1</f>
+        <f t="shared" ref="Z22" si="186">Z8/V8-1</f>
         <v>-6.656580937972767E-2</v>
       </c>
       <c r="AA22" s="9">
-        <f t="shared" ref="AA22" si="186">AA8/W8-1</f>
+        <f t="shared" ref="AA22" si="187">AA8/W8-1</f>
         <v>0.22245762711864403</v>
       </c>
       <c r="AB22" s="9">
-        <f t="shared" ref="AB22" si="187">AB8/X8-1</f>
+        <f t="shared" ref="AB22" si="188">AB8/X8-1</f>
         <v>0.39404084365584202</v>
       </c>
       <c r="AC22" s="9">
-        <f t="shared" ref="AC22" si="188">AC8/Y8-1</f>
+        <f t="shared" ref="AC22" si="189">AC8/Y8-1</f>
         <v>-0.38829787234042556</v>
       </c>
       <c r="AD22" s="9">
-        <f t="shared" ref="AD22" si="189">AD8/Z8-1</f>
+        <f t="shared" ref="AD22" si="190">AD8/Z8-1</f>
         <v>-0.25802269043760129</v>
       </c>
       <c r="AE22" s="9">
-        <f t="shared" ref="AE22" si="190">AE8/AA8-1</f>
+        <f t="shared" ref="AE22" si="191">AE8/AA8-1</f>
         <v>0.19757365684575401</v>
       </c>
       <c r="AF22" s="9">
-        <f t="shared" ref="AF22" si="191">AF8/AB8-1</f>
+        <f t="shared" ref="AF22" si="192">AF8/AB8-1</f>
         <v>-0.12151777137367914</v>
       </c>
       <c r="AG22" s="9">
-        <f t="shared" ref="AG22" si="192">AG8/AC8-1</f>
+        <f t="shared" ref="AG22" si="193">AG8/AC8-1</f>
         <v>-9.9033816425120769E-2</v>
       </c>
       <c r="AH22" s="9">
-        <f t="shared" ref="AH22" si="193">AH8/AD8-1</f>
+        <f t="shared" ref="AH22" si="194">AH8/AD8-1</f>
         <v>9.6111839231105556E-3</v>
       </c>
       <c r="AI22" s="9">
-        <f t="shared" ref="AI22" si="194">AI8/AE8-1</f>
+        <f t="shared" ref="AI22" si="195">AI8/AE8-1</f>
         <v>-0.34008683068017365</v>
       </c>
       <c r="AJ22" s="9">
-        <f t="shared" ref="AJ22" si="195">AJ8/AF8-1</f>
+        <f t="shared" ref="AJ22" si="196">AJ8/AF8-1</f>
+        <v>-0.27200656096227449</v>
+      </c>
+      <c r="AK22" s="9">
+        <f t="shared" ref="AK22" si="197">AK8/AG8-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AK22" s="9">
-        <f t="shared" ref="AK22" si="196">AK8/AG8-1</f>
-        <v>2.0000000000000018E-2</v>
-      </c>
       <c r="AL22" s="9">
-        <f t="shared" ref="AL22" si="197">AL8/AH8-1</f>
+        <f t="shared" ref="AL22" si="198">AL8/AH8-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AN22" s="9"/>
       <c r="AO22" s="9">
-        <f t="shared" ref="AO22:BA22" si="198">AO8/AN8-1</f>
+        <f t="shared" ref="AO22:BA22" si="199">AO8/AN8-1</f>
         <v>0.37147397695669437</v>
       </c>
       <c r="AP22" s="9">
-        <f t="shared" si="198"/>
+        <f t="shared" si="199"/>
         <v>2.0315758980301273</v>
       </c>
       <c r="AQ22" s="9">
-        <f t="shared" si="198"/>
+        <f t="shared" si="199"/>
         <v>-0.37267080745341619</v>
       </c>
       <c r="AR22" s="9">
-        <f t="shared" si="198"/>
+        <f t="shared" si="199"/>
         <v>0.49718202589489713</v>
       </c>
       <c r="AS22" s="9">
-        <f t="shared" si="198"/>
+        <f t="shared" si="199"/>
         <v>0.20215688269406851</v>
       </c>
       <c r="AT22" s="9">
-        <f t="shared" si="198"/>
+        <f t="shared" si="199"/>
         <v>-3.4529451591063021E-2</v>
       </c>
       <c r="AU22" s="9">
-        <f t="shared" si="198"/>
+        <f t="shared" si="199"/>
         <v>-1.0431276297335201E-2</v>
       </c>
       <c r="AV22" s="9">
-        <f t="shared" si="198"/>
-        <v>-9.0204623970236542E-2</v>
+        <f t="shared" si="199"/>
+        <v>-0.18482416511648503</v>
       </c>
       <c r="AW22" s="9">
-        <f t="shared" si="198"/>
+        <f t="shared" si="199"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AX22" s="9">
-        <f t="shared" si="198"/>
+        <f t="shared" si="199"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AY22" s="9">
-        <f t="shared" si="198"/>
+        <f t="shared" si="199"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AZ22" s="9">
-        <f t="shared" si="198"/>
+        <f t="shared" si="199"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BA22" s="9">
-        <f t="shared" si="198"/>
+        <f t="shared" si="199"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BB22" s="9">
-        <f t="shared" ref="BB22" si="199">BB8/BA8-1</f>
+        <f t="shared" ref="BB22" si="200">BB8/BA8-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BC22" s="9">
-        <f t="shared" ref="BC22" si="200">BC8/BB8-1</f>
+        <f t="shared" ref="BC22" si="201">BC8/BB8-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BD22" s="9">
-        <f t="shared" ref="BD22" si="201">BD8/BC8-1</f>
+        <f t="shared" ref="BD22" si="202">BD8/BC8-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BE22" s="9">
-        <f t="shared" ref="BE22" si="202">BE8/BD8-1</f>
+        <f t="shared" ref="BE22" si="203">BE8/BD8-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BF22" s="9">
-        <f t="shared" ref="BF22" si="203">BF8/BE8-1</f>
+        <f t="shared" ref="BF22" si="204">BF8/BE8-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BH22" t="s">
@@ -5752,7 +5745,7 @@
       </c>
       <c r="BI22" s="20">
         <f>BI20+BI21</f>
-        <v>1628926.4157635346</v>
+        <v>2098907.1424818356</v>
       </c>
     </row>
     <row r="23" spans="2:61" x14ac:dyDescent="0.3">
@@ -5764,227 +5757,227 @@
         <v>0.10240610328638497</v>
       </c>
       <c r="D23" s="9">
-        <f t="shared" ref="D23:R23" si="204">D12/D11</f>
+        <f t="shared" ref="D23:R23" si="205">D12/D11</f>
         <v>0.13324420677361853</v>
       </c>
       <c r="E23" s="9">
-        <f t="shared" si="204"/>
+        <f t="shared" si="205"/>
         <v>0.10103132161955691</v>
       </c>
       <c r="F23" s="9">
-        <f t="shared" si="204"/>
+        <f t="shared" si="205"/>
         <v>0.52452425623157328</v>
       </c>
       <c r="G23" s="9">
-        <f t="shared" si="204"/>
+        <f t="shared" si="205"/>
         <v>0.11105169340463458</v>
       </c>
       <c r="H23" s="9">
-        <f t="shared" si="204"/>
+        <f t="shared" si="205"/>
         <v>0.12985685071574643</v>
       </c>
       <c r="I23" s="9">
-        <f t="shared" si="204"/>
+        <f t="shared" si="205"/>
         <v>0.13108930987821379</v>
       </c>
       <c r="J23" s="9">
-        <f t="shared" si="204"/>
+        <f t="shared" si="205"/>
         <v>0.13662024840045164</v>
       </c>
       <c r="K23" s="9">
-        <f t="shared" si="204"/>
+        <f t="shared" si="205"/>
         <v>0.30241240666283747</v>
       </c>
       <c r="L23" s="9">
-        <f t="shared" si="204"/>
+        <f t="shared" si="205"/>
         <v>0.46051537822111388</v>
       </c>
       <c r="M23" s="9">
-        <f t="shared" si="204"/>
+        <f t="shared" si="205"/>
         <v>0.16891799699822621</v>
       </c>
       <c r="N23" s="9">
-        <f t="shared" si="204"/>
+        <f t="shared" si="205"/>
         <v>0.19849492856363835</v>
       </c>
       <c r="O23" s="9">
-        <f t="shared" si="204"/>
+        <f t="shared" si="205"/>
         <v>0.16362395495649207</v>
       </c>
       <c r="P23" s="9">
-        <f t="shared" si="204"/>
+        <f t="shared" si="205"/>
         <v>0.15543956940140272</v>
       </c>
       <c r="Q23" s="9">
-        <f t="shared" si="204"/>
+        <f t="shared" si="205"/>
         <v>3.5288331488995447E-2</v>
       </c>
       <c r="R23" s="9">
-        <f t="shared" si="204"/>
+        <f t="shared" si="205"/>
         <v>0.14063577173496744</v>
       </c>
       <c r="S23" s="9">
-        <f t="shared" ref="S23:V23" si="205">S12/S11</f>
+        <f t="shared" ref="S23:V23" si="206">S12/S11</f>
         <v>0.17438928975049986</v>
       </c>
       <c r="T23" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="206"/>
         <v>0.16934388236234316</v>
       </c>
       <c r="U23" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="206"/>
         <v>0.12976810222432561</v>
       </c>
       <c r="V23" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="206"/>
         <v>0.19028499448905684</v>
       </c>
       <c r="W23" s="9">
-        <f t="shared" ref="W23:AE23" si="206">W12/W11</f>
+        <f t="shared" ref="W23:AE23" si="207">W12/W11</f>
         <v>0.1619892231701841</v>
       </c>
       <c r="X23" s="9">
-        <f t="shared" si="206"/>
+        <f t="shared" si="207"/>
         <v>0.18311751771316884</v>
       </c>
       <c r="Y23" s="9">
-        <f t="shared" si="206"/>
+        <f t="shared" si="207"/>
         <v>0.21180057388809181</v>
       </c>
       <c r="Z23" s="9">
-        <f t="shared" si="206"/>
+        <f t="shared" si="207"/>
         <v>0.24345422019840623</v>
       </c>
       <c r="AA23" s="9">
-        <f t="shared" si="206"/>
+        <f t="shared" si="207"/>
         <v>0.21869440262761736</v>
       </c>
       <c r="AB23" s="9">
-        <f t="shared" si="206"/>
+        <f t="shared" si="207"/>
         <v>0.16194985472936618</v>
       </c>
       <c r="AC23" s="9">
-        <f t="shared" si="206"/>
+        <f t="shared" si="207"/>
         <v>0.17053883834849545</v>
       </c>
       <c r="AD23" s="9">
-        <f t="shared" si="206"/>
+        <f t="shared" si="207"/>
         <v>0.16605188005711566</v>
       </c>
       <c r="AE23" s="9">
-        <f t="shared" si="206"/>
+        <f t="shared" si="207"/>
         <v>0.12789959811041388</v>
       </c>
       <c r="AF23" s="9">
-        <f t="shared" ref="AF23:AH23" si="207">AF12/AF11</f>
+        <f t="shared" ref="AF23:AH23" si="208">AF12/AF11</f>
         <v>0.10863233152389778</v>
       </c>
       <c r="AG23" s="9">
-        <f t="shared" si="207"/>
+        <f t="shared" si="208"/>
         <v>0.11973964762652901</v>
       </c>
       <c r="AH23" s="9">
-        <f t="shared" si="207"/>
+        <f t="shared" si="208"/>
         <v>0.12339226469117848</v>
       </c>
       <c r="AI23" s="9">
-        <f t="shared" ref="AI23:AL23" si="208">AI12/AI11</f>
+        <f t="shared" ref="AI23:AL23" si="209">AI12/AI11</f>
         <v>9.4549015341094556E-2</v>
       </c>
       <c r="AJ23" s="9">
-        <f t="shared" si="208"/>
+        <f t="shared" si="209"/>
+        <v>0.10699327943897925</v>
+      </c>
+      <c r="AK23" s="9">
+        <f t="shared" si="209"/>
+        <v>0.12</v>
+      </c>
+      <c r="AL23" s="9">
+        <f t="shared" si="209"/>
         <v>0.12000000000000001</v>
       </c>
-      <c r="AK23" s="9">
-        <f t="shared" si="208"/>
-        <v>0.12</v>
-      </c>
-      <c r="AL23" s="9">
-        <f t="shared" si="208"/>
-        <v>0.12000000000000001</v>
-      </c>
       <c r="AN23" s="9">
-        <f t="shared" ref="AN23" si="209">AN12/AN11</f>
+        <f t="shared" ref="AN23" si="210">AN12/AN11</f>
         <v>0.26172671651937457</v>
       </c>
       <c r="AO23" s="9">
-        <f t="shared" ref="AO23:BA23" si="210">AO12/AO11</f>
+        <f t="shared" ref="AO23:BA23" si="211">AO12/AO11</f>
         <v>0.12811009029612397</v>
       </c>
       <c r="AP23" s="9">
-        <f t="shared" si="210"/>
+        <f t="shared" si="211"/>
         <v>0.25520329138431752</v>
       </c>
       <c r="AQ23" s="9">
-        <f t="shared" si="210"/>
+        <f t="shared" si="211"/>
         <v>0.12160940325497288</v>
       </c>
       <c r="AR23" s="9">
-        <f t="shared" si="210"/>
+        <f t="shared" si="211"/>
         <v>0.1673540173000867</v>
       </c>
       <c r="AS23" s="9">
-        <f t="shared" si="210"/>
+        <f t="shared" si="211"/>
         <v>0.19501023630243935</v>
       </c>
       <c r="AT23" s="9">
-        <f t="shared" si="210"/>
+        <f t="shared" si="211"/>
         <v>0.17466141137993207</v>
       </c>
       <c r="AU23" s="9">
-        <f t="shared" si="210"/>
+        <f t="shared" si="211"/>
         <v>0.1201493185172324</v>
       </c>
       <c r="AV23" s="9">
-        <f t="shared" si="210"/>
-        <v>0.11409271264328527</v>
+        <f t="shared" si="211"/>
+        <v>0.11159361251166676</v>
       </c>
       <c r="AW23" s="9">
-        <f t="shared" si="210"/>
-        <v>0.12</v>
+        <f t="shared" si="211"/>
+        <v>0.11999999999999998</v>
       </c>
       <c r="AX23" s="9">
-        <f t="shared" si="210"/>
-        <v>0.12</v>
-      </c>
-      <c r="AY23" s="9">
-        <f t="shared" si="210"/>
-        <v>0.12</v>
-      </c>
-      <c r="AZ23" s="9">
-        <f t="shared" si="210"/>
-        <v>0.12</v>
-      </c>
-      <c r="BA23" s="9">
-        <f t="shared" si="210"/>
-        <v>0.12</v>
-      </c>
-      <c r="BB23" s="9">
-        <f t="shared" ref="BB23:BF23" si="211">BB12/BB11</f>
-        <v>0.12</v>
-      </c>
-      <c r="BC23" s="9">
         <f t="shared" si="211"/>
         <v>0.12</v>
       </c>
-      <c r="BD23" s="9">
+      <c r="AY23" s="9">
         <f t="shared" si="211"/>
         <v>0.12</v>
       </c>
-      <c r="BE23" s="9">
+      <c r="AZ23" s="9">
         <f t="shared" si="211"/>
         <v>0.12</v>
       </c>
-      <c r="BF23" s="9">
+      <c r="BA23" s="9">
         <f t="shared" si="211"/>
         <v>0.12</v>
       </c>
+      <c r="BB23" s="9">
+        <f t="shared" ref="BB23:BF23" si="212">BB12/BB11</f>
+        <v>0.12</v>
+      </c>
+      <c r="BC23" s="9">
+        <f t="shared" si="212"/>
+        <v>0.12</v>
+      </c>
+      <c r="BD23" s="9">
+        <f t="shared" si="212"/>
+        <v>0.11999999999999998</v>
+      </c>
+      <c r="BE23" s="9">
+        <f t="shared" si="212"/>
+        <v>0.12</v>
+      </c>
+      <c r="BF23" s="9">
+        <f t="shared" si="212"/>
+        <v>0.11999999999999998</v>
+      </c>
       <c r="BH23" t="s">
         <v>48</v>
       </c>
       <c r="BI23" s="5">
         <f>BI22/BA14</f>
-        <v>644.6087913587395</v>
+        <v>833.56121623583624</v>
       </c>
     </row>
     <row r="24" spans="2:61" x14ac:dyDescent="0.3">
@@ -5993,7 +5986,7 @@
       </c>
       <c r="BI24" s="5">
         <f>Main!D3</f>
-        <v>640.84</v>
+        <v>782.98</v>
       </c>
     </row>
     <row r="25" spans="2:61" x14ac:dyDescent="0.3">
@@ -6005,7 +5998,7 @@
       </c>
       <c r="BI25" s="10">
         <f>BI23/BI24-1</f>
-        <v>5.8810176623484978E-3</v>
+        <v>6.4600904538859583E-2</v>
       </c>
     </row>
     <row r="26" spans="2:61" x14ac:dyDescent="0.3">
@@ -6013,7 +6006,7 @@
         <v>67</v>
       </c>
       <c r="BI26" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/FB.xlsx
+++ b/Financial Analysis/FB.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C17C0067-D4CA-49B3-8642-FDB2D2CAB839}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D5633A4-1E05-4F9E-9A7A-24A185497790}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{BFE532A1-2353-49AA-A72E-D2C0AD0DD88D}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
     <sheet name="Model" sheetId="2" r:id="rId2"/>
+    <sheet name="Earnings" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -85,7 +86,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="159">
   <si>
     <t>Price</t>
   </si>
@@ -363,21 +364,217 @@
     <t>META</t>
   </si>
   <si>
-    <t>Fairly valued</t>
-  </si>
-  <si>
     <t>Q225 8K</t>
+  </si>
+  <si>
+    <t>Slightly undervalued</t>
+  </si>
+  <si>
+    <t>Net Margin</t>
+  </si>
+  <si>
+    <t>as of 8/10/25</t>
+  </si>
+  <si>
+    <t>Q1 (Mar)</t>
+  </si>
+  <si>
+    <t>Q2 (Jun)</t>
+  </si>
+  <si>
+    <t>Q3 (Sep)</t>
+  </si>
+  <si>
+    <t>Q4 (Dec)</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Annual</t>
+  </si>
+  <si>
+    <t>27.91B</t>
+  </si>
+  <si>
+    <t>28.82B</t>
+  </si>
+  <si>
+    <t>27.71B</t>
+  </si>
+  <si>
+    <t>32.16B</t>
+  </si>
+  <si>
+    <t>116.61B</t>
+  </si>
+  <si>
+    <t>134.90B</t>
+  </si>
+  <si>
+    <t>164.50B</t>
+  </si>
+  <si>
+    <t>196.76B</t>
+  </si>
+  <si>
+    <t>229.39B</t>
+  </si>
+  <si>
+    <t>28.64B</t>
+  </si>
+  <si>
+    <t>32.00B</t>
+  </si>
+  <si>
+    <t>34.15B</t>
+  </si>
+  <si>
+    <t>40.11B</t>
+  </si>
+  <si>
+    <t>42.31B</t>
+  </si>
+  <si>
+    <t>47.52B</t>
+  </si>
+  <si>
+    <t>49.34B</t>
+  </si>
+  <si>
+    <t>57.09B</t>
+  </si>
+  <si>
+    <t>36.45B</t>
+  </si>
+  <si>
+    <t>39.07B</t>
+  </si>
+  <si>
+    <t>40.59B</t>
+  </si>
+  <si>
+    <t>48.38B</t>
+  </si>
+  <si>
+    <t>50.51B</t>
+  </si>
+  <si>
+    <t>55.30B</t>
+  </si>
+  <si>
+    <t>57.20B</t>
+  </si>
+  <si>
+    <t>66.52B</t>
+  </si>
+  <si>
+    <t>58.04B</t>
+  </si>
+  <si>
+    <t>64.18B</t>
+  </si>
+  <si>
+    <t>66.39B</t>
+  </si>
+  <si>
+    <t>Sum</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>Running Total</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Net Income</t>
+  </si>
+  <si>
+    <t>7.46B</t>
+  </si>
+  <si>
+    <t>16.86B</t>
+  </si>
+  <si>
+    <t>21.02B</t>
+  </si>
+  <si>
+    <t>20.52B</t>
+  </si>
+  <si>
+    <t>6.69B</t>
+  </si>
+  <si>
+    <t>4.39B</t>
+  </si>
+  <si>
+    <t>4.65B</t>
+  </si>
+  <si>
+    <t>5.71B</t>
+  </si>
+  <si>
+    <t>11.58B</t>
+  </si>
+  <si>
+    <t>14.02B</t>
+  </si>
+  <si>
+    <t>13.46B</t>
+  </si>
+  <si>
+    <t>15.69B</t>
+  </si>
+  <si>
+    <t>20.84B</t>
+  </si>
+  <si>
+    <t>18.02B</t>
+  </si>
+  <si>
+    <t>7.79B</t>
+  </si>
+  <si>
+    <t>12.37B</t>
+  </si>
+  <si>
+    <t>16.64B</t>
+  </si>
+  <si>
+    <t>18.34B</t>
+  </si>
+  <si>
+    <t>17.00B</t>
+  </si>
+  <si>
+    <t>18.70B</t>
+  </si>
+  <si>
+    <t>18.38B</t>
+  </si>
+  <si>
+    <t>22.35B</t>
+  </si>
+  <si>
+    <t>20.39B</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="[$$-409]#,##0.00"/>
     <numFmt numFmtId="165" formatCode="[$$-409]#,##0"/>
+    <numFmt numFmtId="170" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -420,16 +617,52 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="5" tint="0.39997558519241921"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -517,11 +750,267 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="5" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </right>
+      <top style="thin">
+        <color theme="5" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </left>
+      <right style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </right>
+      <top style="thin">
+        <color theme="5" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </left>
+      <right style="thin">
+        <color theme="5" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="5" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="5" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </left>
+      <right style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </left>
+      <right style="thin">
+        <color theme="5" tint="0.39997558519241921"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="5" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </right>
+      <top style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </left>
+      <right style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </right>
+      <top style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </left>
+      <right style="thin">
+        <color theme="5" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="5" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </right>
+      <top style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </top>
+      <bottom style="thin">
+        <color theme="5" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </left>
+      <right style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </right>
+      <top style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </top>
+      <bottom style="thin">
+        <color theme="5" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </left>
+      <right style="thin">
+        <color theme="5" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </top>
+      <bottom style="thin">
+        <color theme="5" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </left>
+      <right style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </right>
+      <top style="thin">
+        <color theme="5" tint="0.59999389629810485"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </left>
+      <right style="thin">
+        <color theme="5" tint="0.59999389629810485"/>
+      </right>
+      <top style="thin">
+        <color theme="5" tint="0.59999389629810485"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </left>
+      <right style="thin">
+        <color theme="5" tint="0.59999389629810485"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </left>
+      <right style="thin">
+        <color theme="5" tint="0.59999389629810485"/>
+      </right>
+      <top style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="5" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="5" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </right>
+      <top style="thin">
+        <color theme="5" tint="0.59999389629810485"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -567,6 +1056,97 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="8" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="7" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="8" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="8" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="7" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="8" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="7" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="7" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="7" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="7" fillId="3" borderId="24" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -987,7 +1567,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13F0E0E7-EF61-4826-BB53-1423A2545910}">
   <dimension ref="B2:K9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="5" max="6" width="15.77734375" style="3" customWidth="1"/>
     <col min="7" max="7" width="15.77734375" style="1" customWidth="1"/>
@@ -996,7 +1576,7 @@
     <col min="11" max="11" width="64.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:11">
       <c r="E2" s="1" t="s">
         <v>7</v>
       </c>
@@ -1016,7 +1596,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:11">
       <c r="B3" s="6" t="s">
         <v>91</v>
       </c>
@@ -1024,14 +1604,14 @@
         <v>0</v>
       </c>
       <c r="D3" s="5">
-        <v>782.98</v>
+        <v>714.06</v>
       </c>
       <c r="E3" s="2">
-        <v>45887</v>
+        <v>45938</v>
       </c>
       <c r="F3" s="2">
         <f ca="1">TODAY()</f>
-        <v>45887</v>
+        <v>45938</v>
       </c>
       <c r="G3" s="2">
         <v>45960</v>
@@ -1046,7 +1626,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:11">
       <c r="C4" t="s">
         <v>1</v>
       </c>
@@ -1054,7 +1634,7 @@
         <v>2518</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F4" s="1"/>
       <c r="I4" s="14" t="s">
@@ -1067,13 +1647,13 @@
         <v>62</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:11">
       <c r="C5" t="s">
         <v>2</v>
       </c>
       <c r="D5" s="4">
         <f>D3*D4</f>
-        <v>1971543.6400000001</v>
+        <v>1798003.0799999998</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -1087,7 +1667,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:11">
       <c r="C6" t="s">
         <v>3</v>
       </c>
@@ -1109,7 +1689,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:11">
       <c r="C7" t="s">
         <v>4</v>
       </c>
@@ -1131,7 +1711,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:11">
       <c r="C8" t="s">
         <v>5</v>
       </c>
@@ -1142,13 +1722,13 @@
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:11">
       <c r="C9" t="s">
         <v>6</v>
       </c>
       <c r="D9" s="4">
         <f>D5-D8</f>
-        <v>1931316.6400000001</v>
+        <v>1757776.0799999998</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
@@ -1162,7 +1742,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15DD6CAC-9C85-445D-A50B-99FA437D4B08}">
   <dimension ref="B2:FI26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="15.21875" bestFit="1" customWidth="1"/>
     <col min="55" max="56" width="8.88671875" customWidth="1"/>
@@ -1170,7 +1750,7 @@
     <col min="61" max="61" width="17.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:165" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:165">
       <c r="C2" s="3" t="s">
         <v>11</v>
       </c>
@@ -1337,7 +1917,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="3" spans="2:165" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:165" s="6" customFormat="1">
       <c r="B3" s="6" t="s">
         <v>10</v>
       </c>
@@ -1528,7 +2108,7 @@
         <v>289557.86303750786</v>
       </c>
     </row>
-    <row r="4" spans="2:165" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:165">
       <c r="B4" t="s">
         <v>26</v>
       </c>
@@ -1719,7 +2299,7 @@
         <v>52120.415346751426</v>
       </c>
     </row>
-    <row r="5" spans="2:165" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:165" s="6" customFormat="1">
       <c r="B5" s="6" t="s">
         <v>30</v>
       </c>
@@ -1944,7 +2524,7 @@
         <v>237437.44769075644</v>
       </c>
     </row>
-    <row r="6" spans="2:165" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:165">
       <c r="B6" t="s">
         <v>27</v>
       </c>
@@ -2135,7 +2715,7 @@
         <v>67503.646302624766</v>
       </c>
     </row>
-    <row r="7" spans="2:165" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:165">
       <c r="B7" t="s">
         <v>28</v>
       </c>
@@ -2326,7 +2906,7 @@
         <v>18821.261097438011</v>
       </c>
     </row>
-    <row r="8" spans="2:165" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:165">
       <c r="B8" t="s">
         <v>29</v>
       </c>
@@ -2518,7 +3098,7 @@
         <v>10165.307201539119</v>
       </c>
     </row>
-    <row r="9" spans="2:165" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:165" s="6" customFormat="1">
       <c r="B9" s="6" t="s">
         <v>31</v>
       </c>
@@ -2743,7 +3323,7 @@
         <v>140947.23308915456</v>
       </c>
     </row>
-    <row r="10" spans="2:165" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:165">
       <c r="B10" t="s">
         <v>32</v>
       </c>
@@ -2934,7 +3514,7 @@
         <v>-2472.9334666960208</v>
       </c>
     </row>
-    <row r="11" spans="2:165" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:165" s="6" customFormat="1">
       <c r="B11" s="6" t="s">
         <v>33</v>
       </c>
@@ -3159,7 +3739,7 @@
         <v>143420.16655585059</v>
       </c>
     </row>
-    <row r="12" spans="2:165" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:165">
       <c r="B12" t="s">
         <v>34</v>
       </c>
@@ -3354,7 +3934,7 @@
         <v>17210.419986702069</v>
       </c>
     </row>
-    <row r="13" spans="2:165" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:165" s="6" customFormat="1">
       <c r="B13" s="6" t="s">
         <v>35</v>
       </c>
@@ -4007,7 +4587,7 @@
         <v>43058.482161681815</v>
       </c>
     </row>
-    <row r="14" spans="2:165" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:165">
       <c r="B14" t="s">
         <v>1</v>
       </c>
@@ -4189,7 +4769,7 @@
         <v>2518</v>
       </c>
     </row>
-    <row r="15" spans="2:165" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:165" s="6" customFormat="1">
       <c r="B15" s="6" t="s">
         <v>36</v>
       </c>
@@ -4414,7 +4994,7 @@
         <v>50.123012934530792</v>
       </c>
     </row>
-    <row r="17" spans="2:61" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:61">
       <c r="B17" s="6" t="s">
         <v>41</v>
       </c>
@@ -4575,9 +5155,8 @@
         <f t="shared" si="110"/>
         <v>0.21697701430040461</v>
       </c>
-      <c r="AV17" s="9">
-        <f t="shared" si="110"/>
-        <v>0.16078127659574459</v>
+      <c r="AV17" s="9" t="s">
+        <v>158</v>
       </c>
       <c r="AW17" s="9">
         <f t="shared" si="110"/>
@@ -4620,7 +5199,7 @@
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
-    <row r="18" spans="2:61" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:61">
       <c r="B18" s="6" t="s">
         <v>37</v>
       </c>
@@ -4851,7 +5430,7 @@
         <v>-0.01</v>
       </c>
     </row>
-    <row r="19" spans="2:61" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:61">
       <c r="B19" t="s">
         <v>39</v>
       </c>
@@ -5082,7 +5661,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="20" spans="2:61" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:61">
       <c r="B20" t="s">
         <v>69</v>
       </c>
@@ -5299,7 +5878,7 @@
         <v>2058680.1424818356</v>
       </c>
     </row>
-    <row r="21" spans="2:61" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:61">
       <c r="B21" t="s">
         <v>38</v>
       </c>
@@ -5531,7 +6110,7 @@
         <v>40227</v>
       </c>
     </row>
-    <row r="22" spans="2:61" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:61">
       <c r="B22" t="s">
         <v>70</v>
       </c>
@@ -5748,7 +6327,7 @@
         <v>2098907.1424818356</v>
       </c>
     </row>
-    <row r="23" spans="2:61" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:61">
       <c r="B23" t="s">
         <v>40</v>
       </c>
@@ -5980,16 +6559,239 @@
         <v>833.56121623583624</v>
       </c>
     </row>
-    <row r="24" spans="2:61" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:61">
+      <c r="B24" t="s">
+        <v>94</v>
+      </c>
+      <c r="C24" s="9">
+        <f>C13/C3</f>
+        <v>0.38085159362549803</v>
+      </c>
+      <c r="D24" s="9">
+        <f t="shared" ref="D24:AL24" si="213">D13/D3</f>
+        <v>0.41733719557987342</v>
+      </c>
+      <c r="E24" s="9">
+        <f t="shared" si="213"/>
+        <v>0.4557513555383424</v>
+      </c>
+      <c r="F24" s="9">
+        <f t="shared" si="213"/>
+        <v>0.2735121800801727</v>
+      </c>
+      <c r="G24" s="9">
+        <f t="shared" si="213"/>
+        <v>0.41676416513454789</v>
+      </c>
+      <c r="H24" s="9">
+        <f t="shared" si="213"/>
+        <v>0.38591187363011109</v>
+      </c>
+      <c r="I24" s="9">
+        <f t="shared" si="213"/>
+        <v>0.37422597799956292</v>
+      </c>
+      <c r="J24" s="9">
+        <f t="shared" si="213"/>
+        <v>0.40688187300461154</v>
+      </c>
+      <c r="K24" s="9">
+        <f t="shared" si="213"/>
+        <v>0.16110632088611793</v>
+      </c>
+      <c r="L24" s="9">
+        <f t="shared" si="213"/>
+        <v>0.15391912723823076</v>
+      </c>
+      <c r="M24" s="9">
+        <f t="shared" si="213"/>
+        <v>0.34506004985270788</v>
+      </c>
+      <c r="N24" s="9">
+        <f t="shared" si="213"/>
+        <v>0.34859121525471964</v>
+      </c>
+      <c r="O24" s="9">
+        <f t="shared" si="213"/>
+        <v>0.27637142696059086</v>
+      </c>
+      <c r="P24" s="9">
+        <f t="shared" si="213"/>
+        <v>0.27709102584684542</v>
+      </c>
+      <c r="Q24" s="9">
+        <f t="shared" si="213"/>
+        <v>0.3654401490451793</v>
+      </c>
+      <c r="R24" s="9">
+        <f t="shared" si="213"/>
+        <v>0.39965089769165002</v>
+      </c>
+      <c r="S24" s="9">
+        <f t="shared" si="213"/>
+        <v>0.36288257995491191</v>
+      </c>
+      <c r="T24" s="9">
+        <f t="shared" si="213"/>
+        <v>0.35746466279189737</v>
+      </c>
+      <c r="U24" s="9">
+        <f t="shared" si="213"/>
+        <v>0.31692519820751464</v>
+      </c>
+      <c r="V24" s="9">
+        <f t="shared" si="213"/>
+        <v>0.30545573342045085</v>
+      </c>
+      <c r="W24" s="9">
+        <f t="shared" si="213"/>
+        <v>0.26748602551239786</v>
+      </c>
+      <c r="X24" s="9">
+        <f t="shared" si="213"/>
+        <v>0.23201026993269031</v>
+      </c>
+      <c r="Y24" s="9">
+        <f t="shared" si="213"/>
+        <v>0.15858410911452694</v>
+      </c>
+      <c r="Z24" s="9">
+        <f t="shared" si="213"/>
+        <v>0.1446292554018343</v>
+      </c>
+      <c r="AA24" s="9">
+        <f t="shared" si="213"/>
+        <v>0.19930179787048349</v>
+      </c>
+      <c r="AB24" s="9">
+        <f t="shared" si="213"/>
+        <v>0.24338260570642833</v>
+      </c>
+      <c r="AC24" s="9">
+        <f t="shared" si="213"/>
+        <v>0.34440376569037656</v>
+      </c>
+      <c r="AD24" s="9">
+        <f t="shared" si="213"/>
+        <v>0.34945526164892421</v>
+      </c>
+      <c r="AE24" s="9">
+        <f t="shared" si="213"/>
+        <v>0.33929502125908656</v>
+      </c>
+      <c r="AF24" s="9">
+        <f t="shared" si="213"/>
+        <v>0.34462900872770086</v>
+      </c>
+      <c r="AG24" s="9">
+        <f t="shared" si="213"/>
+        <v>0.38650865998176848</v>
+      </c>
+      <c r="AH24" s="9">
+        <f t="shared" si="213"/>
+        <v>0.39863594089077192</v>
+      </c>
+      <c r="AI24" s="9">
+        <f t="shared" si="213"/>
+        <v>0.39334499220116276</v>
+      </c>
+      <c r="AJ24" s="9">
+        <f t="shared" si="213"/>
+        <v>0.38591211381429413</v>
+      </c>
+      <c r="AK24" s="9">
+        <f t="shared" si="213"/>
+        <v>0.406236090683332</v>
+      </c>
+      <c r="AL24" s="9">
+        <f t="shared" si="213"/>
+        <v>0.41311451896248835</v>
+      </c>
+      <c r="AN24" s="9">
+        <f t="shared" ref="AN24:BF24" si="214">AN13/AN3</f>
+        <v>0.37399453914840231</v>
+      </c>
+      <c r="AO24" s="9">
+        <f t="shared" si="214"/>
+        <v>0.39600272216053584</v>
+      </c>
+      <c r="AP24" s="9">
+        <f t="shared" si="214"/>
+        <v>0.26125896684918715</v>
+      </c>
+      <c r="AQ24" s="9">
+        <f t="shared" si="214"/>
+        <v>0.33902938370983876</v>
+      </c>
+      <c r="AR24" s="9">
+        <f t="shared" si="214"/>
+        <v>0.33384494059985248</v>
+      </c>
+      <c r="AS24" s="9">
+        <f t="shared" si="214"/>
+        <v>0.19894690804311846</v>
+      </c>
+      <c r="AT24" s="9">
+        <f t="shared" si="214"/>
+        <v>0.29123850530069317</v>
+      </c>
+      <c r="AU24" s="9">
+        <f t="shared" si="214"/>
+        <v>0.36966565349544073</v>
+      </c>
+      <c r="AV24" s="9">
+        <f t="shared" si="214"/>
+        <v>0.39968199956721312</v>
+      </c>
+      <c r="AW24" s="9">
+        <f t="shared" si="214"/>
+        <v>0.41105997530320143</v>
+      </c>
+      <c r="AX24" s="9">
+        <f t="shared" si="214"/>
+        <v>0.42215596194208721</v>
+      </c>
+      <c r="AY24" s="9">
+        <f t="shared" si="214"/>
+        <v>0.43018697555420715</v>
+      </c>
+      <c r="AZ24" s="9">
+        <f t="shared" si="214"/>
+        <v>0.43343249662027727</v>
+      </c>
+      <c r="BA24" s="9">
+        <f t="shared" si="214"/>
+        <v>0.43420127848484802</v>
+      </c>
+      <c r="BB24" s="9">
+        <f t="shared" si="214"/>
+        <v>0.43460532555500836</v>
+      </c>
+      <c r="BC24" s="9">
+        <f t="shared" si="214"/>
+        <v>0.43492734978020037</v>
+      </c>
+      <c r="BD24" s="9">
+        <f t="shared" si="214"/>
+        <v>0.43524486995990475</v>
+      </c>
+      <c r="BE24" s="9">
+        <f t="shared" si="214"/>
+        <v>0.43555925395526268</v>
+      </c>
+      <c r="BF24" s="9">
+        <f t="shared" si="214"/>
+        <v>0.43587055535355967</v>
+      </c>
       <c r="BH24" t="s">
         <v>49</v>
       </c>
       <c r="BI24" s="5">
         <f>Main!D3</f>
-        <v>782.98</v>
-      </c>
-    </row>
-    <row r="25" spans="2:61" x14ac:dyDescent="0.3">
+        <v>714.06</v>
+      </c>
+    </row>
+    <row r="25" spans="2:61">
       <c r="C25" t="s">
         <v>42</v>
       </c>
@@ -5998,15 +6800,15 @@
       </c>
       <c r="BI25" s="10">
         <f>BI23/BI24-1</f>
-        <v>6.4600904538859583E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="2:61" x14ac:dyDescent="0.3">
+        <v>0.16735458677959314</v>
+      </c>
+    </row>
+    <row r="26" spans="2:61">
       <c r="BH26" t="s">
         <v>67</v>
       </c>
       <c r="BI26" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -6015,4 +6817,764 @@
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53BFD22F-6DC0-487C-A29A-CD9585335F7B}">
+  <dimension ref="B2:W91"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="10" max="10" width="10.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:23">
+      <c r="B2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="2:23">
+      <c r="B4" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="22">
+        <v>2022</v>
+      </c>
+      <c r="D4" s="22">
+        <v>2023</v>
+      </c>
+      <c r="E4" s="22">
+        <v>2024</v>
+      </c>
+      <c r="F4" s="22">
+        <v>2025</v>
+      </c>
+      <c r="G4" s="22">
+        <v>2026</v>
+      </c>
+      <c r="H4" s="23">
+        <v>2027</v>
+      </c>
+      <c r="J4" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="K4" s="22">
+        <v>2022</v>
+      </c>
+      <c r="L4" s="22">
+        <v>2023</v>
+      </c>
+      <c r="M4" s="22">
+        <v>2024</v>
+      </c>
+      <c r="N4" s="22">
+        <v>2025</v>
+      </c>
+      <c r="O4" s="22">
+        <v>2026</v>
+      </c>
+      <c r="P4" s="23">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="5" spans="2:23">
+      <c r="B5" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>102</v>
+      </c>
+      <c r="D5" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="E5" s="25" t="s">
+        <v>119</v>
+      </c>
+      <c r="F5" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="G5" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="H5" s="27" t="s">
+        <v>127</v>
+      </c>
+      <c r="J5" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="K5" s="25" t="s">
+        <v>135</v>
+      </c>
+      <c r="L5" s="25" t="s">
+        <v>142</v>
+      </c>
+      <c r="M5" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="N5" s="25" t="s">
+        <v>151</v>
+      </c>
+      <c r="O5" s="26" t="s">
+        <v>136</v>
+      </c>
+      <c r="P5" s="27" t="s">
+        <v>148</v>
+      </c>
+      <c r="R5" s="25" t="str">
+        <f>LEFT(K5,4)</f>
+        <v>7.46</v>
+      </c>
+      <c r="S5" s="25" t="str">
+        <f t="shared" ref="S5:S8" si="0">LEFT(L5,4)</f>
+        <v>5.71</v>
+      </c>
+      <c r="T5" s="25" t="str">
+        <f t="shared" ref="T5:T8" si="1">LEFT(M5,4)</f>
+        <v>12.3</v>
+      </c>
+      <c r="U5" s="25" t="str">
+        <f t="shared" ref="U5:U8" si="2">LEFT(N5,4)</f>
+        <v>16.6</v>
+      </c>
+      <c r="V5" s="25" t="str">
+        <f t="shared" ref="V5:V8" si="3">LEFT(O5,4)</f>
+        <v>16.8</v>
+      </c>
+      <c r="W5" s="25" t="str">
+        <f t="shared" ref="W5:W8" si="4">LEFT(P5,4)</f>
+        <v>18.0</v>
+      </c>
+    </row>
+    <row r="6" spans="2:23">
+      <c r="B6" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="C6" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="E6" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="F6" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="G6" s="30" t="s">
+        <v>124</v>
+      </c>
+      <c r="H6" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="J6" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="K6" s="29" t="s">
+        <v>139</v>
+      </c>
+      <c r="L6" s="29" t="s">
+        <v>149</v>
+      </c>
+      <c r="M6" s="29" t="s">
+        <v>145</v>
+      </c>
+      <c r="N6" s="29" t="s">
+        <v>152</v>
+      </c>
+      <c r="O6" s="30" t="s">
+        <v>154</v>
+      </c>
+      <c r="P6" s="31" t="s">
+        <v>137</v>
+      </c>
+      <c r="R6" s="25" t="str">
+        <f t="shared" ref="R6:R8" si="5">LEFT(K6,4)</f>
+        <v>6.69</v>
+      </c>
+      <c r="S6" s="25" t="str">
+        <f t="shared" si="0"/>
+        <v>7.79</v>
+      </c>
+      <c r="T6" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>13.4</v>
+      </c>
+      <c r="U6" s="25" t="str">
+        <f t="shared" si="2"/>
+        <v>18.3</v>
+      </c>
+      <c r="V6" s="25" t="str">
+        <f t="shared" si="3"/>
+        <v>18.7</v>
+      </c>
+      <c r="W6" s="25" t="str">
+        <f t="shared" si="4"/>
+        <v>21.0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:23">
+      <c r="B7" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="D7" s="29" t="s">
+        <v>113</v>
+      </c>
+      <c r="E7" s="29" t="s">
+        <v>121</v>
+      </c>
+      <c r="F7" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="G7" s="30" t="s">
+        <v>125</v>
+      </c>
+      <c r="H7" s="31" t="s">
+        <v>129</v>
+      </c>
+      <c r="J7" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="K7" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="L7" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="M7" s="29" t="s">
+        <v>146</v>
+      </c>
+      <c r="N7" s="30" t="s">
+        <v>153</v>
+      </c>
+      <c r="O7" s="30" t="s">
+        <v>155</v>
+      </c>
+      <c r="P7" s="31" t="s">
+        <v>157</v>
+      </c>
+      <c r="R7" s="25" t="str">
+        <f t="shared" si="5"/>
+        <v>4.39</v>
+      </c>
+      <c r="S7" s="25" t="str">
+        <f t="shared" si="0"/>
+        <v>11.5</v>
+      </c>
+      <c r="T7" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>15.6</v>
+      </c>
+      <c r="U7" s="25" t="str">
+        <f t="shared" si="2"/>
+        <v>17.0</v>
+      </c>
+      <c r="V7" s="25" t="str">
+        <f t="shared" si="3"/>
+        <v>18.3</v>
+      </c>
+      <c r="W7" s="25" t="str">
+        <f t="shared" si="4"/>
+        <v>20.3</v>
+      </c>
+    </row>
+    <row r="8" spans="2:23">
+      <c r="B8" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="C8" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="D8" s="29" t="s">
+        <v>114</v>
+      </c>
+      <c r="E8" s="29" t="s">
+        <v>122</v>
+      </c>
+      <c r="F8" s="30" t="s">
+        <v>118</v>
+      </c>
+      <c r="G8" s="30" t="s">
+        <v>126</v>
+      </c>
+      <c r="H8" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="J8" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="K8" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="L8" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="M8" s="29" t="s">
+        <v>147</v>
+      </c>
+      <c r="N8" s="30" t="s">
+        <v>138</v>
+      </c>
+      <c r="O8" s="30" t="s">
+        <v>156</v>
+      </c>
+      <c r="P8" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="R8" s="25" t="str">
+        <f t="shared" si="5"/>
+        <v>4.65</v>
+      </c>
+      <c r="S8" s="25" t="str">
+        <f t="shared" si="0"/>
+        <v>14.0</v>
+      </c>
+      <c r="T8" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>20.8</v>
+      </c>
+      <c r="U8" s="25" t="str">
+        <f t="shared" si="2"/>
+        <v>20.5</v>
+      </c>
+      <c r="V8" s="25" t="str">
+        <f t="shared" si="3"/>
+        <v>22.3</v>
+      </c>
+      <c r="W8" s="25" t="str">
+        <f t="shared" si="4"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="9" spans="2:23">
+      <c r="B9" s="28"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="32"/>
+      <c r="J9" s="28"/>
+      <c r="K9" s="29"/>
+      <c r="L9" s="29"/>
+      <c r="M9" s="29"/>
+      <c r="N9" s="30"/>
+      <c r="O9" s="30"/>
+      <c r="P9" s="32"/>
+    </row>
+    <row r="10" spans="2:23">
+      <c r="B10" s="33" t="s">
+        <v>101</v>
+      </c>
+      <c r="C10" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="D10" s="34" t="s">
+        <v>107</v>
+      </c>
+      <c r="E10" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="F10" s="35" t="s">
+        <v>109</v>
+      </c>
+      <c r="G10" s="35" t="s">
+        <v>110</v>
+      </c>
+      <c r="H10" s="36" t="s">
+        <v>100</v>
+      </c>
+      <c r="J10" s="33" t="s">
+        <v>101</v>
+      </c>
+      <c r="K10" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="L10" s="34" t="s">
+        <v>107</v>
+      </c>
+      <c r="M10" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="N10" s="35" t="s">
+        <v>109</v>
+      </c>
+      <c r="O10" s="35" t="s">
+        <v>110</v>
+      </c>
+      <c r="P10" s="36" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="2:23">
+      <c r="J12" s="51" t="s">
+        <v>96</v>
+      </c>
+      <c r="K12" s="45">
+        <v>-0.21340000000000001</v>
+      </c>
+      <c r="L12" s="45">
+        <f>S5/R5-1</f>
+        <v>-0.23458445040214482</v>
+      </c>
+      <c r="M12" s="45">
+        <f t="shared" ref="M12:M15" si="6">T5/S5-1</f>
+        <v>1.1541155866900175</v>
+      </c>
+      <c r="N12" s="45">
+        <f t="shared" ref="N12:P15" si="7">U5/T5-1</f>
+        <v>0.34959349593495936</v>
+      </c>
+      <c r="O12" s="46">
+        <f t="shared" si="7"/>
+        <v>1.2048192771084265E-2</v>
+      </c>
+      <c r="P12" s="47">
+        <f t="shared" si="7"/>
+        <v>7.1428571428571397E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="2:23">
+      <c r="J13" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="K13" s="42">
+        <v>-0.35699999999999998</v>
+      </c>
+      <c r="L13" s="40">
+        <f t="shared" ref="L13:L15" si="8">S6/R6-1</f>
+        <v>0.16442451420029891</v>
+      </c>
+      <c r="M13" s="40">
+        <f t="shared" si="6"/>
+        <v>0.72015404364569968</v>
+      </c>
+      <c r="N13" s="40">
+        <f t="shared" si="7"/>
+        <v>0.36567164179104483</v>
+      </c>
+      <c r="O13" s="41">
+        <f t="shared" si="7"/>
+        <v>2.1857923497267784E-2</v>
+      </c>
+      <c r="P13" s="48">
+        <f t="shared" si="7"/>
+        <v>0.12299465240641716</v>
+      </c>
+    </row>
+    <row r="14" spans="2:23">
+      <c r="J14" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="K14" s="42">
+        <v>-0.52200000000000002</v>
+      </c>
+      <c r="L14" s="40">
+        <f t="shared" si="8"/>
+        <v>1.619589977220957</v>
+      </c>
+      <c r="M14" s="40">
+        <f t="shared" si="6"/>
+        <v>0.35652173913043472</v>
+      </c>
+      <c r="N14" s="41">
+        <f t="shared" si="7"/>
+        <v>8.9743589743589869E-2</v>
+      </c>
+      <c r="O14" s="41">
+        <f t="shared" si="7"/>
+        <v>7.6470588235294068E-2</v>
+      </c>
+      <c r="P14" s="48">
+        <f t="shared" si="7"/>
+        <v>0.1092896174863387</v>
+      </c>
+      <c r="S14" s="50"/>
+    </row>
+    <row r="15" spans="2:23">
+      <c r="J15" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="K15" s="42">
+        <v>-0.54800000000000004</v>
+      </c>
+      <c r="L15" s="40">
+        <f t="shared" si="8"/>
+        <v>2.010752688172043</v>
+      </c>
+      <c r="M15" s="40">
+        <f t="shared" si="6"/>
+        <v>0.48571428571428577</v>
+      </c>
+      <c r="N15" s="41">
+        <f t="shared" si="7"/>
+        <v>-1.4423076923076983E-2</v>
+      </c>
+      <c r="O15" s="41">
+        <f t="shared" si="7"/>
+        <v>8.7804878048780566E-2</v>
+      </c>
+      <c r="P15" s="49" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="2:23">
+      <c r="J16" s="28"/>
+      <c r="K16" s="29"/>
+      <c r="L16" s="29"/>
+      <c r="M16" s="29"/>
+      <c r="N16" s="30"/>
+      <c r="O16" s="30"/>
+      <c r="P16" s="32"/>
+    </row>
+    <row r="17" spans="10:16">
+      <c r="J17" s="33" t="s">
+        <v>101</v>
+      </c>
+      <c r="K17" s="43">
+        <v>-0.41399999999999998</v>
+      </c>
+      <c r="L17" s="43">
+        <v>0.68500000000000005</v>
+      </c>
+      <c r="M17" s="43">
+        <v>0.59499999999999997</v>
+      </c>
+      <c r="N17" s="44">
+        <v>0.16300000000000001</v>
+      </c>
+      <c r="O17" s="44">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="P17" s="36" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="10:16">
+      <c r="J18" s="37"/>
+    </row>
+    <row r="19" spans="10:16">
+      <c r="J19" s="37"/>
+    </row>
+    <row r="20" spans="10:16">
+      <c r="J20" s="37"/>
+    </row>
+    <row r="21" spans="10:16">
+      <c r="J21" s="37"/>
+    </row>
+    <row r="22" spans="10:16">
+      <c r="J22" s="37"/>
+    </row>
+    <row r="23" spans="10:16">
+      <c r="J23" s="37"/>
+    </row>
+    <row r="24" spans="10:16">
+      <c r="J24" s="37"/>
+    </row>
+    <row r="25" spans="10:16">
+      <c r="J25" s="38"/>
+    </row>
+    <row r="26" spans="10:16">
+      <c r="J26" s="38"/>
+    </row>
+    <row r="27" spans="10:16">
+      <c r="J27" s="38"/>
+    </row>
+    <row r="28" spans="10:16">
+      <c r="J28" s="37"/>
+    </row>
+    <row r="29" spans="10:16">
+      <c r="J29" s="37"/>
+    </row>
+    <row r="30" spans="10:16">
+      <c r="J30" s="37"/>
+    </row>
+    <row r="31" spans="10:16">
+      <c r="J31" s="37"/>
+    </row>
+    <row r="32" spans="10:16">
+      <c r="J32" s="37"/>
+    </row>
+    <row r="33" spans="10:10">
+      <c r="J33" s="38"/>
+    </row>
+    <row r="34" spans="10:10">
+      <c r="J34" s="37"/>
+    </row>
+    <row r="35" spans="10:10">
+      <c r="J35" s="37"/>
+    </row>
+    <row r="36" spans="10:10">
+      <c r="J36" s="37"/>
+    </row>
+    <row r="37" spans="10:10">
+      <c r="J37" s="37"/>
+    </row>
+    <row r="38" spans="10:10">
+      <c r="J38" s="38"/>
+    </row>
+    <row r="39" spans="10:10">
+      <c r="J39" s="38"/>
+    </row>
+    <row r="40" spans="10:10">
+      <c r="J40" s="37"/>
+    </row>
+    <row r="41" spans="10:10">
+      <c r="J41" s="37"/>
+    </row>
+    <row r="42" spans="10:10">
+      <c r="J42" s="37"/>
+    </row>
+    <row r="43" spans="10:10">
+      <c r="J43" s="38"/>
+    </row>
+    <row r="44" spans="10:10">
+      <c r="J44" s="37"/>
+    </row>
+    <row r="45" spans="10:10">
+      <c r="J45" s="38"/>
+    </row>
+    <row r="46" spans="10:10">
+      <c r="J46" s="37"/>
+    </row>
+    <row r="47" spans="10:10">
+      <c r="J47" s="37"/>
+    </row>
+    <row r="48" spans="10:10">
+      <c r="J48" s="37"/>
+    </row>
+    <row r="49" spans="10:10">
+      <c r="J49" s="38"/>
+    </row>
+    <row r="50" spans="10:10">
+      <c r="J50" s="38"/>
+    </row>
+    <row r="51" spans="10:10">
+      <c r="J51" s="38"/>
+    </row>
+    <row r="52" spans="10:10">
+      <c r="J52" s="38"/>
+    </row>
+    <row r="53" spans="10:10">
+      <c r="J53" s="37"/>
+    </row>
+    <row r="54" spans="10:10">
+      <c r="J54" s="37"/>
+    </row>
+    <row r="55" spans="10:10">
+      <c r="J55" s="37"/>
+    </row>
+    <row r="56" spans="10:10">
+      <c r="J56" s="37"/>
+    </row>
+    <row r="57" spans="10:10">
+      <c r="J57" s="37"/>
+    </row>
+    <row r="58" spans="10:10">
+      <c r="J58" s="37"/>
+    </row>
+    <row r="59" spans="10:10">
+      <c r="J59" s="37"/>
+    </row>
+    <row r="60" spans="10:10">
+      <c r="J60" s="37"/>
+    </row>
+    <row r="61" spans="10:10">
+      <c r="J61" s="37"/>
+    </row>
+    <row r="62" spans="10:10">
+      <c r="J62" s="37"/>
+    </row>
+    <row r="63" spans="10:10">
+      <c r="J63" s="37"/>
+    </row>
+    <row r="64" spans="10:10">
+      <c r="J64" s="37"/>
+    </row>
+    <row r="65" spans="10:10">
+      <c r="J65" s="37"/>
+    </row>
+    <row r="66" spans="10:10">
+      <c r="J66" s="37"/>
+    </row>
+    <row r="67" spans="10:10">
+      <c r="J67" s="37"/>
+    </row>
+    <row r="68" spans="10:10">
+      <c r="J68" s="37"/>
+    </row>
+    <row r="69" spans="10:10">
+      <c r="J69" s="37"/>
+    </row>
+    <row r="70" spans="10:10">
+      <c r="J70" s="37"/>
+    </row>
+    <row r="71" spans="10:10">
+      <c r="J71" s="37"/>
+    </row>
+    <row r="72" spans="10:10">
+      <c r="J72" s="37"/>
+    </row>
+    <row r="73" spans="10:10">
+      <c r="J73" s="37"/>
+    </row>
+    <row r="74" spans="10:10">
+      <c r="J74" s="37"/>
+    </row>
+    <row r="75" spans="10:10">
+      <c r="J75" s="37"/>
+    </row>
+    <row r="76" spans="10:10">
+      <c r="J76" s="37"/>
+    </row>
+    <row r="77" spans="10:10">
+      <c r="J77" s="37"/>
+    </row>
+    <row r="78" spans="10:10">
+      <c r="J78" s="37"/>
+    </row>
+    <row r="79" spans="10:10">
+      <c r="J79" s="37"/>
+    </row>
+    <row r="80" spans="10:10">
+      <c r="J80" s="38"/>
+    </row>
+    <row r="81" spans="10:10">
+      <c r="J81" s="37"/>
+    </row>
+    <row r="82" spans="10:10">
+      <c r="J82" s="38"/>
+    </row>
+    <row r="83" spans="10:10">
+      <c r="J83" s="38"/>
+    </row>
+    <row r="84" spans="10:10">
+      <c r="J84" s="38"/>
+    </row>
+    <row r="85" spans="10:10">
+      <c r="J85" s="38"/>
+    </row>
+    <row r="86" spans="10:10">
+      <c r="J86" s="37"/>
+    </row>
+    <row r="87" spans="10:10">
+      <c r="J87" s="38"/>
+    </row>
+    <row r="88" spans="10:10">
+      <c r="J88" s="38"/>
+    </row>
+    <row r="89" spans="10:10">
+      <c r="J89" s="38"/>
+    </row>
+    <row r="90" spans="10:10">
+      <c r="J90" s="37"/>
+    </row>
+    <row r="91" spans="10:10">
+      <c r="J91" s="39"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Financial Analysis/FB.xlsx
+++ b/Financial Analysis/FB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D5633A4-1E05-4F9E-9A7A-24A185497790}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB7B836A-FA2E-4714-980C-1D44417F731B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{BFE532A1-2353-49AA-A72E-D2C0AD0DD88D}"/>
   </bookViews>
@@ -81,12 +81,36 @@
         </r>
       </text>
     </comment>
+    <comment ref="AK12" authorId="0" shapeId="0" xr:uid="{2884C3D2-24EC-46C8-AB47-9FAF4B1AEF01}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Anton Mniszek:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Provision for income taxes includes a one-time, non-cash income tax charge of $15.93 billion accrued in the third quarter of 2025 related to the implementation of the One Big Beautiful Bill Act. For more information, see the section entitled "Provision for Income Taxes - One-Time, Non-Cash Charge Impact" in this press release (Q325 8K)</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="154">
   <si>
     <t>Price</t>
   </si>
@@ -364,9 +388,6 @@
     <t>META</t>
   </si>
   <si>
-    <t>Q225 8K</t>
-  </si>
-  <si>
     <t>Slightly undervalued</t>
   </si>
   <si>
@@ -478,18 +499,6 @@
     <t>66.39B</t>
   </si>
   <si>
-    <t>Sum</t>
-  </si>
-  <si>
-    <t>Average</t>
-  </si>
-  <si>
-    <t>Running Total</t>
-  </si>
-  <si>
-    <t>Count</t>
-  </si>
-  <si>
     <t>Net Income</t>
   </si>
   <si>
@@ -562,7 +571,7 @@
     <t>20.39B</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <t>Q325 8K</t>
   </si>
 </sst>
 </file>
@@ -572,7 +581,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="[$$-409]#,##0.00"/>
     <numFmt numFmtId="165" formatCode="[$$-409]#,##0"/>
-    <numFmt numFmtId="170" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -1113,34 +1122,34 @@
     <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="8" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="7" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="8" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="8" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="7" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="8" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="7" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="7" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="7" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="7" fillId="3" borderId="24" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="3" borderId="24" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
@@ -1168,14 +1177,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>36</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>36</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
       <xdr:row>35</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
@@ -1192,7 +1201,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="22395180" y="0"/>
+          <a:off x="23012400" y="0"/>
           <a:ext cx="0" cy="6477000"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1604,17 +1613,17 @@
         <v>0</v>
       </c>
       <c r="D3" s="5">
-        <v>714.06</v>
+        <v>686.46</v>
       </c>
       <c r="E3" s="2">
-        <v>45938</v>
+        <v>45960</v>
       </c>
       <c r="F3" s="2">
         <f ca="1">TODAY()</f>
-        <v>45938</v>
+        <v>45960</v>
       </c>
       <c r="G3" s="2">
-        <v>45960</v>
+        <v>46057</v>
       </c>
       <c r="I3" s="14" t="s">
         <v>51</v>
@@ -1631,10 +1640,11 @@
         <v>1</v>
       </c>
       <c r="D4" s="4">
-        <v>2518</v>
+        <f>2517</f>
+        <v>2517</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>92</v>
+        <v>153</v>
       </c>
       <c r="F4" s="1"/>
       <c r="I4" s="14" t="s">
@@ -1653,7 +1663,7 @@
       </c>
       <c r="D5" s="4">
         <f>D3*D4</f>
-        <v>1798003.0799999998</v>
+        <v>1727819.82</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -1672,11 +1682,11 @@
         <v>3</v>
       </c>
       <c r="D6" s="4">
-        <f>12005+35066+21988</f>
-        <v>69059</v>
+        <f>10187+34261+25074</f>
+        <v>69522</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F6" s="1"/>
       <c r="I6" s="14" t="s">
@@ -1694,11 +1704,11 @@
         <v>4</v>
       </c>
       <c r="D7" s="4">
-        <f>28832</f>
-        <v>28832</v>
+        <f>28834</f>
+        <v>28834</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F7" s="1"/>
       <c r="I7" s="17" t="s">
@@ -1717,7 +1727,7 @@
       </c>
       <c r="D8" s="4">
         <f>D6-D7</f>
-        <v>40227</v>
+        <v>40688</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
@@ -1728,7 +1738,7 @@
       </c>
       <c r="D9" s="4">
         <f>D5-D8</f>
-        <v>1757776.0799999998</v>
+        <v>1687131.82</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
@@ -2024,12 +2034,11 @@
         <v>47516</v>
       </c>
       <c r="AK3" s="8">
-        <f>AG3*1.18</f>
-        <v>47895.02</v>
+        <v>51242</v>
       </c>
       <c r="AL3" s="8">
-        <f>AH3*1.1</f>
-        <v>53223.500000000007</v>
+        <f>AH3*1.2</f>
+        <v>58062</v>
       </c>
       <c r="AN3" s="8">
         <f>SUM(C3:F3)</f>
@@ -2065,47 +2074,47 @@
       </c>
       <c r="AV3" s="8">
         <f>SUM(AI3:AL3)</f>
-        <v>190948.52</v>
+        <v>199134</v>
       </c>
       <c r="AW3" s="8">
-        <f>AV3*1.12</f>
-        <v>213862.34239999999</v>
+        <f>AV3*1.14</f>
+        <v>227012.75999999998</v>
       </c>
       <c r="AX3" s="8">
         <f>AW3*1.08</f>
-        <v>230971.329792</v>
+        <v>245173.78080000001</v>
       </c>
       <c r="AY3" s="8">
         <f>AX3*1.06</f>
-        <v>244829.60957952001</v>
+        <v>259884.20764800001</v>
       </c>
       <c r="AZ3" s="8">
         <f>AY3*1.04</f>
-        <v>254622.79396270082</v>
+        <v>270279.57595392002</v>
       </c>
       <c r="BA3" s="8">
         <f>AZ3*1.03</f>
-        <v>262261.47778158187</v>
+        <v>278387.96323253762</v>
       </c>
       <c r="BB3" s="8">
         <f t="shared" ref="BB3" si="0">BA3*1.02</f>
-        <v>267506.70733721351</v>
+        <v>283955.72249718837</v>
       </c>
       <c r="BC3" s="8">
         <f t="shared" ref="BC3" si="1">BB3*1.02</f>
-        <v>272856.84148395777</v>
+        <v>289634.83694713213</v>
       </c>
       <c r="BD3" s="8">
         <f t="shared" ref="BD3" si="2">BC3*1.02</f>
-        <v>278313.97831363691</v>
+        <v>295427.53368607478</v>
       </c>
       <c r="BE3" s="8">
         <f t="shared" ref="BE3" si="3">BD3*1.02</f>
-        <v>283880.25787990965</v>
+        <v>301336.08435979625</v>
       </c>
       <c r="BF3" s="8">
         <f t="shared" ref="BF3" si="4">BE3*1.02</f>
-        <v>289557.86303750786</v>
+        <v>307362.80604699219</v>
       </c>
     </row>
     <row r="4" spans="2:165">
@@ -2215,12 +2224,11 @@
         <v>8491</v>
       </c>
       <c r="AK4" s="4">
-        <f t="shared" ref="AK4:AL4" si="5">AK3-AK5</f>
-        <v>8621.1036000000022</v>
+        <v>9206</v>
       </c>
       <c r="AL4" s="4">
-        <f t="shared" si="5"/>
-        <v>9580.2300000000032</v>
+        <f t="shared" ref="AL4" si="5">AL3-AL5</f>
+        <v>10451.160000000003</v>
       </c>
       <c r="AN4" s="4">
         <f>SUM(C4:F4)</f>
@@ -2256,47 +2264,47 @@
       </c>
       <c r="AV4" s="4">
         <f>SUM(AI4:AL4)</f>
-        <v>34264.333600000005</v>
+        <v>35720.160000000003</v>
       </c>
       <c r="AW4" s="4">
         <f t="shared" ref="AW4:BA4" si="6">AW3-AW5</f>
-        <v>38495.221632000001</v>
+        <v>40862.296800000011</v>
       </c>
       <c r="AX4" s="4">
         <f t="shared" si="6"/>
-        <v>41574.839362560015</v>
+        <v>44131.280544000008</v>
       </c>
       <c r="AY4" s="4">
         <f t="shared" si="6"/>
-        <v>44069.329724313604</v>
+        <v>46779.157376640011</v>
       </c>
       <c r="AZ4" s="4">
         <f t="shared" si="6"/>
-        <v>45832.102913286159</v>
+        <v>48650.323671705613</v>
       </c>
       <c r="BA4" s="4">
         <f t="shared" si="6"/>
-        <v>47207.066000684747</v>
+        <v>50109.833381856792</v>
       </c>
       <c r="BB4" s="4">
         <f t="shared" ref="BB4:BF4" si="7">BB3-BB5</f>
-        <v>48151.20732069845</v>
+        <v>51112.030049493915</v>
       </c>
       <c r="BC4" s="4">
         <f t="shared" si="7"/>
-        <v>49114.231467112404</v>
+        <v>52134.270650483784</v>
       </c>
       <c r="BD4" s="4">
         <f t="shared" si="7"/>
-        <v>50096.516096454667</v>
+        <v>53176.956063493475</v>
       </c>
       <c r="BE4" s="4">
         <f t="shared" si="7"/>
-        <v>51098.446418383741</v>
+        <v>54240.495184763335</v>
       </c>
       <c r="BF4" s="4">
         <f t="shared" si="7"/>
-        <v>52120.415346751426</v>
+        <v>55325.305088458612</v>
       </c>
     </row>
     <row r="5" spans="2:165" s="6" customFormat="1">
@@ -2416,7 +2424,7 @@
         <v>32416</v>
       </c>
       <c r="AE5" s="8">
-        <f t="shared" ref="AE5:AJ5" si="16">AE3-AE4</f>
+        <f t="shared" ref="AE5:AK5" si="16">AE3-AE4</f>
         <v>29815</v>
       </c>
       <c r="AF5" s="8">
@@ -2440,12 +2448,12 @@
         <v>39025</v>
       </c>
       <c r="AK5" s="8">
-        <f t="shared" ref="AK5:AL5" si="17">AK3*0.82</f>
-        <v>39273.916399999995</v>
+        <f t="shared" si="16"/>
+        <v>42036</v>
       </c>
       <c r="AL5" s="8">
-        <f t="shared" si="17"/>
-        <v>43643.270000000004</v>
+        <f t="shared" ref="AL5" si="17">AL3*0.82</f>
+        <v>47610.84</v>
       </c>
       <c r="AN5" s="8">
         <f t="shared" ref="AN5:AU5" si="18">AN3-AN4</f>
@@ -2481,47 +2489,47 @@
       </c>
       <c r="AV5" s="8">
         <f>AV3*0.82</f>
-        <v>156577.78639999998</v>
+        <v>163289.88</v>
       </c>
       <c r="AW5" s="8">
         <f t="shared" ref="AW5:BF5" si="19">AW3*0.82</f>
-        <v>175367.12076799999</v>
+        <v>186150.46319999997</v>
       </c>
       <c r="AX5" s="8">
         <f t="shared" si="19"/>
-        <v>189396.49042943999</v>
+        <v>201042.500256</v>
       </c>
       <c r="AY5" s="8">
         <f t="shared" si="19"/>
-        <v>200760.27985520641</v>
+        <v>213105.05027136</v>
       </c>
       <c r="AZ5" s="8">
         <f t="shared" si="19"/>
-        <v>208790.69104941466</v>
+        <v>221629.25228221441</v>
       </c>
       <c r="BA5" s="8">
         <f t="shared" si="19"/>
-        <v>215054.41178089712</v>
+        <v>228278.12985068082</v>
       </c>
       <c r="BB5" s="8">
         <f t="shared" si="19"/>
-        <v>219355.50001651506</v>
+        <v>232843.69244769446</v>
       </c>
       <c r="BC5" s="8">
         <f t="shared" si="19"/>
-        <v>223742.61001684537</v>
+        <v>237500.56629664835</v>
       </c>
       <c r="BD5" s="8">
         <f t="shared" si="19"/>
-        <v>228217.46221718224</v>
+        <v>242250.5776225813</v>
       </c>
       <c r="BE5" s="8">
         <f t="shared" si="19"/>
-        <v>232781.81146152591</v>
+        <v>247095.58917503292</v>
       </c>
       <c r="BF5" s="8">
         <f t="shared" si="19"/>
-        <v>237437.44769075644</v>
+        <v>252037.50095853358</v>
       </c>
     </row>
     <row r="6" spans="2:165">
@@ -2631,12 +2639,11 @@
         <v>12942</v>
       </c>
       <c r="AK6" s="4">
-        <f>AG6*1.13</f>
-        <v>12630.009999999998</v>
+        <v>15144</v>
       </c>
       <c r="AL6" s="4">
-        <f>AH6*1.07</f>
-        <v>13032.6</v>
+        <f>AH6*1.3</f>
+        <v>15834</v>
       </c>
       <c r="AN6" s="4">
         <f>SUM(C6:F6)</f>
@@ -2672,47 +2679,47 @@
       </c>
       <c r="AV6" s="4">
         <f>SUM(AI6:AL6)</f>
-        <v>50754.609999999993</v>
+        <v>56070</v>
       </c>
       <c r="AW6" s="4">
-        <f>AV6*1.06</f>
-        <v>53799.886599999998</v>
+        <f>AV6*1.14</f>
+        <v>63919.799999999996</v>
       </c>
       <c r="AX6" s="4">
-        <f>AW6*1.04</f>
-        <v>55951.882063999998</v>
+        <f>AW6*1.06</f>
+        <v>67754.987999999998</v>
       </c>
       <c r="AY6" s="4">
-        <f>AX6*1.03</f>
-        <v>57630.438525919999</v>
+        <f>AX6*1.04</f>
+        <v>70465.187520000007</v>
       </c>
       <c r="AZ6" s="4">
         <f t="shared" ref="AZ6:BA6" si="20">AY6*1.03</f>
-        <v>59359.351681697597</v>
+        <v>72579.143145600014</v>
       </c>
       <c r="BA6" s="4">
         <f t="shared" si="20"/>
-        <v>61140.132232148528</v>
+        <v>74756.517439968011</v>
       </c>
       <c r="BB6" s="4">
         <f>BA6*1.02</f>
-        <v>62362.9348767915</v>
+        <v>76251.647788767368</v>
       </c>
       <c r="BC6" s="4">
         <f t="shared" ref="BC6:BF6" si="21">BB6*1.02</f>
-        <v>63610.193574327328</v>
+        <v>77776.680744542711</v>
       </c>
       <c r="BD6" s="4">
         <f t="shared" si="21"/>
-        <v>64882.397445813876</v>
+        <v>79332.214359433565</v>
       </c>
       <c r="BE6" s="4">
         <f t="shared" si="21"/>
-        <v>66180.045394730158</v>
+        <v>80918.858646622233</v>
       </c>
       <c r="BF6" s="4">
         <f t="shared" si="21"/>
-        <v>67503.646302624766</v>
+        <v>82537.235819554684</v>
       </c>
     </row>
     <row r="7" spans="2:165">
@@ -2822,12 +2829,11 @@
         <v>2979</v>
       </c>
       <c r="AK7" s="4">
-        <f t="shared" ref="AK7:AL7" si="22">AK3*0.065</f>
-        <v>3113.1763000000001</v>
+        <v>2845</v>
       </c>
       <c r="AL7" s="4">
-        <f t="shared" si="22"/>
-        <v>3459.5275000000006</v>
+        <f t="shared" ref="AL7" si="22">AL3*0.065</f>
+        <v>3774.03</v>
       </c>
       <c r="AN7" s="4">
         <f>SUM(C7:F7)</f>
@@ -2863,47 +2869,47 @@
       </c>
       <c r="AV7" s="4">
         <f>SUM(AI7:AL7)</f>
-        <v>12308.703799999999</v>
+        <v>12355.03</v>
       </c>
       <c r="AW7" s="4">
         <f>AW3*0.065</f>
-        <v>13901.052256000001</v>
+        <v>14755.829399999999</v>
       </c>
       <c r="AX7" s="4">
         <f t="shared" ref="AX7:BF7" si="23">AX3*0.065</f>
-        <v>15013.136436480001</v>
+        <v>15936.295752000002</v>
       </c>
       <c r="AY7" s="4">
         <f t="shared" si="23"/>
-        <v>15913.924622668801</v>
+        <v>16892.473497120001</v>
       </c>
       <c r="AZ7" s="4">
         <f t="shared" si="23"/>
-        <v>16550.481607575555</v>
+        <v>17568.172437004803</v>
       </c>
       <c r="BA7" s="4">
         <f t="shared" si="23"/>
-        <v>17046.996055802822</v>
+        <v>18095.217610114945</v>
       </c>
       <c r="BB7" s="4">
         <f t="shared" si="23"/>
-        <v>17387.935976918878</v>
+        <v>18457.121962317244</v>
       </c>
       <c r="BC7" s="4">
         <f t="shared" si="23"/>
-        <v>17735.694696457256</v>
+        <v>18826.264401563589</v>
       </c>
       <c r="BD7" s="4">
         <f t="shared" si="23"/>
-        <v>18090.4085903864</v>
+        <v>19202.789689594862</v>
       </c>
       <c r="BE7" s="4">
         <f t="shared" si="23"/>
-        <v>18452.216762194126</v>
+        <v>19586.845483386758</v>
       </c>
       <c r="BF7" s="4">
         <f t="shared" si="23"/>
-        <v>18821.261097438011</v>
+        <v>19978.582393054494</v>
       </c>
     </row>
     <row r="8" spans="2:165">
@@ -3014,12 +3020,11 @@
         <v>2663</v>
       </c>
       <c r="AK8" s="4">
-        <f t="shared" ref="AK8:AL8" si="24">AG8*1.02</f>
-        <v>1902.3</v>
+        <v>3512</v>
       </c>
       <c r="AL8" s="4">
-        <f t="shared" si="24"/>
-        <v>2357.2200000000003</v>
+        <f>AH8*1.65</f>
+        <v>3813.1499999999996</v>
       </c>
       <c r="AN8" s="4">
         <f>SUM(C8:F8)</f>
@@ -3055,47 +3060,47 @@
       </c>
       <c r="AV8" s="4">
         <f>SUM(AI8:AL8)</f>
-        <v>9202.52</v>
+        <v>12268.15</v>
       </c>
       <c r="AW8" s="4">
-        <f t="shared" ref="AW8:BF8" si="25">AV8*1.01</f>
-        <v>9294.5452000000005</v>
+        <f>AV8*1.14</f>
+        <v>13985.690999999999</v>
       </c>
       <c r="AX8" s="4">
-        <f t="shared" si="25"/>
-        <v>9387.4906520000004</v>
+        <f>AW8*1.05</f>
+        <v>14684.975549999999</v>
       </c>
       <c r="AY8" s="4">
-        <f t="shared" si="25"/>
-        <v>9481.3655585200013</v>
+        <f>AX8*1.03</f>
+        <v>15125.524816499999</v>
       </c>
       <c r="AZ8" s="4">
-        <f t="shared" si="25"/>
-        <v>9576.179214105201</v>
+        <f>AY8*1.02</f>
+        <v>15428.035312829999</v>
       </c>
       <c r="BA8" s="4">
-        <f t="shared" si="25"/>
-        <v>9671.9410062462539</v>
+        <f t="shared" ref="BA8:BF8" si="24">AZ8*1.02</f>
+        <v>15736.596019086599</v>
       </c>
       <c r="BB8" s="4">
-        <f t="shared" si="25"/>
-        <v>9768.6604163087159</v>
+        <f t="shared" si="24"/>
+        <v>16051.32793946833</v>
       </c>
       <c r="BC8" s="4">
-        <f t="shared" si="25"/>
-        <v>9866.3470204718033</v>
+        <f t="shared" si="24"/>
+        <v>16372.354498257697</v>
       </c>
       <c r="BD8" s="4">
-        <f t="shared" si="25"/>
-        <v>9965.0104906765209</v>
+        <f t="shared" si="24"/>
+        <v>16699.80158822285</v>
       </c>
       <c r="BE8" s="4">
-        <f t="shared" si="25"/>
-        <v>10064.660595583286</v>
+        <f t="shared" si="24"/>
+        <v>17033.797619987308</v>
       </c>
       <c r="BF8" s="4">
-        <f t="shared" si="25"/>
-        <v>10165.307201539119</v>
+        <f t="shared" si="24"/>
+        <v>17374.473572387054</v>
       </c>
     </row>
     <row r="9" spans="2:165" s="6" customFormat="1">
@@ -3103,148 +3108,148 @@
         <v>31</v>
       </c>
       <c r="C9" s="8">
-        <f t="shared" ref="C9:V9" si="26">C5-C6-C7-C8</f>
+        <f t="shared" ref="C9:V9" si="25">C5-C6-C7-C8</f>
         <v>3327</v>
       </c>
       <c r="D9" s="8">
+        <f t="shared" si="25"/>
+        <v>4401</v>
+      </c>
+      <c r="E9" s="8">
+        <f t="shared" si="25"/>
+        <v>5122</v>
+      </c>
+      <c r="F9" s="8">
+        <f t="shared" si="25"/>
+        <v>7352</v>
+      </c>
+      <c r="G9" s="8">
+        <f t="shared" si="25"/>
+        <v>5449</v>
+      </c>
+      <c r="H9" s="8">
+        <f t="shared" si="25"/>
+        <v>5863</v>
+      </c>
+      <c r="I9" s="8">
+        <f t="shared" si="25"/>
+        <v>5781</v>
+      </c>
+      <c r="J9" s="8">
+        <f t="shared" si="25"/>
+        <v>7820</v>
+      </c>
+      <c r="K9" s="8">
+        <f t="shared" si="25"/>
+        <v>3317</v>
+      </c>
+      <c r="L9" s="8">
+        <f t="shared" si="25"/>
+        <v>4606</v>
+      </c>
+      <c r="M9" s="8">
+        <f t="shared" si="25"/>
+        <v>7185</v>
+      </c>
+      <c r="N9" s="8">
+        <f t="shared" si="25"/>
+        <v>8858</v>
+      </c>
+      <c r="O9" s="8">
+        <f t="shared" si="25"/>
+        <v>5893</v>
+      </c>
+      <c r="P9" s="8">
+        <f t="shared" si="25"/>
+        <v>5963</v>
+      </c>
+      <c r="Q9" s="8">
+        <f t="shared" si="25"/>
+        <v>8040</v>
+      </c>
+      <c r="R9" s="8">
+        <f t="shared" si="25"/>
+        <v>12775</v>
+      </c>
+      <c r="S9" s="8">
+        <f t="shared" si="25"/>
+        <v>11378</v>
+      </c>
+      <c r="T9" s="8">
+        <f t="shared" ref="T9:U9" si="26">T5-T6-T7-T8</f>
+        <v>12367</v>
+      </c>
+      <c r="U9" s="8">
         <f t="shared" si="26"/>
-        <v>4401</v>
-      </c>
-      <c r="E9" s="8">
-        <f t="shared" si="26"/>
-        <v>5122</v>
-      </c>
-      <c r="F9" s="8">
-        <f t="shared" si="26"/>
-        <v>7352</v>
-      </c>
-      <c r="G9" s="8">
-        <f t="shared" si="26"/>
-        <v>5449</v>
-      </c>
-      <c r="H9" s="8">
-        <f t="shared" si="26"/>
-        <v>5863</v>
-      </c>
-      <c r="I9" s="8">
-        <f t="shared" si="26"/>
-        <v>5781</v>
-      </c>
-      <c r="J9" s="8">
-        <f t="shared" si="26"/>
-        <v>7820</v>
-      </c>
-      <c r="K9" s="8">
-        <f t="shared" si="26"/>
-        <v>3317</v>
-      </c>
-      <c r="L9" s="8">
-        <f t="shared" si="26"/>
-        <v>4606</v>
-      </c>
-      <c r="M9" s="8">
-        <f t="shared" si="26"/>
-        <v>7185</v>
-      </c>
-      <c r="N9" s="8">
-        <f t="shared" si="26"/>
-        <v>8858</v>
-      </c>
-      <c r="O9" s="8">
-        <f t="shared" si="26"/>
-        <v>5893</v>
-      </c>
-      <c r="P9" s="8">
-        <f t="shared" si="26"/>
-        <v>5963</v>
-      </c>
-      <c r="Q9" s="8">
-        <f t="shared" si="26"/>
-        <v>8040</v>
-      </c>
-      <c r="R9" s="8">
-        <f t="shared" si="26"/>
-        <v>12775</v>
-      </c>
-      <c r="S9" s="8">
-        <f t="shared" si="26"/>
-        <v>11378</v>
-      </c>
-      <c r="T9" s="8">
-        <f t="shared" ref="T9:U9" si="27">T5-T6-T7-T8</f>
-        <v>12367</v>
-      </c>
-      <c r="U9" s="8">
+        <v>10423</v>
+      </c>
+      <c r="V9" s="8">
+        <f t="shared" si="25"/>
+        <v>12585</v>
+      </c>
+      <c r="W9" s="8">
+        <f t="shared" ref="W9:X9" si="27">W5-W6-W7-W8</f>
+        <v>8524</v>
+      </c>
+      <c r="X9" s="8">
         <f t="shared" si="27"/>
-        <v>10423</v>
-      </c>
-      <c r="V9" s="8">
-        <f t="shared" si="26"/>
-        <v>12585</v>
-      </c>
-      <c r="W9" s="8">
-        <f t="shared" ref="W9:X9" si="28">W5-W6-W7-W8</f>
-        <v>8524</v>
-      </c>
-      <c r="X9" s="8">
-        <f t="shared" si="28"/>
         <v>8358</v>
       </c>
       <c r="Y9" s="8">
-        <f t="shared" ref="Y9" si="29">Y5-Y6-Y7-Y8</f>
+        <f t="shared" ref="Y9" si="28">Y5-Y6-Y7-Y8</f>
         <v>5664</v>
       </c>
       <c r="Z9" s="8">
-        <f t="shared" ref="Z9" si="30">Z5-Z6-Z7-Z8</f>
+        <f t="shared" ref="Z9" si="29">Z5-Z6-Z7-Z8</f>
         <v>6399</v>
       </c>
       <c r="AA9" s="8">
-        <f t="shared" ref="AA9:AC9" si="31">AA5-AA6-AA7-AA8</f>
+        <f t="shared" ref="AA9:AC9" si="30">AA5-AA6-AA7-AA8</f>
         <v>7227</v>
       </c>
       <c r="AB9" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>9392</v>
       </c>
       <c r="AC9" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>14018</v>
       </c>
       <c r="AD9" s="8">
-        <f t="shared" ref="AD9" si="32">AD5-AD6-AD7-AD8</f>
+        <f t="shared" ref="AD9" si="31">AD5-AD6-AD7-AD8</f>
         <v>16384</v>
       </c>
       <c r="AE9" s="8">
-        <f t="shared" ref="AE9:AL9" si="33">AE5-AE6-AE7-AE8</f>
+        <f t="shared" ref="AE9:AL9" si="32">AE5-AE6-AE7-AE8</f>
         <v>13818</v>
       </c>
       <c r="AF9" s="8">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>14847</v>
       </c>
       <c r="AG9" s="8">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>17350</v>
       </c>
       <c r="AH9" s="8">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>21815</v>
       </c>
       <c r="AI9" s="8">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>17555</v>
       </c>
       <c r="AJ9" s="8">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>20441</v>
       </c>
       <c r="AK9" s="8">
-        <f t="shared" si="33"/>
-        <v>21628.430099999998</v>
+        <f t="shared" si="32"/>
+        <v>20535</v>
       </c>
       <c r="AL9" s="8">
-        <f t="shared" si="33"/>
-        <v>24793.922500000004</v>
+        <f t="shared" si="32"/>
+        <v>24189.659999999996</v>
       </c>
       <c r="AN9" s="8">
         <f>AN5-AN6-AN7-AN8</f>
@@ -3263,64 +3268,64 @@
         <v>32671</v>
       </c>
       <c r="AR9" s="8">
-        <f t="shared" ref="AR9:BA9" si="34">AR5-AR6-AR7-AR8</f>
+        <f t="shared" ref="AR9:BA9" si="33">AR5-AR6-AR7-AR8</f>
         <v>46753</v>
       </c>
       <c r="AS9" s="8">
+        <f t="shared" si="33"/>
+        <v>28945</v>
+      </c>
+      <c r="AT9" s="8">
+        <f t="shared" si="33"/>
+        <v>47021</v>
+      </c>
+      <c r="AU9" s="8">
+        <f t="shared" si="33"/>
+        <v>67830</v>
+      </c>
+      <c r="AV9" s="8">
+        <f t="shared" si="33"/>
+        <v>82596.700000000012</v>
+      </c>
+      <c r="AW9" s="8">
+        <f t="shared" si="33"/>
+        <v>93489.142799999972</v>
+      </c>
+      <c r="AX9" s="8">
+        <f t="shared" si="33"/>
+        <v>102666.24095400001</v>
+      </c>
+      <c r="AY9" s="8">
+        <f t="shared" si="33"/>
+        <v>110621.86443774001</v>
+      </c>
+      <c r="AZ9" s="8">
+        <f t="shared" si="33"/>
+        <v>116053.90138677959</v>
+      </c>
+      <c r="BA9" s="8">
+        <f t="shared" si="33"/>
+        <v>119689.79878151126</v>
+      </c>
+      <c r="BB9" s="8">
+        <f t="shared" ref="BB9:BF9" si="34">BB5-BB6-BB7-BB8</f>
+        <v>122083.5947571415</v>
+      </c>
+      <c r="BC9" s="8">
         <f t="shared" si="34"/>
-        <v>28945</v>
-      </c>
-      <c r="AT9" s="8">
+        <v>124525.26665228435</v>
+      </c>
+      <c r="BD9" s="8">
         <f t="shared" si="34"/>
-        <v>47021</v>
-      </c>
-      <c r="AU9" s="8">
+        <v>127015.77198533004</v>
+      </c>
+      <c r="BE9" s="8">
         <f t="shared" si="34"/>
-        <v>67830</v>
-      </c>
-      <c r="AV9" s="8">
+        <v>129556.08742503662</v>
+      </c>
+      <c r="BF9" s="8">
         <f t="shared" si="34"/>
-        <v>84311.95259999999</v>
-      </c>
-      <c r="AW9" s="8">
-        <f t="shared" si="34"/>
-        <v>98371.636712000007</v>
-      </c>
-      <c r="AX9" s="8">
-        <f t="shared" si="34"/>
-        <v>109043.98127696</v>
-      </c>
-      <c r="AY9" s="8">
-        <f t="shared" si="34"/>
-        <v>117734.5511480976</v>
-      </c>
-      <c r="AZ9" s="8">
-        <f t="shared" si="34"/>
-        <v>123304.67854603632</v>
-      </c>
-      <c r="BA9" s="8">
-        <f t="shared" si="34"/>
-        <v>127195.34248669952</v>
-      </c>
-      <c r="BB9" s="8">
-        <f t="shared" ref="BB9:BF9" si="35">BB5-BB6-BB7-BB8</f>
-        <v>129835.96874649597</v>
-      </c>
-      <c r="BC9" s="8">
-        <f t="shared" si="35"/>
-        <v>132530.37472558895</v>
-      </c>
-      <c r="BD9" s="8">
-        <f t="shared" si="35"/>
-        <v>135279.64569030545</v>
-      </c>
-      <c r="BE9" s="8">
-        <f t="shared" si="35"/>
-        <v>138084.88870901833</v>
-      </c>
-      <c r="BF9" s="8">
-        <f t="shared" si="35"/>
-        <v>140947.23308915456</v>
+        <v>132147.20917353733</v>
       </c>
     </row>
     <row r="10" spans="2:165">
@@ -3430,11 +3435,10 @@
         <v>-93</v>
       </c>
       <c r="AK10" s="4">
-        <f t="shared" ref="AK10:AL10" si="36">AG10*1.02</f>
-        <v>-481.44</v>
+        <v>-1128</v>
       </c>
       <c r="AL10" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" ref="AL10" si="35">AH10*1.02</f>
         <v>-191.76</v>
       </c>
       <c r="AN10" s="4">
@@ -3471,47 +3475,47 @@
       </c>
       <c r="AV10" s="4">
         <f>SUM(AI10:AL10)</f>
-        <v>-1593.2</v>
+        <v>-2239.7600000000002</v>
       </c>
       <c r="AW10" s="4">
-        <f t="shared" ref="AW10:BA10" si="37">-AV13*0.02</f>
-        <v>-1526.3737257599996</v>
+        <f t="shared" ref="AW10:BA10" si="36">-AV13*0.02</f>
+        <v>-1499.0337920000002</v>
       </c>
       <c r="AX10" s="4">
-        <f t="shared" si="37"/>
-        <v>-1758.2049837045761</v>
+        <f t="shared" si="36"/>
+        <v>-1671.7919080191996</v>
       </c>
       <c r="AY10" s="4">
-        <f t="shared" si="37"/>
-        <v>-1950.1184781876966</v>
+        <f t="shared" si="36"/>
+        <v>-1836.349378371538</v>
       </c>
       <c r="AZ10" s="4">
-        <f t="shared" si="37"/>
-        <v>-2106.450185422621</v>
+        <f t="shared" si="36"/>
+        <v>-1979.2645631635633</v>
       </c>
       <c r="BA10" s="4">
-        <f t="shared" si="37"/>
-        <v>-2207.2358656736774</v>
+        <f t="shared" si="36"/>
+        <v>-2077.3837207189995</v>
       </c>
       <c r="BB10" s="4">
-        <f t="shared" ref="BB10" si="38">-BA13*0.02</f>
-        <v>-2277.4853790017683</v>
+        <f t="shared" ref="BB10" si="37">-BA13*0.02</f>
+        <v>-2143.1024120392526</v>
       </c>
       <c r="BC10" s="4">
-        <f t="shared" ref="BC10" si="39">-BB13*0.02</f>
-        <v>-2325.1967926087605</v>
+        <f t="shared" ref="BC10" si="38">-BB13*0.02</f>
+        <v>-2186.3898701775815</v>
       </c>
       <c r="BD10" s="4">
-        <f t="shared" ref="BD10" si="40">-BC13*0.02</f>
-        <v>-2373.4580587202795</v>
+        <f t="shared" ref="BD10" si="39">-BC13*0.02</f>
+        <v>-2230.1251547953302</v>
       </c>
       <c r="BE10" s="4">
-        <f t="shared" ref="BE10" si="41">-BD13*0.02</f>
-        <v>-2422.6946259828528</v>
+        <f t="shared" ref="BE10" si="40">-BD13*0.02</f>
+        <v>-2274.7277896662067</v>
       </c>
       <c r="BF10" s="4">
-        <f t="shared" ref="BF10" si="42">-BE13*0.02</f>
-        <v>-2472.9334666960208</v>
+        <f t="shared" ref="BF10" si="41">-BE13*0.02</f>
+        <v>-2320.2223477787697</v>
       </c>
     </row>
     <row r="11" spans="2:165" s="6" customFormat="1">
@@ -3519,148 +3523,148 @@
         <v>33</v>
       </c>
       <c r="C11" s="8">
-        <f t="shared" ref="C11:P11" si="43">C9-C10</f>
+        <f t="shared" ref="C11:P11" si="42">C9-C10</f>
         <v>3408</v>
       </c>
       <c r="D11" s="8">
+        <f t="shared" si="42"/>
+        <v>4488</v>
+      </c>
+      <c r="E11" s="8">
+        <f t="shared" si="42"/>
+        <v>5236</v>
+      </c>
+      <c r="F11" s="8">
+        <f t="shared" si="42"/>
+        <v>7462</v>
+      </c>
+      <c r="G11" s="8">
+        <f t="shared" si="42"/>
+        <v>5610</v>
+      </c>
+      <c r="H11" s="8">
+        <f t="shared" si="42"/>
+        <v>5868</v>
+      </c>
+      <c r="I11" s="8">
+        <f t="shared" si="42"/>
+        <v>5912</v>
+      </c>
+      <c r="J11" s="8">
+        <f t="shared" si="42"/>
+        <v>7971</v>
+      </c>
+      <c r="K11" s="8">
+        <f t="shared" si="42"/>
+        <v>3482</v>
+      </c>
+      <c r="L11" s="8">
+        <f t="shared" si="42"/>
+        <v>4812</v>
+      </c>
+      <c r="M11" s="8">
+        <f t="shared" si="42"/>
+        <v>7329</v>
+      </c>
+      <c r="N11" s="8">
+        <f t="shared" si="42"/>
+        <v>9169</v>
+      </c>
+      <c r="O11" s="8">
+        <f t="shared" si="42"/>
+        <v>5861</v>
+      </c>
+      <c r="P11" s="8">
+        <f t="shared" si="42"/>
+        <v>6131</v>
+      </c>
+      <c r="Q11" s="8">
+        <f t="shared" ref="Q11:V11" si="43">Q9-Q10</f>
+        <v>8133</v>
+      </c>
+      <c r="R11" s="8">
         <f t="shared" si="43"/>
-        <v>4488</v>
-      </c>
-      <c r="E11" s="8">
+        <v>13055</v>
+      </c>
+      <c r="S11" s="8">
         <f t="shared" si="43"/>
-        <v>5236</v>
-      </c>
-      <c r="F11" s="8">
+        <v>11503</v>
+      </c>
+      <c r="T11" s="8">
+        <f t="shared" ref="T11:U11" si="44">T9-T10</f>
+        <v>12513</v>
+      </c>
+      <c r="U11" s="8">
+        <f t="shared" si="44"/>
+        <v>10565</v>
+      </c>
+      <c r="V11" s="8">
         <f t="shared" si="43"/>
-        <v>7462</v>
-      </c>
-      <c r="G11" s="8">
-        <f t="shared" si="43"/>
-        <v>5610</v>
-      </c>
-      <c r="H11" s="8">
-        <f t="shared" si="43"/>
-        <v>5868</v>
-      </c>
-      <c r="I11" s="8">
-        <f t="shared" si="43"/>
-        <v>5912</v>
-      </c>
-      <c r="J11" s="8">
-        <f t="shared" si="43"/>
-        <v>7971</v>
-      </c>
-      <c r="K11" s="8">
-        <f t="shared" si="43"/>
-        <v>3482</v>
-      </c>
-      <c r="L11" s="8">
-        <f t="shared" si="43"/>
-        <v>4812</v>
-      </c>
-      <c r="M11" s="8">
-        <f t="shared" si="43"/>
-        <v>7329</v>
-      </c>
-      <c r="N11" s="8">
-        <f t="shared" si="43"/>
-        <v>9169</v>
-      </c>
-      <c r="O11" s="8">
-        <f t="shared" si="43"/>
-        <v>5861</v>
-      </c>
-      <c r="P11" s="8">
-        <f t="shared" si="43"/>
-        <v>6131</v>
-      </c>
-      <c r="Q11" s="8">
-        <f t="shared" ref="Q11:V11" si="44">Q9-Q10</f>
-        <v>8133</v>
-      </c>
-      <c r="R11" s="8">
-        <f t="shared" si="44"/>
-        <v>13055</v>
-      </c>
-      <c r="S11" s="8">
-        <f t="shared" si="44"/>
-        <v>11503</v>
-      </c>
-      <c r="T11" s="8">
-        <f t="shared" ref="T11:U11" si="45">T9-T10</f>
-        <v>12513</v>
-      </c>
-      <c r="U11" s="8">
+        <v>12702</v>
+      </c>
+      <c r="W11" s="8">
+        <f t="shared" ref="W11:X11" si="45">W9-W10</f>
+        <v>8908</v>
+      </c>
+      <c r="X11" s="8">
         <f t="shared" si="45"/>
-        <v>10565</v>
-      </c>
-      <c r="V11" s="8">
-        <f t="shared" si="44"/>
-        <v>12702</v>
-      </c>
-      <c r="W11" s="8">
-        <f t="shared" ref="W11:X11" si="46">W9-W10</f>
-        <v>8908</v>
-      </c>
-      <c r="X11" s="8">
-        <f t="shared" si="46"/>
         <v>8186</v>
       </c>
       <c r="Y11" s="8">
-        <f t="shared" ref="Y11" si="47">Y9-Y10</f>
+        <f t="shared" ref="Y11" si="46">Y9-Y10</f>
         <v>5576</v>
       </c>
       <c r="Z11" s="8">
-        <f t="shared" ref="Z11" si="48">Z9-Z10</f>
+        <f t="shared" ref="Z11" si="47">Z9-Z10</f>
         <v>6149</v>
       </c>
       <c r="AA11" s="8">
-        <f t="shared" ref="AA11:AC11" si="49">AA9-AA10</f>
+        <f t="shared" ref="AA11:AC11" si="48">AA9-AA10</f>
         <v>7307</v>
       </c>
       <c r="AB11" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>9293</v>
       </c>
       <c r="AC11" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>14290</v>
       </c>
       <c r="AD11" s="8">
-        <f t="shared" ref="AD11" si="50">AD9-AD10</f>
+        <f t="shared" ref="AD11" si="49">AD9-AD10</f>
         <v>16808</v>
       </c>
       <c r="AE11" s="8">
-        <f t="shared" ref="AE11:AL11" si="51">AE9-AE10</f>
+        <f t="shared" ref="AE11:AL11" si="50">AE9-AE10</f>
         <v>14183</v>
       </c>
       <c r="AF11" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="50"/>
         <v>15106</v>
       </c>
       <c r="AG11" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="50"/>
         <v>17822</v>
       </c>
       <c r="AH11" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="50"/>
         <v>22003</v>
       </c>
       <c r="AI11" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="50"/>
         <v>18382</v>
       </c>
       <c r="AJ11" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="50"/>
         <v>20534</v>
       </c>
       <c r="AK11" s="8">
-        <f t="shared" si="51"/>
-        <v>22109.870099999996</v>
+        <f t="shared" si="50"/>
+        <v>21663</v>
       </c>
       <c r="AL11" s="8">
-        <f t="shared" si="51"/>
-        <v>24985.682500000003</v>
+        <f t="shared" si="50"/>
+        <v>24381.419999999995</v>
       </c>
       <c r="AN11" s="8">
         <f>AN9-AN10</f>
@@ -3679,64 +3683,64 @@
         <v>33180</v>
       </c>
       <c r="AR11" s="8">
-        <f t="shared" ref="AR11:BA11" si="52">AR9-AR10</f>
+        <f t="shared" ref="AR11:BA11" si="51">AR9-AR10</f>
         <v>47283</v>
       </c>
       <c r="AS11" s="8">
+        <f t="shared" si="51"/>
+        <v>28819</v>
+      </c>
+      <c r="AT11" s="8">
+        <f t="shared" si="51"/>
+        <v>47698</v>
+      </c>
+      <c r="AU11" s="8">
+        <f t="shared" si="51"/>
+        <v>69114</v>
+      </c>
+      <c r="AV11" s="8">
+        <f t="shared" si="51"/>
+        <v>84836.46</v>
+      </c>
+      <c r="AW11" s="8">
+        <f t="shared" si="51"/>
+        <v>94988.176591999974</v>
+      </c>
+      <c r="AX11" s="8">
+        <f t="shared" si="51"/>
+        <v>104338.0328620192</v>
+      </c>
+      <c r="AY11" s="8">
+        <f t="shared" si="51"/>
+        <v>112458.21381611154</v>
+      </c>
+      <c r="AZ11" s="8">
+        <f t="shared" si="51"/>
+        <v>118033.16594994316</v>
+      </c>
+      <c r="BA11" s="8">
+        <f t="shared" si="51"/>
+        <v>121767.18250223025</v>
+      </c>
+      <c r="BB11" s="8">
+        <f t="shared" ref="BB11:BF11" si="52">BB9-BB10</f>
+        <v>124226.69716918076</v>
+      </c>
+      <c r="BC11" s="8">
         <f t="shared" si="52"/>
-        <v>28819</v>
-      </c>
-      <c r="AT11" s="8">
+        <v>126711.65652246193</v>
+      </c>
+      <c r="BD11" s="8">
         <f t="shared" si="52"/>
-        <v>47698</v>
-      </c>
-      <c r="AU11" s="8">
+        <v>129245.89714012537</v>
+      </c>
+      <c r="BE11" s="8">
         <f t="shared" si="52"/>
-        <v>69114</v>
-      </c>
-      <c r="AV11" s="8">
+        <v>131830.81521470283</v>
+      </c>
+      <c r="BF11" s="8">
         <f t="shared" si="52"/>
-        <v>85905.152599999987</v>
-      </c>
-      <c r="AW11" s="8">
-        <f t="shared" si="52"/>
-        <v>99898.010437760007</v>
-      </c>
-      <c r="AX11" s="8">
-        <f t="shared" si="52"/>
-        <v>110802.18626066457</v>
-      </c>
-      <c r="AY11" s="8">
-        <f t="shared" si="52"/>
-        <v>119684.66962628529</v>
-      </c>
-      <c r="AZ11" s="8">
-        <f t="shared" si="52"/>
-        <v>125411.12873145894</v>
-      </c>
-      <c r="BA11" s="8">
-        <f t="shared" si="52"/>
-        <v>129402.5783523732</v>
-      </c>
-      <c r="BB11" s="8">
-        <f t="shared" ref="BB11:BF11" si="53">BB9-BB10</f>
-        <v>132113.45412549775</v>
-      </c>
-      <c r="BC11" s="8">
-        <f t="shared" si="53"/>
-        <v>134855.57151819771</v>
-      </c>
-      <c r="BD11" s="8">
-        <f t="shared" si="53"/>
-        <v>137653.10374902573</v>
-      </c>
-      <c r="BE11" s="8">
-        <f t="shared" si="53"/>
-        <v>140507.58333500117</v>
-      </c>
-      <c r="BF11" s="8">
-        <f t="shared" si="53"/>
-        <v>143420.16655585059</v>
+        <v>134467.43152131609</v>
       </c>
     </row>
     <row r="12" spans="2:165">
@@ -3850,12 +3854,12 @@
         <v>2197</v>
       </c>
       <c r="AK12" s="4">
-        <f t="shared" ref="AK12:AL12" si="54">AK11*0.12</f>
-        <v>2653.1844119999996</v>
+        <f>18954-15930</f>
+        <v>3024</v>
       </c>
       <c r="AL12" s="4">
-        <f t="shared" si="54"/>
-        <v>2998.2819000000004</v>
+        <f t="shared" ref="AL12" si="53">AL11*0.12</f>
+        <v>2925.7703999999994</v>
       </c>
       <c r="AN12" s="4">
         <f>SUM(C12:F12)</f>
@@ -3891,47 +3895,47 @@
       </c>
       <c r="AV12" s="4">
         <f>SUM(AI12:AL12)</f>
-        <v>9586.4663120000005</v>
+        <v>9884.7703999999994</v>
       </c>
       <c r="AW12" s="4">
         <f>AW11*0.12</f>
-        <v>11987.7612525312</v>
+        <v>11398.581191039997</v>
       </c>
       <c r="AX12" s="4">
-        <f t="shared" ref="AX12:BF12" si="55">AX11*0.12</f>
-        <v>13296.262351279749</v>
+        <f t="shared" ref="AX12:BF12" si="54">AX11*0.12</f>
+        <v>12520.563943442303</v>
       </c>
       <c r="AY12" s="4">
-        <f t="shared" si="55"/>
-        <v>14362.160355154234</v>
+        <f t="shared" si="54"/>
+        <v>13494.985657933385</v>
       </c>
       <c r="AZ12" s="4">
-        <f t="shared" si="55"/>
-        <v>15049.335447775073</v>
+        <f t="shared" si="54"/>
+        <v>14163.979913993178</v>
       </c>
       <c r="BA12" s="4">
-        <f t="shared" si="55"/>
-        <v>15528.309402284784</v>
+        <f t="shared" si="54"/>
+        <v>14612.06190026763</v>
       </c>
       <c r="BB12" s="4">
-        <f t="shared" si="55"/>
-        <v>15853.61449505973</v>
+        <f t="shared" si="54"/>
+        <v>14907.20366030169</v>
       </c>
       <c r="BC12" s="4">
-        <f t="shared" si="55"/>
-        <v>16182.668582183725</v>
+        <f t="shared" si="54"/>
+        <v>15205.398782695431</v>
       </c>
       <c r="BD12" s="4">
-        <f t="shared" si="55"/>
-        <v>16518.372449883085</v>
+        <f t="shared" si="54"/>
+        <v>15509.507656815043</v>
       </c>
       <c r="BE12" s="4">
-        <f t="shared" si="55"/>
-        <v>16860.91000020014</v>
+        <f t="shared" si="54"/>
+        <v>15819.697825764339</v>
       </c>
       <c r="BF12" s="4">
-        <f t="shared" si="55"/>
-        <v>17210.419986702069</v>
+        <f t="shared" si="54"/>
+        <v>16136.091782557931</v>
       </c>
     </row>
     <row r="13" spans="2:165" s="6" customFormat="1">
@@ -3939,148 +3943,148 @@
         <v>35</v>
       </c>
       <c r="C13" s="8">
-        <f t="shared" ref="C13:P13" si="56">C11-C12</f>
+        <f t="shared" ref="C13:P13" si="55">C11-C12</f>
         <v>3059</v>
       </c>
       <c r="D13" s="8">
+        <f t="shared" si="55"/>
+        <v>3890</v>
+      </c>
+      <c r="E13" s="8">
+        <f t="shared" si="55"/>
+        <v>4707</v>
+      </c>
+      <c r="F13" s="8">
+        <f t="shared" si="55"/>
+        <v>3548</v>
+      </c>
+      <c r="G13" s="8">
+        <f t="shared" si="55"/>
+        <v>4987</v>
+      </c>
+      <c r="H13" s="8">
+        <f t="shared" si="55"/>
+        <v>5106</v>
+      </c>
+      <c r="I13" s="8">
+        <f t="shared" si="55"/>
+        <v>5137</v>
+      </c>
+      <c r="J13" s="8">
+        <f t="shared" si="55"/>
+        <v>6882</v>
+      </c>
+      <c r="K13" s="8">
+        <f t="shared" si="55"/>
+        <v>2429</v>
+      </c>
+      <c r="L13" s="8">
+        <f t="shared" si="55"/>
+        <v>2596</v>
+      </c>
+      <c r="M13" s="8">
+        <f t="shared" si="55"/>
+        <v>6091</v>
+      </c>
+      <c r="N13" s="8">
+        <f t="shared" si="55"/>
+        <v>7349</v>
+      </c>
+      <c r="O13" s="8">
+        <f t="shared" si="55"/>
+        <v>4902</v>
+      </c>
+      <c r="P13" s="8">
+        <f t="shared" si="55"/>
+        <v>5178</v>
+      </c>
+      <c r="Q13" s="8">
+        <f t="shared" ref="Q13:R13" si="56">Q11-Q12</f>
+        <v>7846</v>
+      </c>
+      <c r="R13" s="8">
         <f t="shared" si="56"/>
-        <v>3890</v>
-      </c>
-      <c r="E13" s="8">
-        <f t="shared" si="56"/>
-        <v>4707</v>
-      </c>
-      <c r="F13" s="8">
-        <f t="shared" si="56"/>
-        <v>3548</v>
-      </c>
-      <c r="G13" s="8">
-        <f t="shared" si="56"/>
-        <v>4987</v>
-      </c>
-      <c r="H13" s="8">
-        <f t="shared" si="56"/>
-        <v>5106</v>
-      </c>
-      <c r="I13" s="8">
-        <f t="shared" si="56"/>
-        <v>5137</v>
-      </c>
-      <c r="J13" s="8">
-        <f t="shared" si="56"/>
-        <v>6882</v>
-      </c>
-      <c r="K13" s="8">
-        <f t="shared" si="56"/>
-        <v>2429</v>
-      </c>
-      <c r="L13" s="8">
-        <f t="shared" si="56"/>
-        <v>2596</v>
-      </c>
-      <c r="M13" s="8">
-        <f t="shared" si="56"/>
-        <v>6091</v>
-      </c>
-      <c r="N13" s="8">
-        <f t="shared" si="56"/>
-        <v>7349</v>
-      </c>
-      <c r="O13" s="8">
-        <f t="shared" si="56"/>
-        <v>4902</v>
-      </c>
-      <c r="P13" s="8">
-        <f t="shared" si="56"/>
-        <v>5178</v>
-      </c>
-      <c r="Q13" s="8">
-        <f t="shared" ref="Q13:R13" si="57">Q11-Q12</f>
-        <v>7846</v>
-      </c>
-      <c r="R13" s="8">
+        <v>11219</v>
+      </c>
+      <c r="S13" s="8">
+        <f t="shared" ref="S13:V13" si="57">S11-S12</f>
+        <v>9497</v>
+      </c>
+      <c r="T13" s="8">
+        <f t="shared" ref="T13:U13" si="58">T11-T12</f>
+        <v>10394</v>
+      </c>
+      <c r="U13" s="8">
+        <f t="shared" si="58"/>
+        <v>9194</v>
+      </c>
+      <c r="V13" s="8">
         <f t="shared" si="57"/>
-        <v>11219</v>
-      </c>
-      <c r="S13" s="8">
-        <f t="shared" ref="S13:V13" si="58">S11-S12</f>
-        <v>9497</v>
-      </c>
-      <c r="T13" s="8">
-        <f t="shared" ref="T13:U13" si="59">T11-T12</f>
-        <v>10394</v>
-      </c>
-      <c r="U13" s="8">
+        <v>10285</v>
+      </c>
+      <c r="W13" s="8">
+        <f t="shared" ref="W13:X13" si="59">W11-W12</f>
+        <v>7465</v>
+      </c>
+      <c r="X13" s="8">
         <f t="shared" si="59"/>
-        <v>9194</v>
-      </c>
-      <c r="V13" s="8">
-        <f t="shared" si="58"/>
-        <v>10285</v>
-      </c>
-      <c r="W13" s="8">
-        <f t="shared" ref="W13:X13" si="60">W11-W12</f>
-        <v>7465</v>
-      </c>
-      <c r="X13" s="8">
-        <f t="shared" si="60"/>
         <v>6687</v>
       </c>
       <c r="Y13" s="8">
-        <f t="shared" ref="Y13" si="61">Y11-Y12</f>
+        <f t="shared" ref="Y13" si="60">Y11-Y12</f>
         <v>4395</v>
       </c>
       <c r="Z13" s="8">
-        <f t="shared" ref="Z13" si="62">Z11-Z12</f>
+        <f t="shared" ref="Z13" si="61">Z11-Z12</f>
         <v>4652</v>
       </c>
       <c r="AA13" s="8">
-        <f t="shared" ref="AA13:AC13" si="63">AA11-AA12</f>
+        <f t="shared" ref="AA13:AC13" si="62">AA11-AA12</f>
         <v>5709</v>
       </c>
       <c r="AB13" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="62"/>
         <v>7788</v>
       </c>
       <c r="AC13" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="62"/>
         <v>11853</v>
       </c>
       <c r="AD13" s="8">
-        <f t="shared" ref="AD13" si="64">AD11-AD12</f>
+        <f t="shared" ref="AD13" si="63">AD11-AD12</f>
         <v>14017</v>
       </c>
       <c r="AE13" s="8">
-        <f t="shared" ref="AE13" si="65">AE11-AE12</f>
+        <f t="shared" ref="AE13" si="64">AE11-AE12</f>
         <v>12369</v>
       </c>
       <c r="AF13" s="8">
-        <f t="shared" ref="AF13:AH13" si="66">AF11-AF12</f>
+        <f t="shared" ref="AF13:AH13" si="65">AF11-AF12</f>
         <v>13465</v>
       </c>
       <c r="AG13" s="8">
+        <f t="shared" si="65"/>
+        <v>15688</v>
+      </c>
+      <c r="AH13" s="8">
+        <f t="shared" si="65"/>
+        <v>19288</v>
+      </c>
+      <c r="AI13" s="8">
+        <f t="shared" ref="AI13:AL13" si="66">AI11-AI12</f>
+        <v>16644</v>
+      </c>
+      <c r="AJ13" s="8">
         <f t="shared" si="66"/>
-        <v>15688</v>
-      </c>
-      <c r="AH13" s="8">
+        <v>18337</v>
+      </c>
+      <c r="AK13" s="8">
         <f t="shared" si="66"/>
-        <v>19288</v>
-      </c>
-      <c r="AI13" s="8">
-        <f t="shared" ref="AI13:AL13" si="67">AI11-AI12</f>
-        <v>16644</v>
-      </c>
-      <c r="AJ13" s="8">
-        <f t="shared" si="67"/>
-        <v>18337</v>
-      </c>
-      <c r="AK13" s="8">
-        <f t="shared" si="67"/>
-        <v>19456.685687999998</v>
+        <v>18639</v>
       </c>
       <c r="AL13" s="8">
-        <f t="shared" si="67"/>
-        <v>21987.400600000001</v>
+        <f t="shared" si="66"/>
+        <v>21455.649599999997</v>
       </c>
       <c r="AN13" s="8">
         <f>AN11-AN12</f>
@@ -4099,492 +4103,492 @@
         <v>29145</v>
       </c>
       <c r="AR13" s="8">
-        <f t="shared" ref="AR13:BA13" si="68">AR11-AR12</f>
+        <f t="shared" ref="AR13:BA13" si="67">AR11-AR12</f>
         <v>39370</v>
       </c>
       <c r="AS13" s="8">
+        <f t="shared" si="67"/>
+        <v>23199</v>
+      </c>
+      <c r="AT13" s="8">
+        <f t="shared" si="67"/>
+        <v>39367</v>
+      </c>
+      <c r="AU13" s="8">
+        <f t="shared" si="67"/>
+        <v>60810</v>
+      </c>
+      <c r="AV13" s="8">
+        <f t="shared" si="67"/>
+        <v>74951.689600000012</v>
+      </c>
+      <c r="AW13" s="8">
+        <f t="shared" si="67"/>
+        <v>83589.595400959981</v>
+      </c>
+      <c r="AX13" s="8">
+        <f t="shared" si="67"/>
+        <v>91817.468918576895</v>
+      </c>
+      <c r="AY13" s="8">
+        <f t="shared" si="67"/>
+        <v>98963.228158178157</v>
+      </c>
+      <c r="AZ13" s="8">
+        <f t="shared" si="67"/>
+        <v>103869.18603594997</v>
+      </c>
+      <c r="BA13" s="8">
+        <f t="shared" si="67"/>
+        <v>107155.12060196263</v>
+      </c>
+      <c r="BB13" s="8">
+        <f t="shared" ref="BB13:BF13" si="68">BB11-BB12</f>
+        <v>109319.49350887907</v>
+      </c>
+      <c r="BC13" s="8">
         <f t="shared" si="68"/>
-        <v>23199</v>
-      </c>
-      <c r="AT13" s="8">
+        <v>111506.2577397665</v>
+      </c>
+      <c r="BD13" s="8">
         <f t="shared" si="68"/>
-        <v>39367</v>
-      </c>
-      <c r="AU13" s="8">
+        <v>113736.38948331033</v>
+      </c>
+      <c r="BE13" s="8">
         <f t="shared" si="68"/>
-        <v>60810</v>
-      </c>
-      <c r="AV13" s="8">
+        <v>116011.1173889385</v>
+      </c>
+      <c r="BF13" s="8">
         <f t="shared" si="68"/>
-        <v>76318.686287999983</v>
-      </c>
-      <c r="AW13" s="8">
-        <f t="shared" si="68"/>
-        <v>87910.249185228808</v>
-      </c>
-      <c r="AX13" s="8">
-        <f t="shared" si="68"/>
-        <v>97505.92390938483</v>
-      </c>
-      <c r="AY13" s="8">
-        <f t="shared" si="68"/>
-        <v>105322.50927113106</v>
-      </c>
-      <c r="AZ13" s="8">
-        <f t="shared" si="68"/>
-        <v>110361.79328368387</v>
-      </c>
-      <c r="BA13" s="8">
-        <f t="shared" si="68"/>
-        <v>113874.26895008842</v>
-      </c>
-      <c r="BB13" s="8">
-        <f t="shared" ref="BB13:BF13" si="69">BB11-BB12</f>
-        <v>116259.83963043801</v>
-      </c>
-      <c r="BC13" s="8">
-        <f t="shared" si="69"/>
-        <v>118672.90293601398</v>
-      </c>
-      <c r="BD13" s="8">
-        <f t="shared" si="69"/>
-        <v>121134.73129914264</v>
-      </c>
-      <c r="BE13" s="8">
-        <f t="shared" si="69"/>
-        <v>123646.67333480103</v>
-      </c>
-      <c r="BF13" s="8">
-        <f t="shared" si="69"/>
-        <v>126209.74656914853</v>
+        <v>118331.33973875816</v>
       </c>
       <c r="BG13" s="6">
         <f>BF13*(1+$BI$18)</f>
-        <v>124947.64910345704</v>
+        <v>117148.02634137058</v>
       </c>
       <c r="BH13" s="6">
-        <f t="shared" ref="BH13:DS13" si="70">BG13*(1+$BI$18)</f>
-        <v>123698.17261242247</v>
+        <f t="shared" ref="BH13:DS13" si="69">BG13*(1+$BI$18)</f>
+        <v>115976.54607795688</v>
       </c>
       <c r="BI13" s="6">
+        <f t="shared" si="69"/>
+        <v>114816.78061717731</v>
+      </c>
+      <c r="BJ13" s="6">
+        <f t="shared" si="69"/>
+        <v>113668.61281100554</v>
+      </c>
+      <c r="BK13" s="6">
+        <f t="shared" si="69"/>
+        <v>112531.92668289549</v>
+      </c>
+      <c r="BL13" s="6">
+        <f t="shared" si="69"/>
+        <v>111406.60741606653</v>
+      </c>
+      <c r="BM13" s="6">
+        <f t="shared" si="69"/>
+        <v>110292.54134190586</v>
+      </c>
+      <c r="BN13" s="6">
+        <f t="shared" si="69"/>
+        <v>109189.6159284868</v>
+      </c>
+      <c r="BO13" s="6">
+        <f t="shared" si="69"/>
+        <v>108097.71976920194</v>
+      </c>
+      <c r="BP13" s="6">
+        <f t="shared" si="69"/>
+        <v>107016.74257150992</v>
+      </c>
+      <c r="BQ13" s="6">
+        <f t="shared" si="69"/>
+        <v>105946.57514579482</v>
+      </c>
+      <c r="BR13" s="6">
+        <f t="shared" si="69"/>
+        <v>104887.10939433688</v>
+      </c>
+      <c r="BS13" s="6">
+        <f t="shared" si="69"/>
+        <v>103838.23830039351</v>
+      </c>
+      <c r="BT13" s="6">
+        <f t="shared" si="69"/>
+        <v>102799.85591738958</v>
+      </c>
+      <c r="BU13" s="6">
+        <f t="shared" si="69"/>
+        <v>101771.85735821568</v>
+      </c>
+      <c r="BV13" s="6">
+        <f t="shared" si="69"/>
+        <v>100754.13878463353</v>
+      </c>
+      <c r="BW13" s="6">
+        <f t="shared" si="69"/>
+        <v>99746.597396787198</v>
+      </c>
+      <c r="BX13" s="6">
+        <f t="shared" si="69"/>
+        <v>98749.131422819322</v>
+      </c>
+      <c r="BY13" s="6">
+        <f t="shared" si="69"/>
+        <v>97761.640108591135</v>
+      </c>
+      <c r="BZ13" s="6">
+        <f t="shared" si="69"/>
+        <v>96784.023707505228</v>
+      </c>
+      <c r="CA13" s="6">
+        <f t="shared" si="69"/>
+        <v>95816.183470430173</v>
+      </c>
+      <c r="CB13" s="6">
+        <f t="shared" si="69"/>
+        <v>94858.021635725876</v>
+      </c>
+      <c r="CC13" s="6">
+        <f t="shared" si="69"/>
+        <v>93909.44141936861</v>
+      </c>
+      <c r="CD13" s="6">
+        <f t="shared" si="69"/>
+        <v>92970.347005174917</v>
+      </c>
+      <c r="CE13" s="6">
+        <f t="shared" si="69"/>
+        <v>92040.643535123163</v>
+      </c>
+      <c r="CF13" s="6">
+        <f t="shared" si="69"/>
+        <v>91120.237099771926</v>
+      </c>
+      <c r="CG13" s="6">
+        <f t="shared" si="69"/>
+        <v>90209.034728774204</v>
+      </c>
+      <c r="CH13" s="6">
+        <f t="shared" si="69"/>
+        <v>89306.944381486464</v>
+      </c>
+      <c r="CI13" s="6">
+        <f t="shared" si="69"/>
+        <v>88413.8749376716</v>
+      </c>
+      <c r="CJ13" s="6">
+        <f t="shared" si="69"/>
+        <v>87529.73618829489</v>
+      </c>
+      <c r="CK13" s="6">
+        <f t="shared" si="69"/>
+        <v>86654.438826411933</v>
+      </c>
+      <c r="CL13" s="6">
+        <f t="shared" si="69"/>
+        <v>85787.894438147807</v>
+      </c>
+      <c r="CM13" s="6">
+        <f t="shared" si="69"/>
+        <v>84930.015493766332</v>
+      </c>
+      <c r="CN13" s="6">
+        <f t="shared" si="69"/>
+        <v>84080.715338828668</v>
+      </c>
+      <c r="CO13" s="6">
+        <f t="shared" si="69"/>
+        <v>83239.908185440378</v>
+      </c>
+      <c r="CP13" s="6">
+        <f t="shared" si="69"/>
+        <v>82407.509103585966</v>
+      </c>
+      <c r="CQ13" s="6">
+        <f t="shared" si="69"/>
+        <v>81583.434012550104</v>
+      </c>
+      <c r="CR13" s="6">
+        <f t="shared" si="69"/>
+        <v>80767.599672424607</v>
+      </c>
+      <c r="CS13" s="6">
+        <f t="shared" si="69"/>
+        <v>79959.923675700367</v>
+      </c>
+      <c r="CT13" s="6">
+        <f t="shared" si="69"/>
+        <v>79160.324438943368</v>
+      </c>
+      <c r="CU13" s="6">
+        <f t="shared" si="69"/>
+        <v>78368.721194553931</v>
+      </c>
+      <c r="CV13" s="6">
+        <f t="shared" si="69"/>
+        <v>77585.033982608395</v>
+      </c>
+      <c r="CW13" s="6">
+        <f t="shared" si="69"/>
+        <v>76809.183642782315</v>
+      </c>
+      <c r="CX13" s="6">
+        <f t="shared" si="69"/>
+        <v>76041.091806354496</v>
+      </c>
+      <c r="CY13" s="6">
+        <f t="shared" si="69"/>
+        <v>75280.680888290954</v>
+      </c>
+      <c r="CZ13" s="6">
+        <f t="shared" si="69"/>
+        <v>74527.874079408037</v>
+      </c>
+      <c r="DA13" s="6">
+        <f t="shared" si="69"/>
+        <v>73782.595338613959</v>
+      </c>
+      <c r="DB13" s="6">
+        <f t="shared" si="69"/>
+        <v>73044.769385227817</v>
+      </c>
+      <c r="DC13" s="6">
+        <f t="shared" si="69"/>
+        <v>72314.321691375531</v>
+      </c>
+      <c r="DD13" s="6">
+        <f t="shared" si="69"/>
+        <v>71591.178474461776</v>
+      </c>
+      <c r="DE13" s="6">
+        <f t="shared" si="69"/>
+        <v>70875.266689717158</v>
+      </c>
+      <c r="DF13" s="6">
+        <f t="shared" si="69"/>
+        <v>70166.514022819989</v>
+      </c>
+      <c r="DG13" s="6">
+        <f t="shared" si="69"/>
+        <v>69464.848882591788</v>
+      </c>
+      <c r="DH13" s="6">
+        <f t="shared" si="69"/>
+        <v>68770.200393765874</v>
+      </c>
+      <c r="DI13" s="6">
+        <f t="shared" si="69"/>
+        <v>68082.498389828208</v>
+      </c>
+      <c r="DJ13" s="6">
+        <f t="shared" si="69"/>
+        <v>67401.67340592992</v>
+      </c>
+      <c r="DK13" s="6">
+        <f t="shared" si="69"/>
+        <v>66727.656671870616</v>
+      </c>
+      <c r="DL13" s="6">
+        <f t="shared" si="69"/>
+        <v>66060.380105151911</v>
+      </c>
+      <c r="DM13" s="6">
+        <f t="shared" si="69"/>
+        <v>65399.776304100393</v>
+      </c>
+      <c r="DN13" s="6">
+        <f t="shared" si="69"/>
+        <v>64745.778541059386</v>
+      </c>
+      <c r="DO13" s="6">
+        <f t="shared" si="69"/>
+        <v>64098.320755648791</v>
+      </c>
+      <c r="DP13" s="6">
+        <f t="shared" si="69"/>
+        <v>63457.337548092299</v>
+      </c>
+      <c r="DQ13" s="6">
+        <f t="shared" si="69"/>
+        <v>62822.764172611372</v>
+      </c>
+      <c r="DR13" s="6">
+        <f t="shared" si="69"/>
+        <v>62194.536530885256</v>
+      </c>
+      <c r="DS13" s="6">
+        <f t="shared" si="69"/>
+        <v>61572.591165576399</v>
+      </c>
+      <c r="DT13" s="6">
+        <f t="shared" ref="DT13:FI13" si="70">DS13*(1+$BI$18)</f>
+        <v>60956.865253920638</v>
+      </c>
+      <c r="DU13" s="6">
         <f t="shared" si="70"/>
-        <v>122461.19088629824</v>
-      </c>
-      <c r="BJ13" s="6">
+        <v>60347.296601381429</v>
+      </c>
+      <c r="DV13" s="6">
         <f t="shared" si="70"/>
-        <v>121236.57897743526</v>
-      </c>
-      <c r="BK13" s="6">
+        <v>59743.823635367611</v>
+      </c>
+      <c r="DW13" s="6">
         <f t="shared" si="70"/>
-        <v>120024.21318766091</v>
-      </c>
-      <c r="BL13" s="6">
+        <v>59146.385399013932</v>
+      </c>
+      <c r="DX13" s="6">
         <f t="shared" si="70"/>
-        <v>118823.97105578429</v>
-      </c>
-      <c r="BM13" s="6">
+        <v>58554.92154502379</v>
+      </c>
+      <c r="DY13" s="6">
         <f t="shared" si="70"/>
-        <v>117635.73134522645</v>
-      </c>
-      <c r="BN13" s="6">
+        <v>57969.372329573554</v>
+      </c>
+      <c r="DZ13" s="6">
         <f t="shared" si="70"/>
-        <v>116459.37403177419</v>
-      </c>
-      <c r="BO13" s="6">
+        <v>57389.678606277819</v>
+      </c>
+      <c r="EA13" s="6">
         <f t="shared" si="70"/>
-        <v>115294.78029145645</v>
-      </c>
-      <c r="BP13" s="6">
+        <v>56815.781820215037</v>
+      </c>
+      <c r="EB13" s="6">
         <f t="shared" si="70"/>
-        <v>114141.83248854188</v>
-      </c>
-      <c r="BQ13" s="6">
+        <v>56247.62400201289</v>
+      </c>
+      <c r="EC13" s="6">
         <f t="shared" si="70"/>
-        <v>113000.41416365646</v>
-      </c>
-      <c r="BR13" s="6">
+        <v>55685.147761992761</v>
+      </c>
+      <c r="ED13" s="6">
         <f t="shared" si="70"/>
-        <v>111870.41002201989</v>
-      </c>
-      <c r="BS13" s="6">
+        <v>55128.296284372831</v>
+      </c>
+      <c r="EE13" s="6">
         <f t="shared" si="70"/>
-        <v>110751.70592179969</v>
-      </c>
-      <c r="BT13" s="6">
+        <v>54577.013321529099</v>
+      </c>
+      <c r="EF13" s="6">
         <f t="shared" si="70"/>
-        <v>109644.18886258169</v>
-      </c>
-      <c r="BU13" s="6">
+        <v>54031.243188313805</v>
+      </c>
+      <c r="EG13" s="6">
         <f t="shared" si="70"/>
-        <v>108547.74697395587</v>
-      </c>
-      <c r="BV13" s="6">
+        <v>53490.930756430665</v>
+      </c>
+      <c r="EH13" s="6">
         <f t="shared" si="70"/>
-        <v>107462.26950421631</v>
-      </c>
-      <c r="BW13" s="6">
+        <v>52956.021448866355</v>
+      </c>
+      <c r="EI13" s="6">
         <f t="shared" si="70"/>
-        <v>106387.64680917414</v>
-      </c>
-      <c r="BX13" s="6">
+        <v>52426.46123437769</v>
+      </c>
+      <c r="EJ13" s="6">
         <f t="shared" si="70"/>
-        <v>105323.7703410824</v>
-      </c>
-      <c r="BY13" s="6">
+        <v>51902.196622033909</v>
+      </c>
+      <c r="EK13" s="6">
         <f t="shared" si="70"/>
-        <v>104270.53263767158</v>
-      </c>
-      <c r="BZ13" s="6">
+        <v>51383.174655813571</v>
+      </c>
+      <c r="EL13" s="6">
         <f t="shared" si="70"/>
-        <v>103227.82731129487</v>
-      </c>
-      <c r="CA13" s="6">
+        <v>50869.342909255436</v>
+      </c>
+      <c r="EM13" s="6">
         <f t="shared" si="70"/>
-        <v>102195.54903818191</v>
-      </c>
-      <c r="CB13" s="6">
+        <v>50360.64948016288</v>
+      </c>
+      <c r="EN13" s="6">
         <f t="shared" si="70"/>
-        <v>101173.59354780009</v>
-      </c>
-      <c r="CC13" s="6">
+        <v>49857.042985361251</v>
+      </c>
+      <c r="EO13" s="6">
         <f t="shared" si="70"/>
-        <v>100161.85761232208</v>
-      </c>
-      <c r="CD13" s="6">
+        <v>49358.472555507637</v>
+      </c>
+      <c r="EP13" s="6">
         <f t="shared" si="70"/>
-        <v>99160.239036198866</v>
-      </c>
-      <c r="CE13" s="6">
+        <v>48864.88782995256</v>
+      </c>
+      <c r="EQ13" s="6">
         <f t="shared" si="70"/>
-        <v>98168.636645836872</v>
-      </c>
-      <c r="CF13" s="6">
+        <v>48376.238951653031</v>
+      </c>
+      <c r="ER13" s="6">
         <f t="shared" si="70"/>
-        <v>97186.950279378507</v>
-      </c>
-      <c r="CG13" s="6">
+        <v>47892.4765621365</v>
+      </c>
+      <c r="ES13" s="6">
         <f t="shared" si="70"/>
-        <v>96215.080776584728</v>
-      </c>
-      <c r="CH13" s="6">
+        <v>47413.551796515138</v>
+      </c>
+      <c r="ET13" s="6">
         <f t="shared" si="70"/>
-        <v>95252.929968818877</v>
-      </c>
-      <c r="CI13" s="6">
+        <v>46939.416278549987</v>
+      </c>
+      <c r="EU13" s="6">
         <f t="shared" si="70"/>
-        <v>94300.400669130686</v>
-      </c>
-      <c r="CJ13" s="6">
+        <v>46470.022115764485</v>
+      </c>
+      <c r="EV13" s="6">
         <f t="shared" si="70"/>
-        <v>93357.39666243938</v>
-      </c>
-      <c r="CK13" s="6">
+        <v>46005.321894606837</v>
+      </c>
+      <c r="EW13" s="6">
         <f t="shared" si="70"/>
-        <v>92423.82269581499</v>
-      </c>
-      <c r="CL13" s="6">
+        <v>45545.268675660765</v>
+      </c>
+      <c r="EX13" s="6">
         <f t="shared" si="70"/>
-        <v>91499.584468856832</v>
-      </c>
-      <c r="CM13" s="6">
+        <v>45089.815988904156</v>
+      </c>
+      <c r="EY13" s="6">
         <f t="shared" si="70"/>
-        <v>90584.58862416826</v>
-      </c>
-      <c r="CN13" s="6">
+        <v>44638.917829015118</v>
+      </c>
+      <c r="EZ13" s="6">
         <f t="shared" si="70"/>
-        <v>89678.742737926572</v>
-      </c>
-      <c r="CO13" s="6">
+        <v>44192.528650724969</v>
+      </c>
+      <c r="FA13" s="6">
         <f t="shared" si="70"/>
-        <v>88781.955310547302</v>
-      </c>
-      <c r="CP13" s="6">
+        <v>43750.603364217721</v>
+      </c>
+      <c r="FB13" s="6">
         <f t="shared" si="70"/>
-        <v>87894.135757441822</v>
-      </c>
-      <c r="CQ13" s="6">
+        <v>43313.09733057554</v>
+      </c>
+      <c r="FC13" s="6">
         <f t="shared" si="70"/>
-        <v>87015.194399867396</v>
-      </c>
-      <c r="CR13" s="6">
+        <v>42879.966357269783</v>
+      </c>
+      <c r="FD13" s="6">
         <f t="shared" si="70"/>
-        <v>86145.042455868723</v>
-      </c>
-      <c r="CS13" s="6">
+        <v>42451.166693697087</v>
+      </c>
+      <c r="FE13" s="6">
         <f t="shared" si="70"/>
-        <v>85283.592031310036</v>
-      </c>
-      <c r="CT13" s="6">
+        <v>42026.655026760112</v>
+      </c>
+      <c r="FF13" s="6">
         <f t="shared" si="70"/>
-        <v>84430.756110996939</v>
-      </c>
-      <c r="CU13" s="6">
+        <v>41606.38847649251</v>
+      </c>
+      <c r="FG13" s="6">
         <f t="shared" si="70"/>
-        <v>83586.448549886976</v>
-      </c>
-      <c r="CV13" s="6">
+        <v>41190.324591727585</v>
+      </c>
+      <c r="FH13" s="6">
         <f t="shared" si="70"/>
-        <v>82750.584064388109</v>
-      </c>
-      <c r="CW13" s="6">
+        <v>40778.421345810311</v>
+      </c>
+      <c r="FI13" s="6">
         <f t="shared" si="70"/>
-        <v>81923.078223744233</v>
-      </c>
-      <c r="CX13" s="6">
-        <f t="shared" si="70"/>
-        <v>81103.84744150679</v>
-      </c>
-      <c r="CY13" s="6">
-        <f t="shared" si="70"/>
-        <v>80292.808967091725</v>
-      </c>
-      <c r="CZ13" s="6">
-        <f t="shared" si="70"/>
-        <v>79489.880877420801</v>
-      </c>
-      <c r="DA13" s="6">
-        <f t="shared" si="70"/>
-        <v>78694.982068646597</v>
-      </c>
-      <c r="DB13" s="6">
-        <f t="shared" si="70"/>
-        <v>77908.032247960131</v>
-      </c>
-      <c r="DC13" s="6">
-        <f t="shared" si="70"/>
-        <v>77128.951925480535</v>
-      </c>
-      <c r="DD13" s="6">
-        <f t="shared" si="70"/>
-        <v>76357.662406225732</v>
-      </c>
-      <c r="DE13" s="6">
-        <f t="shared" si="70"/>
-        <v>75594.085782163471</v>
-      </c>
-      <c r="DF13" s="6">
-        <f t="shared" si="70"/>
-        <v>74838.144924341832</v>
-      </c>
-      <c r="DG13" s="6">
-        <f t="shared" si="70"/>
-        <v>74089.763475098414</v>
-      </c>
-      <c r="DH13" s="6">
-        <f t="shared" si="70"/>
-        <v>73348.865840347426</v>
-      </c>
-      <c r="DI13" s="6">
-        <f t="shared" si="70"/>
-        <v>72615.377181943957</v>
-      </c>
-      <c r="DJ13" s="6">
-        <f t="shared" si="70"/>
-        <v>71889.223410124512</v>
-      </c>
-      <c r="DK13" s="6">
-        <f t="shared" si="70"/>
-        <v>71170.331176023261</v>
-      </c>
-      <c r="DL13" s="6">
-        <f t="shared" si="70"/>
-        <v>70458.62786426302</v>
-      </c>
-      <c r="DM13" s="6">
-        <f t="shared" si="70"/>
-        <v>69754.041585620391</v>
-      </c>
-      <c r="DN13" s="6">
-        <f t="shared" si="70"/>
-        <v>69056.501169764189</v>
-      </c>
-      <c r="DO13" s="6">
-        <f t="shared" si="70"/>
-        <v>68365.936158066543</v>
-      </c>
-      <c r="DP13" s="6">
-        <f t="shared" si="70"/>
-        <v>67682.276796485879</v>
-      </c>
-      <c r="DQ13" s="6">
-        <f t="shared" si="70"/>
-        <v>67005.454028521024</v>
-      </c>
-      <c r="DR13" s="6">
-        <f t="shared" si="70"/>
-        <v>66335.399488235809</v>
-      </c>
-      <c r="DS13" s="6">
-        <f t="shared" si="70"/>
-        <v>65672.045493353449</v>
-      </c>
-      <c r="DT13" s="6">
-        <f t="shared" ref="DT13:FI13" si="71">DS13*(1+$BI$18)</f>
-        <v>65015.325038419913</v>
-      </c>
-      <c r="DU13" s="6">
-        <f t="shared" si="71"/>
-        <v>64365.17178803571</v>
-      </c>
-      <c r="DV13" s="6">
-        <f t="shared" si="71"/>
-        <v>63721.520070155355</v>
-      </c>
-      <c r="DW13" s="6">
-        <f t="shared" si="71"/>
-        <v>63084.304869453801</v>
-      </c>
-      <c r="DX13" s="6">
-        <f t="shared" si="71"/>
-        <v>62453.461820759265</v>
-      </c>
-      <c r="DY13" s="6">
-        <f t="shared" si="71"/>
-        <v>61828.927202551669</v>
-      </c>
-      <c r="DZ13" s="6">
-        <f t="shared" si="71"/>
-        <v>61210.637930526151</v>
-      </c>
-      <c r="EA13" s="6">
-        <f t="shared" si="71"/>
-        <v>60598.531551220891</v>
-      </c>
-      <c r="EB13" s="6">
-        <f t="shared" si="71"/>
-        <v>59992.54623570868</v>
-      </c>
-      <c r="EC13" s="6">
-        <f t="shared" si="71"/>
-        <v>59392.620773351591</v>
-      </c>
-      <c r="ED13" s="6">
-        <f t="shared" si="71"/>
-        <v>58798.694565618076</v>
-      </c>
-      <c r="EE13" s="6">
-        <f t="shared" si="71"/>
-        <v>58210.707619961897</v>
-      </c>
-      <c r="EF13" s="6">
-        <f t="shared" si="71"/>
-        <v>57628.600543762281</v>
-      </c>
-      <c r="EG13" s="6">
-        <f t="shared" si="71"/>
-        <v>57052.314538324659</v>
-      </c>
-      <c r="EH13" s="6">
-        <f t="shared" si="71"/>
-        <v>56481.791392941414</v>
-      </c>
-      <c r="EI13" s="6">
-        <f t="shared" si="71"/>
-        <v>55916.973479011998</v>
-      </c>
-      <c r="EJ13" s="6">
-        <f t="shared" si="71"/>
-        <v>55357.803744221877</v>
-      </c>
-      <c r="EK13" s="6">
-        <f t="shared" si="71"/>
-        <v>54804.22570677966</v>
-      </c>
-      <c r="EL13" s="6">
-        <f t="shared" si="71"/>
-        <v>54256.183449711862</v>
-      </c>
-      <c r="EM13" s="6">
-        <f t="shared" si="71"/>
-        <v>53713.621615214739</v>
-      </c>
-      <c r="EN13" s="6">
-        <f t="shared" si="71"/>
-        <v>53176.485399062592</v>
-      </c>
-      <c r="EO13" s="6">
-        <f t="shared" si="71"/>
-        <v>52644.720545071963</v>
-      </c>
-      <c r="EP13" s="6">
-        <f t="shared" si="71"/>
-        <v>52118.273339621242</v>
-      </c>
-      <c r="EQ13" s="6">
-        <f t="shared" si="71"/>
-        <v>51597.090606225029</v>
-      </c>
-      <c r="ER13" s="6">
-        <f t="shared" si="71"/>
-        <v>51081.119700162781</v>
-      </c>
-      <c r="ES13" s="6">
-        <f t="shared" si="71"/>
-        <v>50570.308503161155</v>
-      </c>
-      <c r="ET13" s="6">
-        <f t="shared" si="71"/>
-        <v>50064.60541812954</v>
-      </c>
-      <c r="EU13" s="6">
-        <f t="shared" si="71"/>
-        <v>49563.959363948241</v>
-      </c>
-      <c r="EV13" s="6">
-        <f t="shared" si="71"/>
-        <v>49068.319770308757</v>
-      </c>
-      <c r="EW13" s="6">
-        <f t="shared" si="71"/>
-        <v>48577.636572605668</v>
-      </c>
-      <c r="EX13" s="6">
-        <f t="shared" si="71"/>
-        <v>48091.86020687961</v>
-      </c>
-      <c r="EY13" s="6">
-        <f t="shared" si="71"/>
-        <v>47610.941604810811</v>
-      </c>
-      <c r="EZ13" s="6">
-        <f t="shared" si="71"/>
-        <v>47134.832188762703</v>
-      </c>
-      <c r="FA13" s="6">
-        <f t="shared" si="71"/>
-        <v>46663.483866875074</v>
-      </c>
-      <c r="FB13" s="6">
-        <f t="shared" si="71"/>
-        <v>46196.849028206321</v>
-      </c>
-      <c r="FC13" s="6">
-        <f t="shared" si="71"/>
-        <v>45734.880537924255</v>
-      </c>
-      <c r="FD13" s="6">
-        <f t="shared" si="71"/>
-        <v>45277.531732545009</v>
-      </c>
-      <c r="FE13" s="6">
-        <f t="shared" si="71"/>
-        <v>44824.756415219555</v>
-      </c>
-      <c r="FF13" s="6">
-        <f t="shared" si="71"/>
-        <v>44376.50885106736</v>
-      </c>
-      <c r="FG13" s="6">
-        <f t="shared" si="71"/>
-        <v>43932.743762556689</v>
-      </c>
-      <c r="FH13" s="6">
-        <f t="shared" si="71"/>
-        <v>43493.416324931124</v>
-      </c>
-      <c r="FI13" s="6">
-        <f t="shared" si="71"/>
-        <v>43058.482161681815</v>
+        <v>40370.637132352211</v>
       </c>
     </row>
     <row r="14" spans="2:165">
@@ -4632,7 +4636,7 @@
       </c>
       <c r="P14" s="4">
         <f>Main!D4</f>
-        <v>2518</v>
+        <v>2517</v>
       </c>
       <c r="Q14" s="4">
         <v>2848.8</v>
@@ -4698,75 +4702,88 @@
         <v>2518</v>
       </c>
       <c r="AK14" s="4">
-        <v>2518</v>
+        <f>2517</f>
+        <v>2517</v>
       </c>
       <c r="AL14" s="4">
-        <v>2518</v>
+        <f>2517</f>
+        <v>2517</v>
       </c>
       <c r="AN14" s="4">
         <f>P14</f>
-        <v>2518</v>
+        <v>2517</v>
       </c>
       <c r="AO14" s="4">
         <f>AN14</f>
-        <v>2518</v>
+        <v>2517</v>
       </c>
       <c r="AP14" s="4">
         <f>AO14</f>
-        <v>2518</v>
+        <v>2517</v>
       </c>
       <c r="AQ14" s="4">
         <f>AP14</f>
-        <v>2518</v>
+        <v>2517</v>
       </c>
       <c r="AR14" s="4">
-        <f t="shared" ref="AR14" si="72">AQ14</f>
-        <v>2518</v>
+        <f t="shared" ref="AR14" si="71">AQ14</f>
+        <v>2517</v>
       </c>
       <c r="AS14" s="4">
-        <f t="shared" ref="AS14:AT14" si="73">2396+439.4</f>
+        <f t="shared" ref="AS14:AT14" si="72">2396+439.4</f>
         <v>2835.4</v>
       </c>
       <c r="AT14" s="4">
-        <f t="shared" si="73"/>
+        <f t="shared" si="72"/>
         <v>2835.4</v>
       </c>
       <c r="AU14" s="4">
-        <f t="shared" ref="AU14" si="74">2189.9+343.8</f>
+        <f t="shared" ref="AU14" si="73">2189.9+343.8</f>
         <v>2533.7000000000003</v>
       </c>
       <c r="AV14" s="4">
-        <v>2518</v>
+        <f>2517</f>
+        <v>2517</v>
       </c>
       <c r="AW14" s="4">
-        <v>2518</v>
+        <f>2517</f>
+        <v>2517</v>
       </c>
       <c r="AX14" s="4">
-        <v>2518</v>
+        <f>2517</f>
+        <v>2517</v>
       </c>
       <c r="AY14" s="4">
-        <v>2518</v>
+        <f>2517</f>
+        <v>2517</v>
       </c>
       <c r="AZ14" s="4">
-        <v>2518</v>
+        <f>2517</f>
+        <v>2517</v>
       </c>
       <c r="BA14" s="4">
-        <v>2518</v>
+        <f>2517</f>
+        <v>2517</v>
       </c>
       <c r="BB14" s="4">
-        <v>2518</v>
+        <f>2517</f>
+        <v>2517</v>
       </c>
       <c r="BC14" s="4">
-        <v>2518</v>
+        <f>2517</f>
+        <v>2517</v>
       </c>
       <c r="BD14" s="4">
-        <v>2518</v>
+        <f>2517</f>
+        <v>2517</v>
       </c>
       <c r="BE14" s="4">
-        <v>2518</v>
+        <f>2517</f>
+        <v>2517</v>
       </c>
       <c r="BF14" s="4">
-        <v>2518</v>
+        <f>2517</f>
+        <v>2517</v>
       </c>
     </row>
     <row r="15" spans="2:165" s="6" customFormat="1">
@@ -4774,224 +4791,224 @@
         <v>36</v>
       </c>
       <c r="C15" s="7">
-        <f t="shared" ref="C15:P15" si="75">C13/C14</f>
+        <f t="shared" ref="C15:P15" si="74">C13/C14</f>
         <v>1.0737854535242908</v>
       </c>
       <c r="D15" s="7">
+        <f t="shared" si="74"/>
+        <v>1.3654872226902555</v>
+      </c>
+      <c r="E15" s="7">
+        <f t="shared" si="74"/>
+        <v>1.6522746419545071</v>
+      </c>
+      <c r="F15" s="7">
+        <f t="shared" si="74"/>
+        <v>1.2454366750912664</v>
+      </c>
+      <c r="G15" s="7">
+        <f t="shared" si="74"/>
+        <v>1.7505616399887671</v>
+      </c>
+      <c r="H15" s="7">
+        <f t="shared" si="74"/>
+        <v>1.7923336141533277</v>
+      </c>
+      <c r="I15" s="7">
+        <f t="shared" si="74"/>
+        <v>1.8032153889356921</v>
+      </c>
+      <c r="J15" s="7">
+        <f t="shared" si="74"/>
+        <v>2.4157540016849199</v>
+      </c>
+      <c r="K15" s="7">
+        <f t="shared" si="74"/>
+        <v>0.85263970794720578</v>
+      </c>
+      <c r="L15" s="7">
+        <f t="shared" si="74"/>
+        <v>0.91126088177478226</v>
+      </c>
+      <c r="M15" s="7">
+        <f t="shared" si="74"/>
+        <v>2.1380932322381354</v>
+      </c>
+      <c r="N15" s="7">
+        <f t="shared" si="74"/>
+        <v>2.5796826734063463</v>
+      </c>
+      <c r="O15" s="7">
+        <f t="shared" si="74"/>
+        <v>1.7207245155855095</v>
+      </c>
+      <c r="P15" s="7">
+        <f t="shared" si="74"/>
+        <v>2.0572109654350417</v>
+      </c>
+      <c r="Q15" s="7">
+        <f t="shared" ref="Q15:R15" si="75">Q13/Q14</f>
+        <v>2.754142094917158</v>
+      </c>
+      <c r="R15" s="7">
         <f t="shared" si="75"/>
-        <v>1.3654872226902555</v>
-      </c>
-      <c r="E15" s="7">
-        <f t="shared" si="75"/>
-        <v>1.6522746419545071</v>
-      </c>
-      <c r="F15" s="7">
-        <f t="shared" si="75"/>
-        <v>1.2454366750912664</v>
-      </c>
-      <c r="G15" s="7">
-        <f t="shared" si="75"/>
-        <v>1.7505616399887671</v>
-      </c>
-      <c r="H15" s="7">
-        <f t="shared" si="75"/>
-        <v>1.7923336141533277</v>
-      </c>
-      <c r="I15" s="7">
-        <f t="shared" si="75"/>
-        <v>1.8032153889356921</v>
-      </c>
-      <c r="J15" s="7">
-        <f t="shared" si="75"/>
-        <v>2.4157540016849199</v>
-      </c>
-      <c r="K15" s="7">
-        <f t="shared" si="75"/>
-        <v>0.85263970794720578</v>
-      </c>
-      <c r="L15" s="7">
-        <f t="shared" si="75"/>
-        <v>0.91126088177478226</v>
-      </c>
-      <c r="M15" s="7">
-        <f t="shared" si="75"/>
-        <v>2.1380932322381354</v>
-      </c>
-      <c r="N15" s="7">
-        <f t="shared" si="75"/>
-        <v>2.5796826734063463</v>
-      </c>
-      <c r="O15" s="7">
-        <f t="shared" si="75"/>
-        <v>1.7207245155855095</v>
-      </c>
-      <c r="P15" s="7">
-        <f t="shared" si="75"/>
-        <v>2.0563939634630661</v>
-      </c>
-      <c r="Q15" s="7">
-        <f t="shared" ref="Q15:R15" si="76">Q13/Q14</f>
-        <v>2.754142094917158</v>
-      </c>
-      <c r="R15" s="7">
+        <v>3.9381493962370118</v>
+      </c>
+      <c r="S15" s="7">
+        <f t="shared" ref="S15:V15" si="76">S13/S14</f>
+        <v>3.3494392325597797</v>
+      </c>
+      <c r="T15" s="7">
+        <f t="shared" ref="T15:U15" si="77">T13/T14</f>
+        <v>3.667607621736062</v>
+      </c>
+      <c r="U15" s="7">
+        <f t="shared" si="77"/>
+        <v>3.2672352523098791</v>
+      </c>
+      <c r="V15" s="7">
         <f t="shared" si="76"/>
-        <v>3.9381493962370118</v>
-      </c>
-      <c r="S15" s="7">
-        <f t="shared" ref="S15:V15" si="77">S13/S14</f>
-        <v>3.3494392325597797</v>
-      </c>
-      <c r="T15" s="7">
-        <f t="shared" ref="T15:U15" si="78">T13/T14</f>
-        <v>3.667607621736062</v>
-      </c>
-      <c r="U15" s="7">
+        <v>3.7197106690777577</v>
+      </c>
+      <c r="W15" s="7">
+        <f t="shared" ref="W15:X15" si="78">W13/W14</f>
+        <v>2.7394495412844035</v>
+      </c>
+      <c r="X15" s="7">
         <f t="shared" si="78"/>
-        <v>3.2672352523098791</v>
-      </c>
-      <c r="V15" s="7">
-        <f t="shared" si="77"/>
-        <v>3.7197106690777577</v>
-      </c>
-      <c r="W15" s="7">
-        <f t="shared" ref="W15:X15" si="79">W13/W14</f>
-        <v>2.7394495412844035</v>
-      </c>
-      <c r="X15" s="7">
-        <f t="shared" si="79"/>
         <v>2.4730029585798818</v>
       </c>
       <c r="Y15" s="7">
-        <f t="shared" ref="Y15" si="80">Y13/Y14</f>
+        <f t="shared" ref="Y15" si="79">Y13/Y14</f>
         <v>1.638702460850112</v>
       </c>
       <c r="Z15" s="7">
-        <f t="shared" ref="Z15" si="81">Z13/Z14</f>
+        <f t="shared" ref="Z15" si="80">Z13/Z14</f>
         <v>1.7634571645185746</v>
       </c>
       <c r="AA15" s="7">
-        <f t="shared" ref="AA15:AC15" si="82">AA13/AA14</f>
+        <f t="shared" ref="AA15:AC15" si="81">AA13/AA14</f>
         <v>2.206803247004252</v>
       </c>
       <c r="AB15" s="7">
-        <f t="shared" si="82"/>
+        <f t="shared" si="81"/>
         <v>3.0327102803738319</v>
       </c>
       <c r="AC15" s="7">
-        <f t="shared" si="82"/>
+        <f t="shared" si="81"/>
         <v>4.6013198757763973</v>
       </c>
       <c r="AD15" s="7">
-        <f t="shared" ref="AD15" si="83">AD13/AD14</f>
+        <f t="shared" ref="AD15" si="82">AD13/AD14</f>
         <v>5.4625876851130162</v>
       </c>
       <c r="AE15" s="7">
-        <f t="shared" ref="AE15" si="84">AE13/AE14</f>
+        <f t="shared" ref="AE15" si="83">AE13/AE14</f>
         <v>4.8601178781925345</v>
       </c>
       <c r="AF15" s="7">
-        <f t="shared" ref="AF15:AH15" si="85">AF13/AF14</f>
+        <f t="shared" ref="AF15:AH15" si="84">AF13/AF14</f>
         <v>5.2907662082514735</v>
       </c>
       <c r="AG15" s="7">
+        <f t="shared" si="84"/>
+        <v>6.2142998613586853</v>
+      </c>
+      <c r="AH15" s="7">
+        <f t="shared" si="84"/>
+        <v>7.6125823893910081</v>
+      </c>
+      <c r="AI15" s="7">
+        <f t="shared" ref="AI15:AL15" si="85">AI13/AI14</f>
+        <v>6.5864661654135341</v>
+      </c>
+      <c r="AJ15" s="7">
         <f t="shared" si="85"/>
-        <v>6.2142998613586853</v>
-      </c>
-      <c r="AH15" s="7">
+        <v>7.2823669579030978</v>
+      </c>
+      <c r="AK15" s="7">
         <f t="shared" si="85"/>
-        <v>7.6125823893910081</v>
-      </c>
-      <c r="AI15" s="7">
-        <f t="shared" ref="AI15:AL15" si="86">AI13/AI14</f>
-        <v>6.5864661654135341</v>
-      </c>
-      <c r="AJ15" s="7">
-        <f t="shared" si="86"/>
-        <v>7.2823669579030978</v>
-      </c>
-      <c r="AK15" s="7">
-        <f t="shared" si="86"/>
-        <v>7.7270395901509126</v>
+        <v>7.4052443384982123</v>
       </c>
       <c r="AL15" s="7">
-        <f t="shared" si="86"/>
-        <v>8.7320891977760127</v>
+        <f t="shared" si="85"/>
+        <v>8.5242946364719892</v>
       </c>
       <c r="AN15" s="7">
         <f>AN13/AN14</f>
-        <v>6.0381254964257352</v>
+        <v>6.0405244338498214</v>
       </c>
       <c r="AO15" s="7">
         <f>AO13/AO14</f>
-        <v>8.7815726767275617</v>
+        <v>8.7850615812475166</v>
       </c>
       <c r="AP15" s="7">
         <f>AP13/AP14</f>
-        <v>7.3332009531374105</v>
+        <v>7.33611442193087</v>
       </c>
       <c r="AQ15" s="7">
         <f>AQ13/AQ14</f>
-        <v>11.574662430500398</v>
+        <v>11.579261025029798</v>
       </c>
       <c r="AR15" s="7">
-        <f t="shared" ref="AR15:BA15" si="87">AR13/AR14</f>
-        <v>15.635424940428912</v>
+        <f t="shared" ref="AR15:BA15" si="86">AR13/AR14</f>
+        <v>15.641636869288837</v>
       </c>
       <c r="AS15" s="7">
+        <f t="shared" si="86"/>
+        <v>8.1819143683430902</v>
+      </c>
+      <c r="AT15" s="7">
+        <f t="shared" si="86"/>
+        <v>13.884108062354517</v>
+      </c>
+      <c r="AU15" s="7">
+        <f t="shared" si="86"/>
+        <v>24.000473615660887</v>
+      </c>
+      <c r="AV15" s="7">
+        <f t="shared" si="86"/>
+        <v>29.778184187524836</v>
+      </c>
+      <c r="AW15" s="7">
+        <f t="shared" si="86"/>
+        <v>33.210010091760026</v>
+      </c>
+      <c r="AX15" s="7">
+        <f t="shared" si="86"/>
+        <v>36.478930837734168</v>
+      </c>
+      <c r="AY15" s="7">
+        <f t="shared" si="86"/>
+        <v>39.317929343733873</v>
+      </c>
+      <c r="AZ15" s="7">
+        <f t="shared" si="86"/>
+        <v>41.26705841714341</v>
+      </c>
+      <c r="BA15" s="7">
+        <f t="shared" si="86"/>
+        <v>42.572554867684794</v>
+      </c>
+      <c r="BB15" s="7">
+        <f t="shared" ref="BB15:BF15" si="87">BB13/BB14</f>
+        <v>43.43245669800519</v>
+      </c>
+      <c r="BC15" s="7">
         <f t="shared" si="87"/>
-        <v>8.1819143683430902</v>
-      </c>
-      <c r="AT15" s="7">
+        <v>44.301254564865516</v>
+      </c>
+      <c r="BD15" s="7">
         <f t="shared" si="87"/>
-        <v>13.884108062354517</v>
-      </c>
-      <c r="AU15" s="7">
+        <v>45.187282273861868</v>
+      </c>
+      <c r="BE15" s="7">
         <f t="shared" si="87"/>
-        <v>24.000473615660887</v>
-      </c>
-      <c r="AV15" s="7">
+        <v>46.091027965410603</v>
+      </c>
+      <c r="BF15" s="7">
         <f t="shared" si="87"/>
-        <v>30.30924793010325</v>
-      </c>
-      <c r="AW15" s="7">
-        <f t="shared" si="87"/>
-        <v>34.91272803225926</v>
-      </c>
-      <c r="AX15" s="7">
-        <f t="shared" si="87"/>
-        <v>38.723559932241791</v>
-      </c>
-      <c r="AY15" s="7">
-        <f t="shared" si="87"/>
-        <v>41.827843237144982</v>
-      </c>
-      <c r="AZ15" s="7">
-        <f t="shared" si="87"/>
-        <v>43.82914745182044</v>
-      </c>
-      <c r="BA15" s="7">
-        <f t="shared" si="87"/>
-        <v>45.224094102497382</v>
-      </c>
-      <c r="BB15" s="7">
-        <f t="shared" ref="BB15:BF15" si="88">BB13/BB14</f>
-        <v>46.171501044653702</v>
-      </c>
-      <c r="BC15" s="7">
-        <f t="shared" si="88"/>
-        <v>47.129826424151702</v>
-      </c>
-      <c r="BD15" s="7">
-        <f t="shared" si="88"/>
-        <v>48.107518387268726</v>
-      </c>
-      <c r="BE15" s="7">
-        <f t="shared" si="88"/>
-        <v>49.105112523749419</v>
-      </c>
-      <c r="BF15" s="7">
-        <f t="shared" si="88"/>
-        <v>50.123012934530792</v>
+        <v>47.012848525529662</v>
       </c>
     </row>
     <row r="17" spans="2:61">
@@ -5003,128 +5020,128 @@
         <v>0.48979083665338652</v>
       </c>
       <c r="H17" s="9">
-        <f t="shared" ref="H17:R17" si="89">H3/D3-1</f>
+        <f t="shared" ref="H17:R17" si="88">H3/D3-1</f>
         <v>0.41948288810213485</v>
       </c>
       <c r="I17" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="88"/>
         <v>0.32910534469403574</v>
       </c>
       <c r="J17" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="88"/>
         <v>0.30388529139685483</v>
       </c>
       <c r="K17" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="88"/>
         <v>0.25998662878154777</v>
       </c>
       <c r="L17" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="88"/>
         <v>0.27473358022825178</v>
       </c>
       <c r="M17" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="88"/>
         <v>0.2859328331026445</v>
       </c>
       <c r="N17" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="88"/>
         <v>0.2464230814709707</v>
       </c>
       <c r="O17" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="88"/>
         <v>0.17642767128739134</v>
       </c>
       <c r="P17" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="88"/>
         <v>0.10796869441479906</v>
       </c>
       <c r="Q17" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="88"/>
         <v>0.21629277135735325</v>
       </c>
       <c r="R17" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="88"/>
         <v>0.33156247035385644</v>
       </c>
       <c r="S17" s="9">
-        <f t="shared" ref="S17" si="90">S3/O3-1</f>
+        <f t="shared" ref="S17" si="89">S3/O3-1</f>
         <v>0.47550318543158365</v>
       </c>
       <c r="T17" s="9">
-        <f t="shared" ref="T17" si="91">T3/P3-1</f>
+        <f t="shared" ref="T17" si="90">T3/P3-1</f>
         <v>0.5560014983678494</v>
       </c>
       <c r="U17" s="9">
-        <f t="shared" ref="U17" si="92">U3/Q3-1</f>
+        <f t="shared" ref="U17" si="91">U3/Q3-1</f>
         <v>0.35118770377270603</v>
       </c>
       <c r="V17" s="9">
-        <f t="shared" ref="V17" si="93">V3/R3-1</f>
+        <f t="shared" ref="V17" si="92">V3/R3-1</f>
         <v>0.19945141065830718</v>
       </c>
       <c r="W17" s="9">
-        <f t="shared" ref="W17" si="94">W3/S3-1</f>
+        <f t="shared" ref="W17" si="93">W3/S3-1</f>
         <v>6.6371174200450911E-2</v>
       </c>
       <c r="X17" s="9">
-        <f t="shared" ref="X17" si="95">X3/T3-1</f>
+        <f t="shared" ref="X17" si="94">X3/T3-1</f>
         <v>-8.7698180692643568E-3</v>
       </c>
       <c r="Y17" s="9">
-        <f t="shared" ref="Y17" si="96">Y3/U3-1</f>
+        <f t="shared" ref="Y17" si="95">Y3/U3-1</f>
         <v>-4.4674250258531556E-2</v>
       </c>
       <c r="Z17" s="9">
-        <f t="shared" ref="Z17" si="97">Z3/V3-1</f>
+        <f t="shared" ref="Z17" si="96">Z3/V3-1</f>
         <v>-4.4726916337501144E-2</v>
       </c>
       <c r="AA17" s="9">
-        <f t="shared" ref="AA17" si="98">AA3/W3-1</f>
+        <f t="shared" ref="AA17" si="97">AA3/W3-1</f>
         <v>2.6408198366060009E-2</v>
       </c>
       <c r="AB17" s="9">
-        <f t="shared" ref="AB17" si="99">AB3/X3-1</f>
+        <f t="shared" ref="AB17" si="98">AB3/X3-1</f>
         <v>0.11022829782804799</v>
       </c>
       <c r="AC17" s="9">
-        <f t="shared" ref="AC17" si="100">AC3/Y3-1</f>
+        <f t="shared" ref="AC17" si="99">AC3/Y3-1</f>
         <v>0.24182723533232298</v>
       </c>
       <c r="AD17" s="9">
-        <f t="shared" ref="AD17" si="101">AD3/Z3-1</f>
+        <f t="shared" ref="AD17" si="100">AD3/Z3-1</f>
         <v>0.24703870666873939</v>
       </c>
       <c r="AE17" s="9">
-        <f t="shared" ref="AE17" si="102">AE3/AA3-1</f>
+        <f t="shared" ref="AE17" si="101">AE3/AA3-1</f>
         <v>0.27264793157619138</v>
       </c>
       <c r="AF17" s="9">
-        <f t="shared" ref="AF17" si="103">AF3/AB3-1</f>
+        <f t="shared" ref="AF17" si="102">AF3/AB3-1</f>
         <v>0.2210069064658271</v>
       </c>
       <c r="AG17" s="9">
-        <f t="shared" ref="AG17" si="104">AG3/AC3-1</f>
+        <f t="shared" ref="AG17" si="103">AG3/AC3-1</f>
         <v>0.17936424918642491</v>
       </c>
       <c r="AH17" s="9">
-        <f t="shared" ref="AH17" si="105">AH3/AD3-1</f>
+        <f t="shared" ref="AH17" si="104">AH3/AD3-1</f>
         <v>0.20627757971628724</v>
       </c>
       <c r="AI17" s="9">
-        <f t="shared" ref="AI17" si="106">AI3/AE3-1</f>
+        <f t="shared" ref="AI17" si="105">AI3/AE3-1</f>
         <v>0.16071869428062002</v>
       </c>
       <c r="AJ17" s="9">
-        <f t="shared" ref="AJ17" si="107">AJ3/AF3-1</f>
+        <f t="shared" ref="AJ17" si="106">AJ3/AF3-1</f>
         <v>0.21614496685521223</v>
       </c>
       <c r="AK17" s="9">
-        <f t="shared" ref="AK17" si="108">AK3/AG3-1</f>
-        <v>0.17999999999999994</v>
+        <f t="shared" ref="AK17" si="107">AK3/AG3-1</f>
+        <v>0.26246027248761972</v>
       </c>
       <c r="AL17" s="9">
-        <f t="shared" ref="AL17" si="109">AL3/AH3-1</f>
-        <v>0.10000000000000009</v>
+        <f t="shared" ref="AL17" si="108">AL3/AH3-1</f>
+        <v>0.19999999999999996</v>
       </c>
       <c r="AN17" s="9"/>
       <c r="AO17" s="9">
@@ -5132,70 +5149,71 @@
         <v>0.37352716896661997</v>
       </c>
       <c r="AP17" s="9">
-        <f t="shared" ref="AP17:BA17" si="110">AP3/AO3-1</f>
+        <f t="shared" ref="AP17:BA17" si="109">AP3/AO3-1</f>
         <v>0.26575092231097108</v>
       </c>
       <c r="AQ17" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="109"/>
         <v>0.21632214157363783</v>
       </c>
       <c r="AR17" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="109"/>
         <v>0.37180978526394148</v>
       </c>
       <c r="AS17" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="109"/>
         <v>-1.1193175554782941E-2</v>
       </c>
       <c r="AT17" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="109"/>
         <v>0.15918153830321846</v>
       </c>
       <c r="AU17" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="109"/>
         <v>0.21697701430040461</v>
       </c>
-      <c r="AV17" s="9" t="s">
-        <v>158</v>
+      <c r="AV17" s="9">
+        <f t="shared" si="109"/>
+        <v>0.21054103343465047</v>
       </c>
       <c r="AW17" s="9">
-        <f t="shared" si="110"/>
-        <v>0.12000000000000011</v>
+        <f t="shared" si="109"/>
+        <v>0.1399999999999999</v>
       </c>
       <c r="AX17" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="109"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="AY17" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="109"/>
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="AZ17" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="109"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="BA17" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="109"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="BB17" s="9">
-        <f t="shared" ref="BB17" si="111">BB3/BA3-1</f>
+        <f t="shared" ref="BB17" si="110">BB3/BA3-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BC17" s="9">
-        <f t="shared" ref="BC17" si="112">BC3/BB3-1</f>
+        <f t="shared" ref="BC17" si="111">BC3/BB3-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BD17" s="9">
-        <f t="shared" ref="BD17" si="113">BD3/BC3-1</f>
+        <f t="shared" ref="BD17" si="112">BD3/BC3-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BE17" s="9">
-        <f t="shared" ref="BE17" si="114">BE3/BD3-1</f>
+        <f t="shared" ref="BE17" si="113">BE3/BD3-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BF17" s="9">
-        <f t="shared" ref="BF17" si="115">BF3/BE3-1</f>
+        <f t="shared" ref="BF17" si="114">BF3/BE3-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
@@ -5208,219 +5226,219 @@
         <v>0.85570219123505975</v>
       </c>
       <c r="D18" s="9">
-        <f t="shared" ref="D18:R18" si="116">D5/D3</f>
+        <f t="shared" ref="D18:R18" si="115">D5/D3</f>
         <v>0.86728891749812254</v>
       </c>
       <c r="E18" s="9">
+        <f t="shared" si="115"/>
+        <v>0.85979860573199074</v>
+      </c>
+      <c r="F18" s="9">
+        <f t="shared" si="115"/>
+        <v>0.87580943570767811</v>
+      </c>
+      <c r="G18" s="9">
+        <f t="shared" si="115"/>
+        <v>0.8389603877653351</v>
+      </c>
+      <c r="H18" s="9">
+        <f t="shared" si="115"/>
+        <v>0.83266570931902351</v>
+      </c>
+      <c r="I18" s="9">
+        <f t="shared" si="115"/>
+        <v>0.82385080498288044</v>
+      </c>
+      <c r="J18" s="9">
+        <f t="shared" si="115"/>
+        <v>0.83469315360056762</v>
+      </c>
+      <c r="K18" s="9">
+        <f t="shared" si="115"/>
+        <v>0.81322544272733299</v>
+      </c>
+      <c r="L18" s="9">
+        <f t="shared" si="115"/>
+        <v>0.80392505632633704</v>
+      </c>
+      <c r="M18" s="9">
+        <f t="shared" si="115"/>
+        <v>0.82126671198731027</v>
+      </c>
+      <c r="N18" s="9">
+        <f t="shared" si="115"/>
+        <v>0.83436106631249407</v>
+      </c>
+      <c r="O18" s="9">
+        <f t="shared" si="115"/>
+        <v>0.80498393189378137</v>
+      </c>
+      <c r="P18" s="9">
+        <f t="shared" si="115"/>
+        <v>0.7950981966072671</v>
+      </c>
+      <c r="Q18" s="9">
+        <f t="shared" si="115"/>
+        <v>0.80465766185374943</v>
+      </c>
+      <c r="R18" s="9">
+        <f t="shared" si="115"/>
+        <v>0.81440581362211462</v>
+      </c>
+      <c r="S18" s="9">
+        <f t="shared" ref="S18:V18" si="116">S5/S3</f>
+        <v>0.80394329601467274</v>
+      </c>
+      <c r="T18" s="9">
         <f t="shared" si="116"/>
-        <v>0.85979860573199074</v>
-      </c>
-      <c r="F18" s="9">
+        <v>0.81432059703545756</v>
+      </c>
+      <c r="U18" s="9">
         <f t="shared" si="116"/>
-        <v>0.87580943570767811</v>
-      </c>
-      <c r="G18" s="9">
+        <v>0.80106859703550504</v>
+      </c>
+      <c r="V18" s="9">
         <f t="shared" si="116"/>
-        <v>0.8389603877653351</v>
-      </c>
-      <c r="H18" s="9">
-        <f t="shared" si="116"/>
-        <v>0.83266570931902351</v>
-      </c>
-      <c r="I18" s="9">
-        <f t="shared" si="116"/>
-        <v>0.82385080498288044</v>
-      </c>
-      <c r="J18" s="9">
-        <f t="shared" si="116"/>
-        <v>0.83469315360056762</v>
-      </c>
-      <c r="K18" s="9">
-        <f t="shared" si="116"/>
-        <v>0.81322544272733299</v>
-      </c>
-      <c r="L18" s="9">
-        <f t="shared" si="116"/>
-        <v>0.80392505632633704</v>
-      </c>
-      <c r="M18" s="9">
-        <f t="shared" si="116"/>
-        <v>0.82126671198731027</v>
-      </c>
-      <c r="N18" s="9">
-        <f t="shared" si="116"/>
-        <v>0.83436106631249407</v>
-      </c>
-      <c r="O18" s="9">
-        <f t="shared" si="116"/>
-        <v>0.80498393189378137</v>
-      </c>
-      <c r="P18" s="9">
-        <f t="shared" si="116"/>
-        <v>0.7950981966072671</v>
-      </c>
-      <c r="Q18" s="9">
-        <f t="shared" si="116"/>
-        <v>0.80465766185374943</v>
-      </c>
-      <c r="R18" s="9">
-        <f t="shared" si="116"/>
-        <v>0.81440581362211462</v>
-      </c>
-      <c r="S18" s="9">
-        <f t="shared" ref="S18:V18" si="117">S5/S3</f>
-        <v>0.80394329601467274</v>
-      </c>
-      <c r="T18" s="9">
+        <v>0.81146981081642955</v>
+      </c>
+      <c r="W18" s="9">
+        <f t="shared" ref="W18:AE18" si="117">W5/W3</f>
+        <v>0.78482872294682526</v>
+      </c>
+      <c r="X18" s="9">
         <f t="shared" si="117"/>
-        <v>0.81432059703545756</v>
-      </c>
-      <c r="U18" s="9">
+        <v>0.81985982929706469</v>
+      </c>
+      <c r="Y18" s="9">
         <f t="shared" si="117"/>
-        <v>0.80106859703550504</v>
-      </c>
-      <c r="V18" s="9">
+        <v>0.79375045103557773</v>
+      </c>
+      <c r="Z18" s="9">
         <f t="shared" si="117"/>
-        <v>0.81146981081642955</v>
-      </c>
-      <c r="W18" s="9">
-        <f t="shared" ref="W18:AE18" si="118">W5/W3</f>
-        <v>0.78482872294682526</v>
-      </c>
-      <c r="X18" s="9">
+        <v>0.74083631276231932</v>
+      </c>
+      <c r="AA18" s="9">
+        <f t="shared" si="117"/>
+        <v>0.7867690696456624</v>
+      </c>
+      <c r="AB18" s="9">
+        <f t="shared" si="117"/>
+        <v>0.81421294415450485</v>
+      </c>
+      <c r="AC18" s="9">
+        <f t="shared" si="117"/>
+        <v>0.81956066945606698</v>
+      </c>
+      <c r="AD18" s="9">
+        <f t="shared" si="117"/>
+        <v>0.80815736331679588</v>
+      </c>
+      <c r="AE18" s="9">
+        <f t="shared" si="117"/>
+        <v>0.81785763269784661</v>
+      </c>
+      <c r="AF18" s="9">
+        <f t="shared" ref="AF18:AH18" si="118">AF5/AF3</f>
+        <v>0.81295590079598679</v>
+      </c>
+      <c r="AG18" s="9">
         <f t="shared" si="118"/>
-        <v>0.81985982929706469</v>
-      </c>
-      <c r="Y18" s="9">
+        <v>0.81830052477272164</v>
+      </c>
+      <c r="AH18" s="9">
         <f t="shared" si="118"/>
-        <v>0.79375045103557773</v>
-      </c>
-      <c r="Z18" s="9">
-        <f t="shared" si="118"/>
-        <v>0.74083631276231932</v>
-      </c>
-      <c r="AA18" s="9">
-        <f t="shared" si="118"/>
-        <v>0.7867690696456624</v>
-      </c>
-      <c r="AB18" s="9">
-        <f t="shared" si="118"/>
-        <v>0.81421294415450485</v>
-      </c>
-      <c r="AC18" s="9">
-        <f t="shared" si="118"/>
-        <v>0.81956066945606698</v>
-      </c>
-      <c r="AD18" s="9">
-        <f t="shared" si="118"/>
-        <v>0.80815736331679588</v>
-      </c>
-      <c r="AE18" s="9">
-        <f t="shared" si="118"/>
-        <v>0.81785763269784661</v>
-      </c>
-      <c r="AF18" s="9">
-        <f t="shared" ref="AF18:AH18" si="119">AF5/AF3</f>
-        <v>0.81295590079598679</v>
-      </c>
-      <c r="AG18" s="9">
+        <v>0.81731941717474421</v>
+      </c>
+      <c r="AI18" s="9">
+        <f t="shared" ref="AI18:AL18" si="119">AI5/AI3</f>
+        <v>0.82105213404546962</v>
+      </c>
+      <c r="AJ18" s="9">
         <f t="shared" si="119"/>
-        <v>0.81830052477272164</v>
-      </c>
-      <c r="AH18" s="9">
+        <v>0.82130229817324696</v>
+      </c>
+      <c r="AK18" s="9">
         <f t="shared" si="119"/>
-        <v>0.81731941717474421</v>
-      </c>
-      <c r="AI18" s="9">
-        <f t="shared" ref="AI18:AL18" si="120">AI5/AI3</f>
-        <v>0.82105213404546962</v>
-      </c>
-      <c r="AJ18" s="9">
-        <f t="shared" si="120"/>
-        <v>0.82130229817324696</v>
-      </c>
-      <c r="AK18" s="9">
-        <f t="shared" si="120"/>
+        <v>0.82034268763904605</v>
+      </c>
+      <c r="AL18" s="9">
+        <f t="shared" si="119"/>
         <v>0.82</v>
       </c>
-      <c r="AL18" s="9">
-        <f t="shared" si="120"/>
+      <c r="AN18" s="9">
+        <f t="shared" ref="AN18" si="120">AN5/AN3</f>
+        <v>0.86581556096721024</v>
+      </c>
+      <c r="AO18" s="9">
+        <f t="shared" ref="AO18:BA18" si="121">AO5/AO3</f>
+        <v>0.8324617643898421</v>
+      </c>
+      <c r="AP18" s="9">
+        <f t="shared" si="121"/>
+        <v>0.81931887318363827</v>
+      </c>
+      <c r="AQ18" s="9">
+        <f t="shared" si="121"/>
+        <v>0.80583021194425708</v>
+      </c>
+      <c r="AR18" s="9">
+        <f t="shared" si="121"/>
+        <v>0.80794376277251567</v>
+      </c>
+      <c r="AS18" s="9">
+        <f t="shared" si="121"/>
+        <v>0.78347297378418479</v>
+      </c>
+      <c r="AT18" s="9">
+        <f t="shared" si="121"/>
+        <v>0.80796176694705224</v>
+      </c>
+      <c r="AU18" s="9">
+        <f t="shared" si="121"/>
+        <v>0.81664437689969605</v>
+      </c>
+      <c r="AV18" s="9">
+        <f t="shared" si="121"/>
+        <v>0.82000000000000006</v>
+      </c>
+      <c r="AW18" s="9">
+        <f t="shared" si="121"/>
         <v>0.82</v>
       </c>
-      <c r="AN18" s="9">
-        <f t="shared" ref="AN18" si="121">AN5/AN3</f>
-        <v>0.86581556096721024</v>
-      </c>
-      <c r="AO18" s="9">
-        <f t="shared" ref="AO18:BA18" si="122">AO5/AO3</f>
-        <v>0.8324617643898421</v>
-      </c>
-      <c r="AP18" s="9">
-        <f t="shared" si="122"/>
-        <v>0.81931887318363827</v>
-      </c>
-      <c r="AQ18" s="9">
-        <f t="shared" si="122"/>
-        <v>0.80583021194425708</v>
-      </c>
-      <c r="AR18" s="9">
-        <f t="shared" si="122"/>
-        <v>0.80794376277251567</v>
-      </c>
-      <c r="AS18" s="9">
-        <f t="shared" si="122"/>
-        <v>0.78347297378418479</v>
-      </c>
-      <c r="AT18" s="9">
-        <f t="shared" si="122"/>
-        <v>0.80796176694705224</v>
-      </c>
-      <c r="AU18" s="9">
-        <f t="shared" si="122"/>
-        <v>0.81664437689969605</v>
-      </c>
-      <c r="AV18" s="9">
+      <c r="AX18" s="9">
+        <f t="shared" si="121"/>
+        <v>0.82</v>
+      </c>
+      <c r="AY18" s="9">
+        <f t="shared" si="121"/>
+        <v>0.82</v>
+      </c>
+      <c r="AZ18" s="9">
+        <f t="shared" si="121"/>
+        <v>0.82</v>
+      </c>
+      <c r="BA18" s="9">
+        <f t="shared" si="121"/>
+        <v>0.82</v>
+      </c>
+      <c r="BB18" s="9">
+        <f t="shared" ref="BB18:BF18" si="122">BB5/BB3</f>
+        <v>0.82</v>
+      </c>
+      <c r="BC18" s="9">
         <f t="shared" si="122"/>
         <v>0.82</v>
       </c>
-      <c r="AW18" s="9">
+      <c r="BD18" s="9">
         <f t="shared" si="122"/>
         <v>0.82</v>
       </c>
-      <c r="AX18" s="9">
+      <c r="BE18" s="9">
         <f t="shared" si="122"/>
         <v>0.82</v>
       </c>
-      <c r="AY18" s="9">
+      <c r="BF18" s="9">
         <f t="shared" si="122"/>
-        <v>0.82</v>
-      </c>
-      <c r="AZ18" s="9">
-        <f t="shared" si="122"/>
-        <v>0.82</v>
-      </c>
-      <c r="BA18" s="9">
-        <f t="shared" si="122"/>
-        <v>0.82</v>
-      </c>
-      <c r="BB18" s="9">
-        <f t="shared" ref="BB18:BF18" si="123">BB5/BB3</f>
-        <v>0.82</v>
-      </c>
-      <c r="BC18" s="9">
-        <f t="shared" si="123"/>
-        <v>0.82</v>
-      </c>
-      <c r="BD18" s="9">
-        <f t="shared" si="123"/>
-        <v>0.82</v>
-      </c>
-      <c r="BE18" s="9">
-        <f t="shared" si="123"/>
-        <v>0.82</v>
-      </c>
-      <c r="BF18" s="9">
-        <f t="shared" si="123"/>
         <v>0.82</v>
       </c>
       <c r="BH18" t="s">
@@ -5439,220 +5457,220 @@
         <v>0.41421812749003983</v>
       </c>
       <c r="D19" s="9">
-        <f t="shared" ref="D19:R19" si="124">D9/D3</f>
+        <f t="shared" ref="D19:R19" si="123">D9/D3</f>
         <v>0.47215963952365625</v>
       </c>
       <c r="E19" s="9">
+        <f t="shared" si="123"/>
+        <v>0.49593338497288925</v>
+      </c>
+      <c r="F19" s="9">
+        <f t="shared" si="123"/>
+        <v>0.56675917360468697</v>
+      </c>
+      <c r="G19" s="9">
+        <f t="shared" si="123"/>
+        <v>0.45537355841551064</v>
+      </c>
+      <c r="H19" s="9">
+        <f t="shared" si="123"/>
+        <v>0.44312599198851182</v>
+      </c>
+      <c r="I19" s="9">
+        <f t="shared" si="123"/>
+        <v>0.42114081736723247</v>
+      </c>
+      <c r="J19" s="9">
+        <f t="shared" si="123"/>
+        <v>0.46233889085964291</v>
+      </c>
+      <c r="K19" s="9">
+        <f t="shared" si="123"/>
+        <v>0.22000397957153281</v>
+      </c>
+      <c r="L19" s="9">
+        <f t="shared" si="123"/>
+        <v>0.27309379817384088</v>
+      </c>
+      <c r="M19" s="9">
+        <f t="shared" si="123"/>
+        <v>0.40703602991162474</v>
+      </c>
+      <c r="N19" s="9">
+        <f t="shared" si="123"/>
+        <v>0.42016886443411439</v>
+      </c>
+      <c r="O19" s="9">
+        <f t="shared" si="123"/>
+        <v>0.33224333314540228</v>
+      </c>
+      <c r="P19" s="9">
+        <f t="shared" si="123"/>
+        <v>0.31909883876491679</v>
+      </c>
+      <c r="Q19" s="9">
+        <f t="shared" si="123"/>
+        <v>0.37447601304145317</v>
+      </c>
+      <c r="R19" s="9">
+        <f t="shared" si="123"/>
+        <v>0.45507979481333716</v>
+      </c>
+      <c r="S19" s="9">
+        <f t="shared" ref="S19:V19" si="124">S9/S3</f>
+        <v>0.43475602766420846</v>
+      </c>
+      <c r="T19" s="9">
         <f t="shared" si="124"/>
-        <v>0.49593338497288925</v>
-      </c>
-      <c r="F19" s="9">
+        <v>0.42531898063761736</v>
+      </c>
+      <c r="U19" s="9">
         <f t="shared" si="124"/>
-        <v>0.56675917360468697</v>
-      </c>
-      <c r="G19" s="9">
+        <v>0.35928990003447087</v>
+      </c>
+      <c r="V19" s="9">
         <f t="shared" si="124"/>
-        <v>0.45537355841551064</v>
-      </c>
-      <c r="H19" s="9">
-        <f t="shared" si="124"/>
-        <v>0.44312599198851182</v>
-      </c>
-      <c r="I19" s="9">
-        <f t="shared" si="124"/>
-        <v>0.42114081736723247</v>
-      </c>
-      <c r="J19" s="9">
-        <f t="shared" si="124"/>
-        <v>0.46233889085964291</v>
-      </c>
-      <c r="K19" s="9">
-        <f t="shared" si="124"/>
-        <v>0.22000397957153281</v>
-      </c>
-      <c r="L19" s="9">
-        <f t="shared" si="124"/>
-        <v>0.27309379817384088</v>
-      </c>
-      <c r="M19" s="9">
-        <f t="shared" si="124"/>
-        <v>0.40703602991162474</v>
-      </c>
-      <c r="N19" s="9">
-        <f t="shared" si="124"/>
-        <v>0.42016886443411439</v>
-      </c>
-      <c r="O19" s="9">
-        <f t="shared" si="124"/>
-        <v>0.33224333314540228</v>
-      </c>
-      <c r="P19" s="9">
-        <f t="shared" si="124"/>
-        <v>0.31909883876491679</v>
-      </c>
-      <c r="Q19" s="9">
-        <f t="shared" si="124"/>
-        <v>0.37447601304145317</v>
-      </c>
-      <c r="R19" s="9">
-        <f t="shared" si="124"/>
-        <v>0.45507979481333716</v>
-      </c>
-      <c r="S19" s="9">
-        <f t="shared" ref="S19:V19" si="125">S9/S3</f>
-        <v>0.43475602766420846</v>
-      </c>
-      <c r="T19" s="9">
+        <v>0.37376377297971547</v>
+      </c>
+      <c r="W19" s="9">
+        <f t="shared" ref="W19:AE19" si="125">W9/W3</f>
+        <v>0.30543213415508097</v>
+      </c>
+      <c r="X19" s="9">
         <f t="shared" si="125"/>
-        <v>0.42531898063761736</v>
-      </c>
-      <c r="U19" s="9">
+        <v>0.28998681562695161</v>
+      </c>
+      <c r="Y19" s="9">
         <f t="shared" si="125"/>
-        <v>0.35928990003447087</v>
-      </c>
-      <c r="V19" s="9">
+        <v>0.20437324096124701</v>
+      </c>
+      <c r="Z19" s="9">
         <f t="shared" si="125"/>
-        <v>0.37376377297971547</v>
-      </c>
-      <c r="W19" s="9">
-        <f t="shared" ref="W19:AE19" si="126">W9/W3</f>
-        <v>0.30543213415508097</v>
-      </c>
-      <c r="X19" s="9">
+        <v>0.19894295041193844</v>
+      </c>
+      <c r="AA19" s="9">
+        <f t="shared" si="125"/>
+        <v>0.25229533950078548</v>
+      </c>
+      <c r="AB19" s="9">
+        <f t="shared" si="125"/>
+        <v>0.29350917216163003</v>
+      </c>
+      <c r="AC19" s="9">
+        <f t="shared" si="125"/>
+        <v>0.40731055323105531</v>
+      </c>
+      <c r="AD19" s="9">
+        <f t="shared" si="125"/>
+        <v>0.4084665054473835</v>
+      </c>
+      <c r="AE19" s="9">
+        <f t="shared" si="125"/>
+        <v>0.37904265532848719</v>
+      </c>
+      <c r="AF19" s="9">
+        <f t="shared" ref="AF19:AH19" si="126">AF9/AF3</f>
+        <v>0.38000051188861306</v>
+      </c>
+      <c r="AG19" s="9">
         <f t="shared" si="126"/>
-        <v>0.28998681562695161</v>
-      </c>
-      <c r="Y19" s="9">
+        <v>0.4274557146024785</v>
+      </c>
+      <c r="AH19" s="9">
         <f t="shared" si="126"/>
-        <v>0.20437324096124701</v>
-      </c>
-      <c r="Z19" s="9">
-        <f t="shared" si="126"/>
-        <v>0.19894295041193844</v>
-      </c>
-      <c r="AA19" s="9">
-        <f t="shared" si="126"/>
-        <v>0.25229533950078548</v>
-      </c>
-      <c r="AB19" s="9">
-        <f t="shared" si="126"/>
-        <v>0.29350917216163003</v>
-      </c>
-      <c r="AC19" s="9">
-        <f t="shared" si="126"/>
-        <v>0.40731055323105531</v>
-      </c>
-      <c r="AD19" s="9">
-        <f t="shared" si="126"/>
-        <v>0.4084665054473835</v>
-      </c>
-      <c r="AE19" s="9">
-        <f t="shared" si="126"/>
-        <v>0.37904265532848719</v>
-      </c>
-      <c r="AF19" s="9">
-        <f t="shared" ref="AF19:AH19" si="127">AF9/AF3</f>
-        <v>0.38000051188861306</v>
-      </c>
-      <c r="AG19" s="9">
+        <v>0.45086287072439807</v>
+      </c>
+      <c r="AI19" s="9">
+        <f t="shared" ref="AI19:AL19" si="127">AI9/AI3</f>
+        <v>0.41487450961856598</v>
+      </c>
+      <c r="AJ19" s="9">
         <f t="shared" si="127"/>
-        <v>0.4274557146024785</v>
-      </c>
-      <c r="AH19" s="9">
+        <v>0.43019193534809325</v>
+      </c>
+      <c r="AK19" s="9">
         <f t="shared" si="127"/>
-        <v>0.45086287072439807</v>
-      </c>
-      <c r="AI19" s="9">
-        <f t="shared" ref="AI19:AL19" si="128">AI9/AI3</f>
-        <v>0.41487450961856598</v>
-      </c>
-      <c r="AJ19" s="9">
-        <f t="shared" si="128"/>
-        <v>0.43019193534809325</v>
-      </c>
-      <c r="AK19" s="9">
-        <f t="shared" si="128"/>
-        <v>0.45157993670323132</v>
+        <v>0.4007454822216151</v>
       </c>
       <c r="AL19" s="9">
-        <f t="shared" si="128"/>
-        <v>0.46584539723994101</v>
+        <f t="shared" si="127"/>
+        <v>0.41661775343598217</v>
       </c>
       <c r="AN19" s="9">
-        <f t="shared" ref="AN19" si="129">AN9/AN3</f>
+        <f t="shared" ref="AN19" si="128">AN9/AN3</f>
         <v>0.49693749538779425</v>
       </c>
       <c r="AO19" s="9">
-        <f t="shared" ref="AO19:BA19" si="130">AO9/AO3</f>
+        <f t="shared" ref="AO19:BA19" si="129">AO9/AO3</f>
         <v>0.44616569361366809</v>
       </c>
       <c r="AP19" s="9">
+        <f t="shared" si="129"/>
+        <v>0.33909192523734738</v>
+      </c>
+      <c r="AQ19" s="9">
+        <f t="shared" si="129"/>
+        <v>0.38004559942302774</v>
+      </c>
+      <c r="AR19" s="9">
+        <f t="shared" si="129"/>
+        <v>0.39645040660058173</v>
+      </c>
+      <c r="AS19" s="9">
+        <f t="shared" si="129"/>
+        <v>0.24822269293107735</v>
+      </c>
+      <c r="AT19" s="9">
+        <f t="shared" si="129"/>
+        <v>0.34786307713932724</v>
+      </c>
+      <c r="AU19" s="9">
+        <f t="shared" si="129"/>
+        <v>0.41234042553191491</v>
+      </c>
+      <c r="AV19" s="9">
+        <f t="shared" si="129"/>
+        <v>0.41477949521427787</v>
+      </c>
+      <c r="AW19" s="9">
+        <f t="shared" si="129"/>
+        <v>0.41182329486677305</v>
+      </c>
+      <c r="AX19" s="9">
+        <f t="shared" si="129"/>
+        <v>0.41874885894813435</v>
+      </c>
+      <c r="AY19" s="9">
+        <f t="shared" si="129"/>
+        <v>0.42565827850367777</v>
+      </c>
+      <c r="AZ19" s="9">
+        <f t="shared" si="129"/>
+        <v>0.42938465097549816</v>
+      </c>
+      <c r="BA19" s="9">
+        <f t="shared" si="129"/>
+        <v>0.42993884287135758</v>
+      </c>
+      <c r="BB19" s="9">
+        <f t="shared" ref="BB19:BF19" si="130">BB9/BB3</f>
+        <v>0.42993884287135764</v>
+      </c>
+      <c r="BC19" s="9">
         <f t="shared" si="130"/>
-        <v>0.33909192523734738</v>
-      </c>
-      <c r="AQ19" s="9">
+        <v>0.4299388428713577</v>
+      </c>
+      <c r="BD19" s="9">
         <f t="shared" si="130"/>
-        <v>0.38004559942302774</v>
-      </c>
-      <c r="AR19" s="9">
+        <v>0.4299388428713577</v>
+      </c>
+      <c r="BE19" s="9">
         <f t="shared" si="130"/>
-        <v>0.39645040660058173</v>
-      </c>
-      <c r="AS19" s="9">
+        <v>0.42993884287135764</v>
+      </c>
+      <c r="BF19" s="9">
         <f t="shared" si="130"/>
-        <v>0.24822269293107735</v>
-      </c>
-      <c r="AT19" s="9">
-        <f t="shared" si="130"/>
-        <v>0.34786307713932724</v>
-      </c>
-      <c r="AU19" s="9">
-        <f t="shared" si="130"/>
-        <v>0.41234042553191491</v>
-      </c>
-      <c r="AV19" s="9">
-        <f t="shared" si="130"/>
-        <v>0.44154284411316724</v>
-      </c>
-      <c r="AW19" s="9">
-        <f t="shared" si="130"/>
-        <v>0.45997642973539232</v>
-      </c>
-      <c r="AX19" s="9">
-        <f t="shared" si="130"/>
-        <v>0.47211046226022496</v>
-      </c>
-      <c r="AY19" s="9">
-        <f t="shared" si="130"/>
-        <v>0.48088362902795762</v>
-      </c>
-      <c r="AZ19" s="9">
-        <f t="shared" si="130"/>
-        <v>0.48426410152462224</v>
-      </c>
-      <c r="BA19" s="9">
-        <f t="shared" si="130"/>
-        <v>0.48499437874986384</v>
-      </c>
-      <c r="BB19" s="9">
-        <f t="shared" ref="BB19:BF19" si="131">BB9/BB3</f>
-        <v>0.48535593757216483</v>
-      </c>
-      <c r="BC19" s="9">
-        <f t="shared" si="131"/>
-        <v>0.48571395170012943</v>
-      </c>
-      <c r="BD19" s="9">
-        <f t="shared" si="131"/>
-        <v>0.48606845588566322</v>
-      </c>
-      <c r="BE19" s="9">
-        <f t="shared" si="131"/>
-        <v>0.4864194845399662</v>
-      </c>
-      <c r="BF19" s="9">
-        <f t="shared" si="131"/>
-        <v>0.48676707173687411</v>
+        <v>0.42993884287135758</v>
       </c>
       <c r="BH19" t="s">
         <v>44</v>
@@ -5670,204 +5688,204 @@
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
       <c r="G20" s="9">
-        <f t="shared" ref="G20:R20" si="132">G6/C6-1</f>
+        <f t="shared" ref="G20:R20" si="131">G6/C6-1</f>
         <v>0.22028353326063255</v>
       </c>
       <c r="H20" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="131"/>
         <v>0.31474726420010413</v>
       </c>
       <c r="I20" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="131"/>
         <v>0.29483430799220267</v>
       </c>
       <c r="J20" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="131"/>
         <v>0.46485377116469984</v>
       </c>
       <c r="K20" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="131"/>
         <v>0.27792672028596965</v>
       </c>
       <c r="L20" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="131"/>
         <v>0.31391200951248521</v>
       </c>
       <c r="M20" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="131"/>
         <v>0.33534060971019941</v>
       </c>
       <c r="N20" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="131"/>
         <v>0.35796847635726792</v>
       </c>
       <c r="O20" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="131"/>
         <v>0.40384615384615374</v>
       </c>
       <c r="P20" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="131"/>
         <v>0.34600301659125199</v>
       </c>
       <c r="Q20" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="131"/>
         <v>0.34244644870349483</v>
       </c>
       <c r="R20" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="131"/>
         <v>0.34330668042300738</v>
       </c>
       <c r="S20" s="9">
-        <f t="shared" ref="S20" si="133">S6/O6-1</f>
+        <f t="shared" ref="S20" si="132">S6/O6-1</f>
         <v>0.29439601494396017</v>
       </c>
       <c r="T20" s="9">
-        <f t="shared" ref="T20" si="134">T6/P6-1</f>
+        <f t="shared" ref="T20" si="133">T6/P6-1</f>
         <v>0.36620349619004933</v>
       </c>
       <c r="U20" s="9">
-        <f t="shared" ref="U20" si="135">U6/Q6-1</f>
+        <f t="shared" ref="U20" si="134">U6/Q6-1</f>
         <v>0.32605500734830994</v>
       </c>
       <c r="V20" s="9">
-        <f t="shared" ref="V20" si="136">V6/R6-1</f>
+        <f t="shared" ref="V20" si="135">V6/R6-1</f>
         <v>0.35291858678955457</v>
       </c>
       <c r="W20" s="9">
-        <f t="shared" ref="W20" si="137">W6/S6-1</f>
+        <f t="shared" ref="W20" si="136">W6/S6-1</f>
         <v>0.48297094477583213</v>
       </c>
       <c r="X20" s="9">
-        <f t="shared" ref="X20" si="138">X6/T6-1</f>
+        <f t="shared" ref="X20" si="137">X6/T6-1</f>
         <v>0.42552493438320216</v>
       </c>
       <c r="Y20" s="9">
-        <f t="shared" ref="Y20" si="139">Y6/U6-1</f>
+        <f t="shared" ref="Y20" si="138">Y6/U6-1</f>
         <v>0.45186827105763139</v>
       </c>
       <c r="Z20" s="9">
-        <f t="shared" ref="Z20" si="140">Z6/V6-1</f>
+        <f t="shared" ref="Z20" si="139">Z6/V6-1</f>
         <v>0.38674425205790519</v>
       </c>
       <c r="AA20" s="9">
-        <f t="shared" ref="AA20" si="141">AA6/W6-1</f>
+        <f t="shared" ref="AA20" si="140">AA6/W6-1</f>
         <v>0.21720513818606468</v>
       </c>
       <c r="AB20" s="9">
-        <f t="shared" ref="AB20" si="142">AB6/X6-1</f>
+        <f t="shared" ref="AB20" si="141">AB6/X6-1</f>
         <v>7.5258918296893018E-2</v>
       </c>
       <c r="AC20" s="9">
-        <f t="shared" ref="AC20" si="143">AC6/Y6-1</f>
+        <f t="shared" ref="AC20" si="142">AC6/Y6-1</f>
         <v>7.7426390403489975E-3</v>
       </c>
       <c r="AD20" s="9">
-        <f t="shared" ref="AD20" si="144">AD6/Z6-1</f>
+        <f t="shared" ref="AD20" si="143">AD6/Z6-1</f>
         <v>7.6348377852829774E-2</v>
       </c>
       <c r="AE20" s="9">
-        <f t="shared" ref="AE20" si="145">AE6/AA6-1</f>
+        <f t="shared" ref="AE20" si="144">AE6/AA6-1</f>
         <v>6.3639270866645337E-2</v>
       </c>
       <c r="AF20" s="9">
-        <f t="shared" ref="AF20" si="146">AF6/AB6-1</f>
+        <f t="shared" ref="AF20" si="145">AF6/AB6-1</f>
         <v>0.12767551369863006</v>
       </c>
       <c r="AG20" s="9">
-        <f t="shared" ref="AG20" si="147">AG6/AC6-1</f>
+        <f t="shared" ref="AG20" si="146">AG6/AC6-1</f>
         <v>0.20950113624066669</v>
       </c>
       <c r="AH20" s="9">
-        <f t="shared" ref="AH20" si="148">AH6/AD6-1</f>
+        <f t="shared" ref="AH20" si="147">AH6/AD6-1</f>
         <v>0.15812494057240656</v>
       </c>
       <c r="AI20" s="9">
-        <f t="shared" ref="AI20" si="149">AI6/AE6-1</f>
+        <f t="shared" ref="AI20" si="148">AI6/AE6-1</f>
         <v>0.21767889356584491</v>
       </c>
       <c r="AJ20" s="9">
-        <f t="shared" ref="AJ20" si="150">AJ6/AF6-1</f>
+        <f t="shared" ref="AJ20" si="149">AJ6/AF6-1</f>
         <v>0.22824333301698774</v>
       </c>
       <c r="AK20" s="9">
-        <f t="shared" ref="AK20" si="151">AK6/AG6-1</f>
-        <v>0.12999999999999989</v>
+        <f t="shared" ref="AK20" si="150">AK6/AG6-1</f>
+        <v>0.35492529301243625</v>
       </c>
       <c r="AL20" s="9">
-        <f t="shared" ref="AL20" si="152">AL6/AH6-1</f>
-        <v>7.0000000000000062E-2</v>
+        <f t="shared" ref="AL20" si="151">AL6/AH6-1</f>
+        <v>0.30000000000000004</v>
       </c>
       <c r="AN20" s="9"/>
       <c r="AO20" s="9">
-        <f t="shared" ref="AO20:BA20" si="153">AO6/AN6-1</f>
+        <f t="shared" ref="AO20:BA20" si="152">AO6/AN6-1</f>
         <v>0.3248645860201187</v>
       </c>
       <c r="AP20" s="9">
-        <f t="shared" si="153"/>
+        <f t="shared" si="152"/>
         <v>0.32385865861968277</v>
       </c>
       <c r="AQ20" s="9">
-        <f t="shared" si="153"/>
+        <f t="shared" si="152"/>
         <v>0.35647058823529409</v>
       </c>
       <c r="AR20" s="9">
-        <f t="shared" si="153"/>
+        <f t="shared" si="152"/>
         <v>0.3364592367736341</v>
       </c>
       <c r="AS20" s="9">
-        <f t="shared" si="153"/>
+        <f t="shared" si="152"/>
         <v>0.43329953356317175</v>
       </c>
       <c r="AT20" s="9">
-        <f t="shared" si="153"/>
+        <f t="shared" si="152"/>
         <v>8.8997679551757303E-2</v>
       </c>
       <c r="AU20" s="9">
-        <f t="shared" si="153"/>
+        <f t="shared" si="152"/>
         <v>0.14003585999012547</v>
       </c>
       <c r="AV20" s="9">
-        <f t="shared" si="153"/>
-        <v>0.15687933078045213</v>
+        <f t="shared" si="152"/>
+        <v>0.27803610503282283</v>
       </c>
       <c r="AW20" s="9">
-        <f t="shared" si="153"/>
+        <f t="shared" si="152"/>
+        <v>0.1399999999999999</v>
+      </c>
+      <c r="AX20" s="9">
+        <f t="shared" si="152"/>
         <v>6.0000000000000053E-2</v>
       </c>
-      <c r="AX20" s="9">
-        <f t="shared" si="153"/>
+      <c r="AY20" s="9">
+        <f t="shared" si="152"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AY20" s="9">
-        <f t="shared" si="153"/>
+      <c r="AZ20" s="9">
+        <f t="shared" si="152"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AZ20" s="9">
-        <f t="shared" si="153"/>
+      <c r="BA20" s="9">
+        <f t="shared" si="152"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="BA20" s="9">
-        <f t="shared" si="153"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
       <c r="BB20" s="9">
-        <f t="shared" ref="BB20" si="154">BB6/BA6-1</f>
+        <f t="shared" ref="BB20" si="153">BB6/BA6-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BC20" s="9">
-        <f t="shared" ref="BC20" si="155">BC6/BB6-1</f>
+        <f t="shared" ref="BC20" si="154">BC6/BB6-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BD20" s="9">
-        <f t="shared" ref="BD20" si="156">BD6/BC6-1</f>
+        <f t="shared" ref="BD20" si="155">BD6/BC6-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BE20" s="9">
-        <f t="shared" ref="BE20" si="157">BE6/BD6-1</f>
+        <f t="shared" ref="BE20" si="156">BE6/BD6-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BF20" s="9">
-        <f t="shared" ref="BF20" si="158">BF6/BE6-1</f>
+        <f t="shared" ref="BF20" si="157">BF6/BE6-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BH20" t="s">
@@ -5875,7 +5893,7 @@
       </c>
       <c r="BI20" s="20">
         <f>NPV(BI19,AU13:FI13)</f>
-        <v>2058680.1424818356</v>
+        <v>1939462.900855571</v>
       </c>
     </row>
     <row r="21" spans="2:61">
@@ -5887,227 +5905,227 @@
         <v>0.13159860557768924</v>
       </c>
       <c r="D21" s="9">
-        <f t="shared" ref="D21:R21" si="159">D7/D3</f>
+        <f t="shared" ref="D21:R21" si="158">D7/D3</f>
         <v>0.12058791975109967</v>
       </c>
       <c r="E21" s="9">
+        <f t="shared" si="158"/>
+        <v>0.11328427575522851</v>
+      </c>
+      <c r="F21" s="9">
+        <f t="shared" si="158"/>
+        <v>0.1059204440333025</v>
+      </c>
+      <c r="G21" s="9">
+        <f t="shared" si="158"/>
+        <v>0.13329433394618084</v>
+      </c>
+      <c r="H21" s="9">
+        <f t="shared" si="158"/>
+        <v>0.14020104300506386</v>
+      </c>
+      <c r="I21" s="9">
+        <f t="shared" si="158"/>
+        <v>0.14045312158519704</v>
+      </c>
+      <c r="J21" s="9">
+        <f t="shared" si="158"/>
+        <v>0.14585550431595129</v>
+      </c>
+      <c r="K21" s="9">
+        <f t="shared" si="158"/>
+        <v>0.13397890827087616</v>
+      </c>
+      <c r="L21" s="9">
+        <f t="shared" si="158"/>
+        <v>0.14312818688485712</v>
+      </c>
+      <c r="M21" s="9">
+        <f t="shared" si="158"/>
+        <v>0.13686834353047814</v>
+      </c>
+      <c r="N21" s="9">
+        <f t="shared" si="158"/>
+        <v>0.14353476899724885</v>
+      </c>
+      <c r="O21" s="9">
+        <f t="shared" si="158"/>
+        <v>0.15712916502226984</v>
+      </c>
+      <c r="P21" s="9">
+        <f t="shared" si="158"/>
+        <v>0.15197731042971049</v>
+      </c>
+      <c r="Q21" s="9">
+        <f t="shared" si="158"/>
+        <v>0.12496506753609687</v>
+      </c>
+      <c r="R21" s="9">
+        <f t="shared" si="158"/>
+        <v>0.11684240524365916</v>
+      </c>
+      <c r="S21" s="9">
+        <f t="shared" ref="S21:V21" si="159">S7/S3</f>
+        <v>0.10863169156700164</v>
+      </c>
+      <c r="T21" s="9">
         <f t="shared" si="159"/>
-        <v>0.11328427575522851</v>
-      </c>
-      <c r="F21" s="9">
+        <v>0.1120817140695395</v>
+      </c>
+      <c r="U21" s="9">
         <f t="shared" si="159"/>
-        <v>0.1059204440333025</v>
-      </c>
-      <c r="G21" s="9">
+        <v>0.1225094794898311</v>
+      </c>
+      <c r="V21" s="9">
         <f t="shared" si="159"/>
-        <v>0.13329433394618084</v>
-      </c>
-      <c r="H21" s="9">
-        <f t="shared" si="159"/>
-        <v>0.14020104300506386</v>
-      </c>
-      <c r="I21" s="9">
-        <f t="shared" si="159"/>
-        <v>0.14045312158519704</v>
-      </c>
-      <c r="J21" s="9">
-        <f t="shared" si="159"/>
-        <v>0.14585550431595129</v>
-      </c>
-      <c r="K21" s="9">
-        <f t="shared" si="159"/>
-        <v>0.13397890827087616</v>
-      </c>
-      <c r="L21" s="9">
-        <f t="shared" si="159"/>
-        <v>0.14312818688485712</v>
-      </c>
-      <c r="M21" s="9">
-        <f t="shared" si="159"/>
-        <v>0.13686834353047814</v>
-      </c>
-      <c r="N21" s="9">
-        <f t="shared" si="159"/>
-        <v>0.14353476899724885</v>
-      </c>
-      <c r="O21" s="9">
-        <f t="shared" si="159"/>
-        <v>0.15712916502226984</v>
-      </c>
-      <c r="P21" s="9">
-        <f t="shared" si="159"/>
-        <v>0.15197731042971049</v>
-      </c>
-      <c r="Q21" s="9">
-        <f t="shared" si="159"/>
-        <v>0.12496506753609687</v>
-      </c>
-      <c r="R21" s="9">
-        <f t="shared" si="159"/>
-        <v>0.11684240524365916</v>
-      </c>
-      <c r="S21" s="9">
-        <f t="shared" ref="S21:V21" si="160">S7/S3</f>
-        <v>0.10863169156700164</v>
-      </c>
-      <c r="T21" s="9">
+        <v>0.13029016067238872</v>
+      </c>
+      <c r="W21" s="9">
+        <f t="shared" ref="W21:AE21" si="160">W7/W3</f>
+        <v>0.11867564855955282</v>
+      </c>
+      <c r="X21" s="9">
         <f t="shared" si="160"/>
-        <v>0.1120817140695395</v>
-      </c>
-      <c r="U21" s="9">
+        <v>0.12473110818125044</v>
+      </c>
+      <c r="Y21" s="9">
         <f t="shared" si="160"/>
-        <v>0.1225094794898311</v>
-      </c>
-      <c r="V21" s="9">
+        <v>0.13639315869235766</v>
+      </c>
+      <c r="Z21" s="9">
         <f t="shared" si="160"/>
-        <v>0.13029016067238872</v>
-      </c>
-      <c r="W21" s="9">
-        <f t="shared" ref="W21:AE21" si="161">W7/W3</f>
-        <v>0.11867564855955282</v>
-      </c>
-      <c r="X21" s="9">
+        <v>0.142204259288046</v>
+      </c>
+      <c r="AA21" s="9">
+        <f t="shared" si="160"/>
+        <v>0.10626636411241054</v>
+      </c>
+      <c r="AB21" s="9">
+        <f t="shared" si="160"/>
+        <v>9.8565580174380454E-2</v>
+      </c>
+      <c r="AC21" s="9">
+        <f t="shared" si="160"/>
+        <v>8.3594839609483967E-2</v>
+      </c>
+      <c r="AD21" s="9">
+        <f t="shared" si="160"/>
+        <v>8.0426815586746775E-2</v>
+      </c>
+      <c r="AE21" s="9">
+        <f t="shared" si="160"/>
+        <v>7.0333287614867651E-2</v>
+      </c>
+      <c r="AF21" s="9">
+        <f t="shared" ref="AF21:AH21" si="161">AF7/AF3</f>
+        <v>6.9642445803793099E-2</v>
+      </c>
+      <c r="AG21" s="9">
         <f t="shared" si="161"/>
-        <v>0.12473110818125044</v>
-      </c>
-      <c r="Y21" s="9">
+        <v>6.9526226317475182E-2</v>
+      </c>
+      <c r="AH21" s="9">
         <f t="shared" si="161"/>
-        <v>0.13639315869235766</v>
-      </c>
-      <c r="Z21" s="9">
-        <f t="shared" si="161"/>
-        <v>0.142204259288046</v>
-      </c>
-      <c r="AA21" s="9">
-        <f t="shared" si="161"/>
-        <v>0.10626636411241054</v>
-      </c>
-      <c r="AB21" s="9">
-        <f t="shared" si="161"/>
-        <v>9.8565580174380454E-2</v>
-      </c>
-      <c r="AC21" s="9">
-        <f t="shared" si="161"/>
-        <v>8.3594839609483967E-2</v>
-      </c>
-      <c r="AD21" s="9">
-        <f t="shared" si="161"/>
-        <v>8.0426815586746775E-2</v>
-      </c>
-      <c r="AE21" s="9">
-        <f t="shared" si="161"/>
-        <v>7.0333287614867651E-2</v>
-      </c>
-      <c r="AF21" s="9">
-        <f t="shared" ref="AF21:AH21" si="162">AF7/AF3</f>
-        <v>6.9642445803793099E-2</v>
-      </c>
-      <c r="AG21" s="9">
+        <v>6.6962901725741444E-2</v>
+      </c>
+      <c r="AI21" s="9">
+        <f t="shared" ref="AI21:AL21" si="162">AI7/AI3</f>
+        <v>6.5155740416883295E-2</v>
+      </c>
+      <c r="AJ21" s="9">
         <f t="shared" si="162"/>
-        <v>6.9526226317475182E-2</v>
-      </c>
-      <c r="AH21" s="9">
+        <v>6.269467126862531E-2</v>
+      </c>
+      <c r="AK21" s="9">
         <f t="shared" si="162"/>
-        <v>6.6962901725741444E-2</v>
-      </c>
-      <c r="AI21" s="9">
-        <f t="shared" ref="AI21:AL21" si="163">AI7/AI3</f>
-        <v>6.5155740416883295E-2</v>
-      </c>
-      <c r="AJ21" s="9">
-        <f t="shared" si="163"/>
-        <v>6.269467126862531E-2</v>
-      </c>
-      <c r="AK21" s="9">
-        <f t="shared" si="163"/>
+        <v>5.5520861793060379E-2</v>
+      </c>
+      <c r="AL21" s="9">
+        <f t="shared" si="162"/>
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="AL21" s="9">
-        <f t="shared" si="163"/>
+      <c r="AN21" s="9">
+        <f t="shared" ref="AN21" si="163">AN7/AN3</f>
+        <v>0.1162275846800974</v>
+      </c>
+      <c r="AO21" s="9">
+        <f t="shared" ref="AO21:BA21" si="164">AO7/AO3</f>
+        <v>0.14049571976073641</v>
+      </c>
+      <c r="AP21" s="9">
+        <f t="shared" si="164"/>
+        <v>0.13973428413769684</v>
+      </c>
+      <c r="AQ21" s="9">
+        <f t="shared" si="164"/>
+        <v>0.13482074308447525</v>
+      </c>
+      <c r="AR21" s="9">
+        <f t="shared" si="164"/>
+        <v>0.11908012448167965</v>
+      </c>
+      <c r="AS21" s="9">
+        <f t="shared" si="164"/>
+        <v>0.13087326021147597</v>
+      </c>
+      <c r="AT21" s="9">
+        <f t="shared" si="164"/>
+        <v>9.1003247738050325E-2</v>
+      </c>
+      <c r="AU21" s="9">
+        <f t="shared" si="164"/>
+        <v>6.8978723404255315E-2</v>
+      </c>
+      <c r="AV21" s="9">
+        <f t="shared" si="164"/>
+        <v>6.2043799652495311E-2</v>
+      </c>
+      <c r="AW21" s="9">
+        <f t="shared" si="164"/>
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="AN21" s="9">
-        <f t="shared" ref="AN21" si="164">AN7/AN3</f>
-        <v>0.1162275846800974</v>
-      </c>
-      <c r="AO21" s="9">
-        <f t="shared" ref="AO21:BA21" si="165">AO7/AO3</f>
-        <v>0.14049571976073641</v>
-      </c>
-      <c r="AP21" s="9">
-        <f t="shared" si="165"/>
-        <v>0.13973428413769684</v>
-      </c>
-      <c r="AQ21" s="9">
-        <f t="shared" si="165"/>
-        <v>0.13482074308447525</v>
-      </c>
-      <c r="AR21" s="9">
-        <f t="shared" si="165"/>
-        <v>0.11908012448167965</v>
-      </c>
-      <c r="AS21" s="9">
-        <f t="shared" si="165"/>
-        <v>0.13087326021147597</v>
-      </c>
-      <c r="AT21" s="9">
-        <f t="shared" si="165"/>
-        <v>9.1003247738050325E-2</v>
-      </c>
-      <c r="AU21" s="9">
-        <f t="shared" si="165"/>
-        <v>6.8978723404255315E-2</v>
-      </c>
-      <c r="AV21" s="9">
-        <f t="shared" si="165"/>
-        <v>6.4460849447798813E-2</v>
-      </c>
-      <c r="AW21" s="9">
+      <c r="AX21" s="9">
+        <f t="shared" si="164"/>
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="AY21" s="9">
+        <f t="shared" si="164"/>
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="AZ21" s="9">
+        <f t="shared" si="164"/>
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="BA21" s="9">
+        <f t="shared" si="164"/>
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="BB21" s="9">
+        <f t="shared" ref="BB21:BF21" si="165">BB7/BB3</f>
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="BC21" s="9">
         <f t="shared" si="165"/>
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="AX21" s="9">
+      <c r="BD21" s="9">
         <f t="shared" si="165"/>
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="AY21" s="9">
+      <c r="BE21" s="9">
         <f t="shared" si="165"/>
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="AZ21" s="9">
+      <c r="BF21" s="9">
         <f t="shared" si="165"/>
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="BA21" s="9">
-        <f t="shared" si="165"/>
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="BB21" s="9">
-        <f t="shared" ref="BB21:BF21" si="166">BB7/BB3</f>
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="BC21" s="9">
-        <f t="shared" si="166"/>
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="BD21" s="9">
-        <f t="shared" si="166"/>
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="BE21" s="9">
-        <f t="shared" si="166"/>
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="BF21" s="9">
-        <f t="shared" si="166"/>
-        <v>6.5000000000000002E-2</v>
-      </c>
       <c r="BH21" t="s">
         <v>46</v>
       </c>
       <c r="BI21" s="20">
         <f>Main!D8</f>
-        <v>40227</v>
+        <v>40688</v>
       </c>
     </row>
     <row r="22" spans="2:61">
@@ -6119,212 +6137,212 @@
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
       <c r="G22" s="9">
-        <f t="shared" ref="G22" si="167">G8/C8-1</f>
+        <f t="shared" ref="G22" si="166">G8/C8-1</f>
         <v>0.1557251908396946</v>
       </c>
       <c r="H22" s="9">
-        <f t="shared" ref="H22" si="168">H8/D8-1</f>
+        <f t="shared" ref="H22" si="167">H8/D8-1</f>
         <v>0.21249999999999991</v>
       </c>
       <c r="I22" s="9">
-        <f t="shared" ref="I22" si="169">I8/E8-1</f>
+        <f t="shared" ref="I22" si="168">I8/E8-1</f>
         <v>0.75932835820895517</v>
       </c>
       <c r="J22" s="9">
-        <f t="shared" ref="J22" si="170">J8/F8-1</f>
+        <f t="shared" ref="J22" si="169">J8/F8-1</f>
         <v>0.42274052478134116</v>
       </c>
       <c r="K22" s="9">
-        <f t="shared" ref="K22" si="171">K8/G8-1</f>
+        <f t="shared" ref="K22" si="170">K8/G8-1</f>
         <v>4.3685601056803174</v>
       </c>
       <c r="L22" s="9">
-        <f t="shared" ref="L22" si="172">L8/H8-1</f>
+        <f t="shared" ref="L22" si="171">L8/H8-1</f>
         <v>3.1546391752577323</v>
       </c>
       <c r="M22" s="9">
-        <f t="shared" ref="M22" si="173">M8/I8-1</f>
+        <f t="shared" ref="M22" si="172">M8/I8-1</f>
         <v>0.42948038176033942</v>
       </c>
       <c r="N22" s="9">
-        <f t="shared" ref="N22" si="174">N8/J8-1</f>
+        <f t="shared" ref="N22" si="173">N8/J8-1</f>
         <v>0.87397540983606548</v>
       </c>
       <c r="O22" s="9">
-        <f t="shared" ref="O22" si="175">O8/K8-1</f>
+        <f t="shared" ref="O22" si="174">O8/K8-1</f>
         <v>-0.6104822834645669</v>
       </c>
       <c r="P22" s="9">
-        <f t="shared" ref="P22" si="176">P8/L8-1</f>
+        <f t="shared" ref="P22" si="175">P8/L8-1</f>
         <v>-0.50589330024813894</v>
       </c>
       <c r="Q22" s="9">
-        <f t="shared" ref="Q22" si="177">Q8/M8-1</f>
+        <f t="shared" ref="Q22" si="176">Q8/M8-1</f>
         <v>0.32789317507418403</v>
       </c>
       <c r="R22" s="9">
-        <f t="shared" ref="R22" si="178">R8/N8-1</f>
+        <f t="shared" ref="R22" si="177">R8/N8-1</f>
         <v>-0.12575177692728268</v>
       </c>
       <c r="S22" s="9">
-        <f t="shared" ref="S22" si="179">S8/O8-1</f>
+        <f t="shared" ref="S22" si="178">S8/O8-1</f>
         <v>2.4636765634870494E-2</v>
       </c>
       <c r="T22" s="9">
-        <f t="shared" ref="T22" si="180">T8/P8-1</f>
+        <f t="shared" ref="T22" si="179">T8/P8-1</f>
         <v>0.22787193973634645</v>
       </c>
       <c r="U22" s="9">
-        <f t="shared" ref="U22" si="181">U8/Q8-1</f>
+        <f t="shared" ref="U22" si="180">U8/Q8-1</f>
         <v>0.64581005586592188</v>
       </c>
       <c r="V22" s="9">
-        <f t="shared" ref="V22" si="182">V8/R8-1</f>
+        <f t="shared" ref="V22" si="181">V8/R8-1</f>
         <v>1.0669168230143842</v>
       </c>
       <c r="W22" s="9">
-        <f t="shared" ref="W22" si="183">W8/S8-1</f>
+        <f t="shared" ref="W22" si="182">W8/S8-1</f>
         <v>0.45499383477188649</v>
       </c>
       <c r="X22" s="9">
-        <f t="shared" ref="X22" si="184">X8/T8-1</f>
+        <f t="shared" ref="X22" si="183">X8/T8-1</f>
         <v>0.52709611451942751</v>
       </c>
       <c r="Y22" s="9">
-        <f t="shared" ref="Y22" si="185">Y8/U8-1</f>
+        <f t="shared" ref="Y22" si="184">Y8/U8-1</f>
         <v>0.14867617107942976</v>
       </c>
       <c r="Z22" s="9">
-        <f t="shared" ref="Z22" si="186">Z8/V8-1</f>
+        <f t="shared" ref="Z22" si="185">Z8/V8-1</f>
         <v>-6.656580937972767E-2</v>
       </c>
       <c r="AA22" s="9">
-        <f t="shared" ref="AA22" si="187">AA8/W8-1</f>
+        <f t="shared" ref="AA22" si="186">AA8/W8-1</f>
         <v>0.22245762711864403</v>
       </c>
       <c r="AB22" s="9">
-        <f t="shared" ref="AB22" si="188">AB8/X8-1</f>
+        <f t="shared" ref="AB22" si="187">AB8/X8-1</f>
         <v>0.39404084365584202</v>
       </c>
       <c r="AC22" s="9">
-        <f t="shared" ref="AC22" si="189">AC8/Y8-1</f>
+        <f t="shared" ref="AC22" si="188">AC8/Y8-1</f>
         <v>-0.38829787234042556</v>
       </c>
       <c r="AD22" s="9">
-        <f t="shared" ref="AD22" si="190">AD8/Z8-1</f>
+        <f t="shared" ref="AD22" si="189">AD8/Z8-1</f>
         <v>-0.25802269043760129</v>
       </c>
       <c r="AE22" s="9">
-        <f t="shared" ref="AE22" si="191">AE8/AA8-1</f>
+        <f t="shared" ref="AE22" si="190">AE8/AA8-1</f>
         <v>0.19757365684575401</v>
       </c>
       <c r="AF22" s="9">
-        <f t="shared" ref="AF22" si="192">AF8/AB8-1</f>
+        <f t="shared" ref="AF22" si="191">AF8/AB8-1</f>
         <v>-0.12151777137367914</v>
       </c>
       <c r="AG22" s="9">
-        <f t="shared" ref="AG22" si="193">AG8/AC8-1</f>
+        <f t="shared" ref="AG22" si="192">AG8/AC8-1</f>
         <v>-9.9033816425120769E-2</v>
       </c>
       <c r="AH22" s="9">
-        <f t="shared" ref="AH22" si="194">AH8/AD8-1</f>
+        <f t="shared" ref="AH22" si="193">AH8/AD8-1</f>
         <v>9.6111839231105556E-3</v>
       </c>
       <c r="AI22" s="9">
-        <f t="shared" ref="AI22" si="195">AI8/AE8-1</f>
+        <f t="shared" ref="AI22" si="194">AI8/AE8-1</f>
         <v>-0.34008683068017365</v>
       </c>
       <c r="AJ22" s="9">
-        <f t="shared" ref="AJ22" si="196">AJ8/AF8-1</f>
+        <f t="shared" ref="AJ22" si="195">AJ8/AF8-1</f>
         <v>-0.27200656096227449</v>
       </c>
       <c r="AK22" s="9">
-        <f t="shared" ref="AK22" si="197">AK8/AG8-1</f>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" ref="AK22" si="196">AK8/AG8-1</f>
+        <v>0.88310991957104568</v>
       </c>
       <c r="AL22" s="9">
-        <f t="shared" ref="AL22" si="198">AL8/AH8-1</f>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" ref="AL22" si="197">AL8/AH8-1</f>
+        <v>0.64999999999999991</v>
       </c>
       <c r="AN22" s="9"/>
       <c r="AO22" s="9">
-        <f t="shared" ref="AO22:BA22" si="199">AO8/AN8-1</f>
+        <f t="shared" ref="AO22:BA22" si="198">AO8/AN8-1</f>
         <v>0.37147397695669437</v>
       </c>
       <c r="AP22" s="9">
-        <f t="shared" si="199"/>
+        <f t="shared" si="198"/>
         <v>2.0315758980301273</v>
       </c>
       <c r="AQ22" s="9">
-        <f t="shared" si="199"/>
+        <f t="shared" si="198"/>
         <v>-0.37267080745341619</v>
       </c>
       <c r="AR22" s="9">
-        <f t="shared" si="199"/>
+        <f t="shared" si="198"/>
         <v>0.49718202589489713</v>
       </c>
       <c r="AS22" s="9">
-        <f t="shared" si="199"/>
+        <f t="shared" si="198"/>
         <v>0.20215688269406851</v>
       </c>
       <c r="AT22" s="9">
-        <f t="shared" si="199"/>
+        <f t="shared" si="198"/>
         <v>-3.4529451591063021E-2</v>
       </c>
       <c r="AU22" s="9">
-        <f t="shared" si="199"/>
+        <f t="shared" si="198"/>
         <v>-1.0431276297335201E-2</v>
       </c>
       <c r="AV22" s="9">
-        <f t="shared" si="199"/>
-        <v>-0.18482416511648503</v>
+        <f t="shared" si="198"/>
+        <v>8.6734874656745564E-2</v>
       </c>
       <c r="AW22" s="9">
-        <f t="shared" si="199"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="198"/>
+        <v>0.1399999999999999</v>
       </c>
       <c r="AX22" s="9">
-        <f t="shared" si="199"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="198"/>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="AY22" s="9">
-        <f t="shared" si="199"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="198"/>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AZ22" s="9">
-        <f t="shared" si="199"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="198"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="BA22" s="9">
-        <f t="shared" si="199"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="198"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="BB22" s="9">
-        <f t="shared" ref="BB22" si="200">BB8/BA8-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="BB22" si="199">BB8/BA8-1</f>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="BC22" s="9">
-        <f t="shared" ref="BC22" si="201">BC8/BB8-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="BC22" si="200">BC8/BB8-1</f>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="BD22" s="9">
-        <f t="shared" ref="BD22" si="202">BD8/BC8-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="BD22" si="201">BD8/BC8-1</f>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="BE22" s="9">
-        <f t="shared" ref="BE22" si="203">BE8/BD8-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="BE22" si="202">BE8/BD8-1</f>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="BF22" s="9">
-        <f t="shared" ref="BF22" si="204">BF8/BE8-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="BF22" si="203">BF8/BE8-1</f>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="BH22" t="s">
         <v>47</v>
       </c>
       <c r="BI22" s="20">
         <f>BI20+BI21</f>
-        <v>2098907.1424818356</v>
+        <v>1980150.900855571</v>
       </c>
     </row>
     <row r="23" spans="2:61">
@@ -6336,459 +6354,459 @@
         <v>0.10240610328638497</v>
       </c>
       <c r="D23" s="9">
-        <f t="shared" ref="D23:R23" si="205">D12/D11</f>
+        <f t="shared" ref="D23:R23" si="204">D12/D11</f>
         <v>0.13324420677361853</v>
       </c>
       <c r="E23" s="9">
+        <f t="shared" si="204"/>
+        <v>0.10103132161955691</v>
+      </c>
+      <c r="F23" s="9">
+        <f t="shared" si="204"/>
+        <v>0.52452425623157328</v>
+      </c>
+      <c r="G23" s="9">
+        <f t="shared" si="204"/>
+        <v>0.11105169340463458</v>
+      </c>
+      <c r="H23" s="9">
+        <f t="shared" si="204"/>
+        <v>0.12985685071574643</v>
+      </c>
+      <c r="I23" s="9">
+        <f t="shared" si="204"/>
+        <v>0.13108930987821379</v>
+      </c>
+      <c r="J23" s="9">
+        <f t="shared" si="204"/>
+        <v>0.13662024840045164</v>
+      </c>
+      <c r="K23" s="9">
+        <f t="shared" si="204"/>
+        <v>0.30241240666283747</v>
+      </c>
+      <c r="L23" s="9">
+        <f t="shared" si="204"/>
+        <v>0.46051537822111388</v>
+      </c>
+      <c r="M23" s="9">
+        <f t="shared" si="204"/>
+        <v>0.16891799699822621</v>
+      </c>
+      <c r="N23" s="9">
+        <f t="shared" si="204"/>
+        <v>0.19849492856363835</v>
+      </c>
+      <c r="O23" s="9">
+        <f t="shared" si="204"/>
+        <v>0.16362395495649207</v>
+      </c>
+      <c r="P23" s="9">
+        <f t="shared" si="204"/>
+        <v>0.15543956940140272</v>
+      </c>
+      <c r="Q23" s="9">
+        <f t="shared" si="204"/>
+        <v>3.5288331488995447E-2</v>
+      </c>
+      <c r="R23" s="9">
+        <f t="shared" si="204"/>
+        <v>0.14063577173496744</v>
+      </c>
+      <c r="S23" s="9">
+        <f t="shared" ref="S23:V23" si="205">S12/S11</f>
+        <v>0.17438928975049986</v>
+      </c>
+      <c r="T23" s="9">
         <f t="shared" si="205"/>
-        <v>0.10103132161955691</v>
-      </c>
-      <c r="F23" s="9">
+        <v>0.16934388236234316</v>
+      </c>
+      <c r="U23" s="9">
         <f t="shared" si="205"/>
-        <v>0.52452425623157328</v>
-      </c>
-      <c r="G23" s="9">
+        <v>0.12976810222432561</v>
+      </c>
+      <c r="V23" s="9">
         <f t="shared" si="205"/>
-        <v>0.11105169340463458</v>
-      </c>
-      <c r="H23" s="9">
-        <f t="shared" si="205"/>
-        <v>0.12985685071574643</v>
-      </c>
-      <c r="I23" s="9">
-        <f t="shared" si="205"/>
-        <v>0.13108930987821379</v>
-      </c>
-      <c r="J23" s="9">
-        <f t="shared" si="205"/>
-        <v>0.13662024840045164</v>
-      </c>
-      <c r="K23" s="9">
-        <f t="shared" si="205"/>
-        <v>0.30241240666283747</v>
-      </c>
-      <c r="L23" s="9">
-        <f t="shared" si="205"/>
-        <v>0.46051537822111388</v>
-      </c>
-      <c r="M23" s="9">
-        <f t="shared" si="205"/>
-        <v>0.16891799699822621</v>
-      </c>
-      <c r="N23" s="9">
-        <f t="shared" si="205"/>
-        <v>0.19849492856363835</v>
-      </c>
-      <c r="O23" s="9">
-        <f t="shared" si="205"/>
-        <v>0.16362395495649207</v>
-      </c>
-      <c r="P23" s="9">
-        <f t="shared" si="205"/>
-        <v>0.15543956940140272</v>
-      </c>
-      <c r="Q23" s="9">
-        <f t="shared" si="205"/>
-        <v>3.5288331488995447E-2</v>
-      </c>
-      <c r="R23" s="9">
-        <f t="shared" si="205"/>
-        <v>0.14063577173496744</v>
-      </c>
-      <c r="S23" s="9">
-        <f t="shared" ref="S23:V23" si="206">S12/S11</f>
-        <v>0.17438928975049986</v>
-      </c>
-      <c r="T23" s="9">
+        <v>0.19028499448905684</v>
+      </c>
+      <c r="W23" s="9">
+        <f t="shared" ref="W23:AE23" si="206">W12/W11</f>
+        <v>0.1619892231701841</v>
+      </c>
+      <c r="X23" s="9">
         <f t="shared" si="206"/>
-        <v>0.16934388236234316</v>
-      </c>
-      <c r="U23" s="9">
+        <v>0.18311751771316884</v>
+      </c>
+      <c r="Y23" s="9">
         <f t="shared" si="206"/>
-        <v>0.12976810222432561</v>
-      </c>
-      <c r="V23" s="9">
+        <v>0.21180057388809181</v>
+      </c>
+      <c r="Z23" s="9">
         <f t="shared" si="206"/>
-        <v>0.19028499448905684</v>
-      </c>
-      <c r="W23" s="9">
-        <f t="shared" ref="W23:AE23" si="207">W12/W11</f>
-        <v>0.1619892231701841</v>
-      </c>
-      <c r="X23" s="9">
+        <v>0.24345422019840623</v>
+      </c>
+      <c r="AA23" s="9">
+        <f t="shared" si="206"/>
+        <v>0.21869440262761736</v>
+      </c>
+      <c r="AB23" s="9">
+        <f t="shared" si="206"/>
+        <v>0.16194985472936618</v>
+      </c>
+      <c r="AC23" s="9">
+        <f t="shared" si="206"/>
+        <v>0.17053883834849545</v>
+      </c>
+      <c r="AD23" s="9">
+        <f t="shared" si="206"/>
+        <v>0.16605188005711566</v>
+      </c>
+      <c r="AE23" s="9">
+        <f t="shared" si="206"/>
+        <v>0.12789959811041388</v>
+      </c>
+      <c r="AF23" s="9">
+        <f t="shared" ref="AF23:AH23" si="207">AF12/AF11</f>
+        <v>0.10863233152389778</v>
+      </c>
+      <c r="AG23" s="9">
         <f t="shared" si="207"/>
-        <v>0.18311751771316884</v>
-      </c>
-      <c r="Y23" s="9">
+        <v>0.11973964762652901</v>
+      </c>
+      <c r="AH23" s="9">
         <f t="shared" si="207"/>
-        <v>0.21180057388809181</v>
-      </c>
-      <c r="Z23" s="9">
-        <f t="shared" si="207"/>
-        <v>0.24345422019840623</v>
-      </c>
-      <c r="AA23" s="9">
-        <f t="shared" si="207"/>
-        <v>0.21869440262761736</v>
-      </c>
-      <c r="AB23" s="9">
-        <f t="shared" si="207"/>
-        <v>0.16194985472936618</v>
-      </c>
-      <c r="AC23" s="9">
-        <f t="shared" si="207"/>
-        <v>0.17053883834849545</v>
-      </c>
-      <c r="AD23" s="9">
-        <f t="shared" si="207"/>
-        <v>0.16605188005711566</v>
-      </c>
-      <c r="AE23" s="9">
-        <f t="shared" si="207"/>
-        <v>0.12789959811041388</v>
-      </c>
-      <c r="AF23" s="9">
-        <f t="shared" ref="AF23:AH23" si="208">AF12/AF11</f>
-        <v>0.10863233152389778</v>
-      </c>
-      <c r="AG23" s="9">
+        <v>0.12339226469117848</v>
+      </c>
+      <c r="AI23" s="9">
+        <f t="shared" ref="AI23:AL23" si="208">AI12/AI11</f>
+        <v>9.4549015341094556E-2</v>
+      </c>
+      <c r="AJ23" s="9">
         <f t="shared" si="208"/>
-        <v>0.11973964762652901</v>
-      </c>
-      <c r="AH23" s="9">
+        <v>0.10699327943897925</v>
+      </c>
+      <c r="AK23" s="9">
         <f t="shared" si="208"/>
-        <v>0.12339226469117848</v>
-      </c>
-      <c r="AI23" s="9">
-        <f t="shared" ref="AI23:AL23" si="209">AI12/AI11</f>
-        <v>9.4549015341094556E-2</v>
-      </c>
-      <c r="AJ23" s="9">
-        <f t="shared" si="209"/>
-        <v>0.10699327943897925</v>
-      </c>
-      <c r="AK23" s="9">
-        <f t="shared" si="209"/>
+        <v>0.13959285417532197</v>
+      </c>
+      <c r="AL23" s="9">
+        <f t="shared" si="208"/>
+        <v>0.12000000000000001</v>
+      </c>
+      <c r="AN23" s="9">
+        <f t="shared" ref="AN23" si="209">AN12/AN11</f>
+        <v>0.26172671651937457</v>
+      </c>
+      <c r="AO23" s="9">
+        <f t="shared" ref="AO23:BA23" si="210">AO12/AO11</f>
+        <v>0.12811009029612397</v>
+      </c>
+      <c r="AP23" s="9">
+        <f t="shared" si="210"/>
+        <v>0.25520329138431752</v>
+      </c>
+      <c r="AQ23" s="9">
+        <f t="shared" si="210"/>
+        <v>0.12160940325497288</v>
+      </c>
+      <c r="AR23" s="9">
+        <f t="shared" si="210"/>
+        <v>0.1673540173000867</v>
+      </c>
+      <c r="AS23" s="9">
+        <f t="shared" si="210"/>
+        <v>0.19501023630243935</v>
+      </c>
+      <c r="AT23" s="9">
+        <f t="shared" si="210"/>
+        <v>0.17466141137993207</v>
+      </c>
+      <c r="AU23" s="9">
+        <f t="shared" si="210"/>
+        <v>0.1201493185172324</v>
+      </c>
+      <c r="AV23" s="9">
+        <f t="shared" si="210"/>
+        <v>0.11651559247050146</v>
+      </c>
+      <c r="AW23" s="9">
+        <f t="shared" si="210"/>
         <v>0.12</v>
       </c>
-      <c r="AL23" s="9">
-        <f t="shared" si="209"/>
-        <v>0.12000000000000001</v>
-      </c>
-      <c r="AN23" s="9">
-        <f t="shared" ref="AN23" si="210">AN12/AN11</f>
-        <v>0.26172671651937457</v>
-      </c>
-      <c r="AO23" s="9">
-        <f t="shared" ref="AO23:BA23" si="211">AO12/AO11</f>
-        <v>0.12811009029612397</v>
-      </c>
-      <c r="AP23" s="9">
-        <f t="shared" si="211"/>
-        <v>0.25520329138431752</v>
-      </c>
-      <c r="AQ23" s="9">
-        <f t="shared" si="211"/>
-        <v>0.12160940325497288</v>
-      </c>
-      <c r="AR23" s="9">
-        <f t="shared" si="211"/>
-        <v>0.1673540173000867</v>
-      </c>
-      <c r="AS23" s="9">
-        <f t="shared" si="211"/>
-        <v>0.19501023630243935</v>
-      </c>
-      <c r="AT23" s="9">
-        <f t="shared" si="211"/>
-        <v>0.17466141137993207</v>
-      </c>
-      <c r="AU23" s="9">
-        <f t="shared" si="211"/>
-        <v>0.1201493185172324</v>
-      </c>
-      <c r="AV23" s="9">
-        <f t="shared" si="211"/>
-        <v>0.11159361251166676</v>
-      </c>
-      <c r="AW23" s="9">
-        <f t="shared" si="211"/>
+      <c r="AX23" s="9">
+        <f t="shared" si="210"/>
         <v>0.11999999999999998</v>
       </c>
-      <c r="AX23" s="9">
+      <c r="AY23" s="9">
+        <f t="shared" si="210"/>
+        <v>0.12</v>
+      </c>
+      <c r="AZ23" s="9">
+        <f t="shared" si="210"/>
+        <v>0.12</v>
+      </c>
+      <c r="BA23" s="9">
+        <f t="shared" si="210"/>
+        <v>0.12</v>
+      </c>
+      <c r="BB23" s="9">
+        <f t="shared" ref="BB23:BF23" si="211">BB12/BB11</f>
+        <v>0.12</v>
+      </c>
+      <c r="BC23" s="9">
         <f t="shared" si="211"/>
         <v>0.12</v>
       </c>
-      <c r="AY23" s="9">
+      <c r="BD23" s="9">
         <f t="shared" si="211"/>
         <v>0.12</v>
       </c>
-      <c r="AZ23" s="9">
+      <c r="BE23" s="9">
         <f t="shared" si="211"/>
         <v>0.12</v>
       </c>
-      <c r="BA23" s="9">
+      <c r="BF23" s="9">
         <f t="shared" si="211"/>
         <v>0.12</v>
       </c>
-      <c r="BB23" s="9">
-        <f t="shared" ref="BB23:BF23" si="212">BB12/BB11</f>
-        <v>0.12</v>
-      </c>
-      <c r="BC23" s="9">
-        <f t="shared" si="212"/>
-        <v>0.12</v>
-      </c>
-      <c r="BD23" s="9">
-        <f t="shared" si="212"/>
-        <v>0.11999999999999998</v>
-      </c>
-      <c r="BE23" s="9">
-        <f t="shared" si="212"/>
-        <v>0.12</v>
-      </c>
-      <c r="BF23" s="9">
-        <f t="shared" si="212"/>
-        <v>0.11999999999999998</v>
-      </c>
       <c r="BH23" t="s">
         <v>48</v>
       </c>
       <c r="BI23" s="5">
         <f>BI22/BA14</f>
-        <v>833.56121623583624</v>
+        <v>786.71072739593603</v>
       </c>
     </row>
     <row r="24" spans="2:61">
       <c r="B24" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C24" s="9">
         <f>C13/C3</f>
         <v>0.38085159362549803</v>
       </c>
       <c r="D24" s="9">
-        <f t="shared" ref="D24:AL24" si="213">D13/D3</f>
+        <f t="shared" ref="D24:AL24" si="212">D13/D3</f>
         <v>0.41733719557987342</v>
       </c>
       <c r="E24" s="9">
+        <f t="shared" si="212"/>
+        <v>0.4557513555383424</v>
+      </c>
+      <c r="F24" s="9">
+        <f t="shared" si="212"/>
+        <v>0.2735121800801727</v>
+      </c>
+      <c r="G24" s="9">
+        <f t="shared" si="212"/>
+        <v>0.41676416513454789</v>
+      </c>
+      <c r="H24" s="9">
+        <f t="shared" si="212"/>
+        <v>0.38591187363011109</v>
+      </c>
+      <c r="I24" s="9">
+        <f t="shared" si="212"/>
+        <v>0.37422597799956292</v>
+      </c>
+      <c r="J24" s="9">
+        <f t="shared" si="212"/>
+        <v>0.40688187300461154</v>
+      </c>
+      <c r="K24" s="9">
+        <f t="shared" si="212"/>
+        <v>0.16110632088611793</v>
+      </c>
+      <c r="L24" s="9">
+        <f t="shared" si="212"/>
+        <v>0.15391912723823076</v>
+      </c>
+      <c r="M24" s="9">
+        <f t="shared" si="212"/>
+        <v>0.34506004985270788</v>
+      </c>
+      <c r="N24" s="9">
+        <f t="shared" si="212"/>
+        <v>0.34859121525471964</v>
+      </c>
+      <c r="O24" s="9">
+        <f t="shared" si="212"/>
+        <v>0.27637142696059086</v>
+      </c>
+      <c r="P24" s="9">
+        <f t="shared" si="212"/>
+        <v>0.27709102584684542</v>
+      </c>
+      <c r="Q24" s="9">
+        <f t="shared" si="212"/>
+        <v>0.3654401490451793</v>
+      </c>
+      <c r="R24" s="9">
+        <f t="shared" si="212"/>
+        <v>0.39965089769165002</v>
+      </c>
+      <c r="S24" s="9">
+        <f t="shared" si="212"/>
+        <v>0.36288257995491191</v>
+      </c>
+      <c r="T24" s="9">
+        <f t="shared" si="212"/>
+        <v>0.35746466279189737</v>
+      </c>
+      <c r="U24" s="9">
+        <f t="shared" si="212"/>
+        <v>0.31692519820751464</v>
+      </c>
+      <c r="V24" s="9">
+        <f t="shared" si="212"/>
+        <v>0.30545573342045085</v>
+      </c>
+      <c r="W24" s="9">
+        <f t="shared" si="212"/>
+        <v>0.26748602551239786</v>
+      </c>
+      <c r="X24" s="9">
+        <f t="shared" si="212"/>
+        <v>0.23201026993269031</v>
+      </c>
+      <c r="Y24" s="9">
+        <f t="shared" si="212"/>
+        <v>0.15858410911452694</v>
+      </c>
+      <c r="Z24" s="9">
+        <f t="shared" si="212"/>
+        <v>0.1446292554018343</v>
+      </c>
+      <c r="AA24" s="9">
+        <f t="shared" si="212"/>
+        <v>0.19930179787048349</v>
+      </c>
+      <c r="AB24" s="9">
+        <f t="shared" si="212"/>
+        <v>0.24338260570642833</v>
+      </c>
+      <c r="AC24" s="9">
+        <f t="shared" si="212"/>
+        <v>0.34440376569037656</v>
+      </c>
+      <c r="AD24" s="9">
+        <f t="shared" si="212"/>
+        <v>0.34945526164892421</v>
+      </c>
+      <c r="AE24" s="9">
+        <f t="shared" si="212"/>
+        <v>0.33929502125908656</v>
+      </c>
+      <c r="AF24" s="9">
+        <f t="shared" si="212"/>
+        <v>0.34462900872770086</v>
+      </c>
+      <c r="AG24" s="9">
+        <f t="shared" si="212"/>
+        <v>0.38650865998176848</v>
+      </c>
+      <c r="AH24" s="9">
+        <f t="shared" si="212"/>
+        <v>0.39863594089077192</v>
+      </c>
+      <c r="AI24" s="9">
+        <f t="shared" si="212"/>
+        <v>0.39334499220116276</v>
+      </c>
+      <c r="AJ24" s="9">
+        <f t="shared" si="212"/>
+        <v>0.38591211381429413</v>
+      </c>
+      <c r="AK24" s="9">
+        <f t="shared" si="212"/>
+        <v>0.36374458452051051</v>
+      </c>
+      <c r="AL24" s="9">
+        <f t="shared" si="212"/>
+        <v>0.36952997829905959</v>
+      </c>
+      <c r="AN24" s="9">
+        <f t="shared" ref="AN24:BF24" si="213">AN13/AN3</f>
+        <v>0.37399453914840231</v>
+      </c>
+      <c r="AO24" s="9">
         <f t="shared" si="213"/>
-        <v>0.4557513555383424</v>
-      </c>
-      <c r="F24" s="9">
+        <v>0.39600272216053584</v>
+      </c>
+      <c r="AP24" s="9">
         <f t="shared" si="213"/>
-        <v>0.2735121800801727</v>
-      </c>
-      <c r="G24" s="9">
+        <v>0.26125896684918715</v>
+      </c>
+      <c r="AQ24" s="9">
         <f t="shared" si="213"/>
-        <v>0.41676416513454789</v>
-      </c>
-      <c r="H24" s="9">
+        <v>0.33902938370983876</v>
+      </c>
+      <c r="AR24" s="9">
         <f t="shared" si="213"/>
-        <v>0.38591187363011109</v>
-      </c>
-      <c r="I24" s="9">
+        <v>0.33384494059985248</v>
+      </c>
+      <c r="AS24" s="9">
         <f t="shared" si="213"/>
-        <v>0.37422597799956292</v>
-      </c>
-      <c r="J24" s="9">
+        <v>0.19894690804311846</v>
+      </c>
+      <c r="AT24" s="9">
         <f t="shared" si="213"/>
-        <v>0.40688187300461154</v>
-      </c>
-      <c r="K24" s="9">
+        <v>0.29123850530069317</v>
+      </c>
+      <c r="AU24" s="9">
         <f t="shared" si="213"/>
-        <v>0.16110632088611793</v>
-      </c>
-      <c r="L24" s="9">
+        <v>0.36966565349544073</v>
+      </c>
+      <c r="AV24" s="9">
         <f t="shared" si="213"/>
-        <v>0.15391912723823076</v>
-      </c>
-      <c r="M24" s="9">
+        <v>0.37638820894473074</v>
+      </c>
+      <c r="AW24" s="9">
         <f t="shared" si="213"/>
-        <v>0.34506004985270788</v>
-      </c>
-      <c r="N24" s="9">
+        <v>0.36821540516471402</v>
+      </c>
+      <c r="AX24" s="9">
         <f t="shared" si="213"/>
-        <v>0.34859121525471964</v>
-      </c>
-      <c r="O24" s="9">
+        <v>0.37449954321778317</v>
+      </c>
+      <c r="AY24" s="9">
         <f t="shared" si="213"/>
-        <v>0.27637142696059086</v>
-      </c>
-      <c r="P24" s="9">
+        <v>0.38079739070647506</v>
+      </c>
+      <c r="AZ24" s="9">
         <f t="shared" si="213"/>
-        <v>0.27709102584684542</v>
-      </c>
-      <c r="Q24" s="9">
+        <v>0.384302756393471</v>
+      </c>
+      <c r="BA24" s="9">
         <f t="shared" si="213"/>
-        <v>0.3654401490451793</v>
-      </c>
-      <c r="R24" s="9">
+        <v>0.38491290843798409</v>
+      </c>
+      <c r="BB24" s="9">
         <f t="shared" si="213"/>
-        <v>0.39965089769165002</v>
-      </c>
-      <c r="S24" s="9">
+        <v>0.38498781622533251</v>
+      </c>
+      <c r="BC24" s="9">
         <f t="shared" si="213"/>
-        <v>0.36288257995491191</v>
-      </c>
-      <c r="T24" s="9">
+        <v>0.38498910875185932</v>
+      </c>
+      <c r="BD24" s="9">
         <f t="shared" si="213"/>
-        <v>0.35746466279189737</v>
-      </c>
-      <c r="U24" s="9">
+        <v>0.38498913105427784</v>
+      </c>
+      <c r="BE24" s="9">
         <f t="shared" si="213"/>
-        <v>0.31692519820751464</v>
-      </c>
-      <c r="V24" s="9">
+        <v>0.3849891314391039</v>
+      </c>
+      <c r="BF24" s="9">
         <f t="shared" si="213"/>
-        <v>0.30545573342045085</v>
-      </c>
-      <c r="W24" s="9">
-        <f t="shared" si="213"/>
-        <v>0.26748602551239786</v>
-      </c>
-      <c r="X24" s="9">
-        <f t="shared" si="213"/>
-        <v>0.23201026993269031</v>
-      </c>
-      <c r="Y24" s="9">
-        <f t="shared" si="213"/>
-        <v>0.15858410911452694</v>
-      </c>
-      <c r="Z24" s="9">
-        <f t="shared" si="213"/>
-        <v>0.1446292554018343</v>
-      </c>
-      <c r="AA24" s="9">
-        <f t="shared" si="213"/>
-        <v>0.19930179787048349</v>
-      </c>
-      <c r="AB24" s="9">
-        <f t="shared" si="213"/>
-        <v>0.24338260570642833</v>
-      </c>
-      <c r="AC24" s="9">
-        <f t="shared" si="213"/>
-        <v>0.34440376569037656</v>
-      </c>
-      <c r="AD24" s="9">
-        <f t="shared" si="213"/>
-        <v>0.34945526164892421</v>
-      </c>
-      <c r="AE24" s="9">
-        <f t="shared" si="213"/>
-        <v>0.33929502125908656</v>
-      </c>
-      <c r="AF24" s="9">
-        <f t="shared" si="213"/>
-        <v>0.34462900872770086</v>
-      </c>
-      <c r="AG24" s="9">
-        <f t="shared" si="213"/>
-        <v>0.38650865998176848</v>
-      </c>
-      <c r="AH24" s="9">
-        <f t="shared" si="213"/>
-        <v>0.39863594089077192</v>
-      </c>
-      <c r="AI24" s="9">
-        <f t="shared" si="213"/>
-        <v>0.39334499220116276</v>
-      </c>
-      <c r="AJ24" s="9">
-        <f t="shared" si="213"/>
-        <v>0.38591211381429413</v>
-      </c>
-      <c r="AK24" s="9">
-        <f t="shared" si="213"/>
-        <v>0.406236090683332</v>
-      </c>
-      <c r="AL24" s="9">
-        <f t="shared" si="213"/>
-        <v>0.41311451896248835</v>
-      </c>
-      <c r="AN24" s="9">
-        <f t="shared" ref="AN24:BF24" si="214">AN13/AN3</f>
-        <v>0.37399453914840231</v>
-      </c>
-      <c r="AO24" s="9">
-        <f t="shared" si="214"/>
-        <v>0.39600272216053584</v>
-      </c>
-      <c r="AP24" s="9">
-        <f t="shared" si="214"/>
-        <v>0.26125896684918715</v>
-      </c>
-      <c r="AQ24" s="9">
-        <f t="shared" si="214"/>
-        <v>0.33902938370983876</v>
-      </c>
-      <c r="AR24" s="9">
-        <f t="shared" si="214"/>
-        <v>0.33384494059985248</v>
-      </c>
-      <c r="AS24" s="9">
-        <f t="shared" si="214"/>
-        <v>0.19894690804311846</v>
-      </c>
-      <c r="AT24" s="9">
-        <f t="shared" si="214"/>
-        <v>0.29123850530069317</v>
-      </c>
-      <c r="AU24" s="9">
-        <f t="shared" si="214"/>
-        <v>0.36966565349544073</v>
-      </c>
-      <c r="AV24" s="9">
-        <f t="shared" si="214"/>
-        <v>0.39968199956721312</v>
-      </c>
-      <c r="AW24" s="9">
-        <f t="shared" si="214"/>
-        <v>0.41105997530320143</v>
-      </c>
-      <c r="AX24" s="9">
-        <f t="shared" si="214"/>
-        <v>0.42215596194208721</v>
-      </c>
-      <c r="AY24" s="9">
-        <f t="shared" si="214"/>
-        <v>0.43018697555420715</v>
-      </c>
-      <c r="AZ24" s="9">
-        <f t="shared" si="214"/>
-        <v>0.43343249662027727</v>
-      </c>
-      <c r="BA24" s="9">
-        <f t="shared" si="214"/>
-        <v>0.43420127848484802</v>
-      </c>
-      <c r="BB24" s="9">
-        <f t="shared" si="214"/>
-        <v>0.43460532555500836</v>
-      </c>
-      <c r="BC24" s="9">
-        <f t="shared" si="214"/>
-        <v>0.43492734978020037</v>
-      </c>
-      <c r="BD24" s="9">
-        <f t="shared" si="214"/>
-        <v>0.43524486995990475</v>
-      </c>
-      <c r="BE24" s="9">
-        <f t="shared" si="214"/>
-        <v>0.43555925395526268</v>
-      </c>
-      <c r="BF24" s="9">
-        <f t="shared" si="214"/>
-        <v>0.43587055535355967</v>
+        <v>0.38498913144574393</v>
       </c>
       <c r="BH24" t="s">
         <v>49</v>
       </c>
       <c r="BI24" s="5">
         <f>Main!D3</f>
-        <v>714.06</v>
+        <v>686.46</v>
       </c>
     </row>
     <row r="25" spans="2:61">
@@ -6800,7 +6818,7 @@
       </c>
       <c r="BI25" s="10">
         <f>BI23/BI24-1</f>
-        <v>0.16735458677959314</v>
+        <v>0.14604015877973375</v>
       </c>
     </row>
     <row r="26" spans="2:61">
@@ -6808,7 +6826,7 @@
         <v>67</v>
       </c>
       <c r="BI26" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -6829,7 +6847,7 @@
   <sheetData>
     <row r="2" spans="2:23">
       <c r="B2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="2:23">
@@ -6855,7 +6873,7 @@
         <v>2027</v>
       </c>
       <c r="J4" s="21" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="K4" s="22">
         <v>2022</v>
@@ -6878,46 +6896,46 @@
     </row>
     <row r="5" spans="2:23">
       <c r="B5" s="24" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D5" s="25" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E5" s="25" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F5" s="25" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G5" s="26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J5" s="24" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K5" s="25" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="L5" s="25" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="M5" s="25" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="N5" s="25" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="O5" s="26" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="P5" s="27" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="R5" s="25" t="str">
         <f>LEFT(K5,4)</f>
@@ -6946,46 +6964,46 @@
     </row>
     <row r="6" spans="2:23">
       <c r="B6" s="28" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E6" s="29" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F6" s="29" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G6" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H6" s="31" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J6" s="28" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K6" s="29" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="L6" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="M6" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="N6" s="29" t="s">
+        <v>147</v>
+      </c>
+      <c r="O6" s="30" t="s">
         <v>149</v>
       </c>
-      <c r="M6" s="29" t="s">
-        <v>145</v>
-      </c>
-      <c r="N6" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="O6" s="30" t="s">
-        <v>154</v>
-      </c>
       <c r="P6" s="31" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="R6" s="25" t="str">
         <f t="shared" ref="R6:R8" si="5">LEFT(K6,4)</f>
@@ -7014,46 +7032,46 @@
     </row>
     <row r="7" spans="2:23">
       <c r="B7" s="28" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C7" s="29" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D7" s="29" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E7" s="29" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F7" s="30" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G7" s="30" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H7" s="31" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J7" s="28" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K7" s="29" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="L7" s="29" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="M7" s="29" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="N7" s="30" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="O7" s="30" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="P7" s="31" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="R7" s="25" t="str">
         <f t="shared" si="5"/>
@@ -7082,46 +7100,46 @@
     </row>
     <row r="8" spans="2:23">
       <c r="B8" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="D8" s="29" t="s">
+        <v>113</v>
+      </c>
+      <c r="E8" s="29" t="s">
+        <v>121</v>
+      </c>
+      <c r="F8" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="G8" s="30" t="s">
+        <v>125</v>
+      </c>
+      <c r="H8" s="32" t="s">
         <v>99</v>
       </c>
-      <c r="C8" s="29" t="s">
-        <v>105</v>
-      </c>
-      <c r="D8" s="29" t="s">
-        <v>114</v>
-      </c>
-      <c r="E8" s="29" t="s">
-        <v>122</v>
-      </c>
-      <c r="F8" s="30" t="s">
-        <v>118</v>
-      </c>
-      <c r="G8" s="30" t="s">
-        <v>126</v>
-      </c>
-      <c r="H8" s="32" t="s">
-        <v>100</v>
-      </c>
       <c r="J8" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="K8" s="29" t="s">
+        <v>136</v>
+      </c>
+      <c r="L8" s="29" t="s">
+        <v>139</v>
+      </c>
+      <c r="M8" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="N8" s="30" t="s">
+        <v>133</v>
+      </c>
+      <c r="O8" s="30" t="s">
+        <v>151</v>
+      </c>
+      <c r="P8" s="32" t="s">
         <v>99</v>
-      </c>
-      <c r="K8" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="L8" s="29" t="s">
-        <v>144</v>
-      </c>
-      <c r="M8" s="29" t="s">
-        <v>147</v>
-      </c>
-      <c r="N8" s="30" t="s">
-        <v>138</v>
-      </c>
-      <c r="O8" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="P8" s="32" t="s">
-        <v>100</v>
       </c>
       <c r="R8" s="25" t="str">
         <f t="shared" si="5"/>
@@ -7166,51 +7184,51 @@
     </row>
     <row r="10" spans="2:23">
       <c r="B10" s="33" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C10" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="D10" s="34" t="s">
         <v>106</v>
       </c>
-      <c r="D10" s="34" t="s">
+      <c r="E10" s="34" t="s">
         <v>107</v>
       </c>
-      <c r="E10" s="34" t="s">
+      <c r="F10" s="35" t="s">
         <v>108</v>
       </c>
-      <c r="F10" s="35" t="s">
+      <c r="G10" s="35" t="s">
         <v>109</v>
       </c>
-      <c r="G10" s="35" t="s">
-        <v>110</v>
-      </c>
       <c r="H10" s="36" t="s">
+        <v>99</v>
+      </c>
+      <c r="J10" s="33" t="s">
         <v>100</v>
       </c>
-      <c r="J10" s="33" t="s">
-        <v>101</v>
-      </c>
       <c r="K10" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="L10" s="34" t="s">
         <v>106</v>
       </c>
-      <c r="L10" s="34" t="s">
+      <c r="M10" s="34" t="s">
         <v>107</v>
       </c>
-      <c r="M10" s="34" t="s">
+      <c r="N10" s="35" t="s">
         <v>108</v>
       </c>
-      <c r="N10" s="35" t="s">
+      <c r="O10" s="35" t="s">
         <v>109</v>
       </c>
-      <c r="O10" s="35" t="s">
-        <v>110</v>
-      </c>
       <c r="P10" s="36" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12" spans="2:23">
       <c r="J12" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K12" s="45">
         <v>-0.21340000000000001</v>
@@ -7238,7 +7256,7 @@
     </row>
     <row r="13" spans="2:23">
       <c r="J13" s="28" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K13" s="42">
         <v>-0.35699999999999998</v>
@@ -7266,7 +7284,7 @@
     </row>
     <row r="14" spans="2:23">
       <c r="J14" s="28" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K14" s="42">
         <v>-0.52200000000000002</v>
@@ -7295,7 +7313,7 @@
     </row>
     <row r="15" spans="2:23">
       <c r="J15" s="28" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K15" s="42">
         <v>-0.54800000000000004</v>
@@ -7317,7 +7335,7 @@
         <v>8.7804878048780566E-2</v>
       </c>
       <c r="P15" s="49" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" spans="2:23">
@@ -7331,7 +7349,7 @@
     </row>
     <row r="17" spans="10:16">
       <c r="J17" s="33" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K17" s="43">
         <v>-0.41399999999999998</v>
@@ -7349,7 +7367,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
       <c r="P17" s="36" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="10:16">

--- a/Financial Analysis/FB.xlsx
+++ b/Financial Analysis/FB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB7B836A-FA2E-4714-980C-1D44417F731B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E8FE619-CF00-4115-A818-16CF5045EE81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{BFE532A1-2353-49AA-A72E-D2C0AD0DD88D}"/>
   </bookViews>
@@ -110,7 +110,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="158">
   <si>
     <t>Price</t>
   </si>
@@ -572,6 +572,18 @@
   </si>
   <si>
     <t>Q325 8K</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
   </si>
 </sst>
 </file>
@@ -1177,14 +1189,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>37</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>37</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
       <xdr:row>35</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
@@ -1201,7 +1213,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="23012400" y="0"/>
+          <a:off x="23637240" y="0"/>
           <a:ext cx="0" cy="6477000"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1227,13 +1239,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>47</xdr:col>
+      <xdr:col>59</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>47</xdr:col>
+      <xdr:col>59</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
@@ -1251,7 +1263,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="29108400" y="0"/>
+          <a:off x="36423600" y="0"/>
           <a:ext cx="0" cy="6111240"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1613,17 +1625,17 @@
         <v>0</v>
       </c>
       <c r="D3" s="5">
-        <v>686.46</v>
+        <v>726.51</v>
       </c>
       <c r="E3" s="2">
-        <v>45960</v>
+        <v>46052</v>
       </c>
       <c r="F3" s="2">
         <f ca="1">TODAY()</f>
-        <v>45960</v>
+        <v>46059</v>
       </c>
       <c r="G3" s="2">
-        <v>46057</v>
+        <v>46141</v>
       </c>
       <c r="I3" s="14" t="s">
         <v>51</v>
@@ -1663,7 +1675,7 @@
       </c>
       <c r="D5" s="4">
         <f>D3*D4</f>
-        <v>1727819.82</v>
+        <v>1828625.67</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -1682,11 +1694,11 @@
         <v>3</v>
       </c>
       <c r="D6" s="4">
-        <f>10187+34261+25074</f>
-        <v>69522</v>
+        <f>35873+45719+27524</f>
+        <v>109116</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F6" s="1"/>
       <c r="I6" s="14" t="s">
@@ -1704,11 +1716,11 @@
         <v>4</v>
       </c>
       <c r="D7" s="4">
-        <f>28834</f>
-        <v>28834</v>
+        <f>58744</f>
+        <v>58744</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F7" s="1"/>
       <c r="I7" s="17" t="s">
@@ -1727,7 +1739,7 @@
       </c>
       <c r="D8" s="4">
         <f>D6-D7</f>
-        <v>40688</v>
+        <v>50372</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
@@ -1738,7 +1750,7 @@
       </c>
       <c r="D9" s="4">
         <f>D5-D8</f>
-        <v>1687131.82</v>
+        <v>1778253.67</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
@@ -1751,16 +1763,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15DD6CAC-9C85-445D-A50B-99FA437D4B08}">
-  <dimension ref="B2:FI26"/>
+  <dimension ref="B2:FT26"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="55" max="56" width="8.88671875" customWidth="1"/>
-    <col min="60" max="60" width="12" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="66" max="67" width="8.88671875" customWidth="1"/>
+    <col min="71" max="71" width="12" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="17.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:165">
+    <row r="2" spans="2:176">
       <c r="C2" s="3" t="s">
         <v>11</v>
       </c>
@@ -1869,65 +1881,99 @@
       <c r="AL2" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="AN2">
+      <c r="AM2" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="AN2" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="AO2" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="AP2" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="AQ2" s="3"/>
+      <c r="AR2">
+        <v>2010</v>
+      </c>
+      <c r="AS2">
+        <v>2011</v>
+      </c>
+      <c r="AT2">
+        <v>2012</v>
+      </c>
+      <c r="AU2">
+        <v>2013</v>
+      </c>
+      <c r="AV2">
+        <v>2014</v>
+      </c>
+      <c r="AW2">
+        <v>2015</v>
+      </c>
+      <c r="AX2">
+        <v>2016</v>
+      </c>
+      <c r="AY2">
         <v>2017</v>
       </c>
-      <c r="AO2">
+      <c r="AZ2">
         <v>2018</v>
       </c>
-      <c r="AP2">
+      <c r="BA2">
         <v>2019</v>
       </c>
-      <c r="AQ2">
+      <c r="BB2">
         <v>2020</v>
       </c>
-      <c r="AR2">
+      <c r="BC2">
         <v>2021</v>
       </c>
-      <c r="AS2">
+      <c r="BD2">
         <v>2022</v>
       </c>
-      <c r="AT2">
+      <c r="BE2">
         <v>2023</v>
       </c>
-      <c r="AU2">
+      <c r="BF2">
         <v>2024</v>
       </c>
-      <c r="AV2">
+      <c r="BG2">
         <v>2025</v>
       </c>
-      <c r="AW2">
+      <c r="BH2">
         <v>2026</v>
       </c>
-      <c r="AX2">
+      <c r="BI2">
         <v>2027</v>
       </c>
-      <c r="AY2">
+      <c r="BJ2">
         <v>2028</v>
       </c>
-      <c r="AZ2">
+      <c r="BK2">
         <v>2029</v>
       </c>
-      <c r="BA2">
+      <c r="BL2">
         <v>2030</v>
       </c>
-      <c r="BB2">
+      <c r="BM2">
         <v>2031</v>
       </c>
-      <c r="BC2">
+      <c r="BN2">
         <v>2032</v>
       </c>
-      <c r="BD2">
+      <c r="BO2">
         <v>2033</v>
       </c>
-      <c r="BE2">
+      <c r="BP2">
         <v>2034</v>
       </c>
-      <c r="BF2">
+      <c r="BQ2">
         <v>2035</v>
       </c>
     </row>
-    <row r="3" spans="2:165" s="6" customFormat="1">
+    <row r="3" spans="2:176" s="6" customFormat="1">
       <c r="B3" s="6" t="s">
         <v>10</v>
       </c>
@@ -2037,87 +2083,112 @@
         <v>51242</v>
       </c>
       <c r="AL3" s="8">
-        <f>AH3*1.2</f>
-        <v>58062</v>
-      </c>
-      <c r="AN3" s="8">
+        <v>59893</v>
+      </c>
+      <c r="AM3" s="8"/>
+      <c r="AN3" s="8"/>
+      <c r="AO3" s="8"/>
+      <c r="AP3" s="8"/>
+      <c r="AQ3" s="8"/>
+      <c r="AR3" s="8">
+        <v>1974</v>
+      </c>
+      <c r="AS3" s="8">
+        <v>3711</v>
+      </c>
+      <c r="AT3" s="8">
+        <v>5089</v>
+      </c>
+      <c r="AU3" s="8">
+        <v>7872</v>
+      </c>
+      <c r="AV3" s="8">
+        <v>12466</v>
+      </c>
+      <c r="AW3" s="8">
+        <v>17928</v>
+      </c>
+      <c r="AX3" s="8">
+        <v>27638</v>
+      </c>
+      <c r="AY3" s="8">
         <f>SUM(C3:F3)</f>
         <v>40653</v>
       </c>
-      <c r="AO3" s="8">
+      <c r="AZ3" s="8">
         <f>SUM(G3:J3)</f>
         <v>55838</v>
       </c>
-      <c r="AP3" s="8">
+      <c r="BA3" s="8">
         <f>SUM(K3:N3)</f>
         <v>70677</v>
       </c>
-      <c r="AQ3" s="8">
+      <c r="BB3" s="8">
         <f>SUM(O3:R3)</f>
         <v>85966</v>
       </c>
-      <c r="AR3" s="8">
+      <c r="BC3" s="8">
         <f>SUM(S3:V3)</f>
         <v>117929</v>
       </c>
-      <c r="AS3" s="8">
+      <c r="BD3" s="8">
         <f>SUM(W3:Z3)</f>
         <v>116609</v>
       </c>
-      <c r="AT3" s="8">
+      <c r="BE3" s="8">
         <f>SUM(AA3:AD3)</f>
         <v>135171</v>
       </c>
-      <c r="AU3" s="8">
+      <c r="BF3" s="8">
         <f>SUM(AE3:AH3)</f>
         <v>164500</v>
       </c>
-      <c r="AV3" s="8">
+      <c r="BG3" s="8">
         <f>SUM(AI3:AL3)</f>
-        <v>199134</v>
-      </c>
-      <c r="AW3" s="8">
-        <f>AV3*1.14</f>
-        <v>227012.75999999998</v>
-      </c>
-      <c r="AX3" s="8">
-        <f>AW3*1.08</f>
-        <v>245173.78080000001</v>
-      </c>
-      <c r="AY3" s="8">
-        <f>AX3*1.06</f>
-        <v>259884.20764800001</v>
-      </c>
-      <c r="AZ3" s="8">
-        <f>AY3*1.04</f>
-        <v>270279.57595392002</v>
-      </c>
-      <c r="BA3" s="8">
-        <f>AZ3*1.03</f>
-        <v>278387.96323253762</v>
-      </c>
-      <c r="BB3" s="8">
-        <f t="shared" ref="BB3" si="0">BA3*1.02</f>
-        <v>283955.72249718837</v>
-      </c>
-      <c r="BC3" s="8">
-        <f t="shared" ref="BC3" si="1">BB3*1.02</f>
-        <v>289634.83694713213</v>
-      </c>
-      <c r="BD3" s="8">
-        <f t="shared" ref="BD3" si="2">BC3*1.02</f>
-        <v>295427.53368607478</v>
-      </c>
-      <c r="BE3" s="8">
-        <f t="shared" ref="BE3" si="3">BD3*1.02</f>
-        <v>301336.08435979625</v>
-      </c>
-      <c r="BF3" s="8">
-        <f t="shared" ref="BF3" si="4">BE3*1.02</f>
-        <v>307362.80604699219</v>
-      </c>
-    </row>
-    <row r="4" spans="2:165">
+        <v>200965</v>
+      </c>
+      <c r="BH3" s="8">
+        <f>BG3*1.15</f>
+        <v>231109.74999999997</v>
+      </c>
+      <c r="BI3" s="8">
+        <f>BH3*1.08</f>
+        <v>249598.53</v>
+      </c>
+      <c r="BJ3" s="8">
+        <f>BI3*1.06</f>
+        <v>264574.44180000003</v>
+      </c>
+      <c r="BK3" s="8">
+        <f>BJ3*1.04</f>
+        <v>275157.41947200004</v>
+      </c>
+      <c r="BL3" s="8">
+        <f>BK3*1.03</f>
+        <v>283412.14205616002</v>
+      </c>
+      <c r="BM3" s="8">
+        <f t="shared" ref="BM3" si="0">BL3*1.02</f>
+        <v>289080.38489728322</v>
+      </c>
+      <c r="BN3" s="8">
+        <f t="shared" ref="BN3" si="1">BM3*1.02</f>
+        <v>294861.99259522889</v>
+      </c>
+      <c r="BO3" s="8">
+        <f t="shared" ref="BO3" si="2">BN3*1.02</f>
+        <v>300759.23244713346</v>
+      </c>
+      <c r="BP3" s="8">
+        <f t="shared" ref="BP3" si="3">BO3*1.02</f>
+        <v>306774.41709607613</v>
+      </c>
+      <c r="BQ3" s="8">
+        <f t="shared" ref="BQ3" si="4">BP3*1.02</f>
+        <v>312909.90543799766</v>
+      </c>
+    </row>
+    <row r="4" spans="2:176">
       <c r="B4" t="s">
         <v>26</v>
       </c>
@@ -2227,312 +2298,370 @@
         <v>9206</v>
       </c>
       <c r="AL4" s="4">
-        <f t="shared" ref="AL4" si="5">AL3-AL5</f>
-        <v>10451.160000000003</v>
-      </c>
-      <c r="AN4" s="4">
+        <v>10905</v>
+      </c>
+      <c r="AM4" s="4"/>
+      <c r="AN4" s="4"/>
+      <c r="AO4" s="4"/>
+      <c r="AP4" s="4"/>
+      <c r="AQ4" s="4"/>
+      <c r="AR4" s="4">
+        <v>493</v>
+      </c>
+      <c r="AS4" s="4">
+        <v>860</v>
+      </c>
+      <c r="AT4" s="4">
+        <v>1364</v>
+      </c>
+      <c r="AU4" s="4">
+        <v>1875</v>
+      </c>
+      <c r="AV4" s="4">
+        <v>2153</v>
+      </c>
+      <c r="AW4" s="4">
+        <v>2867</v>
+      </c>
+      <c r="AX4" s="4">
+        <v>3789</v>
+      </c>
+      <c r="AY4" s="4">
         <f>SUM(C4:F4)</f>
         <v>5455</v>
       </c>
-      <c r="AO4" s="4">
+      <c r="AZ4" s="4">
         <f>SUM(G4:J4)</f>
         <v>9355</v>
       </c>
-      <c r="AP4" s="4">
+      <c r="BA4" s="4">
         <f>SUM(K4:N4)</f>
         <v>12770</v>
       </c>
-      <c r="AQ4" s="4">
+      <c r="BB4" s="4">
         <f>SUM(O4:R4)</f>
         <v>16692</v>
       </c>
-      <c r="AR4" s="4">
+      <c r="BC4" s="4">
         <f>SUM(S4:V4)</f>
         <v>22649</v>
       </c>
-      <c r="AS4" s="4">
+      <c r="BD4" s="4">
         <f>SUM(W4:Z4)</f>
         <v>25249</v>
       </c>
-      <c r="AT4" s="4">
+      <c r="BE4" s="4">
         <f>SUM(AA4:AD4)</f>
         <v>25958</v>
       </c>
-      <c r="AU4" s="4">
+      <c r="BF4" s="4">
         <f>SUM(AE4:AH4)</f>
         <v>30162</v>
       </c>
-      <c r="AV4" s="4">
+      <c r="BG4" s="4">
         <f>SUM(AI4:AL4)</f>
-        <v>35720.160000000003</v>
-      </c>
-      <c r="AW4" s="4">
-        <f t="shared" ref="AW4:BA4" si="6">AW3-AW5</f>
-        <v>40862.296800000011</v>
-      </c>
-      <c r="AX4" s="4">
+        <v>36174</v>
+      </c>
+      <c r="BH4" s="4">
+        <f t="shared" ref="BH4:BL4" si="5">BH3-BH5</f>
+        <v>41599.755000000005</v>
+      </c>
+      <c r="BI4" s="4">
+        <f t="shared" si="5"/>
+        <v>44927.735400000005</v>
+      </c>
+      <c r="BJ4" s="4">
+        <f t="shared" si="5"/>
+        <v>47623.399524000008</v>
+      </c>
+      <c r="BK4" s="4">
+        <f t="shared" si="5"/>
+        <v>49528.335504960007</v>
+      </c>
+      <c r="BL4" s="4">
+        <f t="shared" si="5"/>
+        <v>51014.185570108821</v>
+      </c>
+      <c r="BM4" s="4">
+        <f t="shared" ref="BM4:BQ4" si="6">BM3-BM5</f>
+        <v>52034.469281511003</v>
+      </c>
+      <c r="BN4" s="4">
         <f t="shared" si="6"/>
-        <v>44131.280544000008</v>
-      </c>
-      <c r="AY4" s="4">
+        <v>53075.158667141222</v>
+      </c>
+      <c r="BO4" s="4">
         <f t="shared" si="6"/>
-        <v>46779.157376640011</v>
-      </c>
-      <c r="AZ4" s="4">
+        <v>54136.661840484041</v>
+      </c>
+      <c r="BP4" s="4">
         <f t="shared" si="6"/>
-        <v>48650.323671705613</v>
-      </c>
-      <c r="BA4" s="4">
+        <v>55219.39507729371</v>
+      </c>
+      <c r="BQ4" s="4">
         <f t="shared" si="6"/>
-        <v>50109.833381856792</v>
-      </c>
-      <c r="BB4" s="4">
-        <f t="shared" ref="BB4:BF4" si="7">BB3-BB5</f>
-        <v>51112.030049493915</v>
-      </c>
-      <c r="BC4" s="4">
-        <f t="shared" si="7"/>
-        <v>52134.270650483784</v>
-      </c>
-      <c r="BD4" s="4">
-        <f t="shared" si="7"/>
-        <v>53176.956063493475</v>
-      </c>
-      <c r="BE4" s="4">
-        <f t="shared" si="7"/>
-        <v>54240.495184763335</v>
-      </c>
-      <c r="BF4" s="4">
-        <f t="shared" si="7"/>
-        <v>55325.305088458612</v>
-      </c>
-    </row>
-    <row r="5" spans="2:165" s="6" customFormat="1">
+        <v>56323.78297883959</v>
+      </c>
+    </row>
+    <row r="5" spans="2:176" s="6" customFormat="1">
       <c r="B5" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C5" s="8">
-        <f t="shared" ref="C5:S5" si="8">C3-C4</f>
+        <f t="shared" ref="C5:S5" si="7">C3-C4</f>
         <v>6873</v>
       </c>
       <c r="D5" s="8">
+        <f t="shared" si="7"/>
+        <v>8084</v>
+      </c>
+      <c r="E5" s="8">
+        <f t="shared" si="7"/>
+        <v>8880</v>
+      </c>
+      <c r="F5" s="8">
+        <f t="shared" si="7"/>
+        <v>11361</v>
+      </c>
+      <c r="G5" s="8">
+        <f t="shared" si="7"/>
+        <v>10039</v>
+      </c>
+      <c r="H5" s="8">
+        <f t="shared" si="7"/>
+        <v>11017</v>
+      </c>
+      <c r="I5" s="8">
+        <f t="shared" si="7"/>
+        <v>11309</v>
+      </c>
+      <c r="J5" s="8">
+        <f t="shared" si="7"/>
+        <v>14118</v>
+      </c>
+      <c r="K5" s="8">
+        <f t="shared" si="7"/>
+        <v>12261</v>
+      </c>
+      <c r="L5" s="8">
+        <f t="shared" si="7"/>
+        <v>13559</v>
+      </c>
+      <c r="M5" s="8">
+        <f t="shared" si="7"/>
+        <v>14497</v>
+      </c>
+      <c r="N5" s="8">
+        <f t="shared" si="7"/>
+        <v>17590</v>
+      </c>
+      <c r="O5" s="8">
+        <f t="shared" si="7"/>
+        <v>14278</v>
+      </c>
+      <c r="P5" s="8">
+        <f t="shared" si="7"/>
+        <v>14858</v>
+      </c>
+      <c r="Q5" s="8">
+        <f t="shared" si="7"/>
+        <v>17276</v>
+      </c>
+      <c r="R5" s="8">
+        <f t="shared" si="7"/>
+        <v>22862</v>
+      </c>
+      <c r="S5" s="8">
+        <f t="shared" si="7"/>
+        <v>21040</v>
+      </c>
+      <c r="T5" s="8">
+        <f t="shared" ref="T5:U5" si="8">T3-T4</f>
+        <v>23678</v>
+      </c>
+      <c r="U5" s="8">
         <f t="shared" si="8"/>
-        <v>8084</v>
-      </c>
-      <c r="E5" s="8">
-        <f t="shared" si="8"/>
-        <v>8880</v>
-      </c>
-      <c r="F5" s="8">
-        <f t="shared" si="8"/>
-        <v>11361</v>
-      </c>
-      <c r="G5" s="8">
-        <f t="shared" si="8"/>
-        <v>10039</v>
-      </c>
-      <c r="H5" s="8">
-        <f t="shared" si="8"/>
-        <v>11017</v>
-      </c>
-      <c r="I5" s="8">
-        <f t="shared" si="8"/>
-        <v>11309</v>
-      </c>
-      <c r="J5" s="8">
-        <f t="shared" si="8"/>
-        <v>14118</v>
-      </c>
-      <c r="K5" s="8">
-        <f t="shared" si="8"/>
-        <v>12261</v>
-      </c>
-      <c r="L5" s="8">
-        <f t="shared" si="8"/>
-        <v>13559</v>
-      </c>
-      <c r="M5" s="8">
-        <f t="shared" si="8"/>
-        <v>14497</v>
-      </c>
-      <c r="N5" s="8">
-        <f t="shared" si="8"/>
-        <v>17590</v>
-      </c>
-      <c r="O5" s="8">
-        <f t="shared" si="8"/>
-        <v>14278</v>
-      </c>
-      <c r="P5" s="8">
-        <f t="shared" si="8"/>
-        <v>14858</v>
-      </c>
-      <c r="Q5" s="8">
-        <f t="shared" si="8"/>
-        <v>17276</v>
-      </c>
-      <c r="R5" s="8">
-        <f t="shared" si="8"/>
-        <v>22862</v>
-      </c>
-      <c r="S5" s="8">
-        <f t="shared" si="8"/>
-        <v>21040</v>
-      </c>
-      <c r="T5" s="8">
-        <f t="shared" ref="T5:U5" si="9">T3-T4</f>
-        <v>23678</v>
-      </c>
-      <c r="U5" s="8">
-        <f t="shared" si="9"/>
         <v>23239</v>
       </c>
       <c r="V5" s="8">
-        <f t="shared" ref="V5" si="10">V3-V4</f>
+        <f t="shared" ref="V5" si="9">V3-V4</f>
         <v>27323</v>
       </c>
       <c r="W5" s="8">
-        <f t="shared" ref="W5:X5" si="11">W3-W4</f>
+        <f t="shared" ref="W5:X5" si="10">W3-W4</f>
         <v>21903</v>
       </c>
       <c r="X5" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>23630</v>
       </c>
       <c r="Y5" s="8">
-        <f t="shared" ref="Y5" si="12">Y3-Y4</f>
+        <f t="shared" ref="Y5" si="11">Y3-Y4</f>
         <v>21998</v>
       </c>
       <c r="Z5" s="8">
-        <f t="shared" ref="Z5" si="13">Z3-Z4</f>
+        <f t="shared" ref="Z5" si="12">Z3-Z4</f>
         <v>23829</v>
       </c>
       <c r="AA5" s="8">
-        <f t="shared" ref="AA5:AC5" si="14">AA3-AA4</f>
+        <f t="shared" ref="AA5:AC5" si="13">AA3-AA4</f>
         <v>22537</v>
       </c>
       <c r="AB5" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>26054</v>
       </c>
       <c r="AC5" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>28206</v>
       </c>
       <c r="AD5" s="8">
-        <f t="shared" ref="AD5" si="15">AD3-AD4</f>
+        <f t="shared" ref="AD5" si="14">AD3-AD4</f>
         <v>32416</v>
       </c>
       <c r="AE5" s="8">
-        <f t="shared" ref="AE5:AK5" si="16">AE3-AE4</f>
+        <f t="shared" ref="AE5:AL5" si="15">AE3-AE4</f>
         <v>29815</v>
       </c>
       <c r="AF5" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>31763</v>
       </c>
       <c r="AG5" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>33214</v>
       </c>
       <c r="AH5" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>39546</v>
       </c>
       <c r="AI5" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>34742</v>
       </c>
       <c r="AJ5" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>39025</v>
       </c>
       <c r="AK5" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>42036</v>
       </c>
       <c r="AL5" s="8">
-        <f t="shared" ref="AL5" si="17">AL3*0.82</f>
-        <v>47610.84</v>
-      </c>
-      <c r="AN5" s="8">
-        <f t="shared" ref="AN5:AU5" si="18">AN3-AN4</f>
+        <f t="shared" si="15"/>
+        <v>48988</v>
+      </c>
+      <c r="AM5" s="8"/>
+      <c r="AN5" s="8"/>
+      <c r="AO5" s="8"/>
+      <c r="AP5" s="8"/>
+      <c r="AQ5" s="8"/>
+      <c r="AR5" s="8">
+        <f t="shared" ref="AR5" si="16">AR3-AR4</f>
+        <v>1481</v>
+      </c>
+      <c r="AS5" s="8">
+        <f t="shared" ref="AS5:AT5" si="17">AS3-AS4</f>
+        <v>2851</v>
+      </c>
+      <c r="AT5" s="8">
+        <f t="shared" si="17"/>
+        <v>3725</v>
+      </c>
+      <c r="AU5" s="8">
+        <f t="shared" ref="AU5" si="18">AU3-AU4</f>
+        <v>5997</v>
+      </c>
+      <c r="AV5" s="8">
+        <f t="shared" ref="AV5" si="19">AV3-AV4</f>
+        <v>10313</v>
+      </c>
+      <c r="AW5" s="8">
+        <f t="shared" ref="AW5:AX5" si="20">AW3-AW4</f>
+        <v>15061</v>
+      </c>
+      <c r="AX5" s="8">
+        <f t="shared" si="20"/>
+        <v>23849</v>
+      </c>
+      <c r="AY5" s="8">
+        <f t="shared" ref="AY5:BF5" si="21">AY3-AY4</f>
         <v>35198</v>
       </c>
-      <c r="AO5" s="8">
-        <f t="shared" si="18"/>
+      <c r="AZ5" s="8">
+        <f t="shared" si="21"/>
         <v>46483</v>
       </c>
-      <c r="AP5" s="8">
-        <f t="shared" si="18"/>
+      <c r="BA5" s="8">
+        <f t="shared" si="21"/>
         <v>57907</v>
       </c>
-      <c r="AQ5" s="8">
-        <f t="shared" si="18"/>
+      <c r="BB5" s="8">
+        <f t="shared" si="21"/>
         <v>69274</v>
       </c>
-      <c r="AR5" s="8">
-        <f t="shared" si="18"/>
+      <c r="BC5" s="8">
+        <f t="shared" si="21"/>
         <v>95280</v>
       </c>
-      <c r="AS5" s="8">
-        <f t="shared" si="18"/>
+      <c r="BD5" s="8">
+        <f t="shared" si="21"/>
         <v>91360</v>
       </c>
-      <c r="AT5" s="8">
-        <f t="shared" si="18"/>
+      <c r="BE5" s="8">
+        <f t="shared" si="21"/>
         <v>109213</v>
       </c>
-      <c r="AU5" s="8">
-        <f t="shared" si="18"/>
+      <c r="BF5" s="8">
+        <f t="shared" si="21"/>
         <v>134338</v>
       </c>
-      <c r="AV5" s="8">
-        <f>AV3*0.82</f>
-        <v>163289.88</v>
-      </c>
-      <c r="AW5" s="8">
-        <f t="shared" ref="AW5:BF5" si="19">AW3*0.82</f>
-        <v>186150.46319999997</v>
-      </c>
-      <c r="AX5" s="8">
-        <f t="shared" si="19"/>
-        <v>201042.500256</v>
-      </c>
-      <c r="AY5" s="8">
-        <f t="shared" si="19"/>
-        <v>213105.05027136</v>
-      </c>
-      <c r="AZ5" s="8">
-        <f t="shared" si="19"/>
-        <v>221629.25228221441</v>
-      </c>
-      <c r="BA5" s="8">
-        <f t="shared" si="19"/>
-        <v>228278.12985068082</v>
-      </c>
-      <c r="BB5" s="8">
-        <f t="shared" si="19"/>
-        <v>232843.69244769446</v>
-      </c>
-      <c r="BC5" s="8">
-        <f t="shared" si="19"/>
-        <v>237500.56629664835</v>
-      </c>
-      <c r="BD5" s="8">
-        <f t="shared" si="19"/>
-        <v>242250.5776225813</v>
-      </c>
-      <c r="BE5" s="8">
-        <f t="shared" si="19"/>
-        <v>247095.58917503292</v>
-      </c>
-      <c r="BF5" s="8">
-        <f t="shared" si="19"/>
-        <v>252037.50095853358</v>
-      </c>
-    </row>
-    <row r="6" spans="2:165">
+      <c r="BG5" s="8">
+        <f>BG3*0.82</f>
+        <v>164791.29999999999</v>
+      </c>
+      <c r="BH5" s="8">
+        <f t="shared" ref="BH5:BQ5" si="22">BH3*0.82</f>
+        <v>189509.99499999997</v>
+      </c>
+      <c r="BI5" s="8">
+        <f t="shared" si="22"/>
+        <v>204670.79459999999</v>
+      </c>
+      <c r="BJ5" s="8">
+        <f t="shared" si="22"/>
+        <v>216951.04227600002</v>
+      </c>
+      <c r="BK5" s="8">
+        <f t="shared" si="22"/>
+        <v>225629.08396704003</v>
+      </c>
+      <c r="BL5" s="8">
+        <f t="shared" si="22"/>
+        <v>232397.9564860512</v>
+      </c>
+      <c r="BM5" s="8">
+        <f t="shared" si="22"/>
+        <v>237045.91561577222</v>
+      </c>
+      <c r="BN5" s="8">
+        <f t="shared" si="22"/>
+        <v>241786.83392808767</v>
+      </c>
+      <c r="BO5" s="8">
+        <f t="shared" si="22"/>
+        <v>246622.57060664942</v>
+      </c>
+      <c r="BP5" s="8">
+        <f t="shared" si="22"/>
+        <v>251555.02201878242</v>
+      </c>
+      <c r="BQ5" s="8">
+        <f t="shared" si="22"/>
+        <v>256586.12245915807</v>
+      </c>
+    </row>
+    <row r="6" spans="2:176">
       <c r="B6" t="s">
         <v>27</v>
       </c>
@@ -2642,87 +2771,112 @@
         <v>15144</v>
       </c>
       <c r="AL6" s="4">
-        <f>AH6*1.3</f>
-        <v>15834</v>
-      </c>
-      <c r="AN6" s="4">
+        <v>17136</v>
+      </c>
+      <c r="AM6" s="4"/>
+      <c r="AN6" s="4"/>
+      <c r="AO6" s="4"/>
+      <c r="AP6" s="4"/>
+      <c r="AQ6" s="4"/>
+      <c r="AR6" s="4">
+        <v>144</v>
+      </c>
+      <c r="AS6" s="4">
+        <v>388</v>
+      </c>
+      <c r="AT6" s="4">
+        <v>1399</v>
+      </c>
+      <c r="AU6" s="4">
+        <v>1415</v>
+      </c>
+      <c r="AV6" s="4">
+        <v>2666</v>
+      </c>
+      <c r="AW6" s="4">
+        <v>4816</v>
+      </c>
+      <c r="AX6" s="4">
+        <v>5919</v>
+      </c>
+      <c r="AY6" s="4">
         <f>SUM(C6:F6)</f>
         <v>7754</v>
       </c>
-      <c r="AO6" s="4">
+      <c r="AZ6" s="4">
         <f>SUM(G6:J6)</f>
         <v>10273</v>
       </c>
-      <c r="AP6" s="4">
+      <c r="BA6" s="4">
         <f>SUM(K6:N6)</f>
         <v>13600</v>
       </c>
-      <c r="AQ6" s="4">
+      <c r="BB6" s="4">
         <f>SUM(O6:R6)</f>
         <v>18448</v>
       </c>
-      <c r="AR6" s="4">
+      <c r="BC6" s="4">
         <f>SUM(S6:V6)</f>
         <v>24655</v>
       </c>
-      <c r="AS6" s="4">
+      <c r="BD6" s="4">
         <f>SUM(W6:Z6)</f>
         <v>35338</v>
       </c>
-      <c r="AT6" s="4">
+      <c r="BE6" s="4">
         <f>SUM(AA6:AD6)</f>
         <v>38483</v>
       </c>
-      <c r="AU6" s="4">
+      <c r="BF6" s="4">
         <f>SUM(AE6:AH6)</f>
         <v>43872</v>
       </c>
-      <c r="AV6" s="4">
+      <c r="BG6" s="4">
         <f>SUM(AI6:AL6)</f>
-        <v>56070</v>
-      </c>
-      <c r="AW6" s="4">
-        <f>AV6*1.14</f>
-        <v>63919.799999999996</v>
-      </c>
-      <c r="AX6" s="4">
-        <f>AW6*1.06</f>
-        <v>67754.987999999998</v>
-      </c>
-      <c r="AY6" s="4">
-        <f>AX6*1.04</f>
-        <v>70465.187520000007</v>
-      </c>
-      <c r="AZ6" s="4">
-        <f t="shared" ref="AZ6:BA6" si="20">AY6*1.03</f>
-        <v>72579.143145600014</v>
-      </c>
-      <c r="BA6" s="4">
-        <f t="shared" si="20"/>
-        <v>74756.517439968011</v>
-      </c>
-      <c r="BB6" s="4">
-        <f>BA6*1.02</f>
-        <v>76251.647788767368</v>
-      </c>
-      <c r="BC6" s="4">
-        <f t="shared" ref="BC6:BF6" si="21">BB6*1.02</f>
-        <v>77776.680744542711</v>
-      </c>
-      <c r="BD6" s="4">
-        <f t="shared" si="21"/>
-        <v>79332.214359433565</v>
-      </c>
-      <c r="BE6" s="4">
-        <f t="shared" si="21"/>
-        <v>80918.858646622233</v>
-      </c>
-      <c r="BF6" s="4">
-        <f t="shared" si="21"/>
-        <v>82537.235819554684</v>
-      </c>
-    </row>
-    <row r="7" spans="2:165">
+        <v>57372</v>
+      </c>
+      <c r="BH6" s="4">
+        <f>BG6*1.14</f>
+        <v>65404.079999999994</v>
+      </c>
+      <c r="BI6" s="4">
+        <f>BH6*1.06</f>
+        <v>69328.324800000002</v>
+      </c>
+      <c r="BJ6" s="4">
+        <f>BI6*1.04</f>
+        <v>72101.457792000001</v>
+      </c>
+      <c r="BK6" s="4">
+        <f t="shared" ref="BK6:BL6" si="23">BJ6*1.03</f>
+        <v>74264.501525760003</v>
+      </c>
+      <c r="BL6" s="4">
+        <f t="shared" si="23"/>
+        <v>76492.436571532802</v>
+      </c>
+      <c r="BM6" s="4">
+        <f>BL6*1.02</f>
+        <v>78022.285302963457</v>
+      </c>
+      <c r="BN6" s="4">
+        <f t="shared" ref="BN6:BQ6" si="24">BM6*1.02</f>
+        <v>79582.731009022726</v>
+      </c>
+      <c r="BO6" s="4">
+        <f t="shared" si="24"/>
+        <v>81174.385629203185</v>
+      </c>
+      <c r="BP6" s="4">
+        <f t="shared" si="24"/>
+        <v>82797.873341787257</v>
+      </c>
+      <c r="BQ6" s="4">
+        <f t="shared" si="24"/>
+        <v>84453.83080862301</v>
+      </c>
+    </row>
+    <row r="7" spans="2:176">
       <c r="B7" t="s">
         <v>28</v>
       </c>
@@ -2832,87 +2986,112 @@
         <v>2845</v>
       </c>
       <c r="AL7" s="4">
-        <f t="shared" ref="AL7" si="22">AL3*0.065</f>
-        <v>3774.03</v>
-      </c>
-      <c r="AN7" s="4">
+        <v>3410</v>
+      </c>
+      <c r="AM7" s="4"/>
+      <c r="AN7" s="4"/>
+      <c r="AO7" s="4"/>
+      <c r="AP7" s="4"/>
+      <c r="AQ7" s="4"/>
+      <c r="AR7" s="4">
+        <v>167</v>
+      </c>
+      <c r="AS7" s="4">
+        <v>393</v>
+      </c>
+      <c r="AT7" s="4">
+        <v>896</v>
+      </c>
+      <c r="AU7" s="4">
+        <v>997</v>
+      </c>
+      <c r="AV7" s="4">
+        <v>1680</v>
+      </c>
+      <c r="AW7" s="4">
+        <v>2725</v>
+      </c>
+      <c r="AX7" s="4">
+        <v>3772</v>
+      </c>
+      <c r="AY7" s="4">
         <f>SUM(C7:F7)</f>
         <v>4725</v>
       </c>
-      <c r="AO7" s="4">
+      <c r="AZ7" s="4">
         <f>SUM(G7:J7)</f>
         <v>7845</v>
       </c>
-      <c r="AP7" s="4">
+      <c r="BA7" s="4">
         <f>SUM(K7:N7)</f>
         <v>9876</v>
       </c>
-      <c r="AQ7" s="4">
+      <c r="BB7" s="4">
         <f>SUM(O7:R7)</f>
         <v>11590</v>
       </c>
-      <c r="AR7" s="4">
+      <c r="BC7" s="4">
         <f>SUM(S7:V7)</f>
         <v>14043</v>
       </c>
-      <c r="AS7" s="4">
+      <c r="BD7" s="4">
         <f>SUM(W7:Z7)</f>
         <v>15261</v>
       </c>
-      <c r="AT7" s="4">
+      <c r="BE7" s="4">
         <f>SUM(AA7:AD7)</f>
         <v>12301</v>
       </c>
-      <c r="AU7" s="4">
+      <c r="BF7" s="4">
         <f>SUM(AE7:AH7)</f>
         <v>11347</v>
       </c>
-      <c r="AV7" s="4">
+      <c r="BG7" s="4">
         <f>SUM(AI7:AL7)</f>
-        <v>12355.03</v>
-      </c>
-      <c r="AW7" s="4">
-        <f>AW3*0.065</f>
-        <v>14755.829399999999</v>
-      </c>
-      <c r="AX7" s="4">
-        <f t="shared" ref="AX7:BF7" si="23">AX3*0.065</f>
-        <v>15936.295752000002</v>
-      </c>
-      <c r="AY7" s="4">
-        <f t="shared" si="23"/>
-        <v>16892.473497120001</v>
-      </c>
-      <c r="AZ7" s="4">
-        <f t="shared" si="23"/>
-        <v>17568.172437004803</v>
-      </c>
-      <c r="BA7" s="4">
-        <f t="shared" si="23"/>
-        <v>18095.217610114945</v>
-      </c>
-      <c r="BB7" s="4">
-        <f t="shared" si="23"/>
-        <v>18457.121962317244</v>
-      </c>
-      <c r="BC7" s="4">
-        <f t="shared" si="23"/>
-        <v>18826.264401563589</v>
-      </c>
-      <c r="BD7" s="4">
-        <f t="shared" si="23"/>
-        <v>19202.789689594862</v>
-      </c>
-      <c r="BE7" s="4">
-        <f t="shared" si="23"/>
-        <v>19586.845483386758</v>
-      </c>
-      <c r="BF7" s="4">
-        <f t="shared" si="23"/>
-        <v>19978.582393054494</v>
-      </c>
-    </row>
-    <row r="8" spans="2:165">
+        <v>11991</v>
+      </c>
+      <c r="BH7" s="4">
+        <f>BH3*0.065</f>
+        <v>15022.133749999999</v>
+      </c>
+      <c r="BI7" s="4">
+        <f t="shared" ref="BI7:BQ7" si="25">BI3*0.065</f>
+        <v>16223.90445</v>
+      </c>
+      <c r="BJ7" s="4">
+        <f t="shared" si="25"/>
+        <v>17197.338717000002</v>
+      </c>
+      <c r="BK7" s="4">
+        <f t="shared" si="25"/>
+        <v>17885.232265680002</v>
+      </c>
+      <c r="BL7" s="4">
+        <f t="shared" si="25"/>
+        <v>18421.789233650401</v>
+      </c>
+      <c r="BM7" s="4">
+        <f t="shared" si="25"/>
+        <v>18790.22501832341</v>
+      </c>
+      <c r="BN7" s="4">
+        <f t="shared" si="25"/>
+        <v>19166.02951868988</v>
+      </c>
+      <c r="BO7" s="4">
+        <f t="shared" si="25"/>
+        <v>19549.350109063675</v>
+      </c>
+      <c r="BP7" s="4">
+        <f t="shared" si="25"/>
+        <v>19940.337111244949</v>
+      </c>
+      <c r="BQ7" s="4">
+        <f t="shared" si="25"/>
+        <v>20339.14385346985</v>
+      </c>
+    </row>
+    <row r="8" spans="2:176">
       <c r="B8" t="s">
         <v>29</v>
       </c>
@@ -3023,312 +3202,370 @@
         <v>3512</v>
       </c>
       <c r="AL8" s="4">
-        <f>AH8*1.65</f>
-        <v>3813.1499999999996</v>
-      </c>
-      <c r="AN8" s="4">
+        <v>3697</v>
+      </c>
+      <c r="AM8" s="4"/>
+      <c r="AN8" s="4"/>
+      <c r="AO8" s="4"/>
+      <c r="AP8" s="4"/>
+      <c r="AQ8" s="4"/>
+      <c r="AR8" s="4">
+        <v>138</v>
+      </c>
+      <c r="AS8" s="4">
+        <v>314</v>
+      </c>
+      <c r="AT8" s="4">
+        <v>892</v>
+      </c>
+      <c r="AU8" s="4">
+        <v>781</v>
+      </c>
+      <c r="AV8" s="4">
+        <v>973</v>
+      </c>
+      <c r="AW8" s="4">
+        <v>1295</v>
+      </c>
+      <c r="AX8" s="4">
+        <v>1731</v>
+      </c>
+      <c r="AY8" s="4">
         <f>SUM(C8:F8)</f>
         <v>2517</v>
       </c>
-      <c r="AO8" s="4">
+      <c r="AZ8" s="4">
         <f>SUM(G8:J8)</f>
         <v>3452</v>
       </c>
-      <c r="AP8" s="4">
+      <c r="BA8" s="4">
         <f>SUM(K8:N8)</f>
         <v>10465</v>
       </c>
-      <c r="AQ8" s="4">
+      <c r="BB8" s="4">
         <f>SUM(O8:R8)</f>
         <v>6565</v>
       </c>
-      <c r="AR8" s="4">
+      <c r="BC8" s="4">
         <f>SUM(S8:V8)</f>
         <v>9829</v>
       </c>
-      <c r="AS8" s="4">
+      <c r="BD8" s="4">
         <f>SUM(W8:Z8)</f>
         <v>11816</v>
       </c>
-      <c r="AT8" s="4">
+      <c r="BE8" s="4">
         <f>SUM(AA8:AD8)</f>
         <v>11408</v>
       </c>
-      <c r="AU8" s="4">
+      <c r="BF8" s="4">
         <f>SUM(AE8:AH8)</f>
         <v>11289</v>
       </c>
-      <c r="AV8" s="4">
+      <c r="BG8" s="4">
         <f>SUM(AI8:AL8)</f>
-        <v>12268.15</v>
-      </c>
-      <c r="AW8" s="4">
-        <f>AV8*1.14</f>
-        <v>13985.690999999999</v>
-      </c>
-      <c r="AX8" s="4">
-        <f>AW8*1.05</f>
-        <v>14684.975549999999</v>
-      </c>
-      <c r="AY8" s="4">
-        <f>AX8*1.03</f>
-        <v>15125.524816499999</v>
-      </c>
-      <c r="AZ8" s="4">
-        <f>AY8*1.02</f>
-        <v>15428.035312829999</v>
-      </c>
-      <c r="BA8" s="4">
-        <f t="shared" ref="BA8:BF8" si="24">AZ8*1.02</f>
-        <v>15736.596019086599</v>
-      </c>
-      <c r="BB8" s="4">
-        <f t="shared" si="24"/>
-        <v>16051.32793946833</v>
-      </c>
-      <c r="BC8" s="4">
-        <f t="shared" si="24"/>
-        <v>16372.354498257697</v>
-      </c>
-      <c r="BD8" s="4">
-        <f t="shared" si="24"/>
-        <v>16699.80158822285</v>
-      </c>
-      <c r="BE8" s="4">
-        <f t="shared" si="24"/>
-        <v>17033.797619987308</v>
-      </c>
-      <c r="BF8" s="4">
-        <f t="shared" si="24"/>
-        <v>17374.473572387054</v>
-      </c>
-    </row>
-    <row r="9" spans="2:165" s="6" customFormat="1">
+        <v>12152</v>
+      </c>
+      <c r="BH8" s="4">
+        <f>BG8*1.14</f>
+        <v>13853.279999999999</v>
+      </c>
+      <c r="BI8" s="4">
+        <f>BH8*1.05</f>
+        <v>14545.944</v>
+      </c>
+      <c r="BJ8" s="4">
+        <f>BI8*1.03</f>
+        <v>14982.322319999999</v>
+      </c>
+      <c r="BK8" s="4">
+        <f>BJ8*1.02</f>
+        <v>15281.968766399999</v>
+      </c>
+      <c r="BL8" s="4">
+        <f t="shared" ref="BL8:BQ8" si="26">BK8*1.02</f>
+        <v>15587.608141728</v>
+      </c>
+      <c r="BM8" s="4">
+        <f t="shared" si="26"/>
+        <v>15899.36030456256</v>
+      </c>
+      <c r="BN8" s="4">
+        <f t="shared" si="26"/>
+        <v>16217.347510653812</v>
+      </c>
+      <c r="BO8" s="4">
+        <f t="shared" si="26"/>
+        <v>16541.694460866889</v>
+      </c>
+      <c r="BP8" s="4">
+        <f t="shared" si="26"/>
+        <v>16872.528350084227</v>
+      </c>
+      <c r="BQ8" s="4">
+        <f t="shared" si="26"/>
+        <v>17209.978917085911</v>
+      </c>
+    </row>
+    <row r="9" spans="2:176" s="6" customFormat="1">
       <c r="B9" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C9" s="8">
-        <f t="shared" ref="C9:V9" si="25">C5-C6-C7-C8</f>
+        <f t="shared" ref="C9:V9" si="27">C5-C6-C7-C8</f>
         <v>3327</v>
       </c>
       <c r="D9" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>4401</v>
       </c>
       <c r="E9" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>5122</v>
       </c>
       <c r="F9" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>7352</v>
       </c>
       <c r="G9" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>5449</v>
       </c>
       <c r="H9" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>5863</v>
       </c>
       <c r="I9" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>5781</v>
       </c>
       <c r="J9" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>7820</v>
       </c>
       <c r="K9" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>3317</v>
       </c>
       <c r="L9" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>4606</v>
       </c>
       <c r="M9" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>7185</v>
       </c>
       <c r="N9" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>8858</v>
       </c>
       <c r="O9" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>5893</v>
       </c>
       <c r="P9" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>5963</v>
       </c>
       <c r="Q9" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>8040</v>
       </c>
       <c r="R9" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>12775</v>
       </c>
       <c r="S9" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>11378</v>
       </c>
       <c r="T9" s="8">
-        <f t="shared" ref="T9:U9" si="26">T5-T6-T7-T8</f>
+        <f t="shared" ref="T9:U9" si="28">T5-T6-T7-T8</f>
         <v>12367</v>
       </c>
       <c r="U9" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>10423</v>
       </c>
       <c r="V9" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>12585</v>
       </c>
       <c r="W9" s="8">
-        <f t="shared" ref="W9:X9" si="27">W5-W6-W7-W8</f>
+        <f t="shared" ref="W9:X9" si="29">W5-W6-W7-W8</f>
         <v>8524</v>
       </c>
       <c r="X9" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>8358</v>
       </c>
       <c r="Y9" s="8">
-        <f t="shared" ref="Y9" si="28">Y5-Y6-Y7-Y8</f>
+        <f t="shared" ref="Y9" si="30">Y5-Y6-Y7-Y8</f>
         <v>5664</v>
       </c>
       <c r="Z9" s="8">
-        <f t="shared" ref="Z9" si="29">Z5-Z6-Z7-Z8</f>
+        <f t="shared" ref="Z9" si="31">Z5-Z6-Z7-Z8</f>
         <v>6399</v>
       </c>
       <c r="AA9" s="8">
-        <f t="shared" ref="AA9:AC9" si="30">AA5-AA6-AA7-AA8</f>
+        <f t="shared" ref="AA9:AC9" si="32">AA5-AA6-AA7-AA8</f>
         <v>7227</v>
       </c>
       <c r="AB9" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>9392</v>
       </c>
       <c r="AC9" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>14018</v>
       </c>
       <c r="AD9" s="8">
-        <f t="shared" ref="AD9" si="31">AD5-AD6-AD7-AD8</f>
+        <f t="shared" ref="AD9" si="33">AD5-AD6-AD7-AD8</f>
         <v>16384</v>
       </c>
       <c r="AE9" s="8">
-        <f t="shared" ref="AE9:AL9" si="32">AE5-AE6-AE7-AE8</f>
+        <f t="shared" ref="AE9:AL9" si="34">AE5-AE6-AE7-AE8</f>
         <v>13818</v>
       </c>
       <c r="AF9" s="8">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>14847</v>
       </c>
       <c r="AG9" s="8">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>17350</v>
       </c>
       <c r="AH9" s="8">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>21815</v>
       </c>
       <c r="AI9" s="8">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>17555</v>
       </c>
       <c r="AJ9" s="8">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>20441</v>
       </c>
       <c r="AK9" s="8">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>20535</v>
       </c>
       <c r="AL9" s="8">
-        <f t="shared" si="32"/>
-        <v>24189.659999999996</v>
-      </c>
-      <c r="AN9" s="8">
-        <f>AN5-AN6-AN7-AN8</f>
+        <f t="shared" si="34"/>
+        <v>24745</v>
+      </c>
+      <c r="AM9" s="8"/>
+      <c r="AN9" s="8"/>
+      <c r="AO9" s="8"/>
+      <c r="AP9" s="8"/>
+      <c r="AQ9" s="8"/>
+      <c r="AR9" s="8">
+        <f t="shared" ref="AR9:BB9" si="35">AR5-AR6-AR7-AR8</f>
+        <v>1032</v>
+      </c>
+      <c r="AS9" s="8">
+        <f t="shared" si="35"/>
+        <v>1756</v>
+      </c>
+      <c r="AT9" s="8">
+        <f t="shared" si="35"/>
+        <v>538</v>
+      </c>
+      <c r="AU9" s="8">
+        <f t="shared" si="35"/>
+        <v>2804</v>
+      </c>
+      <c r="AV9" s="8">
+        <f t="shared" si="35"/>
+        <v>4994</v>
+      </c>
+      <c r="AW9" s="8">
+        <f t="shared" si="35"/>
+        <v>6225</v>
+      </c>
+      <c r="AX9" s="8">
+        <f t="shared" si="35"/>
+        <v>12427</v>
+      </c>
+      <c r="AY9" s="8">
+        <f t="shared" si="35"/>
         <v>20202</v>
       </c>
-      <c r="AO9" s="8">
-        <f>AO5-AO6-AO7-AO8</f>
+      <c r="AZ9" s="8">
+        <f t="shared" si="35"/>
         <v>24913</v>
       </c>
-      <c r="AP9" s="8">
-        <f>AP5-AP6-AP7-AP8</f>
+      <c r="BA9" s="8">
+        <f t="shared" si="35"/>
         <v>23966</v>
       </c>
-      <c r="AQ9" s="8">
-        <f>AQ5-AQ6-AQ7-AQ8</f>
+      <c r="BB9" s="8">
+        <f t="shared" si="35"/>
         <v>32671</v>
       </c>
-      <c r="AR9" s="8">
-        <f t="shared" ref="AR9:BA9" si="33">AR5-AR6-AR7-AR8</f>
+      <c r="BC9" s="8">
+        <f t="shared" ref="BC9:BL9" si="36">BC5-BC6-BC7-BC8</f>
         <v>46753</v>
       </c>
-      <c r="AS9" s="8">
-        <f t="shared" si="33"/>
+      <c r="BD9" s="8">
+        <f t="shared" si="36"/>
         <v>28945</v>
       </c>
-      <c r="AT9" s="8">
-        <f t="shared" si="33"/>
+      <c r="BE9" s="8">
+        <f t="shared" si="36"/>
         <v>47021</v>
       </c>
-      <c r="AU9" s="8">
-        <f t="shared" si="33"/>
+      <c r="BF9" s="8">
+        <f t="shared" si="36"/>
         <v>67830</v>
       </c>
-      <c r="AV9" s="8">
-        <f t="shared" si="33"/>
-        <v>82596.700000000012</v>
-      </c>
-      <c r="AW9" s="8">
-        <f t="shared" si="33"/>
-        <v>93489.142799999972</v>
-      </c>
-      <c r="AX9" s="8">
-        <f t="shared" si="33"/>
-        <v>102666.24095400001</v>
-      </c>
-      <c r="AY9" s="8">
-        <f t="shared" si="33"/>
-        <v>110621.86443774001</v>
-      </c>
-      <c r="AZ9" s="8">
-        <f t="shared" si="33"/>
-        <v>116053.90138677959</v>
-      </c>
-      <c r="BA9" s="8">
-        <f t="shared" si="33"/>
-        <v>119689.79878151126</v>
-      </c>
-      <c r="BB9" s="8">
-        <f t="shared" ref="BB9:BF9" si="34">BB5-BB6-BB7-BB8</f>
-        <v>122083.5947571415</v>
-      </c>
-      <c r="BC9" s="8">
-        <f t="shared" si="34"/>
-        <v>124525.26665228435</v>
-      </c>
-      <c r="BD9" s="8">
-        <f t="shared" si="34"/>
-        <v>127015.77198533004</v>
-      </c>
-      <c r="BE9" s="8">
-        <f t="shared" si="34"/>
-        <v>129556.08742503662</v>
-      </c>
-      <c r="BF9" s="8">
-        <f t="shared" si="34"/>
-        <v>132147.20917353733</v>
-      </c>
-    </row>
-    <row r="10" spans="2:165">
+      <c r="BG9" s="8">
+        <f t="shared" si="36"/>
+        <v>83276.299999999988</v>
+      </c>
+      <c r="BH9" s="8">
+        <f t="shared" si="36"/>
+        <v>95230.501249999987</v>
+      </c>
+      <c r="BI9" s="8">
+        <f t="shared" si="36"/>
+        <v>104572.62134999999</v>
+      </c>
+      <c r="BJ9" s="8">
+        <f t="shared" si="36"/>
+        <v>112669.92344700001</v>
+      </c>
+      <c r="BK9" s="8">
+        <f t="shared" si="36"/>
+        <v>118197.38140920001</v>
+      </c>
+      <c r="BL9" s="8">
+        <f t="shared" si="36"/>
+        <v>121896.12253913999</v>
+      </c>
+      <c r="BM9" s="8">
+        <f t="shared" ref="BM9:BQ9" si="37">BM5-BM6-BM7-BM8</f>
+        <v>124334.0449899228</v>
+      </c>
+      <c r="BN9" s="8">
+        <f t="shared" si="37"/>
+        <v>126820.72588972125</v>
+      </c>
+      <c r="BO9" s="8">
+        <f t="shared" si="37"/>
+        <v>129357.14040751566</v>
+      </c>
+      <c r="BP9" s="8">
+        <f t="shared" si="37"/>
+        <v>131944.28321566599</v>
+      </c>
+      <c r="BQ9" s="8">
+        <f t="shared" si="37"/>
+        <v>134583.16887997932</v>
+      </c>
+    </row>
+    <row r="10" spans="2:176">
       <c r="B10" t="s">
         <v>32</v>
       </c>
@@ -3438,312 +3675,370 @@
         <v>-1128</v>
       </c>
       <c r="AL10" s="4">
-        <f t="shared" ref="AL10" si="35">AH10*1.02</f>
-        <v>-191.76</v>
-      </c>
-      <c r="AN10" s="4">
+        <v>-609</v>
+      </c>
+      <c r="AM10" s="4"/>
+      <c r="AN10" s="4"/>
+      <c r="AO10" s="4"/>
+      <c r="AP10" s="4"/>
+      <c r="AQ10" s="4"/>
+      <c r="AR10" s="4">
+        <v>24</v>
+      </c>
+      <c r="AS10" s="4">
+        <v>61</v>
+      </c>
+      <c r="AT10" s="4">
+        <v>44</v>
+      </c>
+      <c r="AU10" s="4">
+        <v>50</v>
+      </c>
+      <c r="AV10" s="4">
+        <v>84</v>
+      </c>
+      <c r="AW10" s="4">
+        <v>31</v>
+      </c>
+      <c r="AX10" s="4">
+        <v>-91</v>
+      </c>
+      <c r="AY10" s="4">
         <f>SUM(C10:F10)</f>
         <v>-392</v>
       </c>
-      <c r="AO10" s="4">
+      <c r="AZ10" s="4">
         <f>SUM(G10:J10)</f>
         <v>-448</v>
       </c>
-      <c r="AP10" s="4">
+      <c r="BA10" s="4">
         <f>SUM(K10:N10)</f>
         <v>-826</v>
       </c>
-      <c r="AQ10" s="4">
+      <c r="BB10" s="4">
         <f>SUM(O10:R10)</f>
         <v>-509</v>
       </c>
-      <c r="AR10" s="4">
+      <c r="BC10" s="4">
         <f>SUM(S10:V10)</f>
         <v>-530</v>
       </c>
-      <c r="AS10" s="4">
+      <c r="BD10" s="4">
         <f>SUM(W10:Z10)</f>
         <v>126</v>
       </c>
-      <c r="AT10" s="4">
+      <c r="BE10" s="4">
         <f>SUM(AA10:AD10)</f>
         <v>-677</v>
       </c>
-      <c r="AU10" s="4">
+      <c r="BF10" s="4">
         <f>SUM(AE10:AH10)</f>
         <v>-1284</v>
       </c>
-      <c r="AV10" s="4">
+      <c r="BG10" s="4">
         <f>SUM(AI10:AL10)</f>
-        <v>-2239.7600000000002</v>
-      </c>
-      <c r="AW10" s="4">
-        <f t="shared" ref="AW10:BA10" si="36">-AV13*0.02</f>
-        <v>-1499.0337920000002</v>
-      </c>
-      <c r="AX10" s="4">
-        <f t="shared" si="36"/>
-        <v>-1671.7919080191996</v>
-      </c>
-      <c r="AY10" s="4">
-        <f t="shared" si="36"/>
-        <v>-1836.349378371538</v>
-      </c>
-      <c r="AZ10" s="4">
-        <f t="shared" si="36"/>
-        <v>-1979.2645631635633</v>
-      </c>
-      <c r="BA10" s="4">
-        <f t="shared" si="36"/>
-        <v>-2077.3837207189995</v>
-      </c>
-      <c r="BB10" s="4">
-        <f t="shared" ref="BB10" si="37">-BA13*0.02</f>
-        <v>-2143.1024120392526</v>
-      </c>
-      <c r="BC10" s="4">
-        <f t="shared" ref="BC10" si="38">-BB13*0.02</f>
-        <v>-2186.3898701775815</v>
-      </c>
-      <c r="BD10" s="4">
-        <f t="shared" ref="BD10" si="39">-BC13*0.02</f>
-        <v>-2230.1251547953302</v>
-      </c>
-      <c r="BE10" s="4">
-        <f t="shared" ref="BE10" si="40">-BD13*0.02</f>
-        <v>-2274.7277896662067</v>
-      </c>
-      <c r="BF10" s="4">
-        <f t="shared" ref="BF10" si="41">-BE13*0.02</f>
-        <v>-2320.2223477787697</v>
-      </c>
-    </row>
-    <row r="11" spans="2:165" s="6" customFormat="1">
+        <v>-2657</v>
+      </c>
+      <c r="BH10" s="4">
+        <f t="shared" ref="BH10:BL10" si="38">-BG13*0.02</f>
+        <v>-1527.7659999999998</v>
+      </c>
+      <c r="BI10" s="4">
+        <f t="shared" si="38"/>
+        <v>-1702.9455035999999</v>
+      </c>
+      <c r="BJ10" s="4">
+        <f t="shared" si="38"/>
+        <v>-1870.4499766233598</v>
+      </c>
+      <c r="BK10" s="4">
+        <f t="shared" si="38"/>
+        <v>-2015.9105722557713</v>
+      </c>
+      <c r="BL10" s="4">
+        <f t="shared" si="38"/>
+        <v>-2115.7539388736218</v>
+      </c>
+      <c r="BM10" s="4">
+        <f t="shared" ref="BM10" si="39">-BL13*0.02</f>
+        <v>-2182.6090260130395</v>
+      </c>
+      <c r="BN10" s="4">
+        <f t="shared" ref="BN10" si="40">-BM13*0.02</f>
+        <v>-2226.6931106804709</v>
+      </c>
+      <c r="BO10" s="4">
+        <f t="shared" ref="BO10" si="41">-BN13*0.02</f>
+        <v>-2271.2345744070703</v>
+      </c>
+      <c r="BP10" s="4">
+        <f t="shared" ref="BP10" si="42">-BO13*0.02</f>
+        <v>-2316.6593996818401</v>
+      </c>
+      <c r="BQ10" s="4">
+        <f t="shared" ref="BQ10" si="43">-BP13*0.02</f>
+        <v>-2362.9925900301218</v>
+      </c>
+    </row>
+    <row r="11" spans="2:176" s="6" customFormat="1">
       <c r="B11" s="6" t="s">
         <v>33</v>
       </c>
       <c r="C11" s="8">
-        <f t="shared" ref="C11:P11" si="42">C9-C10</f>
+        <f t="shared" ref="C11:P11" si="44">C9-C10</f>
         <v>3408</v>
       </c>
       <c r="D11" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>4488</v>
       </c>
       <c r="E11" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>5236</v>
       </c>
       <c r="F11" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>7462</v>
       </c>
       <c r="G11" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>5610</v>
       </c>
       <c r="H11" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>5868</v>
       </c>
       <c r="I11" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>5912</v>
       </c>
       <c r="J11" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>7971</v>
       </c>
       <c r="K11" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>3482</v>
       </c>
       <c r="L11" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>4812</v>
       </c>
       <c r="M11" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>7329</v>
       </c>
       <c r="N11" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>9169</v>
       </c>
       <c r="O11" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>5861</v>
       </c>
       <c r="P11" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>6131</v>
       </c>
       <c r="Q11" s="8">
-        <f t="shared" ref="Q11:V11" si="43">Q9-Q10</f>
+        <f t="shared" ref="Q11:V11" si="45">Q9-Q10</f>
         <v>8133</v>
       </c>
       <c r="R11" s="8">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>13055</v>
       </c>
       <c r="S11" s="8">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>11503</v>
       </c>
       <c r="T11" s="8">
-        <f t="shared" ref="T11:U11" si="44">T9-T10</f>
+        <f t="shared" ref="T11:U11" si="46">T9-T10</f>
         <v>12513</v>
       </c>
       <c r="U11" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>10565</v>
       </c>
       <c r="V11" s="8">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>12702</v>
       </c>
       <c r="W11" s="8">
-        <f t="shared" ref="W11:X11" si="45">W9-W10</f>
+        <f t="shared" ref="W11:X11" si="47">W9-W10</f>
         <v>8908</v>
       </c>
       <c r="X11" s="8">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>8186</v>
       </c>
       <c r="Y11" s="8">
-        <f t="shared" ref="Y11" si="46">Y9-Y10</f>
+        <f t="shared" ref="Y11" si="48">Y9-Y10</f>
         <v>5576</v>
       </c>
       <c r="Z11" s="8">
-        <f t="shared" ref="Z11" si="47">Z9-Z10</f>
+        <f t="shared" ref="Z11" si="49">Z9-Z10</f>
         <v>6149</v>
       </c>
       <c r="AA11" s="8">
-        <f t="shared" ref="AA11:AC11" si="48">AA9-AA10</f>
+        <f t="shared" ref="AA11:AC11" si="50">AA9-AA10</f>
         <v>7307</v>
       </c>
       <c r="AB11" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>9293</v>
       </c>
       <c r="AC11" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>14290</v>
       </c>
       <c r="AD11" s="8">
-        <f t="shared" ref="AD11" si="49">AD9-AD10</f>
+        <f t="shared" ref="AD11" si="51">AD9-AD10</f>
         <v>16808</v>
       </c>
       <c r="AE11" s="8">
-        <f t="shared" ref="AE11:AL11" si="50">AE9-AE10</f>
+        <f t="shared" ref="AE11:AL11" si="52">AE9-AE10</f>
         <v>14183</v>
       </c>
       <c r="AF11" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>15106</v>
       </c>
       <c r="AG11" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>17822</v>
       </c>
       <c r="AH11" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>22003</v>
       </c>
       <c r="AI11" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>18382</v>
       </c>
       <c r="AJ11" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>20534</v>
       </c>
       <c r="AK11" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>21663</v>
       </c>
       <c r="AL11" s="8">
-        <f t="shared" si="50"/>
-        <v>24381.419999999995</v>
-      </c>
-      <c r="AN11" s="8">
-        <f>AN9-AN10</f>
+        <f t="shared" si="52"/>
+        <v>25354</v>
+      </c>
+      <c r="AM11" s="8"/>
+      <c r="AN11" s="8"/>
+      <c r="AO11" s="8"/>
+      <c r="AP11" s="8"/>
+      <c r="AQ11" s="8"/>
+      <c r="AR11" s="8">
+        <f t="shared" ref="AR11:BB11" si="53">AR9-AR10</f>
+        <v>1008</v>
+      </c>
+      <c r="AS11" s="8">
+        <f t="shared" si="53"/>
+        <v>1695</v>
+      </c>
+      <c r="AT11" s="8">
+        <f t="shared" si="53"/>
+        <v>494</v>
+      </c>
+      <c r="AU11" s="8">
+        <f t="shared" si="53"/>
+        <v>2754</v>
+      </c>
+      <c r="AV11" s="8">
+        <f t="shared" si="53"/>
+        <v>4910</v>
+      </c>
+      <c r="AW11" s="8">
+        <f t="shared" si="53"/>
+        <v>6194</v>
+      </c>
+      <c r="AX11" s="8">
+        <f t="shared" si="53"/>
+        <v>12518</v>
+      </c>
+      <c r="AY11" s="8">
+        <f t="shared" si="53"/>
         <v>20594</v>
       </c>
-      <c r="AO11" s="8">
-        <f>AO9-AO10</f>
+      <c r="AZ11" s="8">
+        <f t="shared" si="53"/>
         <v>25361</v>
       </c>
-      <c r="AP11" s="8">
-        <f>AP9-AP10</f>
+      <c r="BA11" s="8">
+        <f t="shared" si="53"/>
         <v>24792</v>
       </c>
-      <c r="AQ11" s="8">
-        <f>AQ9-AQ10</f>
+      <c r="BB11" s="8">
+        <f t="shared" si="53"/>
         <v>33180</v>
       </c>
-      <c r="AR11" s="8">
-        <f t="shared" ref="AR11:BA11" si="51">AR9-AR10</f>
+      <c r="BC11" s="8">
+        <f t="shared" ref="BC11:BL11" si="54">BC9-BC10</f>
         <v>47283</v>
       </c>
-      <c r="AS11" s="8">
-        <f t="shared" si="51"/>
+      <c r="BD11" s="8">
+        <f t="shared" si="54"/>
         <v>28819</v>
       </c>
-      <c r="AT11" s="8">
-        <f t="shared" si="51"/>
+      <c r="BE11" s="8">
+        <f t="shared" si="54"/>
         <v>47698</v>
       </c>
-      <c r="AU11" s="8">
-        <f t="shared" si="51"/>
+      <c r="BF11" s="8">
+        <f t="shared" si="54"/>
         <v>69114</v>
       </c>
-      <c r="AV11" s="8">
-        <f t="shared" si="51"/>
-        <v>84836.46</v>
-      </c>
-      <c r="AW11" s="8">
-        <f t="shared" si="51"/>
-        <v>94988.176591999974</v>
-      </c>
-      <c r="AX11" s="8">
-        <f t="shared" si="51"/>
-        <v>104338.0328620192</v>
-      </c>
-      <c r="AY11" s="8">
-        <f t="shared" si="51"/>
-        <v>112458.21381611154</v>
-      </c>
-      <c r="AZ11" s="8">
-        <f t="shared" si="51"/>
-        <v>118033.16594994316</v>
-      </c>
-      <c r="BA11" s="8">
-        <f t="shared" si="51"/>
-        <v>121767.18250223025</v>
-      </c>
-      <c r="BB11" s="8">
-        <f t="shared" ref="BB11:BF11" si="52">BB9-BB10</f>
-        <v>124226.69716918076</v>
-      </c>
-      <c r="BC11" s="8">
-        <f t="shared" si="52"/>
-        <v>126711.65652246193</v>
-      </c>
-      <c r="BD11" s="8">
-        <f t="shared" si="52"/>
-        <v>129245.89714012537</v>
-      </c>
-      <c r="BE11" s="8">
-        <f t="shared" si="52"/>
-        <v>131830.81521470283</v>
-      </c>
-      <c r="BF11" s="8">
-        <f t="shared" si="52"/>
-        <v>134467.43152131609</v>
-      </c>
-    </row>
-    <row r="12" spans="2:165">
+      <c r="BG11" s="8">
+        <f t="shared" si="54"/>
+        <v>85933.299999999988</v>
+      </c>
+      <c r="BH11" s="8">
+        <f t="shared" si="54"/>
+        <v>96758.26724999999</v>
+      </c>
+      <c r="BI11" s="8">
+        <f t="shared" si="54"/>
+        <v>106275.56685359999</v>
+      </c>
+      <c r="BJ11" s="8">
+        <f t="shared" si="54"/>
+        <v>114540.37342362337</v>
+      </c>
+      <c r="BK11" s="8">
+        <f t="shared" si="54"/>
+        <v>120213.29198145578</v>
+      </c>
+      <c r="BL11" s="8">
+        <f t="shared" si="54"/>
+        <v>124011.87647801361</v>
+      </c>
+      <c r="BM11" s="8">
+        <f t="shared" ref="BM11:BQ11" si="55">BM9-BM10</f>
+        <v>126516.65401593584</v>
+      </c>
+      <c r="BN11" s="8">
+        <f t="shared" si="55"/>
+        <v>129047.41900040171</v>
+      </c>
+      <c r="BO11" s="8">
+        <f t="shared" si="55"/>
+        <v>131628.37498192274</v>
+      </c>
+      <c r="BP11" s="8">
+        <f t="shared" si="55"/>
+        <v>134260.94261534783</v>
+      </c>
+      <c r="BQ11" s="8">
+        <f t="shared" si="55"/>
+        <v>136946.16147000945</v>
+      </c>
+    </row>
+    <row r="12" spans="2:176">
       <c r="B12" t="s">
         <v>34</v>
       </c>
@@ -3858,740 +4153,798 @@
         <v>3024</v>
       </c>
       <c r="AL12" s="4">
-        <f t="shared" ref="AL12" si="53">AL11*0.12</f>
-        <v>2925.7703999999994</v>
-      </c>
-      <c r="AN12" s="4">
+        <v>2586</v>
+      </c>
+      <c r="AM12" s="4"/>
+      <c r="AN12" s="4"/>
+      <c r="AO12" s="4"/>
+      <c r="AP12" s="4"/>
+      <c r="AQ12" s="4"/>
+      <c r="AR12" s="4">
+        <v>402</v>
+      </c>
+      <c r="AS12" s="4">
+        <v>695</v>
+      </c>
+      <c r="AT12" s="4">
+        <v>441</v>
+      </c>
+      <c r="AU12" s="4">
+        <v>1254</v>
+      </c>
+      <c r="AV12" s="4">
+        <v>1970</v>
+      </c>
+      <c r="AW12" s="4">
+        <v>2506</v>
+      </c>
+      <c r="AX12" s="4">
+        <v>2301</v>
+      </c>
+      <c r="AY12" s="4">
         <f>SUM(C12:F12)</f>
         <v>5390</v>
       </c>
-      <c r="AO12" s="4">
+      <c r="AZ12" s="4">
         <f>SUM(G12:J12)</f>
         <v>3249</v>
       </c>
-      <c r="AP12" s="4">
+      <c r="BA12" s="4">
         <f>SUM(K12:N12)</f>
         <v>6327</v>
       </c>
-      <c r="AQ12" s="4">
+      <c r="BB12" s="4">
         <f>SUM(O12:R12)</f>
         <v>4035</v>
       </c>
-      <c r="AR12" s="4">
+      <c r="BC12" s="4">
         <f>SUM(S12:V12)</f>
         <v>7913</v>
       </c>
-      <c r="AS12" s="4">
+      <c r="BD12" s="4">
         <f>SUM(W12:Z12)</f>
         <v>5620</v>
       </c>
-      <c r="AT12" s="4">
+      <c r="BE12" s="4">
         <f>SUM(AA12:AD12)</f>
         <v>8331</v>
       </c>
-      <c r="AU12" s="4">
+      <c r="BF12" s="4">
         <f>SUM(AE12:AH12)</f>
         <v>8304</v>
       </c>
-      <c r="AV12" s="4">
+      <c r="BG12" s="4">
         <f>SUM(AI12:AL12)</f>
-        <v>9884.7703999999994</v>
-      </c>
-      <c r="AW12" s="4">
-        <f>AW11*0.12</f>
-        <v>11398.581191039997</v>
-      </c>
-      <c r="AX12" s="4">
-        <f t="shared" ref="AX12:BF12" si="54">AX11*0.12</f>
-        <v>12520.563943442303</v>
-      </c>
-      <c r="AY12" s="4">
-        <f t="shared" si="54"/>
-        <v>13494.985657933385</v>
-      </c>
-      <c r="AZ12" s="4">
-        <f t="shared" si="54"/>
-        <v>14163.979913993178</v>
-      </c>
-      <c r="BA12" s="4">
-        <f t="shared" si="54"/>
-        <v>14612.06190026763</v>
-      </c>
-      <c r="BB12" s="4">
-        <f t="shared" si="54"/>
-        <v>14907.20366030169</v>
-      </c>
-      <c r="BC12" s="4">
-        <f t="shared" si="54"/>
-        <v>15205.398782695431</v>
-      </c>
-      <c r="BD12" s="4">
-        <f t="shared" si="54"/>
-        <v>15509.507656815043</v>
-      </c>
-      <c r="BE12" s="4">
-        <f t="shared" si="54"/>
-        <v>15819.697825764339</v>
-      </c>
-      <c r="BF12" s="4">
-        <f t="shared" si="54"/>
-        <v>16136.091782557931</v>
-      </c>
-    </row>
-    <row r="13" spans="2:165" s="6" customFormat="1">
+        <v>9545</v>
+      </c>
+      <c r="BH12" s="4">
+        <f>BH11*0.12</f>
+        <v>11610.992069999998</v>
+      </c>
+      <c r="BI12" s="4">
+        <f t="shared" ref="BI12:BQ12" si="56">BI11*0.12</f>
+        <v>12753.068022431999</v>
+      </c>
+      <c r="BJ12" s="4">
+        <f t="shared" si="56"/>
+        <v>13744.844810834804</v>
+      </c>
+      <c r="BK12" s="4">
+        <f t="shared" si="56"/>
+        <v>14425.595037774694</v>
+      </c>
+      <c r="BL12" s="4">
+        <f t="shared" si="56"/>
+        <v>14881.425177361632</v>
+      </c>
+      <c r="BM12" s="4">
+        <f t="shared" si="56"/>
+        <v>15181.9984819123</v>
+      </c>
+      <c r="BN12" s="4">
+        <f t="shared" si="56"/>
+        <v>15485.690280048206</v>
+      </c>
+      <c r="BO12" s="4">
+        <f t="shared" si="56"/>
+        <v>15795.404997830728</v>
+      </c>
+      <c r="BP12" s="4">
+        <f t="shared" si="56"/>
+        <v>16111.313113841739</v>
+      </c>
+      <c r="BQ12" s="4">
+        <f t="shared" si="56"/>
+        <v>16433.539376401135</v>
+      </c>
+    </row>
+    <row r="13" spans="2:176" s="6" customFormat="1">
       <c r="B13" s="6" t="s">
         <v>35</v>
       </c>
       <c r="C13" s="8">
-        <f t="shared" ref="C13:P13" si="55">C11-C12</f>
+        <f t="shared" ref="C13:P13" si="57">C11-C12</f>
         <v>3059</v>
       </c>
       <c r="D13" s="8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>3890</v>
       </c>
       <c r="E13" s="8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>4707</v>
       </c>
       <c r="F13" s="8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>3548</v>
       </c>
       <c r="G13" s="8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>4987</v>
       </c>
       <c r="H13" s="8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>5106</v>
       </c>
       <c r="I13" s="8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>5137</v>
       </c>
       <c r="J13" s="8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>6882</v>
       </c>
       <c r="K13" s="8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>2429</v>
       </c>
       <c r="L13" s="8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>2596</v>
       </c>
       <c r="M13" s="8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>6091</v>
       </c>
       <c r="N13" s="8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>7349</v>
       </c>
       <c r="O13" s="8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>4902</v>
       </c>
       <c r="P13" s="8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>5178</v>
       </c>
       <c r="Q13" s="8">
-        <f t="shared" ref="Q13:R13" si="56">Q11-Q12</f>
+        <f t="shared" ref="Q13:R13" si="58">Q11-Q12</f>
         <v>7846</v>
       </c>
       <c r="R13" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>11219</v>
       </c>
       <c r="S13" s="8">
-        <f t="shared" ref="S13:V13" si="57">S11-S12</f>
+        <f t="shared" ref="S13:V13" si="59">S11-S12</f>
         <v>9497</v>
       </c>
       <c r="T13" s="8">
-        <f t="shared" ref="T13:U13" si="58">T11-T12</f>
+        <f t="shared" ref="T13:U13" si="60">T11-T12</f>
         <v>10394</v>
       </c>
       <c r="U13" s="8">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>9194</v>
       </c>
       <c r="V13" s="8">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>10285</v>
       </c>
       <c r="W13" s="8">
-        <f t="shared" ref="W13:X13" si="59">W11-W12</f>
+        <f t="shared" ref="W13:X13" si="61">W11-W12</f>
         <v>7465</v>
       </c>
       <c r="X13" s="8">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>6687</v>
       </c>
       <c r="Y13" s="8">
-        <f t="shared" ref="Y13" si="60">Y11-Y12</f>
+        <f t="shared" ref="Y13" si="62">Y11-Y12</f>
         <v>4395</v>
       </c>
       <c r="Z13" s="8">
-        <f t="shared" ref="Z13" si="61">Z11-Z12</f>
+        <f t="shared" ref="Z13" si="63">Z11-Z12</f>
         <v>4652</v>
       </c>
       <c r="AA13" s="8">
-        <f t="shared" ref="AA13:AC13" si="62">AA11-AA12</f>
+        <f t="shared" ref="AA13:AC13" si="64">AA11-AA12</f>
         <v>5709</v>
       </c>
       <c r="AB13" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>7788</v>
       </c>
       <c r="AC13" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>11853</v>
       </c>
       <c r="AD13" s="8">
-        <f t="shared" ref="AD13" si="63">AD11-AD12</f>
+        <f t="shared" ref="AD13" si="65">AD11-AD12</f>
         <v>14017</v>
       </c>
       <c r="AE13" s="8">
-        <f t="shared" ref="AE13" si="64">AE11-AE12</f>
+        <f t="shared" ref="AE13" si="66">AE11-AE12</f>
         <v>12369</v>
       </c>
       <c r="AF13" s="8">
-        <f t="shared" ref="AF13:AH13" si="65">AF11-AF12</f>
+        <f t="shared" ref="AF13:AH13" si="67">AF11-AF12</f>
         <v>13465</v>
       </c>
       <c r="AG13" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>15688</v>
       </c>
       <c r="AH13" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>19288</v>
       </c>
       <c r="AI13" s="8">
-        <f t="shared" ref="AI13:AL13" si="66">AI11-AI12</f>
+        <f t="shared" ref="AI13:AL13" si="68">AI11-AI12</f>
         <v>16644</v>
       </c>
       <c r="AJ13" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>18337</v>
       </c>
       <c r="AK13" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>18639</v>
       </c>
       <c r="AL13" s="8">
-        <f t="shared" si="66"/>
-        <v>21455.649599999997</v>
-      </c>
-      <c r="AN13" s="8">
-        <f>AN11-AN12</f>
+        <f t="shared" si="68"/>
+        <v>22768</v>
+      </c>
+      <c r="AM13" s="8"/>
+      <c r="AN13" s="8"/>
+      <c r="AO13" s="8"/>
+      <c r="AP13" s="8"/>
+      <c r="AQ13" s="8"/>
+      <c r="AR13" s="8">
+        <f t="shared" ref="AR13:BB13" si="69">AR11-AR12</f>
+        <v>606</v>
+      </c>
+      <c r="AS13" s="8">
+        <f t="shared" si="69"/>
+        <v>1000</v>
+      </c>
+      <c r="AT13" s="8">
+        <f t="shared" si="69"/>
+        <v>53</v>
+      </c>
+      <c r="AU13" s="8">
+        <f t="shared" si="69"/>
+        <v>1500</v>
+      </c>
+      <c r="AV13" s="8">
+        <f t="shared" si="69"/>
+        <v>2940</v>
+      </c>
+      <c r="AW13" s="8">
+        <f t="shared" si="69"/>
+        <v>3688</v>
+      </c>
+      <c r="AX13" s="8">
+        <f t="shared" si="69"/>
+        <v>10217</v>
+      </c>
+      <c r="AY13" s="8">
+        <f t="shared" si="69"/>
         <v>15204</v>
       </c>
-      <c r="AO13" s="8">
-        <f>AO11-AO12</f>
+      <c r="AZ13" s="8">
+        <f t="shared" si="69"/>
         <v>22112</v>
       </c>
-      <c r="AP13" s="8">
-        <f>AP11-AP12</f>
+      <c r="BA13" s="8">
+        <f t="shared" si="69"/>
         <v>18465</v>
       </c>
-      <c r="AQ13" s="8">
-        <f>AQ11-AQ12</f>
+      <c r="BB13" s="8">
+        <f t="shared" si="69"/>
         <v>29145</v>
       </c>
-      <c r="AR13" s="8">
-        <f t="shared" ref="AR13:BA13" si="67">AR11-AR12</f>
+      <c r="BC13" s="8">
+        <f t="shared" ref="BC13:BL13" si="70">BC11-BC12</f>
         <v>39370</v>
       </c>
-      <c r="AS13" s="8">
-        <f t="shared" si="67"/>
+      <c r="BD13" s="8">
+        <f t="shared" si="70"/>
         <v>23199</v>
       </c>
-      <c r="AT13" s="8">
-        <f t="shared" si="67"/>
+      <c r="BE13" s="8">
+        <f t="shared" si="70"/>
         <v>39367</v>
       </c>
-      <c r="AU13" s="8">
-        <f t="shared" si="67"/>
+      <c r="BF13" s="8">
+        <f t="shared" si="70"/>
         <v>60810</v>
       </c>
-      <c r="AV13" s="8">
-        <f t="shared" si="67"/>
-        <v>74951.689600000012</v>
-      </c>
-      <c r="AW13" s="8">
-        <f t="shared" si="67"/>
-        <v>83589.595400959981</v>
-      </c>
-      <c r="AX13" s="8">
-        <f t="shared" si="67"/>
-        <v>91817.468918576895</v>
-      </c>
-      <c r="AY13" s="8">
-        <f t="shared" si="67"/>
-        <v>98963.228158178157</v>
-      </c>
-      <c r="AZ13" s="8">
-        <f t="shared" si="67"/>
-        <v>103869.18603594997</v>
-      </c>
-      <c r="BA13" s="8">
-        <f t="shared" si="67"/>
-        <v>107155.12060196263</v>
-      </c>
-      <c r="BB13" s="8">
-        <f t="shared" ref="BB13:BF13" si="68">BB11-BB12</f>
-        <v>109319.49350887907</v>
-      </c>
-      <c r="BC13" s="8">
-        <f t="shared" si="68"/>
-        <v>111506.2577397665</v>
-      </c>
-      <c r="BD13" s="8">
-        <f t="shared" si="68"/>
-        <v>113736.38948331033</v>
-      </c>
-      <c r="BE13" s="8">
-        <f t="shared" si="68"/>
-        <v>116011.1173889385</v>
-      </c>
-      <c r="BF13" s="8">
-        <f t="shared" si="68"/>
-        <v>118331.33973875816</v>
-      </c>
-      <c r="BG13" s="6">
-        <f>BF13*(1+$BI$18)</f>
-        <v>117148.02634137058</v>
-      </c>
-      <c r="BH13" s="6">
-        <f t="shared" ref="BH13:DS13" si="69">BG13*(1+$BI$18)</f>
-        <v>115976.54607795688</v>
-      </c>
-      <c r="BI13" s="6">
-        <f t="shared" si="69"/>
-        <v>114816.78061717731</v>
-      </c>
-      <c r="BJ13" s="6">
-        <f t="shared" si="69"/>
-        <v>113668.61281100554</v>
-      </c>
-      <c r="BK13" s="6">
-        <f t="shared" si="69"/>
-        <v>112531.92668289549</v>
-      </c>
-      <c r="BL13" s="6">
-        <f t="shared" si="69"/>
-        <v>111406.60741606653</v>
-      </c>
-      <c r="BM13" s="6">
-        <f t="shared" si="69"/>
-        <v>110292.54134190586</v>
-      </c>
-      <c r="BN13" s="6">
-        <f t="shared" si="69"/>
-        <v>109189.6159284868</v>
-      </c>
-      <c r="BO13" s="6">
-        <f t="shared" si="69"/>
-        <v>108097.71976920194</v>
-      </c>
-      <c r="BP13" s="6">
-        <f t="shared" si="69"/>
-        <v>107016.74257150992</v>
-      </c>
-      <c r="BQ13" s="6">
-        <f t="shared" si="69"/>
-        <v>105946.57514579482</v>
+      <c r="BG13" s="8">
+        <f t="shared" si="70"/>
+        <v>76388.299999999988</v>
+      </c>
+      <c r="BH13" s="8">
+        <f t="shared" si="70"/>
+        <v>85147.275179999997</v>
+      </c>
+      <c r="BI13" s="8">
+        <f t="shared" si="70"/>
+        <v>93522.498831167992</v>
+      </c>
+      <c r="BJ13" s="8">
+        <f t="shared" si="70"/>
+        <v>100795.52861278856</v>
+      </c>
+      <c r="BK13" s="8">
+        <f t="shared" si="70"/>
+        <v>105787.69694368109</v>
+      </c>
+      <c r="BL13" s="8">
+        <f t="shared" si="70"/>
+        <v>109130.45130065198</v>
+      </c>
+      <c r="BM13" s="8">
+        <f t="shared" ref="BM13:BQ13" si="71">BM11-BM12</f>
+        <v>111334.65553402354</v>
+      </c>
+      <c r="BN13" s="8">
+        <f t="shared" si="71"/>
+        <v>113561.72872035351</v>
+      </c>
+      <c r="BO13" s="8">
+        <f t="shared" si="71"/>
+        <v>115832.96998409201</v>
+      </c>
+      <c r="BP13" s="8">
+        <f t="shared" si="71"/>
+        <v>118149.62950150609</v>
+      </c>
+      <c r="BQ13" s="8">
+        <f t="shared" si="71"/>
+        <v>120512.62209360831</v>
       </c>
       <c r="BR13" s="6">
-        <f t="shared" si="69"/>
-        <v>104887.10939433688</v>
+        <f>BQ13*(1+$BT$18)</f>
+        <v>119307.49587267223</v>
       </c>
       <c r="BS13" s="6">
-        <f t="shared" si="69"/>
-        <v>103838.23830039351</v>
+        <f t="shared" ref="BS13:ED13" si="72">BR13*(1+$BT$18)</f>
+        <v>118114.42091394551</v>
       </c>
       <c r="BT13" s="6">
-        <f t="shared" si="69"/>
-        <v>102799.85591738958</v>
+        <f t="shared" si="72"/>
+        <v>116933.27670480605</v>
       </c>
       <c r="BU13" s="6">
-        <f t="shared" si="69"/>
-        <v>101771.85735821568</v>
+        <f t="shared" si="72"/>
+        <v>115763.94393775798</v>
       </c>
       <c r="BV13" s="6">
-        <f t="shared" si="69"/>
-        <v>100754.13878463353</v>
+        <f t="shared" si="72"/>
+        <v>114606.3044983804</v>
       </c>
       <c r="BW13" s="6">
-        <f t="shared" si="69"/>
-        <v>99746.597396787198</v>
+        <f t="shared" si="72"/>
+        <v>113460.24145339659</v>
       </c>
       <c r="BX13" s="6">
-        <f t="shared" si="69"/>
-        <v>98749.131422819322</v>
+        <f t="shared" si="72"/>
+        <v>112325.63903886263</v>
       </c>
       <c r="BY13" s="6">
-        <f t="shared" si="69"/>
-        <v>97761.640108591135</v>
+        <f t="shared" si="72"/>
+        <v>111202.382648474</v>
       </c>
       <c r="BZ13" s="6">
-        <f t="shared" si="69"/>
-        <v>96784.023707505228</v>
+        <f t="shared" si="72"/>
+        <v>110090.35882198926</v>
       </c>
       <c r="CA13" s="6">
-        <f t="shared" si="69"/>
-        <v>95816.183470430173</v>
+        <f t="shared" si="72"/>
+        <v>108989.45523376936</v>
       </c>
       <c r="CB13" s="6">
-        <f t="shared" si="69"/>
-        <v>94858.021635725876</v>
+        <f t="shared" si="72"/>
+        <v>107899.56068143167</v>
       </c>
       <c r="CC13" s="6">
-        <f t="shared" si="69"/>
-        <v>93909.44141936861</v>
+        <f t="shared" si="72"/>
+        <v>106820.56507461735</v>
       </c>
       <c r="CD13" s="6">
-        <f t="shared" si="69"/>
-        <v>92970.347005174917</v>
+        <f t="shared" si="72"/>
+        <v>105752.35942387118</v>
       </c>
       <c r="CE13" s="6">
-        <f t="shared" si="69"/>
-        <v>92040.643535123163</v>
+        <f t="shared" si="72"/>
+        <v>104694.83582963247</v>
       </c>
       <c r="CF13" s="6">
-        <f t="shared" si="69"/>
-        <v>91120.237099771926</v>
+        <f t="shared" si="72"/>
+        <v>103647.88747133614</v>
       </c>
       <c r="CG13" s="6">
-        <f t="shared" si="69"/>
-        <v>90209.034728774204</v>
+        <f t="shared" si="72"/>
+        <v>102611.40859662279</v>
       </c>
       <c r="CH13" s="6">
-        <f t="shared" si="69"/>
-        <v>89306.944381486464</v>
+        <f t="shared" si="72"/>
+        <v>101585.29451065656</v>
       </c>
       <c r="CI13" s="6">
-        <f t="shared" si="69"/>
-        <v>88413.8749376716</v>
+        <f t="shared" si="72"/>
+        <v>100569.44156554999</v>
       </c>
       <c r="CJ13" s="6">
-        <f t="shared" si="69"/>
-        <v>87529.73618829489</v>
+        <f t="shared" si="72"/>
+        <v>99563.747149894494</v>
       </c>
       <c r="CK13" s="6">
-        <f t="shared" si="69"/>
-        <v>86654.438826411933</v>
+        <f t="shared" si="72"/>
+        <v>98568.109678395544</v>
       </c>
       <c r="CL13" s="6">
-        <f t="shared" si="69"/>
-        <v>85787.894438147807</v>
+        <f t="shared" si="72"/>
+        <v>97582.428581611588</v>
       </c>
       <c r="CM13" s="6">
-        <f t="shared" si="69"/>
-        <v>84930.015493766332</v>
+        <f t="shared" si="72"/>
+        <v>96606.604295795478</v>
       </c>
       <c r="CN13" s="6">
-        <f t="shared" si="69"/>
-        <v>84080.715338828668</v>
+        <f t="shared" si="72"/>
+        <v>95640.538252837519</v>
       </c>
       <c r="CO13" s="6">
-        <f t="shared" si="69"/>
-        <v>83239.908185440378</v>
+        <f t="shared" si="72"/>
+        <v>94684.132870309142</v>
       </c>
       <c r="CP13" s="6">
-        <f t="shared" si="69"/>
-        <v>82407.509103585966</v>
+        <f t="shared" si="72"/>
+        <v>93737.291541606057</v>
       </c>
       <c r="CQ13" s="6">
-        <f t="shared" si="69"/>
-        <v>81583.434012550104</v>
+        <f t="shared" si="72"/>
+        <v>92799.918626189989</v>
       </c>
       <c r="CR13" s="6">
-        <f t="shared" si="69"/>
-        <v>80767.599672424607</v>
+        <f t="shared" si="72"/>
+        <v>91871.919439928082</v>
       </c>
       <c r="CS13" s="6">
-        <f t="shared" si="69"/>
-        <v>79959.923675700367</v>
+        <f t="shared" si="72"/>
+        <v>90953.200245528802</v>
       </c>
       <c r="CT13" s="6">
-        <f t="shared" si="69"/>
-        <v>79160.324438943368</v>
+        <f t="shared" si="72"/>
+        <v>90043.668243073509</v>
       </c>
       <c r="CU13" s="6">
-        <f t="shared" si="69"/>
-        <v>78368.721194553931</v>
+        <f t="shared" si="72"/>
+        <v>89143.231560642773</v>
       </c>
       <c r="CV13" s="6">
-        <f t="shared" si="69"/>
-        <v>77585.033982608395</v>
+        <f t="shared" si="72"/>
+        <v>88251.799245036338</v>
       </c>
       <c r="CW13" s="6">
-        <f t="shared" si="69"/>
-        <v>76809.183642782315</v>
+        <f t="shared" si="72"/>
+        <v>87369.281252585977</v>
       </c>
       <c r="CX13" s="6">
-        <f t="shared" si="69"/>
-        <v>76041.091806354496</v>
+        <f t="shared" si="72"/>
+        <v>86495.588440060121</v>
       </c>
       <c r="CY13" s="6">
-        <f t="shared" si="69"/>
-        <v>75280.680888290954</v>
+        <f t="shared" si="72"/>
+        <v>85630.632555659526</v>
       </c>
       <c r="CZ13" s="6">
-        <f t="shared" si="69"/>
-        <v>74527.874079408037</v>
+        <f t="shared" si="72"/>
+        <v>84774.326230102932</v>
       </c>
       <c r="DA13" s="6">
-        <f t="shared" si="69"/>
-        <v>73782.595338613959</v>
+        <f t="shared" si="72"/>
+        <v>83926.582967801907</v>
       </c>
       <c r="DB13" s="6">
-        <f t="shared" si="69"/>
-        <v>73044.769385227817</v>
+        <f t="shared" si="72"/>
+        <v>83087.317138123894</v>
       </c>
       <c r="DC13" s="6">
-        <f t="shared" si="69"/>
-        <v>72314.321691375531</v>
+        <f t="shared" si="72"/>
+        <v>82256.443966742649</v>
       </c>
       <c r="DD13" s="6">
-        <f t="shared" si="69"/>
-        <v>71591.178474461776</v>
+        <f t="shared" si="72"/>
+        <v>81433.879527075216</v>
       </c>
       <c r="DE13" s="6">
-        <f t="shared" si="69"/>
-        <v>70875.266689717158</v>
+        <f t="shared" si="72"/>
+        <v>80619.54073180446</v>
       </c>
       <c r="DF13" s="6">
-        <f t="shared" si="69"/>
-        <v>70166.514022819989</v>
+        <f t="shared" si="72"/>
+        <v>79813.345324486421</v>
       </c>
       <c r="DG13" s="6">
-        <f t="shared" si="69"/>
-        <v>69464.848882591788</v>
+        <f t="shared" si="72"/>
+        <v>79015.211871241554</v>
       </c>
       <c r="DH13" s="6">
-        <f t="shared" si="69"/>
-        <v>68770.200393765874</v>
+        <f t="shared" si="72"/>
+        <v>78225.059752529138</v>
       </c>
       <c r="DI13" s="6">
-        <f t="shared" si="69"/>
-        <v>68082.498389828208</v>
+        <f t="shared" si="72"/>
+        <v>77442.809155003852</v>
       </c>
       <c r="DJ13" s="6">
-        <f t="shared" si="69"/>
-        <v>67401.67340592992</v>
+        <f t="shared" si="72"/>
+        <v>76668.381063453809</v>
       </c>
       <c r="DK13" s="6">
-        <f t="shared" si="69"/>
-        <v>66727.656671870616</v>
+        <f t="shared" si="72"/>
+        <v>75901.697252819271</v>
       </c>
       <c r="DL13" s="6">
-        <f t="shared" si="69"/>
-        <v>66060.380105151911</v>
+        <f t="shared" si="72"/>
+        <v>75142.680280291082</v>
       </c>
       <c r="DM13" s="6">
-        <f t="shared" si="69"/>
-        <v>65399.776304100393</v>
+        <f t="shared" si="72"/>
+        <v>74391.253477488164</v>
       </c>
       <c r="DN13" s="6">
-        <f t="shared" si="69"/>
-        <v>64745.778541059386</v>
+        <f t="shared" si="72"/>
+        <v>73647.340942713286</v>
       </c>
       <c r="DO13" s="6">
-        <f t="shared" si="69"/>
-        <v>64098.320755648791</v>
+        <f t="shared" si="72"/>
+        <v>72910.867533286146</v>
       </c>
       <c r="DP13" s="6">
-        <f t="shared" si="69"/>
-        <v>63457.337548092299</v>
+        <f t="shared" si="72"/>
+        <v>72181.758857953289</v>
       </c>
       <c r="DQ13" s="6">
-        <f t="shared" si="69"/>
-        <v>62822.764172611372</v>
+        <f t="shared" si="72"/>
+        <v>71459.941269373754</v>
       </c>
       <c r="DR13" s="6">
-        <f t="shared" si="69"/>
-        <v>62194.536530885256</v>
+        <f t="shared" si="72"/>
+        <v>70745.34185668001</v>
       </c>
       <c r="DS13" s="6">
-        <f t="shared" si="69"/>
-        <v>61572.591165576399</v>
+        <f t="shared" si="72"/>
+        <v>70037.888438113208</v>
       </c>
       <c r="DT13" s="6">
-        <f t="shared" ref="DT13:FI13" si="70">DS13*(1+$BI$18)</f>
-        <v>60956.865253920638</v>
+        <f t="shared" si="72"/>
+        <v>69337.509553732074</v>
       </c>
       <c r="DU13" s="6">
-        <f t="shared" si="70"/>
-        <v>60347.296601381429</v>
+        <f t="shared" si="72"/>
+        <v>68644.134458194749</v>
       </c>
       <c r="DV13" s="6">
-        <f t="shared" si="70"/>
-        <v>59743.823635367611</v>
+        <f t="shared" si="72"/>
+        <v>67957.693113612797</v>
       </c>
       <c r="DW13" s="6">
-        <f t="shared" si="70"/>
-        <v>59146.385399013932</v>
+        <f t="shared" si="72"/>
+        <v>67278.116182476675</v>
       </c>
       <c r="DX13" s="6">
-        <f t="shared" si="70"/>
-        <v>58554.92154502379</v>
+        <f t="shared" si="72"/>
+        <v>66605.33502065191</v>
       </c>
       <c r="DY13" s="6">
-        <f t="shared" si="70"/>
-        <v>57969.372329573554</v>
+        <f t="shared" si="72"/>
+        <v>65939.281670445387</v>
       </c>
       <c r="DZ13" s="6">
-        <f t="shared" si="70"/>
-        <v>57389.678606277819</v>
+        <f t="shared" si="72"/>
+        <v>65279.888853740929</v>
       </c>
       <c r="EA13" s="6">
-        <f t="shared" si="70"/>
-        <v>56815.781820215037</v>
+        <f t="shared" si="72"/>
+        <v>64627.089965203522</v>
       </c>
       <c r="EB13" s="6">
-        <f t="shared" si="70"/>
-        <v>56247.62400201289</v>
+        <f t="shared" si="72"/>
+        <v>63980.819065551485</v>
       </c>
       <c r="EC13" s="6">
-        <f t="shared" si="70"/>
-        <v>55685.147761992761</v>
+        <f t="shared" si="72"/>
+        <v>63341.010874895968</v>
       </c>
       <c r="ED13" s="6">
-        <f t="shared" si="70"/>
-        <v>55128.296284372831</v>
+        <f t="shared" si="72"/>
+        <v>62707.600766147007</v>
       </c>
       <c r="EE13" s="6">
-        <f t="shared" si="70"/>
-        <v>54577.013321529099</v>
+        <f t="shared" ref="EE13:FT13" si="73">ED13*(1+$BT$18)</f>
+        <v>62080.524758485539</v>
       </c>
       <c r="EF13" s="6">
-        <f t="shared" si="70"/>
-        <v>54031.243188313805</v>
+        <f t="shared" si="73"/>
+        <v>61459.719510900686</v>
       </c>
       <c r="EG13" s="6">
-        <f t="shared" si="70"/>
-        <v>53490.930756430665</v>
+        <f t="shared" si="73"/>
+        <v>60845.122315791676</v>
       </c>
       <c r="EH13" s="6">
-        <f t="shared" si="70"/>
-        <v>52956.021448866355</v>
+        <f t="shared" si="73"/>
+        <v>60236.671092633762</v>
       </c>
       <c r="EI13" s="6">
-        <f t="shared" si="70"/>
-        <v>52426.46123437769</v>
+        <f t="shared" si="73"/>
+        <v>59634.304381707421</v>
       </c>
       <c r="EJ13" s="6">
-        <f t="shared" si="70"/>
-        <v>51902.196622033909</v>
+        <f t="shared" si="73"/>
+        <v>59037.961337890345</v>
       </c>
       <c r="EK13" s="6">
-        <f t="shared" si="70"/>
-        <v>51383.174655813571</v>
+        <f t="shared" si="73"/>
+        <v>58447.581724511438</v>
       </c>
       <c r="EL13" s="6">
-        <f t="shared" si="70"/>
-        <v>50869.342909255436</v>
+        <f t="shared" si="73"/>
+        <v>57863.105907266319</v>
       </c>
       <c r="EM13" s="6">
-        <f t="shared" si="70"/>
-        <v>50360.64948016288</v>
+        <f t="shared" si="73"/>
+        <v>57284.474848193655</v>
       </c>
       <c r="EN13" s="6">
-        <f t="shared" si="70"/>
-        <v>49857.042985361251</v>
+        <f t="shared" si="73"/>
+        <v>56711.630099711721</v>
       </c>
       <c r="EO13" s="6">
-        <f t="shared" si="70"/>
-        <v>49358.472555507637</v>
+        <f t="shared" si="73"/>
+        <v>56144.513798714601</v>
       </c>
       <c r="EP13" s="6">
-        <f t="shared" si="70"/>
-        <v>48864.88782995256</v>
+        <f t="shared" si="73"/>
+        <v>55583.068660727455</v>
       </c>
       <c r="EQ13" s="6">
-        <f t="shared" si="70"/>
-        <v>48376.238951653031</v>
+        <f t="shared" si="73"/>
+        <v>55027.23797412018</v>
       </c>
       <c r="ER13" s="6">
-        <f t="shared" si="70"/>
-        <v>47892.4765621365</v>
+        <f t="shared" si="73"/>
+        <v>54476.965594378977</v>
       </c>
       <c r="ES13" s="6">
-        <f t="shared" si="70"/>
-        <v>47413.551796515138</v>
+        <f t="shared" si="73"/>
+        <v>53932.195938435187</v>
       </c>
       <c r="ET13" s="6">
-        <f t="shared" si="70"/>
-        <v>46939.416278549987</v>
+        <f t="shared" si="73"/>
+        <v>53392.873979050833</v>
       </c>
       <c r="EU13" s="6">
-        <f t="shared" si="70"/>
-        <v>46470.022115764485</v>
+        <f t="shared" si="73"/>
+        <v>52858.945239260327</v>
       </c>
       <c r="EV13" s="6">
-        <f t="shared" si="70"/>
-        <v>46005.321894606837</v>
+        <f t="shared" si="73"/>
+        <v>52330.355786867724</v>
       </c>
       <c r="EW13" s="6">
-        <f t="shared" si="70"/>
-        <v>45545.268675660765</v>
+        <f t="shared" si="73"/>
+        <v>51807.052228999048</v>
       </c>
       <c r="EX13" s="6">
-        <f t="shared" si="70"/>
-        <v>45089.815988904156</v>
+        <f t="shared" si="73"/>
+        <v>51288.981706709055</v>
       </c>
       <c r="EY13" s="6">
-        <f t="shared" si="70"/>
-        <v>44638.917829015118</v>
+        <f t="shared" si="73"/>
+        <v>50776.091889641961</v>
       </c>
       <c r="EZ13" s="6">
-        <f t="shared" si="70"/>
-        <v>44192.528650724969</v>
+        <f t="shared" si="73"/>
+        <v>50268.330970745541</v>
       </c>
       <c r="FA13" s="6">
-        <f t="shared" si="70"/>
-        <v>43750.603364217721</v>
+        <f t="shared" si="73"/>
+        <v>49765.647661038085</v>
       </c>
       <c r="FB13" s="6">
-        <f t="shared" si="70"/>
-        <v>43313.09733057554</v>
+        <f t="shared" si="73"/>
+        <v>49267.991184427701</v>
       </c>
       <c r="FC13" s="6">
-        <f t="shared" si="70"/>
-        <v>42879.966357269783</v>
+        <f t="shared" si="73"/>
+        <v>48775.311272583422</v>
       </c>
       <c r="FD13" s="6">
-        <f t="shared" si="70"/>
-        <v>42451.166693697087</v>
+        <f t="shared" si="73"/>
+        <v>48287.558159857588</v>
       </c>
       <c r="FE13" s="6">
-        <f t="shared" si="70"/>
-        <v>42026.655026760112</v>
+        <f t="shared" si="73"/>
+        <v>47804.682578259009</v>
       </c>
       <c r="FF13" s="6">
-        <f t="shared" si="70"/>
-        <v>41606.38847649251</v>
+        <f t="shared" si="73"/>
+        <v>47326.635752476417</v>
       </c>
       <c r="FG13" s="6">
-        <f t="shared" si="70"/>
-        <v>41190.324591727585</v>
+        <f t="shared" si="73"/>
+        <v>46853.369394951653</v>
       </c>
       <c r="FH13" s="6">
-        <f t="shared" si="70"/>
-        <v>40778.421345810311</v>
+        <f t="shared" si="73"/>
+        <v>46384.835701002135</v>
       </c>
       <c r="FI13" s="6">
-        <f t="shared" si="70"/>
-        <v>40370.637132352211</v>
-      </c>
-    </row>
-    <row r="14" spans="2:165">
+        <f t="shared" si="73"/>
+        <v>45920.987343992114</v>
+      </c>
+      <c r="FJ13" s="6">
+        <f t="shared" si="73"/>
+        <v>45461.777470552195</v>
+      </c>
+      <c r="FK13" s="6">
+        <f t="shared" si="73"/>
+        <v>45007.159695846676</v>
+      </c>
+      <c r="FL13" s="6">
+        <f t="shared" si="73"/>
+        <v>44557.088098888205</v>
+      </c>
+      <c r="FM13" s="6">
+        <f t="shared" si="73"/>
+        <v>44111.517217899323</v>
+      </c>
+      <c r="FN13" s="6">
+        <f t="shared" si="73"/>
+        <v>43670.40204572033</v>
+      </c>
+      <c r="FO13" s="6">
+        <f t="shared" si="73"/>
+        <v>43233.698025263126</v>
+      </c>
+      <c r="FP13" s="6">
+        <f t="shared" si="73"/>
+        <v>42801.361045010497</v>
+      </c>
+      <c r="FQ13" s="6">
+        <f t="shared" si="73"/>
+        <v>42373.34743456039</v>
+      </c>
+      <c r="FR13" s="6">
+        <f t="shared" si="73"/>
+        <v>41949.613960214789</v>
+      </c>
+      <c r="FS13" s="6">
+        <f t="shared" si="73"/>
+        <v>41530.117820612642</v>
+      </c>
+      <c r="FT13" s="6">
+        <f t="shared" si="73"/>
+        <v>41114.816642406513</v>
+      </c>
+    </row>
+    <row r="14" spans="2:176">
       <c r="B14" t="s">
         <v>1</v>
       </c>
@@ -4709,309 +5062,375 @@
         <f>2517</f>
         <v>2517</v>
       </c>
-      <c r="AN14" s="4">
-        <f>P14</f>
+      <c r="AM14" s="4"/>
+      <c r="AN14" s="4"/>
+      <c r="AO14" s="4"/>
+      <c r="AP14" s="4"/>
+      <c r="AQ14" s="4"/>
+      <c r="AR14" s="4">
+        <f t="shared" ref="AR14:AY14" si="74">I14</f>
+        <v>2848.8</v>
+      </c>
+      <c r="AS14" s="4">
+        <f t="shared" si="74"/>
+        <v>2848.8</v>
+      </c>
+      <c r="AT14" s="4">
+        <f t="shared" si="74"/>
+        <v>2848.8</v>
+      </c>
+      <c r="AU14" s="4">
+        <f t="shared" si="74"/>
+        <v>2848.8</v>
+      </c>
+      <c r="AV14" s="4">
+        <f t="shared" si="74"/>
+        <v>2848.8</v>
+      </c>
+      <c r="AW14" s="4">
+        <f t="shared" si="74"/>
+        <v>2848.8</v>
+      </c>
+      <c r="AX14" s="4">
+        <f t="shared" si="74"/>
+        <v>2848.8</v>
+      </c>
+      <c r="AY14" s="4">
+        <f t="shared" si="74"/>
         <v>2517</v>
       </c>
-      <c r="AO14" s="4">
-        <f>AN14</f>
+      <c r="AZ14" s="4">
+        <f>AY14</f>
         <v>2517</v>
       </c>
-      <c r="AP14" s="4">
-        <f>AO14</f>
+      <c r="BA14" s="4">
+        <f>AZ14</f>
         <v>2517</v>
       </c>
-      <c r="AQ14" s="4">
-        <f>AP14</f>
+      <c r="BB14" s="4">
+        <f>BA14</f>
         <v>2517</v>
       </c>
-      <c r="AR14" s="4">
-        <f t="shared" ref="AR14" si="71">AQ14</f>
+      <c r="BC14" s="4">
+        <f t="shared" ref="BC14" si="75">BB14</f>
         <v>2517</v>
       </c>
-      <c r="AS14" s="4">
-        <f t="shared" ref="AS14:AT14" si="72">2396+439.4</f>
+      <c r="BD14" s="4">
+        <f t="shared" ref="BD14:BE14" si="76">2396+439.4</f>
         <v>2835.4</v>
       </c>
-      <c r="AT14" s="4">
-        <f t="shared" si="72"/>
+      <c r="BE14" s="4">
+        <f t="shared" si="76"/>
         <v>2835.4</v>
       </c>
-      <c r="AU14" s="4">
-        <f t="shared" ref="AU14" si="73">2189.9+343.8</f>
+      <c r="BF14" s="4">
+        <f t="shared" ref="BF14" si="77">2189.9+343.8</f>
         <v>2533.7000000000003</v>
       </c>
-      <c r="AV14" s="4">
+      <c r="BG14" s="4">
         <f>2517</f>
         <v>2517</v>
       </c>
-      <c r="AW14" s="4">
+      <c r="BH14" s="4">
         <f>2517</f>
         <v>2517</v>
       </c>
-      <c r="AX14" s="4">
+      <c r="BI14" s="4">
         <f>2517</f>
         <v>2517</v>
       </c>
-      <c r="AY14" s="4">
+      <c r="BJ14" s="4">
         <f>2517</f>
         <v>2517</v>
       </c>
-      <c r="AZ14" s="4">
+      <c r="BK14" s="4">
         <f>2517</f>
         <v>2517</v>
       </c>
-      <c r="BA14" s="4">
+      <c r="BL14" s="4">
         <f>2517</f>
         <v>2517</v>
       </c>
-      <c r="BB14" s="4">
+      <c r="BM14" s="4">
         <f>2517</f>
         <v>2517</v>
       </c>
-      <c r="BC14" s="4">
+      <c r="BN14" s="4">
         <f>2517</f>
         <v>2517</v>
       </c>
-      <c r="BD14" s="4">
+      <c r="BO14" s="4">
         <f>2517</f>
         <v>2517</v>
       </c>
-      <c r="BE14" s="4">
+      <c r="BP14" s="4">
         <f>2517</f>
         <v>2517</v>
       </c>
-      <c r="BF14" s="4">
+      <c r="BQ14" s="4">
         <f>2517</f>
         <v>2517</v>
       </c>
     </row>
-    <row r="15" spans="2:165" s="6" customFormat="1">
+    <row r="15" spans="2:176" s="6" customFormat="1">
       <c r="B15" s="6" t="s">
         <v>36</v>
       </c>
       <c r="C15" s="7">
-        <f t="shared" ref="C15:P15" si="74">C13/C14</f>
+        <f t="shared" ref="C15:P15" si="78">C13/C14</f>
         <v>1.0737854535242908</v>
       </c>
       <c r="D15" s="7">
-        <f t="shared" si="74"/>
+        <f t="shared" si="78"/>
         <v>1.3654872226902555</v>
       </c>
       <c r="E15" s="7">
-        <f t="shared" si="74"/>
+        <f t="shared" si="78"/>
         <v>1.6522746419545071</v>
       </c>
       <c r="F15" s="7">
-        <f t="shared" si="74"/>
+        <f t="shared" si="78"/>
         <v>1.2454366750912664</v>
       </c>
       <c r="G15" s="7">
-        <f t="shared" si="74"/>
+        <f t="shared" si="78"/>
         <v>1.7505616399887671</v>
       </c>
       <c r="H15" s="7">
-        <f t="shared" si="74"/>
+        <f t="shared" si="78"/>
         <v>1.7923336141533277</v>
       </c>
       <c r="I15" s="7">
-        <f t="shared" si="74"/>
+        <f t="shared" si="78"/>
         <v>1.8032153889356921</v>
       </c>
       <c r="J15" s="7">
-        <f t="shared" si="74"/>
+        <f t="shared" si="78"/>
         <v>2.4157540016849199</v>
       </c>
       <c r="K15" s="7">
-        <f t="shared" si="74"/>
+        <f t="shared" si="78"/>
         <v>0.85263970794720578</v>
       </c>
       <c r="L15" s="7">
-        <f t="shared" si="74"/>
+        <f t="shared" si="78"/>
         <v>0.91126088177478226</v>
       </c>
       <c r="M15" s="7">
-        <f t="shared" si="74"/>
+        <f t="shared" si="78"/>
         <v>2.1380932322381354</v>
       </c>
       <c r="N15" s="7">
-        <f t="shared" si="74"/>
+        <f t="shared" si="78"/>
         <v>2.5796826734063463</v>
       </c>
       <c r="O15" s="7">
-        <f t="shared" si="74"/>
+        <f t="shared" si="78"/>
         <v>1.7207245155855095</v>
       </c>
       <c r="P15" s="7">
-        <f t="shared" si="74"/>
+        <f t="shared" si="78"/>
         <v>2.0572109654350417</v>
       </c>
       <c r="Q15" s="7">
-        <f t="shared" ref="Q15:R15" si="75">Q13/Q14</f>
+        <f t="shared" ref="Q15:R15" si="79">Q13/Q14</f>
         <v>2.754142094917158</v>
       </c>
       <c r="R15" s="7">
-        <f t="shared" si="75"/>
+        <f t="shared" si="79"/>
         <v>3.9381493962370118</v>
       </c>
       <c r="S15" s="7">
-        <f t="shared" ref="S15:V15" si="76">S13/S14</f>
+        <f t="shared" ref="S15:V15" si="80">S13/S14</f>
         <v>3.3494392325597797</v>
       </c>
       <c r="T15" s="7">
-        <f t="shared" ref="T15:U15" si="77">T13/T14</f>
+        <f t="shared" ref="T15:U15" si="81">T13/T14</f>
         <v>3.667607621736062</v>
       </c>
       <c r="U15" s="7">
-        <f t="shared" si="77"/>
+        <f t="shared" si="81"/>
         <v>3.2672352523098791</v>
       </c>
       <c r="V15" s="7">
-        <f t="shared" si="76"/>
+        <f t="shared" si="80"/>
         <v>3.7197106690777577</v>
       </c>
       <c r="W15" s="7">
-        <f t="shared" ref="W15:X15" si="78">W13/W14</f>
+        <f t="shared" ref="W15:X15" si="82">W13/W14</f>
         <v>2.7394495412844035</v>
       </c>
       <c r="X15" s="7">
-        <f t="shared" si="78"/>
+        <f t="shared" si="82"/>
         <v>2.4730029585798818</v>
       </c>
       <c r="Y15" s="7">
-        <f t="shared" ref="Y15" si="79">Y13/Y14</f>
+        <f t="shared" ref="Y15" si="83">Y13/Y14</f>
         <v>1.638702460850112</v>
       </c>
       <c r="Z15" s="7">
-        <f t="shared" ref="Z15" si="80">Z13/Z14</f>
+        <f t="shared" ref="Z15" si="84">Z13/Z14</f>
         <v>1.7634571645185746</v>
       </c>
       <c r="AA15" s="7">
-        <f t="shared" ref="AA15:AC15" si="81">AA13/AA14</f>
+        <f t="shared" ref="AA15:AC15" si="85">AA13/AA14</f>
         <v>2.206803247004252</v>
       </c>
       <c r="AB15" s="7">
-        <f t="shared" si="81"/>
+        <f t="shared" si="85"/>
         <v>3.0327102803738319</v>
       </c>
       <c r="AC15" s="7">
-        <f t="shared" si="81"/>
+        <f t="shared" si="85"/>
         <v>4.6013198757763973</v>
       </c>
       <c r="AD15" s="7">
-        <f t="shared" ref="AD15" si="82">AD13/AD14</f>
+        <f t="shared" ref="AD15" si="86">AD13/AD14</f>
         <v>5.4625876851130162</v>
       </c>
       <c r="AE15" s="7">
-        <f t="shared" ref="AE15" si="83">AE13/AE14</f>
+        <f t="shared" ref="AE15" si="87">AE13/AE14</f>
         <v>4.8601178781925345</v>
       </c>
       <c r="AF15" s="7">
-        <f t="shared" ref="AF15:AH15" si="84">AF13/AF14</f>
+        <f t="shared" ref="AF15:AH15" si="88">AF13/AF14</f>
         <v>5.2907662082514735</v>
       </c>
       <c r="AG15" s="7">
-        <f t="shared" si="84"/>
+        <f t="shared" si="88"/>
         <v>6.2142998613586853</v>
       </c>
       <c r="AH15" s="7">
-        <f t="shared" si="84"/>
+        <f t="shared" si="88"/>
         <v>7.6125823893910081</v>
       </c>
       <c r="AI15" s="7">
-        <f t="shared" ref="AI15:AL15" si="85">AI13/AI14</f>
+        <f t="shared" ref="AI15:AL15" si="89">AI13/AI14</f>
         <v>6.5864661654135341</v>
       </c>
       <c r="AJ15" s="7">
-        <f t="shared" si="85"/>
+        <f t="shared" si="89"/>
         <v>7.2823669579030978</v>
       </c>
       <c r="AK15" s="7">
-        <f t="shared" si="85"/>
+        <f t="shared" si="89"/>
         <v>7.4052443384982123</v>
       </c>
       <c r="AL15" s="7">
-        <f t="shared" si="85"/>
-        <v>8.5242946364719892</v>
-      </c>
-      <c r="AN15" s="7">
-        <f>AN13/AN14</f>
+        <f t="shared" si="89"/>
+        <v>9.0456893126738187</v>
+      </c>
+      <c r="AM15" s="7"/>
+      <c r="AN15" s="7"/>
+      <c r="AO15" s="7"/>
+      <c r="AP15" s="7"/>
+      <c r="AQ15" s="7"/>
+      <c r="AR15" s="7">
+        <f t="shared" ref="AR15:BB15" si="90">AR13/AR14</f>
+        <v>0.21272114574557707</v>
+      </c>
+      <c r="AS15" s="7">
+        <f t="shared" si="90"/>
+        <v>0.35102499297950013</v>
+      </c>
+      <c r="AT15" s="7">
+        <f t="shared" si="90"/>
+        <v>1.8604324627913508E-2</v>
+      </c>
+      <c r="AU15" s="7">
+        <f t="shared" si="90"/>
+        <v>0.52653748946925016</v>
+      </c>
+      <c r="AV15" s="7">
+        <f t="shared" si="90"/>
+        <v>1.0320134793597304</v>
+      </c>
+      <c r="AW15" s="7">
+        <f t="shared" si="90"/>
+        <v>1.2945801741083964</v>
+      </c>
+      <c r="AX15" s="7">
+        <f t="shared" si="90"/>
+        <v>3.5864223532715527</v>
+      </c>
+      <c r="AY15" s="7">
+        <f t="shared" si="90"/>
         <v>6.0405244338498214</v>
       </c>
-      <c r="AO15" s="7">
-        <f>AO13/AO14</f>
+      <c r="AZ15" s="7">
+        <f t="shared" si="90"/>
         <v>8.7850615812475166</v>
       </c>
-      <c r="AP15" s="7">
-        <f>AP13/AP14</f>
+      <c r="BA15" s="7">
+        <f t="shared" si="90"/>
         <v>7.33611442193087</v>
       </c>
-      <c r="AQ15" s="7">
-        <f>AQ13/AQ14</f>
+      <c r="BB15" s="7">
+        <f t="shared" si="90"/>
         <v>11.579261025029798</v>
       </c>
-      <c r="AR15" s="7">
-        <f t="shared" ref="AR15:BA15" si="86">AR13/AR14</f>
+      <c r="BC15" s="7">
+        <f t="shared" ref="BC15:BL15" si="91">BC13/BC14</f>
         <v>15.641636869288837</v>
       </c>
-      <c r="AS15" s="7">
-        <f t="shared" si="86"/>
+      <c r="BD15" s="7">
+        <f t="shared" si="91"/>
         <v>8.1819143683430902</v>
       </c>
-      <c r="AT15" s="7">
-        <f t="shared" si="86"/>
+      <c r="BE15" s="7">
+        <f t="shared" si="91"/>
         <v>13.884108062354517</v>
       </c>
-      <c r="AU15" s="7">
-        <f t="shared" si="86"/>
+      <c r="BF15" s="7">
+        <f t="shared" si="91"/>
         <v>24.000473615660887</v>
       </c>
-      <c r="AV15" s="7">
-        <f t="shared" si="86"/>
-        <v>29.778184187524836</v>
-      </c>
-      <c r="AW15" s="7">
-        <f t="shared" si="86"/>
-        <v>33.210010091760026</v>
-      </c>
-      <c r="AX15" s="7">
-        <f t="shared" si="86"/>
-        <v>36.478930837734168</v>
-      </c>
-      <c r="AY15" s="7">
-        <f t="shared" si="86"/>
-        <v>39.317929343733873</v>
-      </c>
-      <c r="AZ15" s="7">
-        <f t="shared" si="86"/>
-        <v>41.26705841714341</v>
-      </c>
-      <c r="BA15" s="7">
-        <f t="shared" si="86"/>
-        <v>42.572554867684794</v>
-      </c>
-      <c r="BB15" s="7">
-        <f t="shared" ref="BB15:BF15" si="87">BB13/BB14</f>
-        <v>43.43245669800519</v>
-      </c>
-      <c r="BC15" s="7">
-        <f t="shared" si="87"/>
-        <v>44.301254564865516</v>
-      </c>
-      <c r="BD15" s="7">
-        <f t="shared" si="87"/>
-        <v>45.187282273861868</v>
-      </c>
-      <c r="BE15" s="7">
-        <f t="shared" si="87"/>
-        <v>46.091027965410603</v>
-      </c>
-      <c r="BF15" s="7">
-        <f t="shared" si="87"/>
-        <v>47.012848525529662</v>
-      </c>
-    </row>
-    <row r="17" spans="2:61">
+      <c r="BG15" s="7">
+        <f t="shared" si="91"/>
+        <v>30.348947159316641</v>
+      </c>
+      <c r="BH15" s="7">
+        <f t="shared" si="91"/>
+        <v>33.828873730631706</v>
+      </c>
+      <c r="BI15" s="7">
+        <f t="shared" si="91"/>
+        <v>37.156336444643621</v>
+      </c>
+      <c r="BJ15" s="7">
+        <f t="shared" si="91"/>
+        <v>40.045899329673645</v>
+      </c>
+      <c r="BK15" s="7">
+        <f t="shared" si="91"/>
+        <v>42.029279675677827</v>
+      </c>
+      <c r="BL15" s="7">
+        <f t="shared" si="91"/>
+        <v>43.357350536611833</v>
+      </c>
+      <c r="BM15" s="7">
+        <f t="shared" ref="BM15:BQ15" si="92">BM13/BM14</f>
+        <v>44.233077288050673</v>
+      </c>
+      <c r="BN15" s="7">
+        <f t="shared" si="92"/>
+        <v>45.117889837248114</v>
+      </c>
+      <c r="BO15" s="7">
+        <f t="shared" si="92"/>
+        <v>46.020250291653561</v>
+      </c>
+      <c r="BP15" s="7">
+        <f t="shared" si="92"/>
+        <v>46.940655344261458</v>
+      </c>
+      <c r="BQ15" s="7">
+        <f t="shared" si="92"/>
+        <v>47.879468451969927</v>
+      </c>
+    </row>
+    <row r="17" spans="2:72">
       <c r="B17" s="6" t="s">
         <v>41</v>
       </c>
@@ -5020,204 +5439,237 @@
         <v>0.48979083665338652</v>
       </c>
       <c r="H17" s="9">
-        <f t="shared" ref="H17:R17" si="88">H3/D3-1</f>
+        <f t="shared" ref="H17:R17" si="93">H3/D3-1</f>
         <v>0.41948288810213485</v>
       </c>
       <c r="I17" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="93"/>
         <v>0.32910534469403574</v>
       </c>
       <c r="J17" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="93"/>
         <v>0.30388529139685483</v>
       </c>
       <c r="K17" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="93"/>
         <v>0.25998662878154777</v>
       </c>
       <c r="L17" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="93"/>
         <v>0.27473358022825178</v>
       </c>
       <c r="M17" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="93"/>
         <v>0.2859328331026445</v>
       </c>
       <c r="N17" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="93"/>
         <v>0.2464230814709707</v>
       </c>
       <c r="O17" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="93"/>
         <v>0.17642767128739134</v>
       </c>
       <c r="P17" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="93"/>
         <v>0.10796869441479906</v>
       </c>
       <c r="Q17" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="93"/>
         <v>0.21629277135735325</v>
       </c>
       <c r="R17" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="93"/>
         <v>0.33156247035385644</v>
       </c>
       <c r="S17" s="9">
-        <f t="shared" ref="S17" si="89">S3/O3-1</f>
+        <f t="shared" ref="S17" si="94">S3/O3-1</f>
         <v>0.47550318543158365</v>
       </c>
       <c r="T17" s="9">
-        <f t="shared" ref="T17" si="90">T3/P3-1</f>
+        <f t="shared" ref="T17" si="95">T3/P3-1</f>
         <v>0.5560014983678494</v>
       </c>
       <c r="U17" s="9">
-        <f t="shared" ref="U17" si="91">U3/Q3-1</f>
+        <f t="shared" ref="U17" si="96">U3/Q3-1</f>
         <v>0.35118770377270603</v>
       </c>
       <c r="V17" s="9">
-        <f t="shared" ref="V17" si="92">V3/R3-1</f>
+        <f t="shared" ref="V17" si="97">V3/R3-1</f>
         <v>0.19945141065830718</v>
       </c>
       <c r="W17" s="9">
-        <f t="shared" ref="W17" si="93">W3/S3-1</f>
+        <f t="shared" ref="W17" si="98">W3/S3-1</f>
         <v>6.6371174200450911E-2</v>
       </c>
       <c r="X17" s="9">
-        <f t="shared" ref="X17" si="94">X3/T3-1</f>
+        <f t="shared" ref="X17" si="99">X3/T3-1</f>
         <v>-8.7698180692643568E-3</v>
       </c>
       <c r="Y17" s="9">
-        <f t="shared" ref="Y17" si="95">Y3/U3-1</f>
+        <f t="shared" ref="Y17" si="100">Y3/U3-1</f>
         <v>-4.4674250258531556E-2</v>
       </c>
       <c r="Z17" s="9">
-        <f t="shared" ref="Z17" si="96">Z3/V3-1</f>
+        <f t="shared" ref="Z17" si="101">Z3/V3-1</f>
         <v>-4.4726916337501144E-2</v>
       </c>
       <c r="AA17" s="9">
-        <f t="shared" ref="AA17" si="97">AA3/W3-1</f>
+        <f t="shared" ref="AA17" si="102">AA3/W3-1</f>
         <v>2.6408198366060009E-2</v>
       </c>
       <c r="AB17" s="9">
-        <f t="shared" ref="AB17" si="98">AB3/X3-1</f>
+        <f t="shared" ref="AB17" si="103">AB3/X3-1</f>
         <v>0.11022829782804799</v>
       </c>
       <c r="AC17" s="9">
-        <f t="shared" ref="AC17" si="99">AC3/Y3-1</f>
+        <f t="shared" ref="AC17" si="104">AC3/Y3-1</f>
         <v>0.24182723533232298</v>
       </c>
       <c r="AD17" s="9">
-        <f t="shared" ref="AD17" si="100">AD3/Z3-1</f>
+        <f t="shared" ref="AD17" si="105">AD3/Z3-1</f>
         <v>0.24703870666873939</v>
       </c>
       <c r="AE17" s="9">
-        <f t="shared" ref="AE17" si="101">AE3/AA3-1</f>
+        <f t="shared" ref="AE17" si="106">AE3/AA3-1</f>
         <v>0.27264793157619138</v>
       </c>
       <c r="AF17" s="9">
-        <f t="shared" ref="AF17" si="102">AF3/AB3-1</f>
+        <f t="shared" ref="AF17" si="107">AF3/AB3-1</f>
         <v>0.2210069064658271</v>
       </c>
       <c r="AG17" s="9">
-        <f t="shared" ref="AG17" si="103">AG3/AC3-1</f>
+        <f t="shared" ref="AG17" si="108">AG3/AC3-1</f>
         <v>0.17936424918642491</v>
       </c>
       <c r="AH17" s="9">
-        <f t="shared" ref="AH17" si="104">AH3/AD3-1</f>
+        <f t="shared" ref="AH17" si="109">AH3/AD3-1</f>
         <v>0.20627757971628724</v>
       </c>
       <c r="AI17" s="9">
-        <f t="shared" ref="AI17" si="105">AI3/AE3-1</f>
+        <f t="shared" ref="AI17" si="110">AI3/AE3-1</f>
         <v>0.16071869428062002</v>
       </c>
       <c r="AJ17" s="9">
-        <f t="shared" ref="AJ17" si="106">AJ3/AF3-1</f>
+        <f t="shared" ref="AJ17" si="111">AJ3/AF3-1</f>
         <v>0.21614496685521223</v>
       </c>
       <c r="AK17" s="9">
-        <f t="shared" ref="AK17" si="107">AK3/AG3-1</f>
+        <f t="shared" ref="AK17" si="112">AK3/AG3-1</f>
         <v>0.26246027248761972</v>
       </c>
       <c r="AL17" s="9">
-        <f t="shared" ref="AL17" si="108">AL3/AH3-1</f>
-        <v>0.19999999999999996</v>
-      </c>
+        <f t="shared" ref="AL17" si="113">AL3/AH3-1</f>
+        <v>0.23784230649994842</v>
+      </c>
+      <c r="AM17" s="9"/>
       <c r="AN17" s="9"/>
-      <c r="AO17" s="9">
-        <f>AO3/AN3-1</f>
+      <c r="AO17" s="9"/>
+      <c r="AP17" s="9"/>
+      <c r="AQ17" s="9"/>
+      <c r="AR17" s="9"/>
+      <c r="AS17" s="9">
+        <f t="shared" ref="AS17:AV17" si="114">AS3/AR3-1</f>
+        <v>0.87993920972644379</v>
+      </c>
+      <c r="AT17" s="9">
+        <f t="shared" si="114"/>
+        <v>0.37132848288870934</v>
+      </c>
+      <c r="AU17" s="9">
+        <f t="shared" si="114"/>
+        <v>0.5468657889565729</v>
+      </c>
+      <c r="AV17" s="9">
+        <f t="shared" si="114"/>
+        <v>0.58358739837398366</v>
+      </c>
+      <c r="AW17" s="9">
+        <f t="shared" ref="AW17:AY17" si="115">AW3/AV3-1</f>
+        <v>0.43815177282207607</v>
+      </c>
+      <c r="AX17" s="9">
+        <f t="shared" si="115"/>
+        <v>0.54161088799643009</v>
+      </c>
+      <c r="AY17" s="9">
+        <f t="shared" si="115"/>
+        <v>0.47090961719371882</v>
+      </c>
+      <c r="AZ17" s="9">
+        <f>AZ3/AY3-1</f>
         <v>0.37352716896661997</v>
       </c>
-      <c r="AP17" s="9">
-        <f t="shared" ref="AP17:BA17" si="109">AP3/AO3-1</f>
+      <c r="BA17" s="9">
+        <f t="shared" ref="BA17:BL17" si="116">BA3/AZ3-1</f>
         <v>0.26575092231097108</v>
       </c>
-      <c r="AQ17" s="9">
-        <f t="shared" si="109"/>
+      <c r="BB17" s="9">
+        <f t="shared" si="116"/>
         <v>0.21632214157363783</v>
       </c>
-      <c r="AR17" s="9">
-        <f t="shared" si="109"/>
+      <c r="BC17" s="9">
+        <f t="shared" si="116"/>
         <v>0.37180978526394148</v>
       </c>
-      <c r="AS17" s="9">
-        <f t="shared" si="109"/>
+      <c r="BD17" s="9">
+        <f t="shared" si="116"/>
         <v>-1.1193175554782941E-2</v>
       </c>
-      <c r="AT17" s="9">
-        <f t="shared" si="109"/>
+      <c r="BE17" s="9">
+        <f t="shared" si="116"/>
         <v>0.15918153830321846</v>
       </c>
-      <c r="AU17" s="9">
-        <f t="shared" si="109"/>
+      <c r="BF17" s="9">
+        <f t="shared" si="116"/>
         <v>0.21697701430040461</v>
       </c>
-      <c r="AV17" s="9">
-        <f t="shared" si="109"/>
-        <v>0.21054103343465047</v>
-      </c>
-      <c r="AW17" s="9">
-        <f t="shared" si="109"/>
-        <v>0.1399999999999999</v>
-      </c>
-      <c r="AX17" s="9">
-        <f t="shared" si="109"/>
+      <c r="BG17" s="9">
+        <f t="shared" si="116"/>
+        <v>0.22167173252279637</v>
+      </c>
+      <c r="BH17" s="9">
+        <f t="shared" si="116"/>
+        <v>0.14999999999999991</v>
+      </c>
+      <c r="BI17" s="9">
+        <f t="shared" si="116"/>
         <v>8.0000000000000071E-2</v>
       </c>
-      <c r="AY17" s="9">
-        <f t="shared" si="109"/>
+      <c r="BJ17" s="9">
+        <f t="shared" si="116"/>
         <v>6.0000000000000053E-2</v>
       </c>
-      <c r="AZ17" s="9">
-        <f t="shared" si="109"/>
+      <c r="BK17" s="9">
+        <f t="shared" si="116"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="BA17" s="9">
-        <f t="shared" si="109"/>
+      <c r="BL17" s="9">
+        <f t="shared" si="116"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="BB17" s="9">
-        <f t="shared" ref="BB17" si="110">BB3/BA3-1</f>
+      <c r="BM17" s="9">
+        <f t="shared" ref="BM17" si="117">BM3/BL3-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BC17" s="9">
-        <f t="shared" ref="BC17" si="111">BC3/BB3-1</f>
+      <c r="BN17" s="9">
+        <f t="shared" ref="BN17" si="118">BN3/BM3-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BD17" s="9">
-        <f t="shared" ref="BD17" si="112">BD3/BC3-1</f>
+      <c r="BO17" s="9">
+        <f t="shared" ref="BO17" si="119">BO3/BN3-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BE17" s="9">
-        <f t="shared" ref="BE17" si="113">BE3/BD3-1</f>
+      <c r="BP17" s="9">
+        <f t="shared" ref="BP17" si="120">BP3/BO3-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BF17" s="9">
-        <f t="shared" ref="BF17" si="114">BF3/BE3-1</f>
+      <c r="BQ17" s="9">
+        <f t="shared" ref="BQ17" si="121">BQ3/BP3-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
-    <row r="18" spans="2:61">
+    <row r="18" spans="2:72">
       <c r="B18" s="6" t="s">
         <v>37</v>
       </c>
@@ -5226,229 +5678,262 @@
         <v>0.85570219123505975</v>
       </c>
       <c r="D18" s="9">
-        <f t="shared" ref="D18:R18" si="115">D5/D3</f>
+        <f t="shared" ref="D18:R18" si="122">D5/D3</f>
         <v>0.86728891749812254</v>
       </c>
       <c r="E18" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="122"/>
         <v>0.85979860573199074</v>
       </c>
       <c r="F18" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="122"/>
         <v>0.87580943570767811</v>
       </c>
       <c r="G18" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="122"/>
         <v>0.8389603877653351</v>
       </c>
       <c r="H18" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="122"/>
         <v>0.83266570931902351</v>
       </c>
       <c r="I18" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="122"/>
         <v>0.82385080498288044</v>
       </c>
       <c r="J18" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="122"/>
         <v>0.83469315360056762</v>
       </c>
       <c r="K18" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="122"/>
         <v>0.81322544272733299</v>
       </c>
       <c r="L18" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="122"/>
         <v>0.80392505632633704</v>
       </c>
       <c r="M18" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="122"/>
         <v>0.82126671198731027</v>
       </c>
       <c r="N18" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="122"/>
         <v>0.83436106631249407</v>
       </c>
       <c r="O18" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="122"/>
         <v>0.80498393189378137</v>
       </c>
       <c r="P18" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="122"/>
         <v>0.7950981966072671</v>
       </c>
       <c r="Q18" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="122"/>
         <v>0.80465766185374943</v>
       </c>
       <c r="R18" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="122"/>
         <v>0.81440581362211462</v>
       </c>
       <c r="S18" s="9">
-        <f t="shared" ref="S18:V18" si="116">S5/S3</f>
+        <f t="shared" ref="S18:V18" si="123">S5/S3</f>
         <v>0.80394329601467274</v>
       </c>
       <c r="T18" s="9">
-        <f t="shared" si="116"/>
+        <f t="shared" si="123"/>
         <v>0.81432059703545756</v>
       </c>
       <c r="U18" s="9">
-        <f t="shared" si="116"/>
+        <f t="shared" si="123"/>
         <v>0.80106859703550504</v>
       </c>
       <c r="V18" s="9">
-        <f t="shared" si="116"/>
+        <f t="shared" si="123"/>
         <v>0.81146981081642955</v>
       </c>
       <c r="W18" s="9">
-        <f t="shared" ref="W18:AE18" si="117">W5/W3</f>
+        <f t="shared" ref="W18:AE18" si="124">W5/W3</f>
         <v>0.78482872294682526</v>
       </c>
       <c r="X18" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="124"/>
         <v>0.81985982929706469</v>
       </c>
       <c r="Y18" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="124"/>
         <v>0.79375045103557773</v>
       </c>
       <c r="Z18" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="124"/>
         <v>0.74083631276231932</v>
       </c>
       <c r="AA18" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="124"/>
         <v>0.7867690696456624</v>
       </c>
       <c r="AB18" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="124"/>
         <v>0.81421294415450485</v>
       </c>
       <c r="AC18" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="124"/>
         <v>0.81956066945606698</v>
       </c>
       <c r="AD18" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="124"/>
         <v>0.80815736331679588</v>
       </c>
       <c r="AE18" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="124"/>
         <v>0.81785763269784661</v>
       </c>
       <c r="AF18" s="9">
-        <f t="shared" ref="AF18:AH18" si="118">AF5/AF3</f>
+        <f t="shared" ref="AF18:AH18" si="125">AF5/AF3</f>
         <v>0.81295590079598679</v>
       </c>
       <c r="AG18" s="9">
-        <f t="shared" si="118"/>
+        <f t="shared" si="125"/>
         <v>0.81830052477272164</v>
       </c>
       <c r="AH18" s="9">
-        <f t="shared" si="118"/>
+        <f t="shared" si="125"/>
         <v>0.81731941717474421</v>
       </c>
       <c r="AI18" s="9">
-        <f t="shared" ref="AI18:AL18" si="119">AI5/AI3</f>
+        <f t="shared" ref="AI18:AL18" si="126">AI5/AI3</f>
         <v>0.82105213404546962</v>
       </c>
       <c r="AJ18" s="9">
-        <f t="shared" si="119"/>
+        <f t="shared" si="126"/>
         <v>0.82130229817324696</v>
       </c>
       <c r="AK18" s="9">
-        <f t="shared" si="119"/>
+        <f t="shared" si="126"/>
         <v>0.82034268763904605</v>
       </c>
       <c r="AL18" s="9">
-        <f t="shared" si="119"/>
+        <f t="shared" si="126"/>
+        <v>0.8179253001185447</v>
+      </c>
+      <c r="AM18" s="9"/>
+      <c r="AN18" s="9"/>
+      <c r="AO18" s="9"/>
+      <c r="AP18" s="9"/>
+      <c r="AQ18" s="9"/>
+      <c r="AR18" s="9">
+        <f t="shared" ref="AR18:AV18" si="127">AR5/AR3</f>
+        <v>0.75025329280648434</v>
+      </c>
+      <c r="AS18" s="9">
+        <f t="shared" si="127"/>
+        <v>0.76825653462678523</v>
+      </c>
+      <c r="AT18" s="9">
+        <f t="shared" si="127"/>
+        <v>0.73197091766555311</v>
+      </c>
+      <c r="AU18" s="9">
+        <f t="shared" si="127"/>
+        <v>0.76181402439024393</v>
+      </c>
+      <c r="AV18" s="9">
+        <f t="shared" si="127"/>
+        <v>0.82729022942403341</v>
+      </c>
+      <c r="AW18" s="9">
+        <f t="shared" ref="AW18:AY18" si="128">AW5/AW3</f>
+        <v>0.84008255243195007</v>
+      </c>
+      <c r="AX18" s="9">
+        <f t="shared" si="128"/>
+        <v>0.86290614371517471</v>
+      </c>
+      <c r="AY18" s="9">
+        <f t="shared" si="128"/>
+        <v>0.86581556096721024</v>
+      </c>
+      <c r="AZ18" s="9">
+        <f t="shared" ref="AZ18:BL18" si="129">AZ5/AZ3</f>
+        <v>0.8324617643898421</v>
+      </c>
+      <c r="BA18" s="9">
+        <f t="shared" si="129"/>
+        <v>0.81931887318363827</v>
+      </c>
+      <c r="BB18" s="9">
+        <f t="shared" si="129"/>
+        <v>0.80583021194425708</v>
+      </c>
+      <c r="BC18" s="9">
+        <f t="shared" si="129"/>
+        <v>0.80794376277251567</v>
+      </c>
+      <c r="BD18" s="9">
+        <f t="shared" si="129"/>
+        <v>0.78347297378418479</v>
+      </c>
+      <c r="BE18" s="9">
+        <f t="shared" si="129"/>
+        <v>0.80796176694705224</v>
+      </c>
+      <c r="BF18" s="9">
+        <f t="shared" si="129"/>
+        <v>0.81664437689969605</v>
+      </c>
+      <c r="BG18" s="9">
+        <f t="shared" si="129"/>
         <v>0.82</v>
       </c>
-      <c r="AN18" s="9">
-        <f t="shared" ref="AN18" si="120">AN5/AN3</f>
-        <v>0.86581556096721024</v>
-      </c>
-      <c r="AO18" s="9">
-        <f t="shared" ref="AO18:BA18" si="121">AO5/AO3</f>
-        <v>0.8324617643898421</v>
-      </c>
-      <c r="AP18" s="9">
-        <f t="shared" si="121"/>
-        <v>0.81931887318363827</v>
-      </c>
-      <c r="AQ18" s="9">
-        <f t="shared" si="121"/>
-        <v>0.80583021194425708</v>
-      </c>
-      <c r="AR18" s="9">
-        <f t="shared" si="121"/>
-        <v>0.80794376277251567</v>
-      </c>
-      <c r="AS18" s="9">
-        <f t="shared" si="121"/>
-        <v>0.78347297378418479</v>
-      </c>
-      <c r="AT18" s="9">
-        <f t="shared" si="121"/>
-        <v>0.80796176694705224</v>
-      </c>
-      <c r="AU18" s="9">
-        <f t="shared" si="121"/>
-        <v>0.81664437689969605</v>
-      </c>
-      <c r="AV18" s="9">
-        <f t="shared" si="121"/>
-        <v>0.82000000000000006</v>
-      </c>
-      <c r="AW18" s="9">
-        <f t="shared" si="121"/>
+      <c r="BH18" s="9">
+        <f t="shared" si="129"/>
         <v>0.82</v>
       </c>
-      <c r="AX18" s="9">
-        <f t="shared" si="121"/>
+      <c r="BI18" s="9">
+        <f t="shared" si="129"/>
         <v>0.82</v>
       </c>
-      <c r="AY18" s="9">
-        <f t="shared" si="121"/>
+      <c r="BJ18" s="9">
+        <f t="shared" si="129"/>
         <v>0.82</v>
       </c>
-      <c r="AZ18" s="9">
-        <f t="shared" si="121"/>
+      <c r="BK18" s="9">
+        <f t="shared" si="129"/>
         <v>0.82</v>
       </c>
-      <c r="BA18" s="9">
-        <f t="shared" si="121"/>
+      <c r="BL18" s="9">
+        <f t="shared" si="129"/>
         <v>0.82</v>
       </c>
-      <c r="BB18" s="9">
-        <f t="shared" ref="BB18:BF18" si="122">BB5/BB3</f>
+      <c r="BM18" s="9">
+        <f t="shared" ref="BM18:BQ18" si="130">BM5/BM3</f>
         <v>0.82</v>
       </c>
-      <c r="BC18" s="9">
-        <f t="shared" si="122"/>
+      <c r="BN18" s="9">
+        <f t="shared" si="130"/>
         <v>0.82</v>
       </c>
-      <c r="BD18" s="9">
-        <f t="shared" si="122"/>
+      <c r="BO18" s="9">
+        <f t="shared" si="130"/>
         <v>0.82</v>
       </c>
-      <c r="BE18" s="9">
-        <f t="shared" si="122"/>
+      <c r="BP18" s="9">
+        <f t="shared" si="130"/>
         <v>0.82</v>
       </c>
-      <c r="BF18" s="9">
-        <f t="shared" si="122"/>
+      <c r="BQ18" s="9">
+        <f t="shared" si="130"/>
         <v>0.82</v>
       </c>
-      <c r="BH18" t="s">
+      <c r="BS18" t="s">
         <v>43</v>
       </c>
-      <c r="BI18" s="9">
+      <c r="BT18" s="9">
         <v>-0.01</v>
       </c>
     </row>
-    <row r="19" spans="2:61">
+    <row r="19" spans="2:72">
       <c r="B19" t="s">
         <v>39</v>
       </c>
@@ -5457,229 +5942,262 @@
         <v>0.41421812749003983</v>
       </c>
       <c r="D19" s="9">
-        <f t="shared" ref="D19:R19" si="123">D9/D3</f>
+        <f t="shared" ref="D19:R19" si="131">D9/D3</f>
         <v>0.47215963952365625</v>
       </c>
       <c r="E19" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="131"/>
         <v>0.49593338497288925</v>
       </c>
       <c r="F19" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="131"/>
         <v>0.56675917360468697</v>
       </c>
       <c r="G19" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="131"/>
         <v>0.45537355841551064</v>
       </c>
       <c r="H19" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="131"/>
         <v>0.44312599198851182</v>
       </c>
       <c r="I19" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="131"/>
         <v>0.42114081736723247</v>
       </c>
       <c r="J19" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="131"/>
         <v>0.46233889085964291</v>
       </c>
       <c r="K19" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="131"/>
         <v>0.22000397957153281</v>
       </c>
       <c r="L19" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="131"/>
         <v>0.27309379817384088</v>
       </c>
       <c r="M19" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="131"/>
         <v>0.40703602991162474</v>
       </c>
       <c r="N19" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="131"/>
         <v>0.42016886443411439</v>
       </c>
       <c r="O19" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="131"/>
         <v>0.33224333314540228</v>
       </c>
       <c r="P19" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="131"/>
         <v>0.31909883876491679</v>
       </c>
       <c r="Q19" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="131"/>
         <v>0.37447601304145317</v>
       </c>
       <c r="R19" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="131"/>
         <v>0.45507979481333716</v>
       </c>
       <c r="S19" s="9">
-        <f t="shared" ref="S19:V19" si="124">S9/S3</f>
+        <f t="shared" ref="S19:V19" si="132">S9/S3</f>
         <v>0.43475602766420846</v>
       </c>
       <c r="T19" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="132"/>
         <v>0.42531898063761736</v>
       </c>
       <c r="U19" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="132"/>
         <v>0.35928990003447087</v>
       </c>
       <c r="V19" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="132"/>
         <v>0.37376377297971547</v>
       </c>
       <c r="W19" s="9">
-        <f t="shared" ref="W19:AE19" si="125">W9/W3</f>
+        <f t="shared" ref="W19:AE19" si="133">W9/W3</f>
         <v>0.30543213415508097</v>
       </c>
       <c r="X19" s="9">
-        <f t="shared" si="125"/>
+        <f t="shared" si="133"/>
         <v>0.28998681562695161</v>
       </c>
       <c r="Y19" s="9">
-        <f t="shared" si="125"/>
+        <f t="shared" si="133"/>
         <v>0.20437324096124701</v>
       </c>
       <c r="Z19" s="9">
-        <f t="shared" si="125"/>
+        <f t="shared" si="133"/>
         <v>0.19894295041193844</v>
       </c>
       <c r="AA19" s="9">
-        <f t="shared" si="125"/>
+        <f t="shared" si="133"/>
         <v>0.25229533950078548</v>
       </c>
       <c r="AB19" s="9">
-        <f t="shared" si="125"/>
+        <f t="shared" si="133"/>
         <v>0.29350917216163003</v>
       </c>
       <c r="AC19" s="9">
-        <f t="shared" si="125"/>
+        <f t="shared" si="133"/>
         <v>0.40731055323105531</v>
       </c>
       <c r="AD19" s="9">
-        <f t="shared" si="125"/>
+        <f t="shared" si="133"/>
         <v>0.4084665054473835</v>
       </c>
       <c r="AE19" s="9">
-        <f t="shared" si="125"/>
+        <f t="shared" si="133"/>
         <v>0.37904265532848719</v>
       </c>
       <c r="AF19" s="9">
-        <f t="shared" ref="AF19:AH19" si="126">AF9/AF3</f>
+        <f t="shared" ref="AF19:AH19" si="134">AF9/AF3</f>
         <v>0.38000051188861306</v>
       </c>
       <c r="AG19" s="9">
-        <f t="shared" si="126"/>
+        <f t="shared" si="134"/>
         <v>0.4274557146024785</v>
       </c>
       <c r="AH19" s="9">
-        <f t="shared" si="126"/>
+        <f t="shared" si="134"/>
         <v>0.45086287072439807</v>
       </c>
       <c r="AI19" s="9">
-        <f t="shared" ref="AI19:AL19" si="127">AI9/AI3</f>
+        <f t="shared" ref="AI19:AL19" si="135">AI9/AI3</f>
         <v>0.41487450961856598</v>
       </c>
       <c r="AJ19" s="9">
-        <f t="shared" si="127"/>
+        <f t="shared" si="135"/>
         <v>0.43019193534809325</v>
       </c>
       <c r="AK19" s="9">
-        <f t="shared" si="127"/>
+        <f t="shared" si="135"/>
         <v>0.4007454822216151</v>
       </c>
       <c r="AL19" s="9">
-        <f t="shared" si="127"/>
-        <v>0.41661775343598217</v>
-      </c>
-      <c r="AN19" s="9">
-        <f t="shared" ref="AN19" si="128">AN9/AN3</f>
+        <f t="shared" si="135"/>
+        <v>0.41315345699831368</v>
+      </c>
+      <c r="AM19" s="9"/>
+      <c r="AN19" s="9"/>
+      <c r="AO19" s="9"/>
+      <c r="AP19" s="9"/>
+      <c r="AQ19" s="9"/>
+      <c r="AR19" s="9">
+        <f t="shared" ref="AR19:AV19" si="136">AR9/AR3</f>
+        <v>0.52279635258358659</v>
+      </c>
+      <c r="AS19" s="9">
+        <f t="shared" si="136"/>
+        <v>0.47318781999461063</v>
+      </c>
+      <c r="AT19" s="9">
+        <f t="shared" si="136"/>
+        <v>0.10571821575948123</v>
+      </c>
+      <c r="AU19" s="9">
+        <f t="shared" si="136"/>
+        <v>0.35619918699186992</v>
+      </c>
+      <c r="AV19" s="9">
+        <f t="shared" si="136"/>
+        <v>0.40060965827049577</v>
+      </c>
+      <c r="AW19" s="9">
+        <f t="shared" ref="AW19:AY19" si="137">AW9/AW3</f>
+        <v>0.34722222222222221</v>
+      </c>
+      <c r="AX19" s="9">
+        <f t="shared" si="137"/>
+        <v>0.44963456111151312</v>
+      </c>
+      <c r="AY19" s="9">
+        <f t="shared" si="137"/>
         <v>0.49693749538779425</v>
       </c>
-      <c r="AO19" s="9">
-        <f t="shared" ref="AO19:BA19" si="129">AO9/AO3</f>
+      <c r="AZ19" s="9">
+        <f t="shared" ref="AZ19:BL19" si="138">AZ9/AZ3</f>
         <v>0.44616569361366809</v>
       </c>
-      <c r="AP19" s="9">
-        <f t="shared" si="129"/>
+      <c r="BA19" s="9">
+        <f t="shared" si="138"/>
         <v>0.33909192523734738</v>
       </c>
-      <c r="AQ19" s="9">
-        <f t="shared" si="129"/>
+      <c r="BB19" s="9">
+        <f t="shared" si="138"/>
         <v>0.38004559942302774</v>
       </c>
-      <c r="AR19" s="9">
-        <f t="shared" si="129"/>
+      <c r="BC19" s="9">
+        <f t="shared" si="138"/>
         <v>0.39645040660058173</v>
       </c>
-      <c r="AS19" s="9">
-        <f t="shared" si="129"/>
+      <c r="BD19" s="9">
+        <f t="shared" si="138"/>
         <v>0.24822269293107735</v>
       </c>
-      <c r="AT19" s="9">
-        <f t="shared" si="129"/>
+      <c r="BE19" s="9">
+        <f t="shared" si="138"/>
         <v>0.34786307713932724</v>
       </c>
-      <c r="AU19" s="9">
-        <f t="shared" si="129"/>
+      <c r="BF19" s="9">
+        <f t="shared" si="138"/>
         <v>0.41234042553191491</v>
       </c>
-      <c r="AV19" s="9">
-        <f t="shared" si="129"/>
-        <v>0.41477949521427787</v>
-      </c>
-      <c r="AW19" s="9">
-        <f t="shared" si="129"/>
-        <v>0.41182329486677305</v>
-      </c>
-      <c r="AX19" s="9">
-        <f t="shared" si="129"/>
-        <v>0.41874885894813435</v>
-      </c>
-      <c r="AY19" s="9">
-        <f t="shared" si="129"/>
-        <v>0.42565827850367777</v>
-      </c>
-      <c r="AZ19" s="9">
-        <f t="shared" si="129"/>
-        <v>0.42938465097549816</v>
-      </c>
-      <c r="BA19" s="9">
-        <f t="shared" si="129"/>
-        <v>0.42993884287135758</v>
-      </c>
-      <c r="BB19" s="9">
-        <f t="shared" ref="BB19:BF19" si="130">BB9/BB3</f>
-        <v>0.42993884287135764</v>
-      </c>
-      <c r="BC19" s="9">
-        <f t="shared" si="130"/>
-        <v>0.4299388428713577</v>
-      </c>
-      <c r="BD19" s="9">
-        <f t="shared" si="130"/>
-        <v>0.4299388428713577</v>
-      </c>
-      <c r="BE19" s="9">
-        <f t="shared" si="130"/>
-        <v>0.42993884287135764</v>
-      </c>
-      <c r="BF19" s="9">
-        <f t="shared" si="130"/>
-        <v>0.42993884287135758</v>
-      </c>
-      <c r="BH19" t="s">
+      <c r="BG19" s="9">
+        <f t="shared" si="138"/>
+        <v>0.41438210633692429</v>
+      </c>
+      <c r="BH19" s="9">
+        <f t="shared" si="138"/>
+        <v>0.4120574802664102</v>
+      </c>
+      <c r="BI19" s="9">
+        <f t="shared" si="138"/>
+        <v>0.4189632901684156</v>
+      </c>
+      <c r="BJ19" s="9">
+        <f t="shared" si="138"/>
+        <v>0.42585339188647209</v>
+      </c>
+      <c r="BK19" s="9">
+        <f t="shared" si="138"/>
+        <v>0.42956276314848835</v>
+      </c>
+      <c r="BL19" s="9">
+        <f t="shared" si="138"/>
+        <v>0.43010197677058398</v>
+      </c>
+      <c r="BM19" s="9">
+        <f t="shared" ref="BM19:BQ19" si="139">BM9/BM3</f>
+        <v>0.43010197677058404</v>
+      </c>
+      <c r="BN19" s="9">
+        <f t="shared" si="139"/>
+        <v>0.43010197677058398</v>
+      </c>
+      <c r="BO19" s="9">
+        <f t="shared" si="139"/>
+        <v>0.43010197677058398</v>
+      </c>
+      <c r="BP19" s="9">
+        <f t="shared" si="139"/>
+        <v>0.43010197677058404</v>
+      </c>
+      <c r="BQ19" s="9">
+        <f t="shared" si="139"/>
+        <v>0.43010197677058404</v>
+      </c>
+      <c r="BS19" t="s">
         <v>44</v>
       </c>
-      <c r="BI19" s="9">
+      <c r="BT19" s="9">
         <v>0.05</v>
       </c>
     </row>
-    <row r="20" spans="2:61">
+    <row r="20" spans="2:72">
       <c r="B20" t="s">
         <v>69</v>
       </c>
@@ -5688,215 +6206,248 @@
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
       <c r="G20" s="9">
-        <f t="shared" ref="G20:R20" si="131">G6/C6-1</f>
+        <f t="shared" ref="G20:R20" si="140">G6/C6-1</f>
         <v>0.22028353326063255</v>
       </c>
       <c r="H20" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="140"/>
         <v>0.31474726420010413</v>
       </c>
       <c r="I20" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="140"/>
         <v>0.29483430799220267</v>
       </c>
       <c r="J20" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="140"/>
         <v>0.46485377116469984</v>
       </c>
       <c r="K20" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="140"/>
         <v>0.27792672028596965</v>
       </c>
       <c r="L20" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="140"/>
         <v>0.31391200951248521</v>
       </c>
       <c r="M20" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="140"/>
         <v>0.33534060971019941</v>
       </c>
       <c r="N20" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="140"/>
         <v>0.35796847635726792</v>
       </c>
       <c r="O20" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="140"/>
         <v>0.40384615384615374</v>
       </c>
       <c r="P20" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="140"/>
         <v>0.34600301659125199</v>
       </c>
       <c r="Q20" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="140"/>
         <v>0.34244644870349483</v>
       </c>
       <c r="R20" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="140"/>
         <v>0.34330668042300738</v>
       </c>
       <c r="S20" s="9">
-        <f t="shared" ref="S20" si="132">S6/O6-1</f>
+        <f t="shared" ref="S20" si="141">S6/O6-1</f>
         <v>0.29439601494396017</v>
       </c>
       <c r="T20" s="9">
-        <f t="shared" ref="T20" si="133">T6/P6-1</f>
+        <f t="shared" ref="T20" si="142">T6/P6-1</f>
         <v>0.36620349619004933</v>
       </c>
       <c r="U20" s="9">
-        <f t="shared" ref="U20" si="134">U6/Q6-1</f>
+        <f t="shared" ref="U20" si="143">U6/Q6-1</f>
         <v>0.32605500734830994</v>
       </c>
       <c r="V20" s="9">
-        <f t="shared" ref="V20" si="135">V6/R6-1</f>
+        <f t="shared" ref="V20" si="144">V6/R6-1</f>
         <v>0.35291858678955457</v>
       </c>
       <c r="W20" s="9">
-        <f t="shared" ref="W20" si="136">W6/S6-1</f>
+        <f t="shared" ref="W20" si="145">W6/S6-1</f>
         <v>0.48297094477583213</v>
       </c>
       <c r="X20" s="9">
-        <f t="shared" ref="X20" si="137">X6/T6-1</f>
+        <f t="shared" ref="X20" si="146">X6/T6-1</f>
         <v>0.42552493438320216</v>
       </c>
       <c r="Y20" s="9">
-        <f t="shared" ref="Y20" si="138">Y6/U6-1</f>
+        <f t="shared" ref="Y20" si="147">Y6/U6-1</f>
         <v>0.45186827105763139</v>
       </c>
       <c r="Z20" s="9">
-        <f t="shared" ref="Z20" si="139">Z6/V6-1</f>
+        <f t="shared" ref="Z20" si="148">Z6/V6-1</f>
         <v>0.38674425205790519</v>
       </c>
       <c r="AA20" s="9">
-        <f t="shared" ref="AA20" si="140">AA6/W6-1</f>
+        <f t="shared" ref="AA20" si="149">AA6/W6-1</f>
         <v>0.21720513818606468</v>
       </c>
       <c r="AB20" s="9">
-        <f t="shared" ref="AB20" si="141">AB6/X6-1</f>
+        <f t="shared" ref="AB20" si="150">AB6/X6-1</f>
         <v>7.5258918296893018E-2</v>
       </c>
       <c r="AC20" s="9">
-        <f t="shared" ref="AC20" si="142">AC6/Y6-1</f>
+        <f t="shared" ref="AC20" si="151">AC6/Y6-1</f>
         <v>7.7426390403489975E-3</v>
       </c>
       <c r="AD20" s="9">
-        <f t="shared" ref="AD20" si="143">AD6/Z6-1</f>
+        <f t="shared" ref="AD20" si="152">AD6/Z6-1</f>
         <v>7.6348377852829774E-2</v>
       </c>
       <c r="AE20" s="9">
-        <f t="shared" ref="AE20" si="144">AE6/AA6-1</f>
+        <f t="shared" ref="AE20" si="153">AE6/AA6-1</f>
         <v>6.3639270866645337E-2</v>
       </c>
       <c r="AF20" s="9">
-        <f t="shared" ref="AF20" si="145">AF6/AB6-1</f>
+        <f t="shared" ref="AF20" si="154">AF6/AB6-1</f>
         <v>0.12767551369863006</v>
       </c>
       <c r="AG20" s="9">
-        <f t="shared" ref="AG20" si="146">AG6/AC6-1</f>
+        <f t="shared" ref="AG20" si="155">AG6/AC6-1</f>
         <v>0.20950113624066669</v>
       </c>
       <c r="AH20" s="9">
-        <f t="shared" ref="AH20" si="147">AH6/AD6-1</f>
+        <f t="shared" ref="AH20" si="156">AH6/AD6-1</f>
         <v>0.15812494057240656</v>
       </c>
       <c r="AI20" s="9">
-        <f t="shared" ref="AI20" si="148">AI6/AE6-1</f>
+        <f t="shared" ref="AI20" si="157">AI6/AE6-1</f>
         <v>0.21767889356584491</v>
       </c>
       <c r="AJ20" s="9">
-        <f t="shared" ref="AJ20" si="149">AJ6/AF6-1</f>
+        <f t="shared" ref="AJ20" si="158">AJ6/AF6-1</f>
         <v>0.22824333301698774</v>
       </c>
       <c r="AK20" s="9">
-        <f t="shared" ref="AK20" si="150">AK6/AG6-1</f>
+        <f t="shared" ref="AK20" si="159">AK6/AG6-1</f>
         <v>0.35492529301243625</v>
       </c>
       <c r="AL20" s="9">
-        <f t="shared" ref="AL20" si="151">AL6/AH6-1</f>
-        <v>0.30000000000000004</v>
-      </c>
+        <f t="shared" ref="AL20" si="160">AL6/AH6-1</f>
+        <v>0.40689655172413786</v>
+      </c>
+      <c r="AM20" s="9"/>
       <c r="AN20" s="9"/>
-      <c r="AO20" s="9">
-        <f t="shared" ref="AO20:BA20" si="152">AO6/AN6-1</f>
+      <c r="AO20" s="9"/>
+      <c r="AP20" s="9"/>
+      <c r="AQ20" s="9"/>
+      <c r="AR20" s="9"/>
+      <c r="AS20" s="9">
+        <f t="shared" ref="AS20" si="161">AS6/AR6-1</f>
+        <v>1.6944444444444446</v>
+      </c>
+      <c r="AT20" s="9">
+        <f t="shared" ref="AT20" si="162">AT6/AS6-1</f>
+        <v>2.6056701030927836</v>
+      </c>
+      <c r="AU20" s="9">
+        <f t="shared" ref="AU20" si="163">AU6/AT6-1</f>
+        <v>1.1436740528949274E-2</v>
+      </c>
+      <c r="AV20" s="9">
+        <f t="shared" ref="AV20" si="164">AV6/AU6-1</f>
+        <v>0.88409893992932864</v>
+      </c>
+      <c r="AW20" s="9">
+        <f t="shared" ref="AW20" si="165">AW6/AV6-1</f>
+        <v>0.80645161290322576</v>
+      </c>
+      <c r="AX20" s="9">
+        <f t="shared" ref="AX20" si="166">AX6/AW6-1</f>
+        <v>0.22902823920265791</v>
+      </c>
+      <c r="AY20" s="9">
+        <f t="shared" ref="AY20" si="167">AY6/AX6-1</f>
+        <v>0.31001858422030759</v>
+      </c>
+      <c r="AZ20" s="9">
+        <f t="shared" ref="AZ20:BL20" si="168">AZ6/AY6-1</f>
         <v>0.3248645860201187</v>
       </c>
-      <c r="AP20" s="9">
-        <f t="shared" si="152"/>
+      <c r="BA20" s="9">
+        <f t="shared" si="168"/>
         <v>0.32385865861968277</v>
       </c>
-      <c r="AQ20" s="9">
-        <f t="shared" si="152"/>
+      <c r="BB20" s="9">
+        <f t="shared" si="168"/>
         <v>0.35647058823529409</v>
       </c>
-      <c r="AR20" s="9">
-        <f t="shared" si="152"/>
+      <c r="BC20" s="9">
+        <f t="shared" si="168"/>
         <v>0.3364592367736341</v>
       </c>
-      <c r="AS20" s="9">
-        <f t="shared" si="152"/>
+      <c r="BD20" s="9">
+        <f t="shared" si="168"/>
         <v>0.43329953356317175</v>
       </c>
-      <c r="AT20" s="9">
-        <f t="shared" si="152"/>
+      <c r="BE20" s="9">
+        <f t="shared" si="168"/>
         <v>8.8997679551757303E-2</v>
       </c>
-      <c r="AU20" s="9">
-        <f t="shared" si="152"/>
+      <c r="BF20" s="9">
+        <f t="shared" si="168"/>
         <v>0.14003585999012547</v>
       </c>
-      <c r="AV20" s="9">
-        <f t="shared" si="152"/>
-        <v>0.27803610503282283</v>
-      </c>
-      <c r="AW20" s="9">
-        <f t="shared" si="152"/>
+      <c r="BG20" s="9">
+        <f t="shared" si="168"/>
+        <v>0.30771334792122529</v>
+      </c>
+      <c r="BH20" s="9">
+        <f t="shared" si="168"/>
         <v>0.1399999999999999</v>
       </c>
-      <c r="AX20" s="9">
-        <f t="shared" si="152"/>
+      <c r="BI20" s="9">
+        <f t="shared" si="168"/>
         <v>6.0000000000000053E-2</v>
       </c>
-      <c r="AY20" s="9">
-        <f t="shared" si="152"/>
+      <c r="BJ20" s="9">
+        <f t="shared" si="168"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AZ20" s="9">
-        <f t="shared" si="152"/>
+      <c r="BK20" s="9">
+        <f t="shared" si="168"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="BA20" s="9">
-        <f t="shared" si="152"/>
+      <c r="BL20" s="9">
+        <f t="shared" si="168"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="BB20" s="9">
-        <f t="shared" ref="BB20" si="153">BB6/BA6-1</f>
+      <c r="BM20" s="9">
+        <f t="shared" ref="BM20" si="169">BM6/BL6-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BC20" s="9">
-        <f t="shared" ref="BC20" si="154">BC6/BB6-1</f>
+      <c r="BN20" s="9">
+        <f t="shared" ref="BN20" si="170">BN6/BM6-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BD20" s="9">
-        <f t="shared" ref="BD20" si="155">BD6/BC6-1</f>
+      <c r="BO20" s="9">
+        <f t="shared" ref="BO20" si="171">BO6/BN6-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BE20" s="9">
-        <f t="shared" ref="BE20" si="156">BE6/BD6-1</f>
+      <c r="BP20" s="9">
+        <f t="shared" ref="BP20" si="172">BP6/BO6-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BF20" s="9">
-        <f t="shared" ref="BF20" si="157">BF6/BE6-1</f>
+      <c r="BQ20" s="9">
+        <f t="shared" ref="BQ20" si="173">BQ6/BP6-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BH20" t="s">
+      <c r="BS20" t="s">
         <v>45</v>
       </c>
-      <c r="BI20" s="20">
-        <f>NPV(BI19,AU13:FI13)</f>
-        <v>1939462.900855571</v>
-      </c>
-    </row>
-    <row r="21" spans="2:61">
+      <c r="BT20" s="20">
+        <f>NPV(BT19,BH13:FT13)</f>
+        <v>2036350.4827568533</v>
+      </c>
+    </row>
+    <row r="21" spans="2:72">
       <c r="B21" t="s">
         <v>38</v>
       </c>
@@ -5905,230 +6456,263 @@
         <v>0.13159860557768924</v>
       </c>
       <c r="D21" s="9">
-        <f t="shared" ref="D21:R21" si="158">D7/D3</f>
+        <f t="shared" ref="D21:R21" si="174">D7/D3</f>
         <v>0.12058791975109967</v>
       </c>
       <c r="E21" s="9">
-        <f t="shared" si="158"/>
+        <f t="shared" si="174"/>
         <v>0.11328427575522851</v>
       </c>
       <c r="F21" s="9">
-        <f t="shared" si="158"/>
+        <f t="shared" si="174"/>
         <v>0.1059204440333025</v>
       </c>
       <c r="G21" s="9">
-        <f t="shared" si="158"/>
+        <f t="shared" si="174"/>
         <v>0.13329433394618084</v>
       </c>
       <c r="H21" s="9">
-        <f t="shared" si="158"/>
+        <f t="shared" si="174"/>
         <v>0.14020104300506386</v>
       </c>
       <c r="I21" s="9">
-        <f t="shared" si="158"/>
+        <f t="shared" si="174"/>
         <v>0.14045312158519704</v>
       </c>
       <c r="J21" s="9">
-        <f t="shared" si="158"/>
+        <f t="shared" si="174"/>
         <v>0.14585550431595129</v>
       </c>
       <c r="K21" s="9">
-        <f t="shared" si="158"/>
+        <f t="shared" si="174"/>
         <v>0.13397890827087616</v>
       </c>
       <c r="L21" s="9">
-        <f t="shared" si="158"/>
+        <f t="shared" si="174"/>
         <v>0.14312818688485712</v>
       </c>
       <c r="M21" s="9">
-        <f t="shared" si="158"/>
+        <f t="shared" si="174"/>
         <v>0.13686834353047814</v>
       </c>
       <c r="N21" s="9">
-        <f t="shared" si="158"/>
+        <f t="shared" si="174"/>
         <v>0.14353476899724885</v>
       </c>
       <c r="O21" s="9">
-        <f t="shared" si="158"/>
+        <f t="shared" si="174"/>
         <v>0.15712916502226984</v>
       </c>
       <c r="P21" s="9">
-        <f t="shared" si="158"/>
+        <f t="shared" si="174"/>
         <v>0.15197731042971049</v>
       </c>
       <c r="Q21" s="9">
-        <f t="shared" si="158"/>
+        <f t="shared" si="174"/>
         <v>0.12496506753609687</v>
       </c>
       <c r="R21" s="9">
-        <f t="shared" si="158"/>
+        <f t="shared" si="174"/>
         <v>0.11684240524365916</v>
       </c>
       <c r="S21" s="9">
-        <f t="shared" ref="S21:V21" si="159">S7/S3</f>
+        <f t="shared" ref="S21:V21" si="175">S7/S3</f>
         <v>0.10863169156700164</v>
       </c>
       <c r="T21" s="9">
-        <f t="shared" si="159"/>
+        <f t="shared" si="175"/>
         <v>0.1120817140695395</v>
       </c>
       <c r="U21" s="9">
-        <f t="shared" si="159"/>
+        <f t="shared" si="175"/>
         <v>0.1225094794898311</v>
       </c>
       <c r="V21" s="9">
-        <f t="shared" si="159"/>
+        <f t="shared" si="175"/>
         <v>0.13029016067238872</v>
       </c>
       <c r="W21" s="9">
-        <f t="shared" ref="W21:AE21" si="160">W7/W3</f>
+        <f t="shared" ref="W21:AE21" si="176">W7/W3</f>
         <v>0.11867564855955282</v>
       </c>
       <c r="X21" s="9">
-        <f t="shared" si="160"/>
+        <f t="shared" si="176"/>
         <v>0.12473110818125044</v>
       </c>
       <c r="Y21" s="9">
-        <f t="shared" si="160"/>
+        <f t="shared" si="176"/>
         <v>0.13639315869235766</v>
       </c>
       <c r="Z21" s="9">
-        <f t="shared" si="160"/>
+        <f t="shared" si="176"/>
         <v>0.142204259288046</v>
       </c>
       <c r="AA21" s="9">
-        <f t="shared" si="160"/>
+        <f t="shared" si="176"/>
         <v>0.10626636411241054</v>
       </c>
       <c r="AB21" s="9">
-        <f t="shared" si="160"/>
+        <f t="shared" si="176"/>
         <v>9.8565580174380454E-2</v>
       </c>
       <c r="AC21" s="9">
-        <f t="shared" si="160"/>
+        <f t="shared" si="176"/>
         <v>8.3594839609483967E-2</v>
       </c>
       <c r="AD21" s="9">
-        <f t="shared" si="160"/>
+        <f t="shared" si="176"/>
         <v>8.0426815586746775E-2</v>
       </c>
       <c r="AE21" s="9">
-        <f t="shared" si="160"/>
+        <f t="shared" si="176"/>
         <v>7.0333287614867651E-2</v>
       </c>
       <c r="AF21" s="9">
-        <f t="shared" ref="AF21:AH21" si="161">AF7/AF3</f>
+        <f t="shared" ref="AF21:AH21" si="177">AF7/AF3</f>
         <v>6.9642445803793099E-2</v>
       </c>
       <c r="AG21" s="9">
-        <f t="shared" si="161"/>
+        <f t="shared" si="177"/>
         <v>6.9526226317475182E-2</v>
       </c>
       <c r="AH21" s="9">
-        <f t="shared" si="161"/>
+        <f t="shared" si="177"/>
         <v>6.6962901725741444E-2</v>
       </c>
       <c r="AI21" s="9">
-        <f t="shared" ref="AI21:AL21" si="162">AI7/AI3</f>
+        <f t="shared" ref="AI21:AL21" si="178">AI7/AI3</f>
         <v>6.5155740416883295E-2</v>
       </c>
       <c r="AJ21" s="9">
-        <f t="shared" si="162"/>
+        <f t="shared" si="178"/>
         <v>6.269467126862531E-2</v>
       </c>
       <c r="AK21" s="9">
-        <f t="shared" si="162"/>
+        <f t="shared" si="178"/>
         <v>5.5520861793060379E-2</v>
       </c>
       <c r="AL21" s="9">
-        <f t="shared" si="162"/>
+        <f t="shared" si="178"/>
+        <v>5.6934867179803984E-2</v>
+      </c>
+      <c r="AM21" s="9"/>
+      <c r="AN21" s="9"/>
+      <c r="AO21" s="9"/>
+      <c r="AP21" s="9"/>
+      <c r="AQ21" s="9"/>
+      <c r="AR21" s="9">
+        <f t="shared" ref="AR21:AV21" si="179">AR7/AR3</f>
+        <v>8.4599797365754806E-2</v>
+      </c>
+      <c r="AS21" s="9">
+        <f t="shared" si="179"/>
+        <v>0.1059013742926435</v>
+      </c>
+      <c r="AT21" s="9">
+        <f t="shared" si="179"/>
+        <v>0.17606602475928473</v>
+      </c>
+      <c r="AU21" s="9">
+        <f t="shared" si="179"/>
+        <v>0.12665142276422764</v>
+      </c>
+      <c r="AV21" s="9">
+        <f t="shared" si="179"/>
+        <v>0.13476656505695492</v>
+      </c>
+      <c r="AW21" s="9">
+        <f t="shared" ref="AW21:AY21" si="180">AW7/AW3</f>
+        <v>0.15199687639446677</v>
+      </c>
+      <c r="AX21" s="9">
+        <f t="shared" si="180"/>
+        <v>0.13647876112598595</v>
+      </c>
+      <c r="AY21" s="9">
+        <f t="shared" si="180"/>
+        <v>0.1162275846800974</v>
+      </c>
+      <c r="AZ21" s="9">
+        <f t="shared" ref="AZ21:BL21" si="181">AZ7/AZ3</f>
+        <v>0.14049571976073641</v>
+      </c>
+      <c r="BA21" s="9">
+        <f t="shared" si="181"/>
+        <v>0.13973428413769684</v>
+      </c>
+      <c r="BB21" s="9">
+        <f t="shared" si="181"/>
+        <v>0.13482074308447525</v>
+      </c>
+      <c r="BC21" s="9">
+        <f t="shared" si="181"/>
+        <v>0.11908012448167965</v>
+      </c>
+      <c r="BD21" s="9">
+        <f t="shared" si="181"/>
+        <v>0.13087326021147597</v>
+      </c>
+      <c r="BE21" s="9">
+        <f t="shared" si="181"/>
+        <v>9.1003247738050325E-2</v>
+      </c>
+      <c r="BF21" s="9">
+        <f t="shared" si="181"/>
+        <v>6.8978723404255315E-2</v>
+      </c>
+      <c r="BG21" s="9">
+        <f t="shared" si="181"/>
+        <v>5.9667106212524572E-2</v>
+      </c>
+      <c r="BH21" s="9">
+        <f t="shared" si="181"/>
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="AN21" s="9">
-        <f t="shared" ref="AN21" si="163">AN7/AN3</f>
-        <v>0.1162275846800974</v>
-      </c>
-      <c r="AO21" s="9">
-        <f t="shared" ref="AO21:BA21" si="164">AO7/AO3</f>
-        <v>0.14049571976073641</v>
-      </c>
-      <c r="AP21" s="9">
-        <f t="shared" si="164"/>
-        <v>0.13973428413769684</v>
-      </c>
-      <c r="AQ21" s="9">
-        <f t="shared" si="164"/>
-        <v>0.13482074308447525</v>
-      </c>
-      <c r="AR21" s="9">
-        <f t="shared" si="164"/>
-        <v>0.11908012448167965</v>
-      </c>
-      <c r="AS21" s="9">
-        <f t="shared" si="164"/>
-        <v>0.13087326021147597</v>
-      </c>
-      <c r="AT21" s="9">
-        <f t="shared" si="164"/>
-        <v>9.1003247738050325E-2</v>
-      </c>
-      <c r="AU21" s="9">
-        <f t="shared" si="164"/>
-        <v>6.8978723404255315E-2</v>
-      </c>
-      <c r="AV21" s="9">
-        <f t="shared" si="164"/>
-        <v>6.2043799652495311E-2</v>
-      </c>
-      <c r="AW21" s="9">
-        <f t="shared" si="164"/>
+      <c r="BI21" s="9">
+        <f t="shared" si="181"/>
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="AX21" s="9">
-        <f t="shared" si="164"/>
+      <c r="BJ21" s="9">
+        <f t="shared" si="181"/>
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="AY21" s="9">
-        <f t="shared" si="164"/>
+      <c r="BK21" s="9">
+        <f t="shared" si="181"/>
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="AZ21" s="9">
-        <f t="shared" si="164"/>
+      <c r="BL21" s="9">
+        <f t="shared" si="181"/>
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="BA21" s="9">
-        <f t="shared" si="164"/>
+      <c r="BM21" s="9">
+        <f t="shared" ref="BM21:BQ21" si="182">BM7/BM3</f>
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="BB21" s="9">
-        <f t="shared" ref="BB21:BF21" si="165">BB7/BB3</f>
+      <c r="BN21" s="9">
+        <f t="shared" si="182"/>
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="BC21" s="9">
-        <f t="shared" si="165"/>
+      <c r="BO21" s="9">
+        <f t="shared" si="182"/>
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="BD21" s="9">
-        <f t="shared" si="165"/>
+      <c r="BP21" s="9">
+        <f t="shared" si="182"/>
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="BE21" s="9">
-        <f t="shared" si="165"/>
+      <c r="BQ21" s="9">
+        <f t="shared" si="182"/>
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="BF21" s="9">
-        <f t="shared" si="165"/>
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="BH21" t="s">
+      <c r="BS21" t="s">
         <v>46</v>
       </c>
-      <c r="BI21" s="20">
+      <c r="BT21" s="20">
         <f>Main!D8</f>
-        <v>40688</v>
-      </c>
-    </row>
-    <row r="22" spans="2:61">
+        <v>50372</v>
+      </c>
+    </row>
+    <row r="22" spans="2:72">
       <c r="B22" t="s">
         <v>70</v>
       </c>
@@ -6137,215 +6721,248 @@
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
       <c r="G22" s="9">
-        <f t="shared" ref="G22" si="166">G8/C8-1</f>
+        <f t="shared" ref="G22" si="183">G8/C8-1</f>
         <v>0.1557251908396946</v>
       </c>
       <c r="H22" s="9">
-        <f t="shared" ref="H22" si="167">H8/D8-1</f>
+        <f t="shared" ref="H22" si="184">H8/D8-1</f>
         <v>0.21249999999999991</v>
       </c>
       <c r="I22" s="9">
-        <f t="shared" ref="I22" si="168">I8/E8-1</f>
+        <f t="shared" ref="I22" si="185">I8/E8-1</f>
         <v>0.75932835820895517</v>
       </c>
       <c r="J22" s="9">
-        <f t="shared" ref="J22" si="169">J8/F8-1</f>
+        <f t="shared" ref="J22" si="186">J8/F8-1</f>
         <v>0.42274052478134116</v>
       </c>
       <c r="K22" s="9">
-        <f t="shared" ref="K22" si="170">K8/G8-1</f>
+        <f t="shared" ref="K22" si="187">K8/G8-1</f>
         <v>4.3685601056803174</v>
       </c>
       <c r="L22" s="9">
-        <f t="shared" ref="L22" si="171">L8/H8-1</f>
+        <f t="shared" ref="L22" si="188">L8/H8-1</f>
         <v>3.1546391752577323</v>
       </c>
       <c r="M22" s="9">
-        <f t="shared" ref="M22" si="172">M8/I8-1</f>
+        <f t="shared" ref="M22" si="189">M8/I8-1</f>
         <v>0.42948038176033942</v>
       </c>
       <c r="N22" s="9">
-        <f t="shared" ref="N22" si="173">N8/J8-1</f>
+        <f t="shared" ref="N22" si="190">N8/J8-1</f>
         <v>0.87397540983606548</v>
       </c>
       <c r="O22" s="9">
-        <f t="shared" ref="O22" si="174">O8/K8-1</f>
+        <f t="shared" ref="O22" si="191">O8/K8-1</f>
         <v>-0.6104822834645669</v>
       </c>
       <c r="P22" s="9">
-        <f t="shared" ref="P22" si="175">P8/L8-1</f>
+        <f t="shared" ref="P22" si="192">P8/L8-1</f>
         <v>-0.50589330024813894</v>
       </c>
       <c r="Q22" s="9">
-        <f t="shared" ref="Q22" si="176">Q8/M8-1</f>
+        <f t="shared" ref="Q22" si="193">Q8/M8-1</f>
         <v>0.32789317507418403</v>
       </c>
       <c r="R22" s="9">
-        <f t="shared" ref="R22" si="177">R8/N8-1</f>
+        <f t="shared" ref="R22" si="194">R8/N8-1</f>
         <v>-0.12575177692728268</v>
       </c>
       <c r="S22" s="9">
-        <f t="shared" ref="S22" si="178">S8/O8-1</f>
+        <f t="shared" ref="S22" si="195">S8/O8-1</f>
         <v>2.4636765634870494E-2</v>
       </c>
       <c r="T22" s="9">
-        <f t="shared" ref="T22" si="179">T8/P8-1</f>
+        <f t="shared" ref="T22" si="196">T8/P8-1</f>
         <v>0.22787193973634645</v>
       </c>
       <c r="U22" s="9">
-        <f t="shared" ref="U22" si="180">U8/Q8-1</f>
+        <f t="shared" ref="U22" si="197">U8/Q8-1</f>
         <v>0.64581005586592188</v>
       </c>
       <c r="V22" s="9">
-        <f t="shared" ref="V22" si="181">V8/R8-1</f>
+        <f t="shared" ref="V22" si="198">V8/R8-1</f>
         <v>1.0669168230143842</v>
       </c>
       <c r="W22" s="9">
-        <f t="shared" ref="W22" si="182">W8/S8-1</f>
+        <f t="shared" ref="W22" si="199">W8/S8-1</f>
         <v>0.45499383477188649</v>
       </c>
       <c r="X22" s="9">
-        <f t="shared" ref="X22" si="183">X8/T8-1</f>
+        <f t="shared" ref="X22" si="200">X8/T8-1</f>
         <v>0.52709611451942751</v>
       </c>
       <c r="Y22" s="9">
-        <f t="shared" ref="Y22" si="184">Y8/U8-1</f>
+        <f t="shared" ref="Y22" si="201">Y8/U8-1</f>
         <v>0.14867617107942976</v>
       </c>
       <c r="Z22" s="9">
-        <f t="shared" ref="Z22" si="185">Z8/V8-1</f>
+        <f t="shared" ref="Z22" si="202">Z8/V8-1</f>
         <v>-6.656580937972767E-2</v>
       </c>
       <c r="AA22" s="9">
-        <f t="shared" ref="AA22" si="186">AA8/W8-1</f>
+        <f t="shared" ref="AA22" si="203">AA8/W8-1</f>
         <v>0.22245762711864403</v>
       </c>
       <c r="AB22" s="9">
-        <f t="shared" ref="AB22" si="187">AB8/X8-1</f>
+        <f t="shared" ref="AB22" si="204">AB8/X8-1</f>
         <v>0.39404084365584202</v>
       </c>
       <c r="AC22" s="9">
-        <f t="shared" ref="AC22" si="188">AC8/Y8-1</f>
+        <f t="shared" ref="AC22" si="205">AC8/Y8-1</f>
         <v>-0.38829787234042556</v>
       </c>
       <c r="AD22" s="9">
-        <f t="shared" ref="AD22" si="189">AD8/Z8-1</f>
+        <f t="shared" ref="AD22" si="206">AD8/Z8-1</f>
         <v>-0.25802269043760129</v>
       </c>
       <c r="AE22" s="9">
-        <f t="shared" ref="AE22" si="190">AE8/AA8-1</f>
+        <f t="shared" ref="AE22" si="207">AE8/AA8-1</f>
         <v>0.19757365684575401</v>
       </c>
       <c r="AF22" s="9">
-        <f t="shared" ref="AF22" si="191">AF8/AB8-1</f>
+        <f t="shared" ref="AF22" si="208">AF8/AB8-1</f>
         <v>-0.12151777137367914</v>
       </c>
       <c r="AG22" s="9">
-        <f t="shared" ref="AG22" si="192">AG8/AC8-1</f>
+        <f t="shared" ref="AG22" si="209">AG8/AC8-1</f>
         <v>-9.9033816425120769E-2</v>
       </c>
       <c r="AH22" s="9">
-        <f t="shared" ref="AH22" si="193">AH8/AD8-1</f>
+        <f t="shared" ref="AH22" si="210">AH8/AD8-1</f>
         <v>9.6111839231105556E-3</v>
       </c>
       <c r="AI22" s="9">
-        <f t="shared" ref="AI22" si="194">AI8/AE8-1</f>
+        <f t="shared" ref="AI22" si="211">AI8/AE8-1</f>
         <v>-0.34008683068017365</v>
       </c>
       <c r="AJ22" s="9">
-        <f t="shared" ref="AJ22" si="195">AJ8/AF8-1</f>
+        <f t="shared" ref="AJ22" si="212">AJ8/AF8-1</f>
         <v>-0.27200656096227449</v>
       </c>
       <c r="AK22" s="9">
-        <f t="shared" ref="AK22" si="196">AK8/AG8-1</f>
+        <f t="shared" ref="AK22" si="213">AK8/AG8-1</f>
         <v>0.88310991957104568</v>
       </c>
       <c r="AL22" s="9">
-        <f t="shared" ref="AL22" si="197">AL8/AH8-1</f>
-        <v>0.64999999999999991</v>
-      </c>
+        <f t="shared" ref="AL22" si="214">AL8/AH8-1</f>
+        <v>0.59974037213327569</v>
+      </c>
+      <c r="AM22" s="9"/>
       <c r="AN22" s="9"/>
-      <c r="AO22" s="9">
-        <f t="shared" ref="AO22:BA22" si="198">AO8/AN8-1</f>
+      <c r="AO22" s="9"/>
+      <c r="AP22" s="9"/>
+      <c r="AQ22" s="9"/>
+      <c r="AR22" s="9"/>
+      <c r="AS22" s="9">
+        <f t="shared" ref="AS22" si="215">AS8/AR8-1</f>
+        <v>1.2753623188405796</v>
+      </c>
+      <c r="AT22" s="9">
+        <f t="shared" ref="AT22" si="216">AT8/AS8-1</f>
+        <v>1.8407643312101909</v>
+      </c>
+      <c r="AU22" s="9">
+        <f t="shared" ref="AU22" si="217">AU8/AT8-1</f>
+        <v>-0.12443946188340804</v>
+      </c>
+      <c r="AV22" s="9">
+        <f t="shared" ref="AV22" si="218">AV8/AU8-1</f>
+        <v>0.24583866837387958</v>
+      </c>
+      <c r="AW22" s="9">
+        <f t="shared" ref="AW22" si="219">AW8/AV8-1</f>
+        <v>0.33093525179856109</v>
+      </c>
+      <c r="AX22" s="9">
+        <f t="shared" ref="AX22" si="220">AX8/AW8-1</f>
+        <v>0.33667953667953676</v>
+      </c>
+      <c r="AY22" s="9">
+        <f t="shared" ref="AY22" si="221">AY8/AX8-1</f>
+        <v>0.45407279029462733</v>
+      </c>
+      <c r="AZ22" s="9">
+        <f t="shared" ref="AZ22:BL22" si="222">AZ8/AY8-1</f>
         <v>0.37147397695669437</v>
       </c>
-      <c r="AP22" s="9">
-        <f t="shared" si="198"/>
+      <c r="BA22" s="9">
+        <f t="shared" si="222"/>
         <v>2.0315758980301273</v>
       </c>
-      <c r="AQ22" s="9">
-        <f t="shared" si="198"/>
+      <c r="BB22" s="9">
+        <f t="shared" si="222"/>
         <v>-0.37267080745341619</v>
       </c>
-      <c r="AR22" s="9">
-        <f t="shared" si="198"/>
+      <c r="BC22" s="9">
+        <f t="shared" si="222"/>
         <v>0.49718202589489713</v>
       </c>
-      <c r="AS22" s="9">
-        <f t="shared" si="198"/>
+      <c r="BD22" s="9">
+        <f t="shared" si="222"/>
         <v>0.20215688269406851</v>
       </c>
-      <c r="AT22" s="9">
-        <f t="shared" si="198"/>
+      <c r="BE22" s="9">
+        <f t="shared" si="222"/>
         <v>-3.4529451591063021E-2</v>
       </c>
-      <c r="AU22" s="9">
-        <f t="shared" si="198"/>
+      <c r="BF22" s="9">
+        <f t="shared" si="222"/>
         <v>-1.0431276297335201E-2</v>
       </c>
-      <c r="AV22" s="9">
-        <f t="shared" si="198"/>
-        <v>8.6734874656745564E-2</v>
-      </c>
-      <c r="AW22" s="9">
-        <f t="shared" si="198"/>
+      <c r="BG22" s="9">
+        <f t="shared" si="222"/>
+        <v>7.6446097971476723E-2</v>
+      </c>
+      <c r="BH22" s="9">
+        <f t="shared" si="222"/>
         <v>0.1399999999999999</v>
       </c>
-      <c r="AX22" s="9">
-        <f t="shared" si="198"/>
+      <c r="BI22" s="9">
+        <f t="shared" si="222"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AY22" s="9">
-        <f t="shared" si="198"/>
+      <c r="BJ22" s="9">
+        <f t="shared" si="222"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AZ22" s="9">
-        <f t="shared" si="198"/>
+      <c r="BK22" s="9">
+        <f t="shared" si="222"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BA22" s="9">
-        <f t="shared" si="198"/>
+      <c r="BL22" s="9">
+        <f t="shared" si="222"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BB22" s="9">
-        <f t="shared" ref="BB22" si="199">BB8/BA8-1</f>
+      <c r="BM22" s="9">
+        <f t="shared" ref="BM22" si="223">BM8/BL8-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BC22" s="9">
-        <f t="shared" ref="BC22" si="200">BC8/BB8-1</f>
+      <c r="BN22" s="9">
+        <f t="shared" ref="BN22" si="224">BN8/BM8-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BD22" s="9">
-        <f t="shared" ref="BD22" si="201">BD8/BC8-1</f>
+      <c r="BO22" s="9">
+        <f t="shared" ref="BO22" si="225">BO8/BN8-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BE22" s="9">
-        <f t="shared" ref="BE22" si="202">BE8/BD8-1</f>
+      <c r="BP22" s="9">
+        <f t="shared" ref="BP22" si="226">BP8/BO8-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BF22" s="9">
-        <f t="shared" ref="BF22" si="203">BF8/BE8-1</f>
+      <c r="BQ22" s="9">
+        <f t="shared" ref="BQ22" si="227">BQ8/BP8-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BH22" t="s">
+      <c r="BS22" t="s">
         <v>47</v>
       </c>
-      <c r="BI22" s="20">
-        <f>BI20+BI21</f>
-        <v>1980150.900855571</v>
-      </c>
-    </row>
-    <row r="23" spans="2:61">
+      <c r="BT22" s="20">
+        <f>BT20+BT21</f>
+        <v>2086722.4827568533</v>
+      </c>
+    </row>
+    <row r="23" spans="2:72">
       <c r="B23" t="s">
         <v>40</v>
       </c>
@@ -6354,230 +6971,263 @@
         <v>0.10240610328638497</v>
       </c>
       <c r="D23" s="9">
-        <f t="shared" ref="D23:R23" si="204">D12/D11</f>
+        <f t="shared" ref="D23:R23" si="228">D12/D11</f>
         <v>0.13324420677361853</v>
       </c>
       <c r="E23" s="9">
-        <f t="shared" si="204"/>
+        <f t="shared" si="228"/>
         <v>0.10103132161955691</v>
       </c>
       <c r="F23" s="9">
-        <f t="shared" si="204"/>
+        <f t="shared" si="228"/>
         <v>0.52452425623157328</v>
       </c>
       <c r="G23" s="9">
-        <f t="shared" si="204"/>
+        <f t="shared" si="228"/>
         <v>0.11105169340463458</v>
       </c>
       <c r="H23" s="9">
-        <f t="shared" si="204"/>
+        <f t="shared" si="228"/>
         <v>0.12985685071574643</v>
       </c>
       <c r="I23" s="9">
-        <f t="shared" si="204"/>
+        <f t="shared" si="228"/>
         <v>0.13108930987821379</v>
       </c>
       <c r="J23" s="9">
-        <f t="shared" si="204"/>
+        <f t="shared" si="228"/>
         <v>0.13662024840045164</v>
       </c>
       <c r="K23" s="9">
-        <f t="shared" si="204"/>
+        <f t="shared" si="228"/>
         <v>0.30241240666283747</v>
       </c>
       <c r="L23" s="9">
-        <f t="shared" si="204"/>
+        <f t="shared" si="228"/>
         <v>0.46051537822111388</v>
       </c>
       <c r="M23" s="9">
-        <f t="shared" si="204"/>
+        <f t="shared" si="228"/>
         <v>0.16891799699822621</v>
       </c>
       <c r="N23" s="9">
-        <f t="shared" si="204"/>
+        <f t="shared" si="228"/>
         <v>0.19849492856363835</v>
       </c>
       <c r="O23" s="9">
-        <f t="shared" si="204"/>
+        <f t="shared" si="228"/>
         <v>0.16362395495649207</v>
       </c>
       <c r="P23" s="9">
-        <f t="shared" si="204"/>
+        <f t="shared" si="228"/>
         <v>0.15543956940140272</v>
       </c>
       <c r="Q23" s="9">
-        <f t="shared" si="204"/>
+        <f t="shared" si="228"/>
         <v>3.5288331488995447E-2</v>
       </c>
       <c r="R23" s="9">
-        <f t="shared" si="204"/>
+        <f t="shared" si="228"/>
         <v>0.14063577173496744</v>
       </c>
       <c r="S23" s="9">
-        <f t="shared" ref="S23:V23" si="205">S12/S11</f>
+        <f t="shared" ref="S23:V23" si="229">S12/S11</f>
         <v>0.17438928975049986</v>
       </c>
       <c r="T23" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="229"/>
         <v>0.16934388236234316</v>
       </c>
       <c r="U23" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="229"/>
         <v>0.12976810222432561</v>
       </c>
       <c r="V23" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="229"/>
         <v>0.19028499448905684</v>
       </c>
       <c r="W23" s="9">
-        <f t="shared" ref="W23:AE23" si="206">W12/W11</f>
+        <f t="shared" ref="W23:AE23" si="230">W12/W11</f>
         <v>0.1619892231701841</v>
       </c>
       <c r="X23" s="9">
-        <f t="shared" si="206"/>
+        <f t="shared" si="230"/>
         <v>0.18311751771316884</v>
       </c>
       <c r="Y23" s="9">
-        <f t="shared" si="206"/>
+        <f t="shared" si="230"/>
         <v>0.21180057388809181</v>
       </c>
       <c r="Z23" s="9">
-        <f t="shared" si="206"/>
+        <f t="shared" si="230"/>
         <v>0.24345422019840623</v>
       </c>
       <c r="AA23" s="9">
-        <f t="shared" si="206"/>
+        <f t="shared" si="230"/>
         <v>0.21869440262761736</v>
       </c>
       <c r="AB23" s="9">
-        <f t="shared" si="206"/>
+        <f t="shared" si="230"/>
         <v>0.16194985472936618</v>
       </c>
       <c r="AC23" s="9">
-        <f t="shared" si="206"/>
+        <f t="shared" si="230"/>
         <v>0.17053883834849545</v>
       </c>
       <c r="AD23" s="9">
-        <f t="shared" si="206"/>
+        <f t="shared" si="230"/>
         <v>0.16605188005711566</v>
       </c>
       <c r="AE23" s="9">
-        <f t="shared" si="206"/>
+        <f t="shared" si="230"/>
         <v>0.12789959811041388</v>
       </c>
       <c r="AF23" s="9">
-        <f t="shared" ref="AF23:AH23" si="207">AF12/AF11</f>
+        <f t="shared" ref="AF23:AH23" si="231">AF12/AF11</f>
         <v>0.10863233152389778</v>
       </c>
       <c r="AG23" s="9">
-        <f t="shared" si="207"/>
+        <f t="shared" si="231"/>
         <v>0.11973964762652901</v>
       </c>
       <c r="AH23" s="9">
-        <f t="shared" si="207"/>
+        <f t="shared" si="231"/>
         <v>0.12339226469117848</v>
       </c>
       <c r="AI23" s="9">
-        <f t="shared" ref="AI23:AL23" si="208">AI12/AI11</f>
+        <f t="shared" ref="AI23:AL23" si="232">AI12/AI11</f>
         <v>9.4549015341094556E-2</v>
       </c>
       <c r="AJ23" s="9">
-        <f t="shared" si="208"/>
+        <f t="shared" si="232"/>
         <v>0.10699327943897925</v>
       </c>
       <c r="AK23" s="9">
-        <f t="shared" si="208"/>
+        <f t="shared" si="232"/>
         <v>0.13959285417532197</v>
       </c>
       <c r="AL23" s="9">
-        <f t="shared" si="208"/>
+        <f t="shared" si="232"/>
+        <v>0.10199574031710973</v>
+      </c>
+      <c r="AM23" s="9"/>
+      <c r="AN23" s="9"/>
+      <c r="AO23" s="9"/>
+      <c r="AP23" s="9"/>
+      <c r="AQ23" s="9"/>
+      <c r="AR23" s="9">
+        <f t="shared" ref="AR23:AV23" si="233">AR12/AR11</f>
+        <v>0.39880952380952384</v>
+      </c>
+      <c r="AS23" s="9">
+        <f t="shared" si="233"/>
+        <v>0.41002949852507375</v>
+      </c>
+      <c r="AT23" s="9">
+        <f t="shared" si="233"/>
+        <v>0.89271255060728749</v>
+      </c>
+      <c r="AU23" s="9">
+        <f t="shared" si="233"/>
+        <v>0.45533769063180829</v>
+      </c>
+      <c r="AV23" s="9">
+        <f t="shared" si="233"/>
+        <v>0.40122199592668023</v>
+      </c>
+      <c r="AW23" s="9">
+        <f t="shared" ref="AW23:AY23" si="234">AW12/AW11</f>
+        <v>0.4045850823377462</v>
+      </c>
+      <c r="AX23" s="9">
+        <f t="shared" si="234"/>
+        <v>0.18381530595941845</v>
+      </c>
+      <c r="AY23" s="9">
+        <f t="shared" si="234"/>
+        <v>0.26172671651937457</v>
+      </c>
+      <c r="AZ23" s="9">
+        <f t="shared" ref="AZ23:BL23" si="235">AZ12/AZ11</f>
+        <v>0.12811009029612397</v>
+      </c>
+      <c r="BA23" s="9">
+        <f t="shared" si="235"/>
+        <v>0.25520329138431752</v>
+      </c>
+      <c r="BB23" s="9">
+        <f t="shared" si="235"/>
+        <v>0.12160940325497288</v>
+      </c>
+      <c r="BC23" s="9">
+        <f t="shared" si="235"/>
+        <v>0.1673540173000867</v>
+      </c>
+      <c r="BD23" s="9">
+        <f t="shared" si="235"/>
+        <v>0.19501023630243935</v>
+      </c>
+      <c r="BE23" s="9">
+        <f t="shared" si="235"/>
+        <v>0.17466141137993207</v>
+      </c>
+      <c r="BF23" s="9">
+        <f t="shared" si="235"/>
+        <v>0.1201493185172324</v>
+      </c>
+      <c r="BG23" s="9">
+        <f t="shared" si="235"/>
+        <v>0.11107451942378567</v>
+      </c>
+      <c r="BH23" s="9">
+        <f t="shared" si="235"/>
+        <v>0.12</v>
+      </c>
+      <c r="BI23" s="9">
+        <f t="shared" si="235"/>
+        <v>0.12</v>
+      </c>
+      <c r="BJ23" s="9">
+        <f t="shared" si="235"/>
+        <v>0.12</v>
+      </c>
+      <c r="BK23" s="9">
+        <f t="shared" si="235"/>
+        <v>0.12</v>
+      </c>
+      <c r="BL23" s="9">
+        <f t="shared" si="235"/>
+        <v>0.12</v>
+      </c>
+      <c r="BM23" s="9">
+        <f t="shared" ref="BM23:BQ23" si="236">BM12/BM11</f>
+        <v>0.12</v>
+      </c>
+      <c r="BN23" s="9">
+        <f t="shared" si="236"/>
+        <v>0.12</v>
+      </c>
+      <c r="BO23" s="9">
+        <f t="shared" si="236"/>
+        <v>0.12</v>
+      </c>
+      <c r="BP23" s="9">
+        <f t="shared" si="236"/>
+        <v>0.12</v>
+      </c>
+      <c r="BQ23" s="9">
+        <f t="shared" si="236"/>
         <v>0.12000000000000001</v>
       </c>
-      <c r="AN23" s="9">
-        <f t="shared" ref="AN23" si="209">AN12/AN11</f>
-        <v>0.26172671651937457</v>
-      </c>
-      <c r="AO23" s="9">
-        <f t="shared" ref="AO23:BA23" si="210">AO12/AO11</f>
-        <v>0.12811009029612397</v>
-      </c>
-      <c r="AP23" s="9">
-        <f t="shared" si="210"/>
-        <v>0.25520329138431752</v>
-      </c>
-      <c r="AQ23" s="9">
-        <f t="shared" si="210"/>
-        <v>0.12160940325497288</v>
-      </c>
-      <c r="AR23" s="9">
-        <f t="shared" si="210"/>
-        <v>0.1673540173000867</v>
-      </c>
-      <c r="AS23" s="9">
-        <f t="shared" si="210"/>
-        <v>0.19501023630243935</v>
-      </c>
-      <c r="AT23" s="9">
-        <f t="shared" si="210"/>
-        <v>0.17466141137993207</v>
-      </c>
-      <c r="AU23" s="9">
-        <f t="shared" si="210"/>
-        <v>0.1201493185172324</v>
-      </c>
-      <c r="AV23" s="9">
-        <f t="shared" si="210"/>
-        <v>0.11651559247050146</v>
-      </c>
-      <c r="AW23" s="9">
-        <f t="shared" si="210"/>
-        <v>0.12</v>
-      </c>
-      <c r="AX23" s="9">
-        <f t="shared" si="210"/>
-        <v>0.11999999999999998</v>
-      </c>
-      <c r="AY23" s="9">
-        <f t="shared" si="210"/>
-        <v>0.12</v>
-      </c>
-      <c r="AZ23" s="9">
-        <f t="shared" si="210"/>
-        <v>0.12</v>
-      </c>
-      <c r="BA23" s="9">
-        <f t="shared" si="210"/>
-        <v>0.12</v>
-      </c>
-      <c r="BB23" s="9">
-        <f t="shared" ref="BB23:BF23" si="211">BB12/BB11</f>
-        <v>0.12</v>
-      </c>
-      <c r="BC23" s="9">
-        <f t="shared" si="211"/>
-        <v>0.12</v>
-      </c>
-      <c r="BD23" s="9">
-        <f t="shared" si="211"/>
-        <v>0.12</v>
-      </c>
-      <c r="BE23" s="9">
-        <f t="shared" si="211"/>
-        <v>0.12</v>
-      </c>
-      <c r="BF23" s="9">
-        <f t="shared" si="211"/>
-        <v>0.12</v>
-      </c>
-      <c r="BH23" t="s">
+      <c r="BS23" t="s">
         <v>48</v>
       </c>
-      <c r="BI23" s="5">
-        <f>BI22/BA14</f>
-        <v>786.71072739593603</v>
-      </c>
-    </row>
-    <row r="24" spans="2:61">
+      <c r="BT23" s="5">
+        <f>BT22/BL14</f>
+        <v>829.05144328838037</v>
+      </c>
+    </row>
+    <row r="24" spans="2:72">
       <c r="B24" t="s">
         <v>93</v>
       </c>
@@ -6586,246 +7236,279 @@
         <v>0.38085159362549803</v>
       </c>
       <c r="D24" s="9">
-        <f t="shared" ref="D24:AL24" si="212">D13/D3</f>
+        <f t="shared" ref="D24:AL24" si="237">D13/D3</f>
         <v>0.41733719557987342</v>
       </c>
       <c r="E24" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="237"/>
         <v>0.4557513555383424</v>
       </c>
       <c r="F24" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="237"/>
         <v>0.2735121800801727</v>
       </c>
       <c r="G24" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="237"/>
         <v>0.41676416513454789</v>
       </c>
       <c r="H24" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="237"/>
         <v>0.38591187363011109</v>
       </c>
       <c r="I24" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="237"/>
         <v>0.37422597799956292</v>
       </c>
       <c r="J24" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="237"/>
         <v>0.40688187300461154</v>
       </c>
       <c r="K24" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="237"/>
         <v>0.16110632088611793</v>
       </c>
       <c r="L24" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="237"/>
         <v>0.15391912723823076</v>
       </c>
       <c r="M24" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="237"/>
         <v>0.34506004985270788</v>
       </c>
       <c r="N24" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="237"/>
         <v>0.34859121525471964</v>
       </c>
       <c r="O24" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="237"/>
         <v>0.27637142696059086</v>
       </c>
       <c r="P24" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="237"/>
         <v>0.27709102584684542</v>
       </c>
       <c r="Q24" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="237"/>
         <v>0.3654401490451793</v>
       </c>
       <c r="R24" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="237"/>
         <v>0.39965089769165002</v>
       </c>
       <c r="S24" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="237"/>
         <v>0.36288257995491191</v>
       </c>
       <c r="T24" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="237"/>
         <v>0.35746466279189737</v>
       </c>
       <c r="U24" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="237"/>
         <v>0.31692519820751464</v>
       </c>
       <c r="V24" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="237"/>
         <v>0.30545573342045085</v>
       </c>
       <c r="W24" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="237"/>
         <v>0.26748602551239786</v>
       </c>
       <c r="X24" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="237"/>
         <v>0.23201026993269031</v>
       </c>
       <c r="Y24" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="237"/>
         <v>0.15858410911452694</v>
       </c>
       <c r="Z24" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="237"/>
         <v>0.1446292554018343</v>
       </c>
       <c r="AA24" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="237"/>
         <v>0.19930179787048349</v>
       </c>
       <c r="AB24" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="237"/>
         <v>0.24338260570642833</v>
       </c>
       <c r="AC24" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="237"/>
         <v>0.34440376569037656</v>
       </c>
       <c r="AD24" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="237"/>
         <v>0.34945526164892421</v>
       </c>
       <c r="AE24" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="237"/>
         <v>0.33929502125908656</v>
       </c>
       <c r="AF24" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="237"/>
         <v>0.34462900872770086</v>
       </c>
       <c r="AG24" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="237"/>
         <v>0.38650865998176848</v>
       </c>
       <c r="AH24" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="237"/>
         <v>0.39863594089077192</v>
       </c>
       <c r="AI24" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="237"/>
         <v>0.39334499220116276</v>
       </c>
       <c r="AJ24" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="237"/>
         <v>0.38591211381429413</v>
       </c>
       <c r="AK24" s="9">
-        <f t="shared" si="212"/>
+        <f t="shared" si="237"/>
         <v>0.36374458452051051</v>
       </c>
       <c r="AL24" s="9">
-        <f t="shared" si="212"/>
-        <v>0.36952997829905959</v>
-      </c>
-      <c r="AN24" s="9">
-        <f t="shared" ref="AN24:BF24" si="213">AN13/AN3</f>
+        <f t="shared" si="237"/>
+        <v>0.3801445911876179</v>
+      </c>
+      <c r="AM24" s="9"/>
+      <c r="AN24" s="9"/>
+      <c r="AO24" s="9"/>
+      <c r="AP24" s="9"/>
+      <c r="AQ24" s="9"/>
+      <c r="AR24" s="9">
+        <f t="shared" ref="AR24:AV24" si="238">AR13/AR3</f>
+        <v>0.30699088145896658</v>
+      </c>
+      <c r="AS24" s="9">
+        <f t="shared" si="238"/>
+        <v>0.2694691457828079</v>
+      </c>
+      <c r="AT24" s="9">
+        <f t="shared" si="238"/>
+        <v>1.0414619768127334E-2</v>
+      </c>
+      <c r="AU24" s="9">
+        <f t="shared" si="238"/>
+        <v>0.19054878048780488</v>
+      </c>
+      <c r="AV24" s="9">
+        <f t="shared" si="238"/>
+        <v>0.2358414888496711</v>
+      </c>
+      <c r="AW24" s="9">
+        <f t="shared" ref="AW24:AY24" si="239">AW13/AW3</f>
+        <v>0.20571173583221777</v>
+      </c>
+      <c r="AX24" s="9">
+        <f t="shared" si="239"/>
+        <v>0.36967219046240685</v>
+      </c>
+      <c r="AY24" s="9">
+        <f t="shared" si="239"/>
         <v>0.37399453914840231</v>
       </c>
-      <c r="AO24" s="9">
-        <f t="shared" si="213"/>
+      <c r="AZ24" s="9">
+        <f t="shared" ref="AZ24:BQ24" si="240">AZ13/AZ3</f>
         <v>0.39600272216053584</v>
       </c>
-      <c r="AP24" s="9">
-        <f t="shared" si="213"/>
+      <c r="BA24" s="9">
+        <f t="shared" si="240"/>
         <v>0.26125896684918715</v>
       </c>
-      <c r="AQ24" s="9">
-        <f t="shared" si="213"/>
+      <c r="BB24" s="9">
+        <f t="shared" si="240"/>
         <v>0.33902938370983876</v>
       </c>
-      <c r="AR24" s="9">
-        <f t="shared" si="213"/>
+      <c r="BC24" s="9">
+        <f t="shared" si="240"/>
         <v>0.33384494059985248</v>
       </c>
-      <c r="AS24" s="9">
-        <f t="shared" si="213"/>
+      <c r="BD24" s="9">
+        <f t="shared" si="240"/>
         <v>0.19894690804311846</v>
       </c>
-      <c r="AT24" s="9">
-        <f t="shared" si="213"/>
+      <c r="BE24" s="9">
+        <f t="shared" si="240"/>
         <v>0.29123850530069317</v>
       </c>
-      <c r="AU24" s="9">
-        <f t="shared" si="213"/>
+      <c r="BF24" s="9">
+        <f t="shared" si="240"/>
         <v>0.36966565349544073</v>
       </c>
-      <c r="AV24" s="9">
-        <f t="shared" si="213"/>
-        <v>0.37638820894473074</v>
-      </c>
-      <c r="AW24" s="9">
-        <f t="shared" si="213"/>
-        <v>0.36821540516471402</v>
-      </c>
-      <c r="AX24" s="9">
-        <f t="shared" si="213"/>
-        <v>0.37449954321778317</v>
-      </c>
-      <c r="AY24" s="9">
-        <f t="shared" si="213"/>
-        <v>0.38079739070647506</v>
-      </c>
-      <c r="AZ24" s="9">
-        <f t="shared" si="213"/>
-        <v>0.384302756393471</v>
-      </c>
-      <c r="BA24" s="9">
-        <f t="shared" si="213"/>
-        <v>0.38491290843798409</v>
-      </c>
-      <c r="BB24" s="9">
-        <f t="shared" si="213"/>
-        <v>0.38498781622533251</v>
-      </c>
-      <c r="BC24" s="9">
-        <f t="shared" si="213"/>
-        <v>0.38498910875185932</v>
-      </c>
-      <c r="BD24" s="9">
-        <f t="shared" si="213"/>
-        <v>0.38498913105427784</v>
-      </c>
-      <c r="BE24" s="9">
-        <f t="shared" si="213"/>
-        <v>0.3849891314391039</v>
-      </c>
-      <c r="BF24" s="9">
-        <f t="shared" si="213"/>
-        <v>0.38498913144574393</v>
-      </c>
-      <c r="BH24" t="s">
+      <c r="BG24" s="9">
+        <f t="shared" si="240"/>
+        <v>0.38010748140223416</v>
+      </c>
+      <c r="BH24" s="9">
+        <f t="shared" si="240"/>
+        <v>0.36842787974111868</v>
+      </c>
+      <c r="BI24" s="9">
+        <f t="shared" si="240"/>
+        <v>0.37469170524028322</v>
+      </c>
+      <c r="BJ24" s="9">
+        <f t="shared" si="240"/>
+        <v>0.38097228109804726</v>
+      </c>
+      <c r="BK24" s="9">
+        <f t="shared" si="240"/>
+        <v>0.38446245478925212</v>
+      </c>
+      <c r="BL24" s="9">
+        <f t="shared" si="240"/>
+        <v>0.38505919509626035</v>
+      </c>
+      <c r="BM24" s="9">
+        <f t="shared" si="240"/>
+        <v>0.38513389821859845</v>
+      </c>
+      <c r="BN24" s="9">
+        <f t="shared" si="240"/>
+        <v>0.38513518721365053</v>
+      </c>
+      <c r="BO24" s="9">
+        <f t="shared" si="240"/>
+        <v>0.38513520945513374</v>
+      </c>
+      <c r="BP24" s="9">
+        <f t="shared" si="240"/>
+        <v>0.38513520983890842</v>
+      </c>
+      <c r="BQ24" s="9">
+        <f t="shared" si="240"/>
+        <v>0.38513520984553046</v>
+      </c>
+      <c r="BS24" t="s">
         <v>49</v>
       </c>
-      <c r="BI24" s="5">
+      <c r="BT24" s="5">
         <f>Main!D3</f>
-        <v>686.46</v>
-      </c>
-    </row>
-    <row r="25" spans="2:61">
+        <v>726.51</v>
+      </c>
+    </row>
+    <row r="25" spans="2:72">
       <c r="C25" t="s">
         <v>42</v>
       </c>
-      <c r="BH25" s="6" t="s">
+      <c r="BS25" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="BI25" s="10">
-        <f>BI23/BI24-1</f>
-        <v>0.14604015877973375</v>
-      </c>
-    </row>
-    <row r="26" spans="2:61">
-      <c r="BH26" t="s">
+      <c r="BT25" s="10">
+        <f>BT23/BT24-1</f>
+        <v>0.14114250772650117</v>
+      </c>
+    </row>
+    <row r="26" spans="2:72">
+      <c r="BS26" t="s">
         <v>67</v>
       </c>
-      <c r="BI26" s="3" t="s">
+      <c r="BT26" s="3" t="s">
         <v>92</v>
       </c>
     </row>

--- a/Financial Analysis/FB.xlsx
+++ b/Financial Analysis/FB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E8FE619-CF00-4115-A818-16CF5045EE81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F965145-9F85-446E-8841-A9C9B4682CB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{BFE532A1-2353-49AA-A72E-D2C0AD0DD88D}"/>
   </bookViews>
@@ -388,9 +388,6 @@
     <t>META</t>
   </si>
   <si>
-    <t>Slightly undervalued</t>
-  </si>
-  <si>
     <t>Net Margin</t>
   </si>
   <si>
@@ -584,6 +581,9 @@
   </si>
   <si>
     <t>Q426</t>
+  </si>
+  <si>
+    <t>Undervalued</t>
   </si>
 </sst>
 </file>
@@ -1031,7 +1031,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1168,6 +1168,7 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1625,14 +1626,14 @@
         <v>0</v>
       </c>
       <c r="D3" s="5">
-        <v>726.51</v>
+        <v>635.1</v>
       </c>
       <c r="E3" s="2">
-        <v>46052</v>
+        <v>46070</v>
       </c>
       <c r="F3" s="2">
         <f ca="1">TODAY()</f>
-        <v>46059</v>
+        <v>46070</v>
       </c>
       <c r="G3" s="2">
         <v>46141</v>
@@ -1656,7 +1657,7 @@
         <v>2517</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F4" s="1"/>
       <c r="I4" s="14" t="s">
@@ -1675,7 +1676,7 @@
       </c>
       <c r="D5" s="4">
         <f>D3*D4</f>
-        <v>1828625.67</v>
+        <v>1598546.7</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -1750,7 +1751,7 @@
       </c>
       <c r="D9" s="4">
         <f>D5-D8</f>
-        <v>1778253.67</v>
+        <v>1548174.7</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
@@ -1882,16 +1883,16 @@
         <v>90</v>
       </c>
       <c r="AM2" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="AN2" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="AN2" s="3" t="s">
+      <c r="AO2" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="AO2" s="3" t="s">
+      <c r="AP2" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="AP2" s="3" t="s">
-        <v>157</v>
       </c>
       <c r="AQ2" s="3"/>
       <c r="AR2">
@@ -2085,10 +2086,21 @@
       <c r="AL3" s="8">
         <v>59893</v>
       </c>
-      <c r="AM3" s="8"/>
-      <c r="AN3" s="8"/>
-      <c r="AO3" s="8"/>
-      <c r="AP3" s="8"/>
+      <c r="AM3" s="8">
+        <v>54000</v>
+      </c>
+      <c r="AN3" s="8">
+        <f>AJ3*1.25</f>
+        <v>59395</v>
+      </c>
+      <c r="AO3" s="8">
+        <f>AK3*1.2</f>
+        <v>61490.399999999994</v>
+      </c>
+      <c r="AP3" s="8">
+        <f>AL3*1.15</f>
+        <v>68876.95</v>
+      </c>
       <c r="AQ3" s="8"/>
       <c r="AR3" s="8">
         <v>1974</v>
@@ -2148,44 +2160,44 @@
         <v>200965</v>
       </c>
       <c r="BH3" s="8">
-        <f>BG3*1.15</f>
-        <v>231109.74999999997</v>
+        <f>SUM(AM3:AP3)</f>
+        <v>243762.34999999998</v>
       </c>
       <c r="BI3" s="8">
-        <f>BH3*1.08</f>
-        <v>249598.53</v>
+        <f>BH3*1.14</f>
+        <v>277889.07899999997</v>
       </c>
       <c r="BJ3" s="8">
-        <f>BI3*1.06</f>
-        <v>264574.44180000003</v>
+        <f>BI3*1.07</f>
+        <v>297341.31452999997</v>
       </c>
       <c r="BK3" s="8">
-        <f>BJ3*1.04</f>
-        <v>275157.41947200004</v>
+        <f>BJ3*1.05</f>
+        <v>312208.38025649998</v>
       </c>
       <c r="BL3" s="8">
-        <f>BK3*1.03</f>
-        <v>283412.14205616002</v>
+        <f>BK3*1.04</f>
+        <v>324696.71546675998</v>
       </c>
       <c r="BM3" s="8">
-        <f t="shared" ref="BM3" si="0">BL3*1.02</f>
-        <v>289080.38489728322</v>
+        <f>BL3*1.03</f>
+        <v>334437.61693076277</v>
       </c>
       <c r="BN3" s="8">
-        <f t="shared" ref="BN3" si="1">BM3*1.02</f>
-        <v>294861.99259522889</v>
+        <f t="shared" ref="BN3" si="0">BM3*1.02</f>
+        <v>341126.36926937802</v>
       </c>
       <c r="BO3" s="8">
-        <f t="shared" ref="BO3" si="2">BN3*1.02</f>
-        <v>300759.23244713346</v>
+        <f t="shared" ref="BO3" si="1">BN3*1.02</f>
+        <v>347948.89665476559</v>
       </c>
       <c r="BP3" s="8">
-        <f t="shared" ref="BP3" si="3">BO3*1.02</f>
-        <v>306774.41709607613</v>
+        <f t="shared" ref="BP3" si="2">BO3*1.02</f>
+        <v>354907.87458786089</v>
       </c>
       <c r="BQ3" s="8">
-        <f t="shared" ref="BQ3" si="4">BP3*1.02</f>
-        <v>312909.90543799766</v>
+        <f t="shared" ref="BQ3" si="3">BP3*1.02</f>
+        <v>362006.03207961813</v>
       </c>
     </row>
     <row r="4" spans="2:176">
@@ -2300,10 +2312,22 @@
       <c r="AL4" s="4">
         <v>10905</v>
       </c>
-      <c r="AM4" s="4"/>
-      <c r="AN4" s="4"/>
-      <c r="AO4" s="4"/>
-      <c r="AP4" s="4"/>
+      <c r="AM4" s="4">
+        <f>AM3-AM5</f>
+        <v>9720</v>
+      </c>
+      <c r="AN4" s="4">
+        <f t="shared" ref="AN4:AP4" si="4">AN3-AN5</f>
+        <v>10691.100000000006</v>
+      </c>
+      <c r="AO4" s="4">
+        <f t="shared" si="4"/>
+        <v>11068.272000000004</v>
+      </c>
+      <c r="AP4" s="4">
+        <f t="shared" si="4"/>
+        <v>12397.851000000002</v>
+      </c>
       <c r="AQ4" s="4"/>
       <c r="AR4" s="4">
         <v>493</v>
@@ -2362,45 +2386,45 @@
         <f>SUM(AI4:AL4)</f>
         <v>36174</v>
       </c>
-      <c r="BH4" s="4">
-        <f t="shared" ref="BH4:BL4" si="5">BH3-BH5</f>
-        <v>41599.755000000005</v>
+      <c r="BH4" s="52">
+        <f>SUM(AM4:AP4)</f>
+        <v>43877.223000000013</v>
       </c>
       <c r="BI4" s="4">
-        <f t="shared" si="5"/>
-        <v>44927.735400000005</v>
+        <f t="shared" ref="BH4:BL4" si="5">BI3-BI5</f>
+        <v>50020.034220000001</v>
       </c>
       <c r="BJ4" s="4">
         <f t="shared" si="5"/>
-        <v>47623.399524000008</v>
+        <v>53521.436615400016</v>
       </c>
       <c r="BK4" s="4">
         <f t="shared" si="5"/>
-        <v>49528.335504960007</v>
+        <v>56197.508446170017</v>
       </c>
       <c r="BL4" s="4">
         <f t="shared" si="5"/>
-        <v>51014.185570108821</v>
+        <v>58445.408784016792</v>
       </c>
       <c r="BM4" s="4">
         <f t="shared" ref="BM4:BQ4" si="6">BM3-BM5</f>
-        <v>52034.469281511003</v>
+        <v>60198.771047537331</v>
       </c>
       <c r="BN4" s="4">
         <f t="shared" si="6"/>
-        <v>53075.158667141222</v>
+        <v>61402.746468488069</v>
       </c>
       <c r="BO4" s="4">
         <f t="shared" si="6"/>
-        <v>54136.661840484041</v>
+        <v>62630.801397857838</v>
       </c>
       <c r="BP4" s="4">
         <f t="shared" si="6"/>
-        <v>55219.39507729371</v>
+        <v>63883.417425814958</v>
       </c>
       <c r="BQ4" s="4">
         <f t="shared" si="6"/>
-        <v>56323.78297883959</v>
+        <v>65161.085774331295</v>
       </c>
     </row>
     <row r="5" spans="2:176" s="6" customFormat="1">
@@ -2551,69 +2575,81 @@
         <f t="shared" si="15"/>
         <v>48988</v>
       </c>
-      <c r="AM5" s="8"/>
-      <c r="AN5" s="8"/>
-      <c r="AO5" s="8"/>
-      <c r="AP5" s="8"/>
+      <c r="AM5" s="8">
+        <f>AM3*0.82</f>
+        <v>44280</v>
+      </c>
+      <c r="AN5" s="8">
+        <f t="shared" ref="AN5:AP5" si="16">AN3*0.82</f>
+        <v>48703.899999999994</v>
+      </c>
+      <c r="AO5" s="8">
+        <f t="shared" si="16"/>
+        <v>50422.12799999999</v>
+      </c>
+      <c r="AP5" s="8">
+        <f t="shared" si="16"/>
+        <v>56479.098999999995</v>
+      </c>
       <c r="AQ5" s="8"/>
       <c r="AR5" s="8">
-        <f t="shared" ref="AR5" si="16">AR3-AR4</f>
+        <f t="shared" ref="AR5" si="17">AR3-AR4</f>
         <v>1481</v>
       </c>
       <c r="AS5" s="8">
-        <f t="shared" ref="AS5:AT5" si="17">AS3-AS4</f>
+        <f t="shared" ref="AS5:AT5" si="18">AS3-AS4</f>
         <v>2851</v>
       </c>
       <c r="AT5" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3725</v>
       </c>
       <c r="AU5" s="8">
-        <f t="shared" ref="AU5" si="18">AU3-AU4</f>
+        <f t="shared" ref="AU5" si="19">AU3-AU4</f>
         <v>5997</v>
       </c>
       <c r="AV5" s="8">
-        <f t="shared" ref="AV5" si="19">AV3-AV4</f>
+        <f t="shared" ref="AV5" si="20">AV3-AV4</f>
         <v>10313</v>
       </c>
       <c r="AW5" s="8">
-        <f t="shared" ref="AW5:AX5" si="20">AW3-AW4</f>
+        <f t="shared" ref="AW5:AX5" si="21">AW3-AW4</f>
         <v>15061</v>
       </c>
       <c r="AX5" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>23849</v>
       </c>
       <c r="AY5" s="8">
-        <f t="shared" ref="AY5:BF5" si="21">AY3-AY4</f>
+        <f t="shared" ref="AY5:BF5" si="22">AY3-AY4</f>
         <v>35198</v>
       </c>
       <c r="AZ5" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>46483</v>
       </c>
       <c r="BA5" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>57907</v>
       </c>
       <c r="BB5" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>69274</v>
       </c>
       <c r="BC5" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>95280</v>
       </c>
       <c r="BD5" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>91360</v>
       </c>
       <c r="BE5" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>109213</v>
       </c>
       <c r="BF5" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>134338</v>
       </c>
       <c r="BG5" s="8">
@@ -2621,44 +2657,44 @@
         <v>164791.29999999999</v>
       </c>
       <c r="BH5" s="8">
-        <f t="shared" ref="BH5:BQ5" si="22">BH3*0.82</f>
-        <v>189509.99499999997</v>
+        <f t="shared" ref="BH5:BQ5" si="23">BH3*0.82</f>
+        <v>199885.12699999998</v>
       </c>
       <c r="BI5" s="8">
-        <f t="shared" si="22"/>
-        <v>204670.79459999999</v>
+        <f t="shared" si="23"/>
+        <v>227869.04477999997</v>
       </c>
       <c r="BJ5" s="8">
-        <f t="shared" si="22"/>
-        <v>216951.04227600002</v>
+        <f t="shared" si="23"/>
+        <v>243819.87791459996</v>
       </c>
       <c r="BK5" s="8">
-        <f t="shared" si="22"/>
-        <v>225629.08396704003</v>
+        <f t="shared" si="23"/>
+        <v>256010.87181032996</v>
       </c>
       <c r="BL5" s="8">
-        <f t="shared" si="22"/>
-        <v>232397.9564860512</v>
+        <f t="shared" si="23"/>
+        <v>266251.30668274319</v>
       </c>
       <c r="BM5" s="8">
-        <f t="shared" si="22"/>
-        <v>237045.91561577222</v>
+        <f t="shared" si="23"/>
+        <v>274238.84588322544</v>
       </c>
       <c r="BN5" s="8">
-        <f t="shared" si="22"/>
-        <v>241786.83392808767</v>
+        <f t="shared" si="23"/>
+        <v>279723.62280088995</v>
       </c>
       <c r="BO5" s="8">
-        <f t="shared" si="22"/>
-        <v>246622.57060664942</v>
+        <f t="shared" si="23"/>
+        <v>285318.09525690775</v>
       </c>
       <c r="BP5" s="8">
-        <f t="shared" si="22"/>
-        <v>251555.02201878242</v>
+        <f t="shared" si="23"/>
+        <v>291024.45716204593</v>
       </c>
       <c r="BQ5" s="8">
-        <f t="shared" si="22"/>
-        <v>256586.12245915807</v>
+        <f t="shared" si="23"/>
+        <v>296844.94630528684</v>
       </c>
     </row>
     <row r="6" spans="2:176">
@@ -2773,10 +2809,22 @@
       <c r="AL6" s="4">
         <v>17136</v>
       </c>
-      <c r="AM6" s="4"/>
-      <c r="AN6" s="4"/>
-      <c r="AO6" s="4"/>
-      <c r="AP6" s="4"/>
+      <c r="AM6" s="4">
+        <f>AI6*1.45</f>
+        <v>17617.5</v>
+      </c>
+      <c r="AN6" s="4">
+        <f>AJ6*1.4</f>
+        <v>18118.8</v>
+      </c>
+      <c r="AO6" s="4">
+        <f>AK6*1.3</f>
+        <v>19687.2</v>
+      </c>
+      <c r="AP6" s="4">
+        <f>AL6*1.25</f>
+        <v>21420</v>
+      </c>
       <c r="AQ6" s="4"/>
       <c r="AR6" s="4">
         <v>144</v>
@@ -2835,45 +2883,45 @@
         <f>SUM(AI6:AL6)</f>
         <v>57372</v>
       </c>
-      <c r="BH6" s="4">
-        <f>BG6*1.14</f>
-        <v>65404.079999999994</v>
+      <c r="BH6" s="52">
+        <f t="shared" ref="BH6:BH8" si="24">SUM(AM6:AP6)</f>
+        <v>76843.5</v>
       </c>
       <c r="BI6" s="4">
-        <f>BH6*1.06</f>
-        <v>69328.324800000002</v>
+        <f>BH6*1.17</f>
+        <v>89906.89499999999</v>
       </c>
       <c r="BJ6" s="4">
-        <f>BI6*1.04</f>
-        <v>72101.457792000001</v>
+        <f>BI6*1.08</f>
+        <v>97099.446599999996</v>
       </c>
       <c r="BK6" s="4">
-        <f t="shared" ref="BK6:BL6" si="23">BJ6*1.03</f>
-        <v>74264.501525760003</v>
+        <f>BJ6*1.04</f>
+        <v>100983.424464</v>
       </c>
       <c r="BL6" s="4">
-        <f t="shared" si="23"/>
-        <v>76492.436571532802</v>
+        <f t="shared" ref="BL6" si="25">BK6*1.03</f>
+        <v>104012.92719792</v>
       </c>
       <c r="BM6" s="4">
         <f>BL6*1.02</f>
-        <v>78022.285302963457</v>
+        <v>106093.18574187841</v>
       </c>
       <c r="BN6" s="4">
-        <f t="shared" ref="BN6:BQ6" si="24">BM6*1.02</f>
-        <v>79582.731009022726</v>
+        <f t="shared" ref="BN6:BQ6" si="26">BM6*1.02</f>
+        <v>108215.04945671598</v>
       </c>
       <c r="BO6" s="4">
-        <f t="shared" si="24"/>
-        <v>81174.385629203185</v>
+        <f t="shared" si="26"/>
+        <v>110379.3504458503</v>
       </c>
       <c r="BP6" s="4">
-        <f t="shared" si="24"/>
-        <v>82797.873341787257</v>
+        <f t="shared" si="26"/>
+        <v>112586.93745476731</v>
       </c>
       <c r="BQ6" s="4">
-        <f t="shared" si="24"/>
-        <v>84453.83080862301</v>
+        <f t="shared" si="26"/>
+        <v>114838.67620386266</v>
       </c>
     </row>
     <row r="7" spans="2:176">
@@ -2988,10 +3036,22 @@
       <c r="AL7" s="4">
         <v>3410</v>
       </c>
-      <c r="AM7" s="4"/>
-      <c r="AN7" s="4"/>
-      <c r="AO7" s="4"/>
-      <c r="AP7" s="4"/>
+      <c r="AM7" s="4">
+        <f>AM3*0.06</f>
+        <v>3240</v>
+      </c>
+      <c r="AN7" s="4">
+        <f t="shared" ref="AN7:AP7" si="27">AN3*0.06</f>
+        <v>3563.7</v>
+      </c>
+      <c r="AO7" s="4">
+        <f t="shared" si="27"/>
+        <v>3689.4239999999995</v>
+      </c>
+      <c r="AP7" s="4">
+        <f t="shared" si="27"/>
+        <v>4132.6169999999993</v>
+      </c>
       <c r="AQ7" s="4"/>
       <c r="AR7" s="4">
         <v>167</v>
@@ -3050,45 +3110,45 @@
         <f>SUM(AI7:AL7)</f>
         <v>11991</v>
       </c>
-      <c r="BH7" s="4">
-        <f>BH3*0.065</f>
-        <v>15022.133749999999</v>
+      <c r="BH7" s="52">
+        <f t="shared" si="24"/>
+        <v>14625.740999999998</v>
       </c>
       <c r="BI7" s="4">
-        <f t="shared" ref="BI7:BQ7" si="25">BI3*0.065</f>
-        <v>16223.90445</v>
+        <f>BI3*0.06</f>
+        <v>16673.344739999997</v>
       </c>
       <c r="BJ7" s="4">
-        <f t="shared" si="25"/>
-        <v>17197.338717000002</v>
+        <f t="shared" ref="BJ7:BQ7" si="28">BJ3*0.06</f>
+        <v>17840.478871799998</v>
       </c>
       <c r="BK7" s="4">
-        <f t="shared" si="25"/>
-        <v>17885.232265680002</v>
+        <f t="shared" si="28"/>
+        <v>18732.502815389998</v>
       </c>
       <c r="BL7" s="4">
-        <f t="shared" si="25"/>
-        <v>18421.789233650401</v>
+        <f t="shared" si="28"/>
+        <v>19481.8029280056</v>
       </c>
       <c r="BM7" s="4">
-        <f t="shared" si="25"/>
-        <v>18790.22501832341</v>
+        <f t="shared" si="28"/>
+        <v>20066.257015845764</v>
       </c>
       <c r="BN7" s="4">
-        <f t="shared" si="25"/>
-        <v>19166.02951868988</v>
+        <f t="shared" si="28"/>
+        <v>20467.58215616268</v>
       </c>
       <c r="BO7" s="4">
-        <f t="shared" si="25"/>
-        <v>19549.350109063675</v>
+        <f t="shared" si="28"/>
+        <v>20876.933799285933</v>
       </c>
       <c r="BP7" s="4">
-        <f t="shared" si="25"/>
-        <v>19940.337111244949</v>
+        <f t="shared" si="28"/>
+        <v>21294.472475271654</v>
       </c>
       <c r="BQ7" s="4">
-        <f t="shared" si="25"/>
-        <v>20339.14385346985</v>
+        <f t="shared" si="28"/>
+        <v>21720.361924777088</v>
       </c>
     </row>
     <row r="8" spans="2:176">
@@ -3204,10 +3264,22 @@
       <c r="AL8" s="4">
         <v>3697</v>
       </c>
-      <c r="AM8" s="4"/>
-      <c r="AN8" s="4"/>
-      <c r="AO8" s="4"/>
-      <c r="AP8" s="4"/>
+      <c r="AM8" s="4">
+        <f>AI8*1.5</f>
+        <v>3420</v>
+      </c>
+      <c r="AN8" s="4">
+        <f t="shared" ref="AN8:AP9" si="29">AJ8*1.5</f>
+        <v>3994.5</v>
+      </c>
+      <c r="AO8" s="4">
+        <f>AK8*1.2</f>
+        <v>4214.3999999999996</v>
+      </c>
+      <c r="AP8" s="4">
+        <f>AL8*1.2</f>
+        <v>4436.3999999999996</v>
+      </c>
       <c r="AQ8" s="4"/>
       <c r="AR8" s="4">
         <v>138</v>
@@ -3266,303 +3338,316 @@
         <f>SUM(AI8:AL8)</f>
         <v>12152</v>
       </c>
-      <c r="BH8" s="4">
-        <f>BG8*1.14</f>
-        <v>13853.279999999999</v>
+      <c r="BH8" s="52">
+        <f t="shared" si="24"/>
+        <v>16065.3</v>
       </c>
       <c r="BI8" s="4">
-        <f>BH8*1.05</f>
-        <v>14545.944</v>
+        <f>BH8*1.16</f>
+        <v>18635.748</v>
       </c>
       <c r="BJ8" s="4">
-        <f>BI8*1.03</f>
-        <v>14982.322319999999</v>
+        <f>BI8*1.08</f>
+        <v>20126.607840000001</v>
       </c>
       <c r="BK8" s="4">
-        <f>BJ8*1.02</f>
-        <v>15281.968766399999</v>
+        <f>BJ8*1.04</f>
+        <v>20931.6721536</v>
       </c>
       <c r="BL8" s="4">
-        <f t="shared" ref="BL8:BQ8" si="26">BK8*1.02</f>
-        <v>15587.608141728</v>
+        <f>BK8*1.03</f>
+        <v>21559.622318207999</v>
       </c>
       <c r="BM8" s="4">
-        <f t="shared" si="26"/>
-        <v>15899.36030456256</v>
+        <f t="shared" ref="BL8:BQ8" si="30">BL8*1.02</f>
+        <v>21990.814764572158</v>
       </c>
       <c r="BN8" s="4">
-        <f t="shared" si="26"/>
-        <v>16217.347510653812</v>
+        <f t="shared" si="30"/>
+        <v>22430.631059863601</v>
       </c>
       <c r="BO8" s="4">
-        <f t="shared" si="26"/>
-        <v>16541.694460866889</v>
+        <f t="shared" si="30"/>
+        <v>22879.243681060874</v>
       </c>
       <c r="BP8" s="4">
-        <f t="shared" si="26"/>
-        <v>16872.528350084227</v>
+        <f t="shared" si="30"/>
+        <v>23336.828554682092</v>
       </c>
       <c r="BQ8" s="4">
-        <f t="shared" si="26"/>
-        <v>17209.978917085911</v>
-      </c>
+        <f t="shared" si="30"/>
+        <v>23803.565125775734</v>
+      </c>
+      <c r="BR8" s="4"/>
     </row>
     <row r="9" spans="2:176" s="6" customFormat="1">
       <c r="B9" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C9" s="8">
-        <f t="shared" ref="C9:V9" si="27">C5-C6-C7-C8</f>
+        <f t="shared" ref="C9:V9" si="31">C5-C6-C7-C8</f>
         <v>3327</v>
       </c>
       <c r="D9" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>4401</v>
       </c>
       <c r="E9" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>5122</v>
       </c>
       <c r="F9" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>7352</v>
       </c>
       <c r="G9" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>5449</v>
       </c>
       <c r="H9" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>5863</v>
       </c>
       <c r="I9" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>5781</v>
       </c>
       <c r="J9" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>7820</v>
       </c>
       <c r="K9" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>3317</v>
       </c>
       <c r="L9" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>4606</v>
       </c>
       <c r="M9" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>7185</v>
       </c>
       <c r="N9" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>8858</v>
       </c>
       <c r="O9" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>5893</v>
       </c>
       <c r="P9" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>5963</v>
       </c>
       <c r="Q9" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>8040</v>
       </c>
       <c r="R9" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>12775</v>
       </c>
       <c r="S9" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>11378</v>
       </c>
       <c r="T9" s="8">
-        <f t="shared" ref="T9:U9" si="28">T5-T6-T7-T8</f>
+        <f t="shared" ref="T9:U9" si="32">T5-T6-T7-T8</f>
         <v>12367</v>
       </c>
       <c r="U9" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>10423</v>
       </c>
       <c r="V9" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>12585</v>
       </c>
       <c r="W9" s="8">
-        <f t="shared" ref="W9:X9" si="29">W5-W6-W7-W8</f>
+        <f t="shared" ref="W9:X9" si="33">W5-W6-W7-W8</f>
         <v>8524</v>
       </c>
       <c r="X9" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>8358</v>
       </c>
       <c r="Y9" s="8">
-        <f t="shared" ref="Y9" si="30">Y5-Y6-Y7-Y8</f>
+        <f t="shared" ref="Y9" si="34">Y5-Y6-Y7-Y8</f>
         <v>5664</v>
       </c>
       <c r="Z9" s="8">
-        <f t="shared" ref="Z9" si="31">Z5-Z6-Z7-Z8</f>
+        <f t="shared" ref="Z9" si="35">Z5-Z6-Z7-Z8</f>
         <v>6399</v>
       </c>
       <c r="AA9" s="8">
-        <f t="shared" ref="AA9:AC9" si="32">AA5-AA6-AA7-AA8</f>
+        <f t="shared" ref="AA9:AC9" si="36">AA5-AA6-AA7-AA8</f>
         <v>7227</v>
       </c>
       <c r="AB9" s="8">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>9392</v>
       </c>
       <c r="AC9" s="8">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>14018</v>
       </c>
       <c r="AD9" s="8">
-        <f t="shared" ref="AD9" si="33">AD5-AD6-AD7-AD8</f>
+        <f t="shared" ref="AD9" si="37">AD5-AD6-AD7-AD8</f>
         <v>16384</v>
       </c>
       <c r="AE9" s="8">
-        <f t="shared" ref="AE9:AL9" si="34">AE5-AE6-AE7-AE8</f>
+        <f t="shared" ref="AE9:AP10" si="38">AE5-AE6-AE7-AE8</f>
         <v>13818</v>
       </c>
       <c r="AF9" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>14847</v>
       </c>
       <c r="AG9" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>17350</v>
       </c>
       <c r="AH9" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>21815</v>
       </c>
       <c r="AI9" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>17555</v>
       </c>
       <c r="AJ9" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>20441</v>
       </c>
       <c r="AK9" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>20535</v>
       </c>
       <c r="AL9" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>24745</v>
       </c>
-      <c r="AM9" s="8"/>
-      <c r="AN9" s="8"/>
-      <c r="AO9" s="8"/>
-      <c r="AP9" s="8"/>
+      <c r="AM9" s="8">
+        <f t="shared" si="38"/>
+        <v>20002.5</v>
+      </c>
+      <c r="AN9" s="8">
+        <f t="shared" si="38"/>
+        <v>23026.899999999994</v>
+      </c>
+      <c r="AO9" s="8">
+        <f t="shared" si="38"/>
+        <v>22831.103999999992</v>
+      </c>
+      <c r="AP9" s="8">
+        <f t="shared" si="38"/>
+        <v>26490.081999999995</v>
+      </c>
       <c r="AQ9" s="8"/>
       <c r="AR9" s="8">
-        <f t="shared" ref="AR9:BB9" si="35">AR5-AR6-AR7-AR8</f>
+        <f t="shared" ref="AR9:BB9" si="39">AR5-AR6-AR7-AR8</f>
         <v>1032</v>
       </c>
       <c r="AS9" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>1756</v>
       </c>
       <c r="AT9" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>538</v>
       </c>
       <c r="AU9" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>2804</v>
       </c>
       <c r="AV9" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>4994</v>
       </c>
       <c r="AW9" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>6225</v>
       </c>
       <c r="AX9" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>12427</v>
       </c>
       <c r="AY9" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>20202</v>
       </c>
       <c r="AZ9" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>24913</v>
       </c>
       <c r="BA9" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>23966</v>
       </c>
       <c r="BB9" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>32671</v>
       </c>
       <c r="BC9" s="8">
-        <f t="shared" ref="BC9:BL9" si="36">BC5-BC6-BC7-BC8</f>
+        <f t="shared" ref="BC9:BL9" si="40">BC5-BC6-BC7-BC8</f>
         <v>46753</v>
       </c>
       <c r="BD9" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>28945</v>
       </c>
       <c r="BE9" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>47021</v>
       </c>
       <c r="BF9" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>67830</v>
       </c>
       <c r="BG9" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>83276.299999999988</v>
       </c>
       <c r="BH9" s="8">
-        <f t="shared" si="36"/>
-        <v>95230.501249999987</v>
+        <f t="shared" si="40"/>
+        <v>92350.585999999981</v>
       </c>
       <c r="BI9" s="8">
-        <f t="shared" si="36"/>
-        <v>104572.62134999999</v>
+        <f t="shared" si="40"/>
+        <v>102653.05703999999</v>
       </c>
       <c r="BJ9" s="8">
-        <f t="shared" si="36"/>
-        <v>112669.92344700001</v>
+        <f t="shared" si="40"/>
+        <v>108753.34460279996</v>
       </c>
       <c r="BK9" s="8">
-        <f t="shared" si="36"/>
-        <v>118197.38140920001</v>
+        <f t="shared" si="40"/>
+        <v>115363.27237733998</v>
       </c>
       <c r="BL9" s="8">
-        <f t="shared" si="36"/>
-        <v>121896.12253913999</v>
+        <f t="shared" si="40"/>
+        <v>121196.9542386096</v>
       </c>
       <c r="BM9" s="8">
-        <f t="shared" ref="BM9:BQ9" si="37">BM5-BM6-BM7-BM8</f>
-        <v>124334.0449899228</v>
+        <f t="shared" ref="BM9:BQ9" si="41">BM5-BM6-BM7-BM8</f>
+        <v>126088.5883609291</v>
       </c>
       <c r="BN9" s="8">
-        <f t="shared" si="37"/>
-        <v>126820.72588972125</v>
+        <f t="shared" si="41"/>
+        <v>128610.36012814767</v>
       </c>
       <c r="BO9" s="8">
-        <f t="shared" si="37"/>
-        <v>129357.14040751566</v>
+        <f t="shared" si="41"/>
+        <v>131182.56733071065</v>
       </c>
       <c r="BP9" s="8">
-        <f t="shared" si="37"/>
-        <v>131944.28321566599</v>
+        <f t="shared" si="41"/>
+        <v>133806.21867732491</v>
       </c>
       <c r="BQ9" s="8">
-        <f t="shared" si="37"/>
-        <v>134583.16887997932</v>
+        <f t="shared" si="41"/>
+        <v>136482.34305087136</v>
       </c>
     </row>
     <row r="10" spans="2:176">
@@ -3677,10 +3762,18 @@
       <c r="AL10" s="4">
         <v>-609</v>
       </c>
-      <c r="AM10" s="4"/>
-      <c r="AN10" s="4"/>
-      <c r="AO10" s="4"/>
-      <c r="AP10" s="4"/>
+      <c r="AM10" s="4">
+        <v>-400</v>
+      </c>
+      <c r="AN10" s="4">
+        <v>-400</v>
+      </c>
+      <c r="AO10" s="4">
+        <v>-400</v>
+      </c>
+      <c r="AP10" s="4">
+        <v>-400</v>
+      </c>
       <c r="AQ10" s="4"/>
       <c r="AR10" s="4">
         <v>24</v>
@@ -3739,45 +3832,45 @@
         <f>SUM(AI10:AL10)</f>
         <v>-2657</v>
       </c>
-      <c r="BH10" s="4">
-        <f t="shared" ref="BH10:BL10" si="38">-BG13*0.02</f>
-        <v>-1527.7659999999998</v>
+      <c r="BH10" s="52">
+        <f>SUM(AM10:AP10)</f>
+        <v>-1600</v>
       </c>
       <c r="BI10" s="4">
-        <f t="shared" si="38"/>
-        <v>-1702.9455035999999</v>
+        <f t="shared" ref="BH10:BL10" si="42">-BH13*0.02</f>
+        <v>-1615.9500791999999</v>
       </c>
       <c r="BJ10" s="4">
-        <f t="shared" si="38"/>
-        <v>-1870.4499766233598</v>
+        <f t="shared" si="42"/>
+        <v>-1835.1345252979197</v>
       </c>
       <c r="BK10" s="4">
-        <f t="shared" si="38"/>
-        <v>-2015.9105722557713</v>
+        <f t="shared" si="42"/>
+        <v>-1946.3572326545229</v>
       </c>
       <c r="BL10" s="4">
-        <f t="shared" si="38"/>
-        <v>-2115.7539388736218</v>
+        <f t="shared" si="42"/>
+        <v>-2064.6494811359034</v>
       </c>
       <c r="BM10" s="4">
-        <f t="shared" ref="BM10" si="39">-BL13*0.02</f>
-        <v>-2182.6090260130395</v>
+        <f t="shared" ref="BM10" si="43">-BL13*0.02</f>
+        <v>-2169.404225467521</v>
       </c>
       <c r="BN10" s="4">
-        <f t="shared" ref="BN10" si="40">-BM13*0.02</f>
-        <v>-2226.6931106804709</v>
+        <f t="shared" ref="BN10" si="44">-BM13*0.02</f>
+        <v>-2257.3406695205808</v>
       </c>
       <c r="BO10" s="4">
-        <f t="shared" ref="BO10" si="41">-BN13*0.02</f>
-        <v>-2271.2345744070703</v>
+        <f t="shared" ref="BO10" si="45">-BN13*0.02</f>
+        <v>-2303.2715340389614</v>
       </c>
       <c r="BP10" s="4">
-        <f t="shared" ref="BP10" si="42">-BO13*0.02</f>
-        <v>-2316.6593996818401</v>
+        <f t="shared" ref="BP10" si="46">-BO13*0.02</f>
+        <v>-2349.350764019593</v>
       </c>
       <c r="BQ10" s="4">
-        <f t="shared" ref="BQ10" si="43">-BP13*0.02</f>
-        <v>-2362.9925900301218</v>
+        <f t="shared" ref="BQ10" si="47">-BP13*0.02</f>
+        <v>-2396.338022167663</v>
       </c>
     </row>
     <row r="11" spans="2:176" s="6" customFormat="1">
@@ -3785,257 +3878,269 @@
         <v>33</v>
       </c>
       <c r="C11" s="8">
-        <f t="shared" ref="C11:P11" si="44">C9-C10</f>
+        <f t="shared" ref="C11:P11" si="48">C9-C10</f>
         <v>3408</v>
       </c>
       <c r="D11" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>4488</v>
       </c>
       <c r="E11" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>5236</v>
       </c>
       <c r="F11" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>7462</v>
       </c>
       <c r="G11" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>5610</v>
       </c>
       <c r="H11" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>5868</v>
       </c>
       <c r="I11" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>5912</v>
       </c>
       <c r="J11" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>7971</v>
       </c>
       <c r="K11" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>3482</v>
       </c>
       <c r="L11" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>4812</v>
       </c>
       <c r="M11" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>7329</v>
       </c>
       <c r="N11" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>9169</v>
       </c>
       <c r="O11" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>5861</v>
       </c>
       <c r="P11" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>6131</v>
       </c>
       <c r="Q11" s="8">
-        <f t="shared" ref="Q11:V11" si="45">Q9-Q10</f>
+        <f t="shared" ref="Q11:V11" si="49">Q9-Q10</f>
         <v>8133</v>
       </c>
       <c r="R11" s="8">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>13055</v>
       </c>
       <c r="S11" s="8">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>11503</v>
       </c>
       <c r="T11" s="8">
-        <f t="shared" ref="T11:U11" si="46">T9-T10</f>
+        <f t="shared" ref="T11:U11" si="50">T9-T10</f>
         <v>12513</v>
       </c>
       <c r="U11" s="8">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>10565</v>
       </c>
       <c r="V11" s="8">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>12702</v>
       </c>
       <c r="W11" s="8">
-        <f t="shared" ref="W11:X11" si="47">W9-W10</f>
+        <f t="shared" ref="W11:X11" si="51">W9-W10</f>
         <v>8908</v>
       </c>
       <c r="X11" s="8">
-        <f t="shared" si="47"/>
+        <f t="shared" si="51"/>
         <v>8186</v>
       </c>
       <c r="Y11" s="8">
-        <f t="shared" ref="Y11" si="48">Y9-Y10</f>
+        <f t="shared" ref="Y11" si="52">Y9-Y10</f>
         <v>5576</v>
       </c>
       <c r="Z11" s="8">
-        <f t="shared" ref="Z11" si="49">Z9-Z10</f>
+        <f t="shared" ref="Z11" si="53">Z9-Z10</f>
         <v>6149</v>
       </c>
       <c r="AA11" s="8">
-        <f t="shared" ref="AA11:AC11" si="50">AA9-AA10</f>
+        <f t="shared" ref="AA11:AC11" si="54">AA9-AA10</f>
         <v>7307</v>
       </c>
       <c r="AB11" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v>9293</v>
       </c>
       <c r="AC11" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v>14290</v>
       </c>
       <c r="AD11" s="8">
-        <f t="shared" ref="AD11" si="51">AD9-AD10</f>
+        <f t="shared" ref="AD11" si="55">AD9-AD10</f>
         <v>16808</v>
       </c>
       <c r="AE11" s="8">
-        <f t="shared" ref="AE11:AL11" si="52">AE9-AE10</f>
+        <f t="shared" ref="AE11:AP11" si="56">AE9-AE10</f>
         <v>14183</v>
       </c>
       <c r="AF11" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v>15106</v>
       </c>
       <c r="AG11" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v>17822</v>
       </c>
       <c r="AH11" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v>22003</v>
       </c>
       <c r="AI11" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v>18382</v>
       </c>
       <c r="AJ11" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v>20534</v>
       </c>
       <c r="AK11" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v>21663</v>
       </c>
       <c r="AL11" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v>25354</v>
       </c>
-      <c r="AM11" s="8"/>
-      <c r="AN11" s="8"/>
-      <c r="AO11" s="8"/>
-      <c r="AP11" s="8"/>
+      <c r="AM11" s="8">
+        <f t="shared" si="56"/>
+        <v>20402.5</v>
+      </c>
+      <c r="AN11" s="8">
+        <f t="shared" si="56"/>
+        <v>23426.899999999994</v>
+      </c>
+      <c r="AO11" s="8">
+        <f t="shared" si="56"/>
+        <v>23231.103999999992</v>
+      </c>
+      <c r="AP11" s="8">
+        <f t="shared" si="56"/>
+        <v>26890.081999999995</v>
+      </c>
       <c r="AQ11" s="8"/>
       <c r="AR11" s="8">
-        <f t="shared" ref="AR11:BB11" si="53">AR9-AR10</f>
+        <f t="shared" ref="AR11:BB11" si="57">AR9-AR10</f>
         <v>1008</v>
       </c>
       <c r="AS11" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>1695</v>
       </c>
       <c r="AT11" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>494</v>
       </c>
       <c r="AU11" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>2754</v>
       </c>
       <c r="AV11" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>4910</v>
       </c>
       <c r="AW11" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>6194</v>
       </c>
       <c r="AX11" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>12518</v>
       </c>
       <c r="AY11" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>20594</v>
       </c>
       <c r="AZ11" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>25361</v>
       </c>
       <c r="BA11" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>24792</v>
       </c>
       <c r="BB11" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>33180</v>
       </c>
       <c r="BC11" s="8">
-        <f t="shared" ref="BC11:BL11" si="54">BC9-BC10</f>
+        <f t="shared" ref="BC11:BL11" si="58">BC9-BC10</f>
         <v>47283</v>
       </c>
       <c r="BD11" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>28819</v>
       </c>
       <c r="BE11" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>47698</v>
       </c>
       <c r="BF11" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>69114</v>
       </c>
       <c r="BG11" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>85933.299999999988</v>
       </c>
       <c r="BH11" s="8">
-        <f t="shared" si="54"/>
-        <v>96758.26724999999</v>
+        <f t="shared" si="58"/>
+        <v>93950.585999999981</v>
       </c>
       <c r="BI11" s="8">
-        <f t="shared" si="54"/>
-        <v>106275.56685359999</v>
+        <f t="shared" si="58"/>
+        <v>104269.00711919999</v>
       </c>
       <c r="BJ11" s="8">
-        <f t="shared" si="54"/>
-        <v>114540.37342362337</v>
+        <f t="shared" si="58"/>
+        <v>110588.47912809788</v>
       </c>
       <c r="BK11" s="8">
-        <f t="shared" si="54"/>
-        <v>120213.29198145578</v>
+        <f t="shared" si="58"/>
+        <v>117309.6296099945</v>
       </c>
       <c r="BL11" s="8">
-        <f t="shared" si="54"/>
-        <v>124011.87647801361</v>
+        <f t="shared" si="58"/>
+        <v>123261.6037197455</v>
       </c>
       <c r="BM11" s="8">
-        <f t="shared" ref="BM11:BQ11" si="55">BM9-BM10</f>
-        <v>126516.65401593584</v>
+        <f t="shared" ref="BM11:BQ11" si="59">BM9-BM10</f>
+        <v>128257.99258639662</v>
       </c>
       <c r="BN11" s="8">
-        <f t="shared" si="55"/>
-        <v>129047.41900040171</v>
+        <f t="shared" si="59"/>
+        <v>130867.70079766825</v>
       </c>
       <c r="BO11" s="8">
-        <f t="shared" si="55"/>
-        <v>131628.37498192274</v>
+        <f t="shared" si="59"/>
+        <v>133485.83886474962</v>
       </c>
       <c r="BP11" s="8">
-        <f t="shared" si="55"/>
-        <v>134260.94261534783</v>
+        <f t="shared" si="59"/>
+        <v>136155.5694413445</v>
       </c>
       <c r="BQ11" s="8">
-        <f t="shared" si="55"/>
-        <v>136946.16147000945</v>
+        <f t="shared" si="59"/>
+        <v>138878.68107303901</v>
       </c>
     </row>
     <row r="12" spans="2:176">
@@ -4155,10 +4260,22 @@
       <c r="AL12" s="4">
         <v>2586</v>
       </c>
-      <c r="AM12" s="4"/>
-      <c r="AN12" s="4"/>
-      <c r="AO12" s="4"/>
-      <c r="AP12" s="4"/>
+      <c r="AM12" s="4">
+        <f>AM11*0.14</f>
+        <v>2856.3500000000004</v>
+      </c>
+      <c r="AN12" s="4">
+        <f t="shared" ref="AN12:AP12" si="60">AN11*0.14</f>
+        <v>3279.7659999999996</v>
+      </c>
+      <c r="AO12" s="4">
+        <f t="shared" si="60"/>
+        <v>3252.3545599999993</v>
+      </c>
+      <c r="AP12" s="4">
+        <f t="shared" si="60"/>
+        <v>3764.6114799999996</v>
+      </c>
       <c r="AQ12" s="4"/>
       <c r="AR12" s="4">
         <v>402</v>
@@ -4217,45 +4334,45 @@
         <f>SUM(AI12:AL12)</f>
         <v>9545</v>
       </c>
-      <c r="BH12" s="4">
-        <f>BH11*0.12</f>
-        <v>11610.992069999998</v>
+      <c r="BH12" s="52">
+        <f>SUM(AM12:AP12)</f>
+        <v>13153.082039999999</v>
       </c>
       <c r="BI12" s="4">
-        <f t="shared" ref="BI12:BQ12" si="56">BI11*0.12</f>
-        <v>12753.068022431999</v>
+        <f t="shared" ref="BI12:BQ12" si="61">BI11*0.12</f>
+        <v>12512.280854303997</v>
       </c>
       <c r="BJ12" s="4">
-        <f t="shared" si="56"/>
-        <v>13744.844810834804</v>
+        <f t="shared" si="61"/>
+        <v>13270.617495371745</v>
       </c>
       <c r="BK12" s="4">
-        <f t="shared" si="56"/>
-        <v>14425.595037774694</v>
+        <f t="shared" si="61"/>
+        <v>14077.15555319934</v>
       </c>
       <c r="BL12" s="4">
-        <f t="shared" si="56"/>
-        <v>14881.425177361632</v>
+        <f t="shared" si="61"/>
+        <v>14791.39244636946</v>
       </c>
       <c r="BM12" s="4">
-        <f t="shared" si="56"/>
-        <v>15181.9984819123</v>
+        <f t="shared" si="61"/>
+        <v>15390.959110367594</v>
       </c>
       <c r="BN12" s="4">
-        <f t="shared" si="56"/>
-        <v>15485.690280048206</v>
+        <f t="shared" si="61"/>
+        <v>15704.12409572019</v>
       </c>
       <c r="BO12" s="4">
-        <f t="shared" si="56"/>
-        <v>15795.404997830728</v>
+        <f t="shared" si="61"/>
+        <v>16018.300663769953</v>
       </c>
       <c r="BP12" s="4">
-        <f t="shared" si="56"/>
-        <v>16111.313113841739</v>
+        <f t="shared" si="61"/>
+        <v>16338.668332961339</v>
       </c>
       <c r="BQ12" s="4">
-        <f t="shared" si="56"/>
-        <v>16433.539376401135</v>
+        <f t="shared" si="61"/>
+        <v>16665.441728764679</v>
       </c>
     </row>
     <row r="13" spans="2:176" s="6" customFormat="1">
@@ -4263,685 +4380,697 @@
         <v>35</v>
       </c>
       <c r="C13" s="8">
-        <f t="shared" ref="C13:P13" si="57">C11-C12</f>
+        <f t="shared" ref="C13:P13" si="62">C11-C12</f>
         <v>3059</v>
       </c>
       <c r="D13" s="8">
-        <f t="shared" si="57"/>
+        <f t="shared" si="62"/>
         <v>3890</v>
       </c>
       <c r="E13" s="8">
-        <f t="shared" si="57"/>
+        <f t="shared" si="62"/>
         <v>4707</v>
       </c>
       <c r="F13" s="8">
-        <f t="shared" si="57"/>
+        <f t="shared" si="62"/>
         <v>3548</v>
       </c>
       <c r="G13" s="8">
-        <f t="shared" si="57"/>
+        <f t="shared" si="62"/>
         <v>4987</v>
       </c>
       <c r="H13" s="8">
-        <f t="shared" si="57"/>
+        <f t="shared" si="62"/>
         <v>5106</v>
       </c>
       <c r="I13" s="8">
-        <f t="shared" si="57"/>
+        <f t="shared" si="62"/>
         <v>5137</v>
       </c>
       <c r="J13" s="8">
-        <f t="shared" si="57"/>
+        <f t="shared" si="62"/>
         <v>6882</v>
       </c>
       <c r="K13" s="8">
-        <f t="shared" si="57"/>
+        <f t="shared" si="62"/>
         <v>2429</v>
       </c>
       <c r="L13" s="8">
-        <f t="shared" si="57"/>
+        <f t="shared" si="62"/>
         <v>2596</v>
       </c>
       <c r="M13" s="8">
-        <f t="shared" si="57"/>
+        <f t="shared" si="62"/>
         <v>6091</v>
       </c>
       <c r="N13" s="8">
-        <f t="shared" si="57"/>
+        <f t="shared" si="62"/>
         <v>7349</v>
       </c>
       <c r="O13" s="8">
-        <f t="shared" si="57"/>
+        <f t="shared" si="62"/>
         <v>4902</v>
       </c>
       <c r="P13" s="8">
-        <f t="shared" si="57"/>
+        <f t="shared" si="62"/>
         <v>5178</v>
       </c>
       <c r="Q13" s="8">
-        <f t="shared" ref="Q13:R13" si="58">Q11-Q12</f>
+        <f t="shared" ref="Q13:R13" si="63">Q11-Q12</f>
         <v>7846</v>
       </c>
       <c r="R13" s="8">
-        <f t="shared" si="58"/>
+        <f t="shared" si="63"/>
         <v>11219</v>
       </c>
       <c r="S13" s="8">
-        <f t="shared" ref="S13:V13" si="59">S11-S12</f>
+        <f t="shared" ref="S13:V13" si="64">S11-S12</f>
         <v>9497</v>
       </c>
       <c r="T13" s="8">
-        <f t="shared" ref="T13:U13" si="60">T11-T12</f>
+        <f t="shared" ref="T13:U13" si="65">T11-T12</f>
         <v>10394</v>
       </c>
       <c r="U13" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="65"/>
         <v>9194</v>
       </c>
       <c r="V13" s="8">
-        <f t="shared" si="59"/>
+        <f t="shared" si="64"/>
         <v>10285</v>
       </c>
       <c r="W13" s="8">
-        <f t="shared" ref="W13:X13" si="61">W11-W12</f>
+        <f t="shared" ref="W13:X13" si="66">W11-W12</f>
         <v>7465</v>
       </c>
       <c r="X13" s="8">
-        <f t="shared" si="61"/>
+        <f t="shared" si="66"/>
         <v>6687</v>
       </c>
       <c r="Y13" s="8">
-        <f t="shared" ref="Y13" si="62">Y11-Y12</f>
+        <f t="shared" ref="Y13" si="67">Y11-Y12</f>
         <v>4395</v>
       </c>
       <c r="Z13" s="8">
-        <f t="shared" ref="Z13" si="63">Z11-Z12</f>
+        <f t="shared" ref="Z13" si="68">Z11-Z12</f>
         <v>4652</v>
       </c>
       <c r="AA13" s="8">
-        <f t="shared" ref="AA13:AC13" si="64">AA11-AA12</f>
+        <f t="shared" ref="AA13:AC13" si="69">AA11-AA12</f>
         <v>5709</v>
       </c>
       <c r="AB13" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>7788</v>
       </c>
       <c r="AC13" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>11853</v>
       </c>
       <c r="AD13" s="8">
-        <f t="shared" ref="AD13" si="65">AD11-AD12</f>
+        <f t="shared" ref="AD13" si="70">AD11-AD12</f>
         <v>14017</v>
       </c>
       <c r="AE13" s="8">
-        <f t="shared" ref="AE13" si="66">AE11-AE12</f>
+        <f t="shared" ref="AE13" si="71">AE11-AE12</f>
         <v>12369</v>
       </c>
       <c r="AF13" s="8">
-        <f t="shared" ref="AF13:AH13" si="67">AF11-AF12</f>
+        <f t="shared" ref="AF13:AH13" si="72">AF11-AF12</f>
         <v>13465</v>
       </c>
       <c r="AG13" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="72"/>
         <v>15688</v>
       </c>
       <c r="AH13" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="72"/>
         <v>19288</v>
       </c>
       <c r="AI13" s="8">
-        <f t="shared" ref="AI13:AL13" si="68">AI11-AI12</f>
+        <f t="shared" ref="AI13:AL13" si="73">AI11-AI12</f>
         <v>16644</v>
       </c>
       <c r="AJ13" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="73"/>
         <v>18337</v>
       </c>
       <c r="AK13" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="73"/>
         <v>18639</v>
       </c>
       <c r="AL13" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="73"/>
         <v>22768</v>
       </c>
-      <c r="AM13" s="8"/>
-      <c r="AN13" s="8"/>
-      <c r="AO13" s="8"/>
-      <c r="AP13" s="8"/>
+      <c r="AM13" s="8">
+        <f t="shared" ref="AM13:AP13" si="74">AM11-AM12</f>
+        <v>17546.150000000001</v>
+      </c>
+      <c r="AN13" s="8">
+        <f t="shared" si="74"/>
+        <v>20147.133999999995</v>
+      </c>
+      <c r="AO13" s="8">
+        <f t="shared" si="74"/>
+        <v>19978.749439999992</v>
+      </c>
+      <c r="AP13" s="8">
+        <f t="shared" si="74"/>
+        <v>23125.470519999995</v>
+      </c>
       <c r="AQ13" s="8"/>
       <c r="AR13" s="8">
-        <f t="shared" ref="AR13:BB13" si="69">AR11-AR12</f>
+        <f t="shared" ref="AR13:BB13" si="75">AR11-AR12</f>
         <v>606</v>
       </c>
       <c r="AS13" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="75"/>
         <v>1000</v>
       </c>
       <c r="AT13" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="75"/>
         <v>53</v>
       </c>
       <c r="AU13" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="75"/>
         <v>1500</v>
       </c>
       <c r="AV13" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="75"/>
         <v>2940</v>
       </c>
       <c r="AW13" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="75"/>
         <v>3688</v>
       </c>
       <c r="AX13" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="75"/>
         <v>10217</v>
       </c>
       <c r="AY13" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="75"/>
         <v>15204</v>
       </c>
       <c r="AZ13" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="75"/>
         <v>22112</v>
       </c>
       <c r="BA13" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="75"/>
         <v>18465</v>
       </c>
       <c r="BB13" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="75"/>
         <v>29145</v>
       </c>
       <c r="BC13" s="8">
-        <f t="shared" ref="BC13:BL13" si="70">BC11-BC12</f>
+        <f t="shared" ref="BC13:BL13" si="76">BC11-BC12</f>
         <v>39370</v>
       </c>
       <c r="BD13" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="76"/>
         <v>23199</v>
       </c>
       <c r="BE13" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="76"/>
         <v>39367</v>
       </c>
       <c r="BF13" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="76"/>
         <v>60810</v>
       </c>
       <c r="BG13" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="76"/>
         <v>76388.299999999988</v>
       </c>
       <c r="BH13" s="8">
-        <f t="shared" si="70"/>
-        <v>85147.275179999997</v>
+        <f t="shared" si="76"/>
+        <v>80797.503959999987</v>
       </c>
       <c r="BI13" s="8">
-        <f t="shared" si="70"/>
-        <v>93522.498831167992</v>
+        <f t="shared" si="76"/>
+        <v>91756.726264895988</v>
       </c>
       <c r="BJ13" s="8">
-        <f t="shared" si="70"/>
-        <v>100795.52861278856</v>
+        <f t="shared" si="76"/>
+        <v>97317.861632726141</v>
       </c>
       <c r="BK13" s="8">
-        <f t="shared" si="70"/>
-        <v>105787.69694368109</v>
+        <f t="shared" si="76"/>
+        <v>103232.47405679517</v>
       </c>
       <c r="BL13" s="8">
-        <f t="shared" si="70"/>
-        <v>109130.45130065198</v>
+        <f t="shared" si="76"/>
+        <v>108470.21127337604</v>
       </c>
       <c r="BM13" s="8">
-        <f t="shared" ref="BM13:BQ13" si="71">BM11-BM12</f>
-        <v>111334.65553402354</v>
+        <f t="shared" ref="BM13:BQ13" si="77">BM11-BM12</f>
+        <v>112867.03347602903</v>
       </c>
       <c r="BN13" s="8">
-        <f t="shared" si="71"/>
-        <v>113561.72872035351</v>
+        <f t="shared" si="77"/>
+        <v>115163.57670194806</v>
       </c>
       <c r="BO13" s="8">
-        <f t="shared" si="71"/>
-        <v>115832.96998409201</v>
+        <f t="shared" si="77"/>
+        <v>117467.53820097966</v>
       </c>
       <c r="BP13" s="8">
-        <f t="shared" si="71"/>
-        <v>118149.62950150609</v>
+        <f t="shared" si="77"/>
+        <v>119816.90110838316</v>
       </c>
       <c r="BQ13" s="8">
-        <f t="shared" si="71"/>
-        <v>120512.62209360831</v>
+        <f t="shared" si="77"/>
+        <v>122213.23934427433</v>
       </c>
       <c r="BR13" s="6">
         <f>BQ13*(1+$BT$18)</f>
-        <v>119307.49587267223</v>
+        <v>120991.10695083158</v>
       </c>
       <c r="BS13" s="6">
-        <f t="shared" ref="BS13:ED13" si="72">BR13*(1+$BT$18)</f>
-        <v>118114.42091394551</v>
+        <f t="shared" ref="BS13:ED13" si="78">BR13*(1+$BT$18)</f>
+        <v>119781.19588132326</v>
       </c>
       <c r="BT13" s="6">
-        <f t="shared" si="72"/>
-        <v>116933.27670480605</v>
+        <f t="shared" si="78"/>
+        <v>118583.38392251002</v>
       </c>
       <c r="BU13" s="6">
-        <f t="shared" si="72"/>
-        <v>115763.94393775798</v>
+        <f t="shared" si="78"/>
+        <v>117397.55008328492</v>
       </c>
       <c r="BV13" s="6">
-        <f t="shared" si="72"/>
-        <v>114606.3044983804</v>
+        <f t="shared" si="78"/>
+        <v>116223.57458245207</v>
       </c>
       <c r="BW13" s="6">
-        <f t="shared" si="72"/>
-        <v>113460.24145339659</v>
+        <f t="shared" si="78"/>
+        <v>115061.33883662755</v>
       </c>
       <c r="BX13" s="6">
-        <f t="shared" si="72"/>
-        <v>112325.63903886263</v>
+        <f t="shared" si="78"/>
+        <v>113910.72544826128</v>
       </c>
       <c r="BY13" s="6">
-        <f t="shared" si="72"/>
-        <v>111202.382648474</v>
+        <f t="shared" si="78"/>
+        <v>112771.61819377866</v>
       </c>
       <c r="BZ13" s="6">
-        <f t="shared" si="72"/>
-        <v>110090.35882198926</v>
+        <f t="shared" si="78"/>
+        <v>111643.90201184087</v>
       </c>
       <c r="CA13" s="6">
-        <f t="shared" si="72"/>
-        <v>108989.45523376936</v>
+        <f t="shared" si="78"/>
+        <v>110527.46299172245</v>
       </c>
       <c r="CB13" s="6">
-        <f t="shared" si="72"/>
-        <v>107899.56068143167</v>
+        <f t="shared" si="78"/>
+        <v>109422.18836180522</v>
       </c>
       <c r="CC13" s="6">
-        <f t="shared" si="72"/>
-        <v>106820.56507461735</v>
+        <f t="shared" si="78"/>
+        <v>108327.96647818717</v>
       </c>
       <c r="CD13" s="6">
-        <f t="shared" si="72"/>
-        <v>105752.35942387118</v>
+        <f t="shared" si="78"/>
+        <v>107244.68681340529</v>
       </c>
       <c r="CE13" s="6">
-        <f t="shared" si="72"/>
-        <v>104694.83582963247</v>
+        <f t="shared" si="78"/>
+        <v>106172.23994527124</v>
       </c>
       <c r="CF13" s="6">
-        <f t="shared" si="72"/>
-        <v>103647.88747133614</v>
+        <f t="shared" si="78"/>
+        <v>105110.51754581853</v>
       </c>
       <c r="CG13" s="6">
-        <f t="shared" si="72"/>
-        <v>102611.40859662279</v>
+        <f t="shared" si="78"/>
+        <v>104059.41237036034</v>
       </c>
       <c r="CH13" s="6">
-        <f t="shared" si="72"/>
-        <v>101585.29451065656</v>
+        <f t="shared" si="78"/>
+        <v>103018.81824665674</v>
       </c>
       <c r="CI13" s="6">
-        <f t="shared" si="72"/>
-        <v>100569.44156554999</v>
+        <f t="shared" si="78"/>
+        <v>101988.63006419018</v>
       </c>
       <c r="CJ13" s="6">
-        <f t="shared" si="72"/>
-        <v>99563.747149894494</v>
+        <f t="shared" si="78"/>
+        <v>100968.74376354828</v>
       </c>
       <c r="CK13" s="6">
-        <f t="shared" si="72"/>
-        <v>98568.109678395544</v>
+        <f t="shared" si="78"/>
+        <v>99959.056325912796</v>
       </c>
       <c r="CL13" s="6">
-        <f t="shared" si="72"/>
-        <v>97582.428581611588</v>
+        <f t="shared" si="78"/>
+        <v>98959.465762653665</v>
       </c>
       <c r="CM13" s="6">
-        <f t="shared" si="72"/>
-        <v>96606.604295795478</v>
+        <f t="shared" si="78"/>
+        <v>97969.871105027123</v>
       </c>
       <c r="CN13" s="6">
-        <f t="shared" si="72"/>
-        <v>95640.538252837519</v>
+        <f t="shared" si="78"/>
+        <v>96990.172393976856</v>
       </c>
       <c r="CO13" s="6">
-        <f t="shared" si="72"/>
-        <v>94684.132870309142</v>
+        <f t="shared" si="78"/>
+        <v>96020.270670037091</v>
       </c>
       <c r="CP13" s="6">
-        <f t="shared" si="72"/>
-        <v>93737.291541606057</v>
+        <f t="shared" si="78"/>
+        <v>95060.067963336725</v>
       </c>
       <c r="CQ13" s="6">
-        <f t="shared" si="72"/>
-        <v>92799.918626189989</v>
+        <f t="shared" si="78"/>
+        <v>94109.467283703358</v>
       </c>
       <c r="CR13" s="6">
-        <f t="shared" si="72"/>
-        <v>91871.919439928082</v>
+        <f t="shared" si="78"/>
+        <v>93168.372610866325</v>
       </c>
       <c r="CS13" s="6">
-        <f t="shared" si="72"/>
-        <v>90953.200245528802</v>
+        <f t="shared" si="78"/>
+        <v>92236.688884757663</v>
       </c>
       <c r="CT13" s="6">
-        <f t="shared" si="72"/>
-        <v>90043.668243073509</v>
+        <f t="shared" si="78"/>
+        <v>91314.321995910082</v>
       </c>
       <c r="CU13" s="6">
-        <f t="shared" si="72"/>
-        <v>89143.231560642773</v>
+        <f t="shared" si="78"/>
+        <v>90401.178775950975</v>
       </c>
       <c r="CV13" s="6">
-        <f t="shared" si="72"/>
-        <v>88251.799245036338</v>
+        <f t="shared" si="78"/>
+        <v>89497.166988191471</v>
       </c>
       <c r="CW13" s="6">
-        <f t="shared" si="72"/>
-        <v>87369.281252585977</v>
+        <f t="shared" si="78"/>
+        <v>88602.195318309561</v>
       </c>
       <c r="CX13" s="6">
-        <f t="shared" si="72"/>
-        <v>86495.588440060121</v>
+        <f t="shared" si="78"/>
+        <v>87716.173365126466</v>
       </c>
       <c r="CY13" s="6">
-        <f t="shared" si="72"/>
-        <v>85630.632555659526</v>
+        <f t="shared" si="78"/>
+        <v>86839.011631475194</v>
       </c>
       <c r="CZ13" s="6">
-        <f t="shared" si="72"/>
-        <v>84774.326230102932</v>
+        <f t="shared" si="78"/>
+        <v>85970.621515160441</v>
       </c>
       <c r="DA13" s="6">
-        <f t="shared" si="72"/>
-        <v>83926.582967801907</v>
+        <f t="shared" si="78"/>
+        <v>85110.915300008841</v>
       </c>
       <c r="DB13" s="6">
-        <f t="shared" si="72"/>
-        <v>83087.317138123894</v>
+        <f t="shared" si="78"/>
+        <v>84259.806147008756</v>
       </c>
       <c r="DC13" s="6">
-        <f t="shared" si="72"/>
-        <v>82256.443966742649</v>
+        <f t="shared" si="78"/>
+        <v>83417.208085538674</v>
       </c>
       <c r="DD13" s="6">
-        <f t="shared" si="72"/>
-        <v>81433.879527075216</v>
+        <f t="shared" si="78"/>
+        <v>82583.036004683279</v>
       </c>
       <c r="DE13" s="6">
-        <f t="shared" si="72"/>
-        <v>80619.54073180446</v>
+        <f t="shared" si="78"/>
+        <v>81757.205644636444</v>
       </c>
       <c r="DF13" s="6">
-        <f t="shared" si="72"/>
-        <v>79813.345324486421</v>
+        <f t="shared" si="78"/>
+        <v>80939.633588190074</v>
       </c>
       <c r="DG13" s="6">
-        <f t="shared" si="72"/>
-        <v>79015.211871241554</v>
+        <f t="shared" si="78"/>
+        <v>80130.237252308172</v>
       </c>
       <c r="DH13" s="6">
-        <f t="shared" si="72"/>
-        <v>78225.059752529138</v>
+        <f t="shared" si="78"/>
+        <v>79328.934879785083</v>
       </c>
       <c r="DI13" s="6">
-        <f t="shared" si="72"/>
-        <v>77442.809155003852</v>
+        <f t="shared" si="78"/>
+        <v>78535.645530987225</v>
       </c>
       <c r="DJ13" s="6">
-        <f t="shared" si="72"/>
-        <v>76668.381063453809</v>
+        <f t="shared" si="78"/>
+        <v>77750.289075677356</v>
       </c>
       <c r="DK13" s="6">
-        <f t="shared" si="72"/>
-        <v>75901.697252819271</v>
+        <f t="shared" si="78"/>
+        <v>76972.78618492058</v>
       </c>
       <c r="DL13" s="6">
-        <f t="shared" si="72"/>
-        <v>75142.680280291082</v>
+        <f t="shared" si="78"/>
+        <v>76203.058323071367</v>
       </c>
       <c r="DM13" s="6">
-        <f t="shared" si="72"/>
-        <v>74391.253477488164</v>
+        <f t="shared" si="78"/>
+        <v>75441.027739840647</v>
       </c>
       <c r="DN13" s="6">
-        <f t="shared" si="72"/>
-        <v>73647.340942713286</v>
+        <f t="shared" si="78"/>
+        <v>74686.617462442242</v>
       </c>
       <c r="DO13" s="6">
-        <f t="shared" si="72"/>
-        <v>72910.867533286146</v>
+        <f t="shared" si="78"/>
+        <v>73939.751287817824</v>
       </c>
       <c r="DP13" s="6">
-        <f t="shared" si="72"/>
-        <v>72181.758857953289</v>
+        <f t="shared" si="78"/>
+        <v>73200.353774939649</v>
       </c>
       <c r="DQ13" s="6">
-        <f t="shared" si="72"/>
-        <v>71459.941269373754</v>
+        <f t="shared" si="78"/>
+        <v>72468.350237190258</v>
       </c>
       <c r="DR13" s="6">
-        <f t="shared" si="72"/>
-        <v>70745.34185668001</v>
+        <f t="shared" si="78"/>
+        <v>71743.666734818355</v>
       </c>
       <c r="DS13" s="6">
-        <f t="shared" si="72"/>
-        <v>70037.888438113208</v>
+        <f t="shared" si="78"/>
+        <v>71026.230067470169</v>
       </c>
       <c r="DT13" s="6">
-        <f t="shared" si="72"/>
-        <v>69337.509553732074</v>
+        <f t="shared" si="78"/>
+        <v>70315.967766795467</v>
       </c>
       <c r="DU13" s="6">
-        <f t="shared" si="72"/>
-        <v>68644.134458194749</v>
+        <f t="shared" si="78"/>
+        <v>69612.808089127517</v>
       </c>
       <c r="DV13" s="6">
-        <f t="shared" si="72"/>
-        <v>67957.693113612797</v>
+        <f t="shared" si="78"/>
+        <v>68916.680008236246</v>
       </c>
       <c r="DW13" s="6">
-        <f t="shared" si="72"/>
-        <v>67278.116182476675</v>
+        <f t="shared" si="78"/>
+        <v>68227.513208153876</v>
       </c>
       <c r="DX13" s="6">
-        <f t="shared" si="72"/>
-        <v>66605.33502065191</v>
+        <f t="shared" si="78"/>
+        <v>67545.238076072332</v>
       </c>
       <c r="DY13" s="6">
-        <f t="shared" si="72"/>
-        <v>65939.281670445387</v>
+        <f t="shared" si="78"/>
+        <v>66869.785695311613</v>
       </c>
       <c r="DZ13" s="6">
-        <f t="shared" si="72"/>
-        <v>65279.888853740929</v>
+        <f t="shared" si="78"/>
+        <v>66201.087838358493</v>
       </c>
       <c r="EA13" s="6">
-        <f t="shared" si="72"/>
-        <v>64627.089965203522</v>
+        <f t="shared" si="78"/>
+        <v>65539.076959974904</v>
       </c>
       <c r="EB13" s="6">
-        <f t="shared" si="72"/>
-        <v>63980.819065551485</v>
+        <f t="shared" si="78"/>
+        <v>64883.686190375156</v>
       </c>
       <c r="EC13" s="6">
-        <f t="shared" si="72"/>
-        <v>63341.010874895968</v>
+        <f t="shared" si="78"/>
+        <v>64234.849328471406</v>
       </c>
       <c r="ED13" s="6">
-        <f t="shared" si="72"/>
-        <v>62707.600766147007</v>
+        <f t="shared" si="78"/>
+        <v>63592.500835186693</v>
       </c>
       <c r="EE13" s="6">
-        <f t="shared" ref="EE13:FT13" si="73">ED13*(1+$BT$18)</f>
-        <v>62080.524758485539</v>
+        <f t="shared" ref="EE13:FT13" si="79">ED13*(1+$BT$18)</f>
+        <v>62956.575826834822</v>
       </c>
       <c r="EF13" s="6">
-        <f t="shared" si="73"/>
-        <v>61459.719510900686</v>
+        <f t="shared" si="79"/>
+        <v>62327.010068566473</v>
       </c>
       <c r="EG13" s="6">
-        <f t="shared" si="73"/>
-        <v>60845.122315791676</v>
+        <f t="shared" si="79"/>
+        <v>61703.739967880807</v>
       </c>
       <c r="EH13" s="6">
-        <f t="shared" si="73"/>
-        <v>60236.671092633762</v>
+        <f t="shared" si="79"/>
+        <v>61086.702568201996</v>
       </c>
       <c r="EI13" s="6">
-        <f t="shared" si="73"/>
-        <v>59634.304381707421</v>
+        <f t="shared" si="79"/>
+        <v>60475.835542519977</v>
       </c>
       <c r="EJ13" s="6">
-        <f t="shared" si="73"/>
-        <v>59037.961337890345</v>
+        <f t="shared" si="79"/>
+        <v>59871.077187094779</v>
       </c>
       <c r="EK13" s="6">
-        <f t="shared" si="73"/>
-        <v>58447.581724511438</v>
+        <f t="shared" si="79"/>
+        <v>59272.366415223834</v>
       </c>
       <c r="EL13" s="6">
-        <f t="shared" si="73"/>
-        <v>57863.105907266319</v>
+        <f t="shared" si="79"/>
+        <v>58679.642751071595</v>
       </c>
       <c r="EM13" s="6">
-        <f t="shared" si="73"/>
-        <v>57284.474848193655</v>
+        <f t="shared" si="79"/>
+        <v>58092.84632356088</v>
       </c>
       <c r="EN13" s="6">
-        <f t="shared" si="73"/>
-        <v>56711.630099711721</v>
+        <f t="shared" si="79"/>
+        <v>57511.917860325273</v>
       </c>
       <c r="EO13" s="6">
-        <f t="shared" si="73"/>
-        <v>56144.513798714601</v>
+        <f t="shared" si="79"/>
+        <v>56936.798681722023</v>
       </c>
       <c r="EP13" s="6">
-        <f t="shared" si="73"/>
-        <v>55583.068660727455</v>
+        <f t="shared" si="79"/>
+        <v>56367.430694904804</v>
       </c>
       <c r="EQ13" s="6">
-        <f t="shared" si="73"/>
-        <v>55027.23797412018</v>
+        <f t="shared" si="79"/>
+        <v>55803.756387955757</v>
       </c>
       <c r="ER13" s="6">
-        <f t="shared" si="73"/>
-        <v>54476.965594378977</v>
+        <f t="shared" si="79"/>
+        <v>55245.718824076197</v>
       </c>
       <c r="ES13" s="6">
-        <f t="shared" si="73"/>
-        <v>53932.195938435187</v>
+        <f t="shared" si="79"/>
+        <v>54693.261635835435</v>
       </c>
       <c r="ET13" s="6">
-        <f t="shared" si="73"/>
-        <v>53392.873979050833</v>
+        <f t="shared" si="79"/>
+        <v>54146.329019477082</v>
       </c>
       <c r="EU13" s="6">
-        <f t="shared" si="73"/>
-        <v>52858.945239260327</v>
+        <f t="shared" si="79"/>
+        <v>53604.865729282312</v>
       </c>
       <c r="EV13" s="6">
-        <f t="shared" si="73"/>
-        <v>52330.355786867724</v>
+        <f t="shared" si="79"/>
+        <v>53068.817071989492</v>
       </c>
       <c r="EW13" s="6">
-        <f t="shared" si="73"/>
-        <v>51807.052228999048</v>
+        <f t="shared" si="79"/>
+        <v>52538.1289012696</v>
       </c>
       <c r="EX13" s="6">
-        <f t="shared" si="73"/>
-        <v>51288.981706709055</v>
+        <f t="shared" si="79"/>
+        <v>52012.747612256906</v>
       </c>
       <c r="EY13" s="6">
-        <f t="shared" si="73"/>
-        <v>50776.091889641961</v>
+        <f t="shared" si="79"/>
+        <v>51492.620136134334</v>
       </c>
       <c r="EZ13" s="6">
-        <f t="shared" si="73"/>
-        <v>50268.330970745541</v>
+        <f t="shared" si="79"/>
+        <v>50977.693934772993</v>
       </c>
       <c r="FA13" s="6">
-        <f t="shared" si="73"/>
-        <v>49765.647661038085</v>
+        <f t="shared" si="79"/>
+        <v>50467.916995425265</v>
       </c>
       <c r="FB13" s="6">
-        <f t="shared" si="73"/>
-        <v>49267.991184427701</v>
+        <f t="shared" si="79"/>
+        <v>49963.237825471013</v>
       </c>
       <c r="FC13" s="6">
-        <f t="shared" si="73"/>
-        <v>48775.311272583422</v>
+        <f t="shared" si="79"/>
+        <v>49463.605447216301</v>
       </c>
       <c r="FD13" s="6">
-        <f t="shared" si="73"/>
-        <v>48287.558159857588</v>
+        <f t="shared" si="79"/>
+        <v>48968.96939274414</v>
       </c>
       <c r="FE13" s="6">
-        <f t="shared" si="73"/>
-        <v>47804.682578259009</v>
+        <f t="shared" si="79"/>
+        <v>48479.279698816696</v>
       </c>
       <c r="FF13" s="6">
-        <f t="shared" si="73"/>
-        <v>47326.635752476417</v>
+        <f t="shared" si="79"/>
+        <v>47994.486901828532</v>
       </c>
       <c r="FG13" s="6">
-        <f t="shared" si="73"/>
-        <v>46853.369394951653</v>
+        <f t="shared" si="79"/>
+        <v>47514.542032810248</v>
       </c>
       <c r="FH13" s="6">
-        <f t="shared" si="73"/>
-        <v>46384.835701002135</v>
+        <f t="shared" si="79"/>
+        <v>47039.396612482145</v>
       </c>
       <c r="FI13" s="6">
-        <f t="shared" si="73"/>
-        <v>45920.987343992114</v>
+        <f t="shared" si="79"/>
+        <v>46569.002646357323</v>
       </c>
       <c r="FJ13" s="6">
-        <f t="shared" si="73"/>
-        <v>45461.777470552195</v>
+        <f t="shared" si="79"/>
+        <v>46103.312619893746</v>
       </c>
       <c r="FK13" s="6">
-        <f t="shared" si="73"/>
-        <v>45007.159695846676</v>
+        <f t="shared" si="79"/>
+        <v>45642.279493694805</v>
       </c>
       <c r="FL13" s="6">
-        <f t="shared" si="73"/>
-        <v>44557.088098888205</v>
+        <f t="shared" si="79"/>
+        <v>45185.85669875786</v>
       </c>
       <c r="FM13" s="6">
-        <f t="shared" si="73"/>
-        <v>44111.517217899323</v>
+        <f t="shared" si="79"/>
+        <v>44733.998131770284</v>
       </c>
       <c r="FN13" s="6">
-        <f t="shared" si="73"/>
-        <v>43670.40204572033</v>
+        <f t="shared" si="79"/>
+        <v>44286.658150452582</v>
       </c>
       <c r="FO13" s="6">
-        <f t="shared" si="73"/>
-        <v>43233.698025263126</v>
+        <f t="shared" si="79"/>
+        <v>43843.791568948058</v>
       </c>
       <c r="FP13" s="6">
-        <f t="shared" si="73"/>
-        <v>42801.361045010497</v>
+        <f t="shared" si="79"/>
+        <v>43405.353653258579</v>
       </c>
       <c r="FQ13" s="6">
-        <f t="shared" si="73"/>
-        <v>42373.34743456039</v>
+        <f t="shared" si="79"/>
+        <v>42971.300116725994</v>
       </c>
       <c r="FR13" s="6">
-        <f t="shared" si="73"/>
-        <v>41949.613960214789</v>
+        <f t="shared" si="79"/>
+        <v>42541.58711555873</v>
       </c>
       <c r="FS13" s="6">
-        <f t="shared" si="73"/>
-        <v>41530.117820612642</v>
+        <f t="shared" si="79"/>
+        <v>42116.171244403144</v>
       </c>
       <c r="FT13" s="6">
-        <f t="shared" si="73"/>
-        <v>41114.816642406513</v>
+        <f t="shared" si="79"/>
+        <v>41695.009531959113</v>
       </c>
     </row>
     <row r="14" spans="2:176">
@@ -5062,41 +5191,53 @@
         <f>2517</f>
         <v>2517</v>
       </c>
-      <c r="AM14" s="4"/>
-      <c r="AN14" s="4"/>
-      <c r="AO14" s="4"/>
-      <c r="AP14" s="4"/>
+      <c r="AM14" s="4">
+        <f>2517</f>
+        <v>2517</v>
+      </c>
+      <c r="AN14" s="4">
+        <f>2517</f>
+        <v>2517</v>
+      </c>
+      <c r="AO14" s="4">
+        <f>2517</f>
+        <v>2517</v>
+      </c>
+      <c r="AP14" s="4">
+        <f>2517</f>
+        <v>2517</v>
+      </c>
       <c r="AQ14" s="4"/>
       <c r="AR14" s="4">
-        <f t="shared" ref="AR14:AY14" si="74">I14</f>
+        <f t="shared" ref="AR14:AY14" si="80">I14</f>
         <v>2848.8</v>
       </c>
       <c r="AS14" s="4">
-        <f t="shared" si="74"/>
+        <f t="shared" si="80"/>
         <v>2848.8</v>
       </c>
       <c r="AT14" s="4">
-        <f t="shared" si="74"/>
+        <f t="shared" si="80"/>
         <v>2848.8</v>
       </c>
       <c r="AU14" s="4">
-        <f t="shared" si="74"/>
+        <f t="shared" si="80"/>
         <v>2848.8</v>
       </c>
       <c r="AV14" s="4">
-        <f t="shared" si="74"/>
+        <f t="shared" si="80"/>
         <v>2848.8</v>
       </c>
       <c r="AW14" s="4">
-        <f t="shared" si="74"/>
+        <f t="shared" si="80"/>
         <v>2848.8</v>
       </c>
       <c r="AX14" s="4">
-        <f t="shared" si="74"/>
+        <f t="shared" si="80"/>
         <v>2848.8</v>
       </c>
       <c r="AY14" s="4">
-        <f t="shared" si="74"/>
+        <f t="shared" si="80"/>
         <v>2517</v>
       </c>
       <c r="AZ14" s="4">
@@ -5112,19 +5253,19 @@
         <v>2517</v>
       </c>
       <c r="BC14" s="4">
-        <f t="shared" ref="BC14" si="75">BB14</f>
+        <f t="shared" ref="BC14" si="81">BB14</f>
         <v>2517</v>
       </c>
       <c r="BD14" s="4">
-        <f t="shared" ref="BD14:BE14" si="76">2396+439.4</f>
+        <f t="shared" ref="BD14:BE14" si="82">2396+439.4</f>
         <v>2835.4</v>
       </c>
       <c r="BE14" s="4">
-        <f t="shared" si="76"/>
+        <f t="shared" si="82"/>
         <v>2835.4</v>
       </c>
       <c r="BF14" s="4">
-        <f t="shared" ref="BF14" si="77">2189.9+343.8</f>
+        <f t="shared" ref="BF14" si="83">2189.9+343.8</f>
         <v>2533.7000000000003</v>
       </c>
       <c r="BG14" s="4">
@@ -5177,257 +5318,269 @@
         <v>36</v>
       </c>
       <c r="C15" s="7">
-        <f t="shared" ref="C15:P15" si="78">C13/C14</f>
+        <f t="shared" ref="C15:P15" si="84">C13/C14</f>
         <v>1.0737854535242908</v>
       </c>
       <c r="D15" s="7">
-        <f t="shared" si="78"/>
+        <f t="shared" si="84"/>
         <v>1.3654872226902555</v>
       </c>
       <c r="E15" s="7">
-        <f t="shared" si="78"/>
+        <f t="shared" si="84"/>
         <v>1.6522746419545071</v>
       </c>
       <c r="F15" s="7">
-        <f t="shared" si="78"/>
+        <f t="shared" si="84"/>
         <v>1.2454366750912664</v>
       </c>
       <c r="G15" s="7">
-        <f t="shared" si="78"/>
+        <f t="shared" si="84"/>
         <v>1.7505616399887671</v>
       </c>
       <c r="H15" s="7">
-        <f t="shared" si="78"/>
+        <f t="shared" si="84"/>
         <v>1.7923336141533277</v>
       </c>
       <c r="I15" s="7">
-        <f t="shared" si="78"/>
+        <f t="shared" si="84"/>
         <v>1.8032153889356921</v>
       </c>
       <c r="J15" s="7">
-        <f t="shared" si="78"/>
+        <f t="shared" si="84"/>
         <v>2.4157540016849199</v>
       </c>
       <c r="K15" s="7">
-        <f t="shared" si="78"/>
+        <f t="shared" si="84"/>
         <v>0.85263970794720578</v>
       </c>
       <c r="L15" s="7">
-        <f t="shared" si="78"/>
+        <f t="shared" si="84"/>
         <v>0.91126088177478226</v>
       </c>
       <c r="M15" s="7">
-        <f t="shared" si="78"/>
+        <f t="shared" si="84"/>
         <v>2.1380932322381354</v>
       </c>
       <c r="N15" s="7">
-        <f t="shared" si="78"/>
+        <f t="shared" si="84"/>
         <v>2.5796826734063463</v>
       </c>
       <c r="O15" s="7">
-        <f t="shared" si="78"/>
+        <f t="shared" si="84"/>
         <v>1.7207245155855095</v>
       </c>
       <c r="P15" s="7">
-        <f t="shared" si="78"/>
+        <f t="shared" si="84"/>
         <v>2.0572109654350417</v>
       </c>
       <c r="Q15" s="7">
-        <f t="shared" ref="Q15:R15" si="79">Q13/Q14</f>
+        <f t="shared" ref="Q15:R15" si="85">Q13/Q14</f>
         <v>2.754142094917158</v>
       </c>
       <c r="R15" s="7">
-        <f t="shared" si="79"/>
+        <f t="shared" si="85"/>
         <v>3.9381493962370118</v>
       </c>
       <c r="S15" s="7">
-        <f t="shared" ref="S15:V15" si="80">S13/S14</f>
+        <f t="shared" ref="S15:V15" si="86">S13/S14</f>
         <v>3.3494392325597797</v>
       </c>
       <c r="T15" s="7">
-        <f t="shared" ref="T15:U15" si="81">T13/T14</f>
+        <f t="shared" ref="T15:U15" si="87">T13/T14</f>
         <v>3.667607621736062</v>
       </c>
       <c r="U15" s="7">
-        <f t="shared" si="81"/>
+        <f t="shared" si="87"/>
         <v>3.2672352523098791</v>
       </c>
       <c r="V15" s="7">
-        <f t="shared" si="80"/>
+        <f t="shared" si="86"/>
         <v>3.7197106690777577</v>
       </c>
       <c r="W15" s="7">
-        <f t="shared" ref="W15:X15" si="82">W13/W14</f>
+        <f t="shared" ref="W15:X15" si="88">W13/W14</f>
         <v>2.7394495412844035</v>
       </c>
       <c r="X15" s="7">
-        <f t="shared" si="82"/>
+        <f t="shared" si="88"/>
         <v>2.4730029585798818</v>
       </c>
       <c r="Y15" s="7">
-        <f t="shared" ref="Y15" si="83">Y13/Y14</f>
+        <f t="shared" ref="Y15" si="89">Y13/Y14</f>
         <v>1.638702460850112</v>
       </c>
       <c r="Z15" s="7">
-        <f t="shared" ref="Z15" si="84">Z13/Z14</f>
+        <f t="shared" ref="Z15" si="90">Z13/Z14</f>
         <v>1.7634571645185746</v>
       </c>
       <c r="AA15" s="7">
-        <f t="shared" ref="AA15:AC15" si="85">AA13/AA14</f>
+        <f t="shared" ref="AA15:AC15" si="91">AA13/AA14</f>
         <v>2.206803247004252</v>
       </c>
       <c r="AB15" s="7">
-        <f t="shared" si="85"/>
+        <f t="shared" si="91"/>
         <v>3.0327102803738319</v>
       </c>
       <c r="AC15" s="7">
-        <f t="shared" si="85"/>
+        <f t="shared" si="91"/>
         <v>4.6013198757763973</v>
       </c>
       <c r="AD15" s="7">
-        <f t="shared" ref="AD15" si="86">AD13/AD14</f>
+        <f t="shared" ref="AD15" si="92">AD13/AD14</f>
         <v>5.4625876851130162</v>
       </c>
       <c r="AE15" s="7">
-        <f t="shared" ref="AE15" si="87">AE13/AE14</f>
+        <f t="shared" ref="AE15" si="93">AE13/AE14</f>
         <v>4.8601178781925345</v>
       </c>
       <c r="AF15" s="7">
-        <f t="shared" ref="AF15:AH15" si="88">AF13/AF14</f>
+        <f t="shared" ref="AF15:AH15" si="94">AF13/AF14</f>
         <v>5.2907662082514735</v>
       </c>
       <c r="AG15" s="7">
-        <f t="shared" si="88"/>
+        <f t="shared" si="94"/>
         <v>6.2142998613586853</v>
       </c>
       <c r="AH15" s="7">
-        <f t="shared" si="88"/>
+        <f t="shared" si="94"/>
         <v>7.6125823893910081</v>
       </c>
       <c r="AI15" s="7">
-        <f t="shared" ref="AI15:AL15" si="89">AI13/AI14</f>
+        <f t="shared" ref="AI15:AL15" si="95">AI13/AI14</f>
         <v>6.5864661654135341</v>
       </c>
       <c r="AJ15" s="7">
-        <f t="shared" si="89"/>
+        <f t="shared" si="95"/>
         <v>7.2823669579030978</v>
       </c>
       <c r="AK15" s="7">
-        <f t="shared" si="89"/>
+        <f t="shared" si="95"/>
         <v>7.4052443384982123</v>
       </c>
       <c r="AL15" s="7">
-        <f t="shared" si="89"/>
+        <f t="shared" si="95"/>
         <v>9.0456893126738187</v>
       </c>
-      <c r="AM15" s="7"/>
-      <c r="AN15" s="7"/>
-      <c r="AO15" s="7"/>
-      <c r="AP15" s="7"/>
+      <c r="AM15" s="7">
+        <f t="shared" ref="AM15:AP15" si="96">AM13/AM14</f>
+        <v>6.9710568136670643</v>
+      </c>
+      <c r="AN15" s="7">
+        <f t="shared" si="96"/>
+        <v>8.0044235200635647</v>
+      </c>
+      <c r="AO15" s="7">
+        <f t="shared" si="96"/>
+        <v>7.9375246086611018</v>
+      </c>
+      <c r="AP15" s="7">
+        <f t="shared" si="96"/>
+        <v>9.1877117679777491</v>
+      </c>
       <c r="AQ15" s="7"/>
       <c r="AR15" s="7">
-        <f t="shared" ref="AR15:BB15" si="90">AR13/AR14</f>
+        <f t="shared" ref="AR15:BB15" si="97">AR13/AR14</f>
         <v>0.21272114574557707</v>
       </c>
       <c r="AS15" s="7">
-        <f t="shared" si="90"/>
+        <f t="shared" si="97"/>
         <v>0.35102499297950013</v>
       </c>
       <c r="AT15" s="7">
-        <f t="shared" si="90"/>
+        <f t="shared" si="97"/>
         <v>1.8604324627913508E-2</v>
       </c>
       <c r="AU15" s="7">
-        <f t="shared" si="90"/>
+        <f t="shared" si="97"/>
         <v>0.52653748946925016</v>
       </c>
       <c r="AV15" s="7">
-        <f t="shared" si="90"/>
+        <f t="shared" si="97"/>
         <v>1.0320134793597304</v>
       </c>
       <c r="AW15" s="7">
-        <f t="shared" si="90"/>
+        <f t="shared" si="97"/>
         <v>1.2945801741083964</v>
       </c>
       <c r="AX15" s="7">
-        <f t="shared" si="90"/>
+        <f t="shared" si="97"/>
         <v>3.5864223532715527</v>
       </c>
       <c r="AY15" s="7">
-        <f t="shared" si="90"/>
+        <f t="shared" si="97"/>
         <v>6.0405244338498214</v>
       </c>
       <c r="AZ15" s="7">
-        <f t="shared" si="90"/>
+        <f t="shared" si="97"/>
         <v>8.7850615812475166</v>
       </c>
       <c r="BA15" s="7">
-        <f t="shared" si="90"/>
+        <f t="shared" si="97"/>
         <v>7.33611442193087</v>
       </c>
       <c r="BB15" s="7">
-        <f t="shared" si="90"/>
+        <f t="shared" si="97"/>
         <v>11.579261025029798</v>
       </c>
       <c r="BC15" s="7">
-        <f t="shared" ref="BC15:BL15" si="91">BC13/BC14</f>
+        <f t="shared" ref="BC15:BL15" si="98">BC13/BC14</f>
         <v>15.641636869288837</v>
       </c>
       <c r="BD15" s="7">
-        <f t="shared" si="91"/>
+        <f t="shared" si="98"/>
         <v>8.1819143683430902</v>
       </c>
       <c r="BE15" s="7">
-        <f t="shared" si="91"/>
+        <f t="shared" si="98"/>
         <v>13.884108062354517</v>
       </c>
       <c r="BF15" s="7">
-        <f t="shared" si="91"/>
+        <f t="shared" si="98"/>
         <v>24.000473615660887</v>
       </c>
       <c r="BG15" s="7">
-        <f t="shared" si="91"/>
+        <f t="shared" si="98"/>
         <v>30.348947159316641</v>
       </c>
       <c r="BH15" s="7">
-        <f t="shared" si="91"/>
-        <v>33.828873730631706</v>
+        <f t="shared" si="98"/>
+        <v>32.100716710369483</v>
       </c>
       <c r="BI15" s="7">
-        <f t="shared" si="91"/>
-        <v>37.156336444643621</v>
+        <f t="shared" si="98"/>
+        <v>36.454797880371864</v>
       </c>
       <c r="BJ15" s="7">
-        <f t="shared" si="91"/>
-        <v>40.045899329673645</v>
+        <f t="shared" si="98"/>
+        <v>38.664227903347694</v>
       </c>
       <c r="BK15" s="7">
-        <f t="shared" si="91"/>
-        <v>42.029279675677827</v>
+        <f t="shared" si="98"/>
+        <v>41.014093784980204</v>
       </c>
       <c r="BL15" s="7">
-        <f t="shared" si="91"/>
-        <v>43.357350536611833</v>
+        <f t="shared" si="98"/>
+        <v>43.095038249255481</v>
       </c>
       <c r="BM15" s="7">
-        <f t="shared" ref="BM15:BQ15" si="92">BM13/BM14</f>
-        <v>44.233077288050673</v>
+        <f t="shared" ref="BM15:BQ15" si="99">BM13/BM14</f>
+        <v>44.841888548283286</v>
       </c>
       <c r="BN15" s="7">
-        <f t="shared" si="92"/>
-        <v>45.117889837248114</v>
+        <f t="shared" si="99"/>
+        <v>45.754301431048098</v>
       </c>
       <c r="BO15" s="7">
-        <f t="shared" si="92"/>
-        <v>46.020250291653561</v>
+        <f t="shared" si="99"/>
+        <v>46.669661581636731</v>
       </c>
       <c r="BP15" s="7">
-        <f t="shared" si="92"/>
-        <v>46.940655344261458</v>
+        <f t="shared" si="99"/>
+        <v>47.603059637816116</v>
       </c>
       <c r="BQ15" s="7">
-        <f t="shared" si="92"/>
-        <v>47.879468451969927</v>
+        <f t="shared" si="99"/>
+        <v>48.555120915484437</v>
       </c>
     </row>
     <row r="17" spans="2:72">
@@ -5439,161 +5592,173 @@
         <v>0.48979083665338652</v>
       </c>
       <c r="H17" s="9">
-        <f t="shared" ref="H17:R17" si="93">H3/D3-1</f>
+        <f t="shared" ref="H17:R17" si="100">H3/D3-1</f>
         <v>0.41948288810213485</v>
       </c>
       <c r="I17" s="9">
-        <f t="shared" si="93"/>
+        <f t="shared" si="100"/>
         <v>0.32910534469403574</v>
       </c>
       <c r="J17" s="9">
-        <f t="shared" si="93"/>
+        <f t="shared" si="100"/>
         <v>0.30388529139685483</v>
       </c>
       <c r="K17" s="9">
-        <f t="shared" si="93"/>
+        <f t="shared" si="100"/>
         <v>0.25998662878154777</v>
       </c>
       <c r="L17" s="9">
-        <f t="shared" si="93"/>
+        <f t="shared" si="100"/>
         <v>0.27473358022825178</v>
       </c>
       <c r="M17" s="9">
-        <f t="shared" si="93"/>
+        <f t="shared" si="100"/>
         <v>0.2859328331026445</v>
       </c>
       <c r="N17" s="9">
-        <f t="shared" si="93"/>
+        <f t="shared" si="100"/>
         <v>0.2464230814709707</v>
       </c>
       <c r="O17" s="9">
-        <f t="shared" si="93"/>
+        <f t="shared" si="100"/>
         <v>0.17642767128739134</v>
       </c>
       <c r="P17" s="9">
-        <f t="shared" si="93"/>
+        <f t="shared" si="100"/>
         <v>0.10796869441479906</v>
       </c>
       <c r="Q17" s="9">
-        <f t="shared" si="93"/>
+        <f t="shared" si="100"/>
         <v>0.21629277135735325</v>
       </c>
       <c r="R17" s="9">
-        <f t="shared" si="93"/>
+        <f t="shared" si="100"/>
         <v>0.33156247035385644</v>
       </c>
       <c r="S17" s="9">
-        <f t="shared" ref="S17" si="94">S3/O3-1</f>
+        <f t="shared" ref="S17" si="101">S3/O3-1</f>
         <v>0.47550318543158365</v>
       </c>
       <c r="T17" s="9">
-        <f t="shared" ref="T17" si="95">T3/P3-1</f>
+        <f t="shared" ref="T17" si="102">T3/P3-1</f>
         <v>0.5560014983678494</v>
       </c>
       <c r="U17" s="9">
-        <f t="shared" ref="U17" si="96">U3/Q3-1</f>
+        <f t="shared" ref="U17" si="103">U3/Q3-1</f>
         <v>0.35118770377270603</v>
       </c>
       <c r="V17" s="9">
-        <f t="shared" ref="V17" si="97">V3/R3-1</f>
+        <f t="shared" ref="V17" si="104">V3/R3-1</f>
         <v>0.19945141065830718</v>
       </c>
       <c r="W17" s="9">
-        <f t="shared" ref="W17" si="98">W3/S3-1</f>
+        <f t="shared" ref="W17" si="105">W3/S3-1</f>
         <v>6.6371174200450911E-2</v>
       </c>
       <c r="X17" s="9">
-        <f t="shared" ref="X17" si="99">X3/T3-1</f>
+        <f t="shared" ref="X17" si="106">X3/T3-1</f>
         <v>-8.7698180692643568E-3</v>
       </c>
       <c r="Y17" s="9">
-        <f t="shared" ref="Y17" si="100">Y3/U3-1</f>
+        <f t="shared" ref="Y17" si="107">Y3/U3-1</f>
         <v>-4.4674250258531556E-2</v>
       </c>
       <c r="Z17" s="9">
-        <f t="shared" ref="Z17" si="101">Z3/V3-1</f>
+        <f t="shared" ref="Z17" si="108">Z3/V3-1</f>
         <v>-4.4726916337501144E-2</v>
       </c>
       <c r="AA17" s="9">
-        <f t="shared" ref="AA17" si="102">AA3/W3-1</f>
+        <f t="shared" ref="AA17" si="109">AA3/W3-1</f>
         <v>2.6408198366060009E-2</v>
       </c>
       <c r="AB17" s="9">
-        <f t="shared" ref="AB17" si="103">AB3/X3-1</f>
+        <f t="shared" ref="AB17" si="110">AB3/X3-1</f>
         <v>0.11022829782804799</v>
       </c>
       <c r="AC17" s="9">
-        <f t="shared" ref="AC17" si="104">AC3/Y3-1</f>
+        <f t="shared" ref="AC17" si="111">AC3/Y3-1</f>
         <v>0.24182723533232298</v>
       </c>
       <c r="AD17" s="9">
-        <f t="shared" ref="AD17" si="105">AD3/Z3-1</f>
+        <f t="shared" ref="AD17" si="112">AD3/Z3-1</f>
         <v>0.24703870666873939</v>
       </c>
       <c r="AE17" s="9">
-        <f t="shared" ref="AE17" si="106">AE3/AA3-1</f>
+        <f t="shared" ref="AE17" si="113">AE3/AA3-1</f>
         <v>0.27264793157619138</v>
       </c>
       <c r="AF17" s="9">
-        <f t="shared" ref="AF17" si="107">AF3/AB3-1</f>
+        <f t="shared" ref="AF17" si="114">AF3/AB3-1</f>
         <v>0.2210069064658271</v>
       </c>
       <c r="AG17" s="9">
-        <f t="shared" ref="AG17" si="108">AG3/AC3-1</f>
+        <f t="shared" ref="AG17" si="115">AG3/AC3-1</f>
         <v>0.17936424918642491</v>
       </c>
       <c r="AH17" s="9">
-        <f t="shared" ref="AH17" si="109">AH3/AD3-1</f>
+        <f t="shared" ref="AH17" si="116">AH3/AD3-1</f>
         <v>0.20627757971628724</v>
       </c>
       <c r="AI17" s="9">
-        <f t="shared" ref="AI17" si="110">AI3/AE3-1</f>
+        <f t="shared" ref="AI17" si="117">AI3/AE3-1</f>
         <v>0.16071869428062002</v>
       </c>
       <c r="AJ17" s="9">
-        <f t="shared" ref="AJ17" si="111">AJ3/AF3-1</f>
+        <f t="shared" ref="AJ17" si="118">AJ3/AF3-1</f>
         <v>0.21614496685521223</v>
       </c>
       <c r="AK17" s="9">
-        <f t="shared" ref="AK17" si="112">AK3/AG3-1</f>
+        <f t="shared" ref="AK17" si="119">AK3/AG3-1</f>
         <v>0.26246027248761972</v>
       </c>
       <c r="AL17" s="9">
-        <f t="shared" ref="AL17" si="113">AL3/AH3-1</f>
+        <f t="shared" ref="AL17" si="120">AL3/AH3-1</f>
         <v>0.23784230649994842</v>
       </c>
-      <c r="AM17" s="9"/>
-      <c r="AN17" s="9"/>
-      <c r="AO17" s="9"/>
-      <c r="AP17" s="9"/>
+      <c r="AM17" s="9">
+        <f t="shared" ref="AM17" si="121">AM3/AI3-1</f>
+        <v>0.27617337051566859</v>
+      </c>
+      <c r="AN17" s="9">
+        <f t="shared" ref="AN17" si="122">AN3/AJ3-1</f>
+        <v>0.25</v>
+      </c>
+      <c r="AO17" s="9">
+        <f t="shared" ref="AO17" si="123">AO3/AK3-1</f>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="AP17" s="9">
+        <f t="shared" ref="AP17" si="124">AP3/AL3-1</f>
+        <v>0.14999999999999991</v>
+      </c>
       <c r="AQ17" s="9"/>
       <c r="AR17" s="9"/>
       <c r="AS17" s="9">
-        <f t="shared" ref="AS17:AV17" si="114">AS3/AR3-1</f>
+        <f t="shared" ref="AS17:AV17" si="125">AS3/AR3-1</f>
         <v>0.87993920972644379</v>
       </c>
       <c r="AT17" s="9">
-        <f t="shared" si="114"/>
+        <f t="shared" si="125"/>
         <v>0.37132848288870934</v>
       </c>
       <c r="AU17" s="9">
-        <f t="shared" si="114"/>
+        <f t="shared" si="125"/>
         <v>0.5468657889565729</v>
       </c>
       <c r="AV17" s="9">
-        <f t="shared" si="114"/>
+        <f t="shared" si="125"/>
         <v>0.58358739837398366</v>
       </c>
       <c r="AW17" s="9">
-        <f t="shared" ref="AW17:AY17" si="115">AW3/AV3-1</f>
+        <f t="shared" ref="AW17:AY17" si="126">AW3/AV3-1</f>
         <v>0.43815177282207607</v>
       </c>
       <c r="AX17" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="126"/>
         <v>0.54161088799643009</v>
       </c>
       <c r="AY17" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="126"/>
         <v>0.47090961719371882</v>
       </c>
       <c r="AZ17" s="9">
@@ -5601,71 +5766,71 @@
         <v>0.37352716896661997</v>
       </c>
       <c r="BA17" s="9">
-        <f t="shared" ref="BA17:BL17" si="116">BA3/AZ3-1</f>
+        <f t="shared" ref="BA17:BL17" si="127">BA3/AZ3-1</f>
         <v>0.26575092231097108</v>
       </c>
       <c r="BB17" s="9">
-        <f t="shared" si="116"/>
+        <f t="shared" si="127"/>
         <v>0.21632214157363783</v>
       </c>
       <c r="BC17" s="9">
-        <f t="shared" si="116"/>
+        <f t="shared" si="127"/>
         <v>0.37180978526394148</v>
       </c>
       <c r="BD17" s="9">
-        <f t="shared" si="116"/>
+        <f t="shared" si="127"/>
         <v>-1.1193175554782941E-2</v>
       </c>
       <c r="BE17" s="9">
-        <f t="shared" si="116"/>
+        <f t="shared" si="127"/>
         <v>0.15918153830321846</v>
       </c>
       <c r="BF17" s="9">
-        <f t="shared" si="116"/>
+        <f t="shared" si="127"/>
         <v>0.21697701430040461</v>
       </c>
       <c r="BG17" s="9">
-        <f t="shared" si="116"/>
+        <f t="shared" si="127"/>
         <v>0.22167173252279637</v>
       </c>
       <c r="BH17" s="9">
-        <f t="shared" si="116"/>
-        <v>0.14999999999999991</v>
+        <f t="shared" si="127"/>
+        <v>0.21295922175503179</v>
       </c>
       <c r="BI17" s="9">
-        <f t="shared" si="116"/>
-        <v>8.0000000000000071E-2</v>
+        <f t="shared" si="127"/>
+        <v>0.1399999999999999</v>
       </c>
       <c r="BJ17" s="9">
-        <f t="shared" si="116"/>
-        <v>6.0000000000000053E-2</v>
+        <f t="shared" si="127"/>
+        <v>7.0000000000000062E-2</v>
       </c>
       <c r="BK17" s="9">
-        <f t="shared" si="116"/>
+        <f t="shared" si="127"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="BL17" s="9">
+        <f t="shared" si="127"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="BL17" s="9">
-        <f t="shared" si="116"/>
+      <c r="BM17" s="9">
+        <f t="shared" ref="BM17" si="128">BM3/BL3-1</f>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="BM17" s="9">
-        <f t="shared" ref="BM17" si="117">BM3/BL3-1</f>
+      <c r="BN17" s="9">
+        <f t="shared" ref="BN17" si="129">BN3/BM3-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BN17" s="9">
-        <f t="shared" ref="BN17" si="118">BN3/BM3-1</f>
+      <c r="BO17" s="9">
+        <f t="shared" ref="BO17" si="130">BO3/BN3-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BO17" s="9">
-        <f t="shared" ref="BO17" si="119">BO3/BN3-1</f>
+      <c r="BP17" s="9">
+        <f t="shared" ref="BP17" si="131">BP3/BO3-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BP17" s="9">
-        <f t="shared" ref="BP17" si="120">BP3/BO3-1</f>
-        <v>2.0000000000000018E-2</v>
-      </c>
       <c r="BQ17" s="9">
-        <f t="shared" ref="BQ17" si="121">BQ3/BP3-1</f>
+        <f t="shared" ref="BQ17" si="132">BQ3/BP3-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
@@ -5678,252 +5843,264 @@
         <v>0.85570219123505975</v>
       </c>
       <c r="D18" s="9">
-        <f t="shared" ref="D18:R18" si="122">D5/D3</f>
+        <f t="shared" ref="D18:R18" si="133">D5/D3</f>
         <v>0.86728891749812254</v>
       </c>
       <c r="E18" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="133"/>
         <v>0.85979860573199074</v>
       </c>
       <c r="F18" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="133"/>
         <v>0.87580943570767811</v>
       </c>
       <c r="G18" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="133"/>
         <v>0.8389603877653351</v>
       </c>
       <c r="H18" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="133"/>
         <v>0.83266570931902351</v>
       </c>
       <c r="I18" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="133"/>
         <v>0.82385080498288044</v>
       </c>
       <c r="J18" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="133"/>
         <v>0.83469315360056762</v>
       </c>
       <c r="K18" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="133"/>
         <v>0.81322544272733299</v>
       </c>
       <c r="L18" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="133"/>
         <v>0.80392505632633704</v>
       </c>
       <c r="M18" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="133"/>
         <v>0.82126671198731027</v>
       </c>
       <c r="N18" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="133"/>
         <v>0.83436106631249407</v>
       </c>
       <c r="O18" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="133"/>
         <v>0.80498393189378137</v>
       </c>
       <c r="P18" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="133"/>
         <v>0.7950981966072671</v>
       </c>
       <c r="Q18" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="133"/>
         <v>0.80465766185374943</v>
       </c>
       <c r="R18" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="133"/>
         <v>0.81440581362211462</v>
       </c>
       <c r="S18" s="9">
-        <f t="shared" ref="S18:V18" si="123">S5/S3</f>
+        <f t="shared" ref="S18:V18" si="134">S5/S3</f>
         <v>0.80394329601467274</v>
       </c>
       <c r="T18" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="134"/>
         <v>0.81432059703545756</v>
       </c>
       <c r="U18" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="134"/>
         <v>0.80106859703550504</v>
       </c>
       <c r="V18" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="134"/>
         <v>0.81146981081642955</v>
       </c>
       <c r="W18" s="9">
-        <f t="shared" ref="W18:AE18" si="124">W5/W3</f>
+        <f t="shared" ref="W18:AE18" si="135">W5/W3</f>
         <v>0.78482872294682526</v>
       </c>
       <c r="X18" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="135"/>
         <v>0.81985982929706469</v>
       </c>
       <c r="Y18" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="135"/>
         <v>0.79375045103557773</v>
       </c>
       <c r="Z18" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="135"/>
         <v>0.74083631276231932</v>
       </c>
       <c r="AA18" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="135"/>
         <v>0.7867690696456624</v>
       </c>
       <c r="AB18" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="135"/>
         <v>0.81421294415450485</v>
       </c>
       <c r="AC18" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="135"/>
         <v>0.81956066945606698</v>
       </c>
       <c r="AD18" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="135"/>
         <v>0.80815736331679588</v>
       </c>
       <c r="AE18" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="135"/>
         <v>0.81785763269784661</v>
       </c>
       <c r="AF18" s="9">
-        <f t="shared" ref="AF18:AH18" si="125">AF5/AF3</f>
+        <f t="shared" ref="AF18:AH18" si="136">AF5/AF3</f>
         <v>0.81295590079598679</v>
       </c>
       <c r="AG18" s="9">
-        <f t="shared" si="125"/>
+        <f t="shared" si="136"/>
         <v>0.81830052477272164</v>
       </c>
       <c r="AH18" s="9">
-        <f t="shared" si="125"/>
+        <f t="shared" si="136"/>
         <v>0.81731941717474421</v>
       </c>
       <c r="AI18" s="9">
-        <f t="shared" ref="AI18:AL18" si="126">AI5/AI3</f>
+        <f t="shared" ref="AI18:AL18" si="137">AI5/AI3</f>
         <v>0.82105213404546962</v>
       </c>
       <c r="AJ18" s="9">
-        <f t="shared" si="126"/>
+        <f t="shared" si="137"/>
         <v>0.82130229817324696</v>
       </c>
       <c r="AK18" s="9">
-        <f t="shared" si="126"/>
+        <f t="shared" si="137"/>
         <v>0.82034268763904605</v>
       </c>
       <c r="AL18" s="9">
-        <f t="shared" si="126"/>
+        <f t="shared" si="137"/>
         <v>0.8179253001185447</v>
       </c>
-      <c r="AM18" s="9"/>
-      <c r="AN18" s="9"/>
-      <c r="AO18" s="9"/>
-      <c r="AP18" s="9"/>
+      <c r="AM18" s="9">
+        <f t="shared" ref="AM18:AP18" si="138">AM5/AM3</f>
+        <v>0.82</v>
+      </c>
+      <c r="AN18" s="9">
+        <f t="shared" si="138"/>
+        <v>0.82</v>
+      </c>
+      <c r="AO18" s="9">
+        <f t="shared" si="138"/>
+        <v>0.82</v>
+      </c>
+      <c r="AP18" s="9">
+        <f t="shared" si="138"/>
+        <v>0.82</v>
+      </c>
       <c r="AQ18" s="9"/>
       <c r="AR18" s="9">
-        <f t="shared" ref="AR18:AV18" si="127">AR5/AR3</f>
+        <f t="shared" ref="AR18:AV18" si="139">AR5/AR3</f>
         <v>0.75025329280648434</v>
       </c>
       <c r="AS18" s="9">
-        <f t="shared" si="127"/>
+        <f t="shared" si="139"/>
         <v>0.76825653462678523</v>
       </c>
       <c r="AT18" s="9">
-        <f t="shared" si="127"/>
+        <f t="shared" si="139"/>
         <v>0.73197091766555311</v>
       </c>
       <c r="AU18" s="9">
-        <f t="shared" si="127"/>
+        <f t="shared" si="139"/>
         <v>0.76181402439024393</v>
       </c>
       <c r="AV18" s="9">
-        <f t="shared" si="127"/>
+        <f t="shared" si="139"/>
         <v>0.82729022942403341</v>
       </c>
       <c r="AW18" s="9">
-        <f t="shared" ref="AW18:AY18" si="128">AW5/AW3</f>
+        <f t="shared" ref="AW18:AY18" si="140">AW5/AW3</f>
         <v>0.84008255243195007</v>
       </c>
       <c r="AX18" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="140"/>
         <v>0.86290614371517471</v>
       </c>
       <c r="AY18" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="140"/>
         <v>0.86581556096721024</v>
       </c>
       <c r="AZ18" s="9">
-        <f t="shared" ref="AZ18:BL18" si="129">AZ5/AZ3</f>
+        <f t="shared" ref="AZ18:BL18" si="141">AZ5/AZ3</f>
         <v>0.8324617643898421</v>
       </c>
       <c r="BA18" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="141"/>
         <v>0.81931887318363827</v>
       </c>
       <c r="BB18" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="141"/>
         <v>0.80583021194425708</v>
       </c>
       <c r="BC18" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="141"/>
         <v>0.80794376277251567</v>
       </c>
       <c r="BD18" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="141"/>
         <v>0.78347297378418479</v>
       </c>
       <c r="BE18" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="141"/>
         <v>0.80796176694705224</v>
       </c>
       <c r="BF18" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="141"/>
         <v>0.81664437689969605</v>
       </c>
       <c r="BG18" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="141"/>
         <v>0.82</v>
       </c>
       <c r="BH18" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="141"/>
         <v>0.82</v>
       </c>
       <c r="BI18" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="141"/>
         <v>0.82</v>
       </c>
       <c r="BJ18" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="141"/>
         <v>0.82</v>
       </c>
       <c r="BK18" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="141"/>
         <v>0.82</v>
       </c>
       <c r="BL18" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="141"/>
+        <v>0.82000000000000006</v>
+      </c>
+      <c r="BM18" s="9">
+        <f t="shared" ref="BM18:BQ18" si="142">BM5/BM3</f>
         <v>0.82</v>
       </c>
-      <c r="BM18" s="9">
-        <f t="shared" ref="BM18:BQ18" si="130">BM5/BM3</f>
+      <c r="BN18" s="9">
+        <f t="shared" si="142"/>
         <v>0.82</v>
       </c>
-      <c r="BN18" s="9">
-        <f t="shared" si="130"/>
+      <c r="BO18" s="9">
+        <f t="shared" si="142"/>
         <v>0.82</v>
       </c>
-      <c r="BO18" s="9">
-        <f t="shared" si="130"/>
+      <c r="BP18" s="9">
+        <f t="shared" si="142"/>
         <v>0.82</v>
       </c>
-      <c r="BP18" s="9">
-        <f t="shared" si="130"/>
-        <v>0.82</v>
-      </c>
       <c r="BQ18" s="9">
-        <f t="shared" si="130"/>
+        <f t="shared" si="142"/>
         <v>0.82</v>
       </c>
       <c r="BS18" t="s">
@@ -5942,253 +6119,265 @@
         <v>0.41421812749003983</v>
       </c>
       <c r="D19" s="9">
-        <f t="shared" ref="D19:R19" si="131">D9/D3</f>
+        <f t="shared" ref="D19:R19" si="143">D9/D3</f>
         <v>0.47215963952365625</v>
       </c>
       <c r="E19" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="143"/>
         <v>0.49593338497288925</v>
       </c>
       <c r="F19" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="143"/>
         <v>0.56675917360468697</v>
       </c>
       <c r="G19" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="143"/>
         <v>0.45537355841551064</v>
       </c>
       <c r="H19" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="143"/>
         <v>0.44312599198851182</v>
       </c>
       <c r="I19" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="143"/>
         <v>0.42114081736723247</v>
       </c>
       <c r="J19" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="143"/>
         <v>0.46233889085964291</v>
       </c>
       <c r="K19" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="143"/>
         <v>0.22000397957153281</v>
       </c>
       <c r="L19" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="143"/>
         <v>0.27309379817384088</v>
       </c>
       <c r="M19" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="143"/>
         <v>0.40703602991162474</v>
       </c>
       <c r="N19" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="143"/>
         <v>0.42016886443411439</v>
       </c>
       <c r="O19" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="143"/>
         <v>0.33224333314540228</v>
       </c>
       <c r="P19" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="143"/>
         <v>0.31909883876491679</v>
       </c>
       <c r="Q19" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="143"/>
         <v>0.37447601304145317</v>
       </c>
       <c r="R19" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="143"/>
         <v>0.45507979481333716</v>
       </c>
       <c r="S19" s="9">
-        <f t="shared" ref="S19:V19" si="132">S9/S3</f>
+        <f t="shared" ref="S19:V19" si="144">S9/S3</f>
         <v>0.43475602766420846</v>
       </c>
       <c r="T19" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="144"/>
         <v>0.42531898063761736</v>
       </c>
       <c r="U19" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="144"/>
         <v>0.35928990003447087</v>
       </c>
       <c r="V19" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="144"/>
         <v>0.37376377297971547</v>
       </c>
       <c r="W19" s="9">
-        <f t="shared" ref="W19:AE19" si="133">W9/W3</f>
+        <f t="shared" ref="W19:AE19" si="145">W9/W3</f>
         <v>0.30543213415508097</v>
       </c>
       <c r="X19" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="145"/>
         <v>0.28998681562695161</v>
       </c>
       <c r="Y19" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="145"/>
         <v>0.20437324096124701</v>
       </c>
       <c r="Z19" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="145"/>
         <v>0.19894295041193844</v>
       </c>
       <c r="AA19" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="145"/>
         <v>0.25229533950078548</v>
       </c>
       <c r="AB19" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="145"/>
         <v>0.29350917216163003</v>
       </c>
       <c r="AC19" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="145"/>
         <v>0.40731055323105531</v>
       </c>
       <c r="AD19" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="145"/>
         <v>0.4084665054473835</v>
       </c>
       <c r="AE19" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="145"/>
         <v>0.37904265532848719</v>
       </c>
       <c r="AF19" s="9">
-        <f t="shared" ref="AF19:AH19" si="134">AF9/AF3</f>
+        <f t="shared" ref="AF19:AH19" si="146">AF9/AF3</f>
         <v>0.38000051188861306</v>
       </c>
       <c r="AG19" s="9">
-        <f t="shared" si="134"/>
+        <f t="shared" si="146"/>
         <v>0.4274557146024785</v>
       </c>
       <c r="AH19" s="9">
-        <f t="shared" si="134"/>
+        <f t="shared" si="146"/>
         <v>0.45086287072439807</v>
       </c>
       <c r="AI19" s="9">
-        <f t="shared" ref="AI19:AL19" si="135">AI9/AI3</f>
+        <f t="shared" ref="AI19:AL19" si="147">AI9/AI3</f>
         <v>0.41487450961856598</v>
       </c>
       <c r="AJ19" s="9">
-        <f t="shared" si="135"/>
+        <f t="shared" si="147"/>
         <v>0.43019193534809325</v>
       </c>
       <c r="AK19" s="9">
-        <f t="shared" si="135"/>
+        <f t="shared" si="147"/>
         <v>0.4007454822216151</v>
       </c>
       <c r="AL19" s="9">
-        <f t="shared" si="135"/>
+        <f t="shared" si="147"/>
         <v>0.41315345699831368</v>
       </c>
-      <c r="AM19" s="9"/>
-      <c r="AN19" s="9"/>
-      <c r="AO19" s="9"/>
-      <c r="AP19" s="9"/>
+      <c r="AM19" s="9">
+        <f t="shared" ref="AM19:AP19" si="148">AM9/AM3</f>
+        <v>0.37041666666666667</v>
+      </c>
+      <c r="AN19" s="9">
+        <f t="shared" si="148"/>
+        <v>0.3876908830709655</v>
+      </c>
+      <c r="AO19" s="9">
+        <f t="shared" si="148"/>
+        <v>0.37129542172436664</v>
+      </c>
+      <c r="AP19" s="9">
+        <f t="shared" si="148"/>
+        <v>0.38460010206607576</v>
+      </c>
       <c r="AQ19" s="9"/>
       <c r="AR19" s="9">
-        <f t="shared" ref="AR19:AV19" si="136">AR9/AR3</f>
+        <f t="shared" ref="AR19:AV19" si="149">AR9/AR3</f>
         <v>0.52279635258358659</v>
       </c>
       <c r="AS19" s="9">
-        <f t="shared" si="136"/>
+        <f t="shared" si="149"/>
         <v>0.47318781999461063</v>
       </c>
       <c r="AT19" s="9">
-        <f t="shared" si="136"/>
+        <f t="shared" si="149"/>
         <v>0.10571821575948123</v>
       </c>
       <c r="AU19" s="9">
-        <f t="shared" si="136"/>
+        <f t="shared" si="149"/>
         <v>0.35619918699186992</v>
       </c>
       <c r="AV19" s="9">
-        <f t="shared" si="136"/>
+        <f t="shared" si="149"/>
         <v>0.40060965827049577</v>
       </c>
       <c r="AW19" s="9">
-        <f t="shared" ref="AW19:AY19" si="137">AW9/AW3</f>
+        <f t="shared" ref="AW19:AY19" si="150">AW9/AW3</f>
         <v>0.34722222222222221</v>
       </c>
       <c r="AX19" s="9">
-        <f t="shared" si="137"/>
+        <f t="shared" si="150"/>
         <v>0.44963456111151312</v>
       </c>
       <c r="AY19" s="9">
-        <f t="shared" si="137"/>
+        <f t="shared" si="150"/>
         <v>0.49693749538779425</v>
       </c>
       <c r="AZ19" s="9">
-        <f t="shared" ref="AZ19:BL19" si="138">AZ9/AZ3</f>
+        <f t="shared" ref="AZ19:BL19" si="151">AZ9/AZ3</f>
         <v>0.44616569361366809</v>
       </c>
       <c r="BA19" s="9">
-        <f t="shared" si="138"/>
+        <f t="shared" si="151"/>
         <v>0.33909192523734738</v>
       </c>
       <c r="BB19" s="9">
-        <f t="shared" si="138"/>
+        <f t="shared" si="151"/>
         <v>0.38004559942302774</v>
       </c>
       <c r="BC19" s="9">
-        <f t="shared" si="138"/>
+        <f t="shared" si="151"/>
         <v>0.39645040660058173</v>
       </c>
       <c r="BD19" s="9">
-        <f t="shared" si="138"/>
+        <f t="shared" si="151"/>
         <v>0.24822269293107735</v>
       </c>
       <c r="BE19" s="9">
-        <f t="shared" si="138"/>
+        <f t="shared" si="151"/>
         <v>0.34786307713932724</v>
       </c>
       <c r="BF19" s="9">
-        <f t="shared" si="138"/>
+        <f t="shared" si="151"/>
         <v>0.41234042553191491</v>
       </c>
       <c r="BG19" s="9">
-        <f t="shared" si="138"/>
+        <f t="shared" si="151"/>
         <v>0.41438210633692429</v>
       </c>
       <c r="BH19" s="9">
-        <f t="shared" si="138"/>
-        <v>0.4120574802664102</v>
+        <f t="shared" si="151"/>
+        <v>0.37885500365417379</v>
       </c>
       <c r="BI19" s="9">
-        <f t="shared" si="138"/>
-        <v>0.4189632901684156</v>
+        <f t="shared" si="151"/>
+        <v>0.36940299132806148</v>
       </c>
       <c r="BJ19" s="9">
-        <f t="shared" si="138"/>
-        <v>0.42585339188647209</v>
+        <f t="shared" si="151"/>
+        <v>0.36575255199467882</v>
       </c>
       <c r="BK19" s="9">
-        <f t="shared" si="138"/>
-        <v>0.42956276314848835</v>
+        <f t="shared" si="151"/>
+        <v>0.36950728959472956</v>
       </c>
       <c r="BL19" s="9">
-        <f t="shared" si="138"/>
-        <v>0.43010197677058398</v>
+        <f t="shared" si="151"/>
+        <v>0.3732620271947803</v>
       </c>
       <c r="BM19" s="9">
-        <f t="shared" ref="BM19:BQ19" si="139">BM9/BM3</f>
-        <v>0.43010197677058404</v>
+        <f t="shared" ref="BM19:BQ19" si="152">BM9/BM3</f>
+        <v>0.37701676479483076</v>
       </c>
       <c r="BN19" s="9">
-        <f t="shared" si="139"/>
-        <v>0.43010197677058398</v>
+        <f t="shared" si="152"/>
+        <v>0.37701676479483076</v>
       </c>
       <c r="BO19" s="9">
-        <f t="shared" si="139"/>
-        <v>0.43010197677058398</v>
+        <f t="shared" si="152"/>
+        <v>0.37701676479483082</v>
       </c>
       <c r="BP19" s="9">
-        <f t="shared" si="139"/>
-        <v>0.43010197677058404</v>
+        <f t="shared" si="152"/>
+        <v>0.37701676479483098</v>
       </c>
       <c r="BQ19" s="9">
-        <f t="shared" si="139"/>
-        <v>0.43010197677058404</v>
+        <f t="shared" si="152"/>
+        <v>0.37701676479483082</v>
       </c>
       <c r="BS19" t="s">
         <v>44</v>
@@ -6206,237 +6395,249 @@
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
       <c r="G20" s="9">
-        <f t="shared" ref="G20:R20" si="140">G6/C6-1</f>
+        <f t="shared" ref="G20:R20" si="153">G6/C6-1</f>
         <v>0.22028353326063255</v>
       </c>
       <c r="H20" s="9">
-        <f t="shared" si="140"/>
+        <f t="shared" si="153"/>
         <v>0.31474726420010413</v>
       </c>
       <c r="I20" s="9">
-        <f t="shared" si="140"/>
+        <f t="shared" si="153"/>
         <v>0.29483430799220267</v>
       </c>
       <c r="J20" s="9">
-        <f t="shared" si="140"/>
+        <f t="shared" si="153"/>
         <v>0.46485377116469984</v>
       </c>
       <c r="K20" s="9">
-        <f t="shared" si="140"/>
+        <f t="shared" si="153"/>
         <v>0.27792672028596965</v>
       </c>
       <c r="L20" s="9">
-        <f t="shared" si="140"/>
+        <f t="shared" si="153"/>
         <v>0.31391200951248521</v>
       </c>
       <c r="M20" s="9">
-        <f t="shared" si="140"/>
+        <f t="shared" si="153"/>
         <v>0.33534060971019941</v>
       </c>
       <c r="N20" s="9">
-        <f t="shared" si="140"/>
+        <f t="shared" si="153"/>
         <v>0.35796847635726792</v>
       </c>
       <c r="O20" s="9">
-        <f t="shared" si="140"/>
+        <f t="shared" si="153"/>
         <v>0.40384615384615374</v>
       </c>
       <c r="P20" s="9">
-        <f t="shared" si="140"/>
+        <f t="shared" si="153"/>
         <v>0.34600301659125199</v>
       </c>
       <c r="Q20" s="9">
-        <f t="shared" si="140"/>
+        <f t="shared" si="153"/>
         <v>0.34244644870349483</v>
       </c>
       <c r="R20" s="9">
-        <f t="shared" si="140"/>
+        <f t="shared" si="153"/>
         <v>0.34330668042300738</v>
       </c>
       <c r="S20" s="9">
-        <f t="shared" ref="S20" si="141">S6/O6-1</f>
+        <f t="shared" ref="S20" si="154">S6/O6-1</f>
         <v>0.29439601494396017</v>
       </c>
       <c r="T20" s="9">
-        <f t="shared" ref="T20" si="142">T6/P6-1</f>
+        <f t="shared" ref="T20" si="155">T6/P6-1</f>
         <v>0.36620349619004933</v>
       </c>
       <c r="U20" s="9">
-        <f t="shared" ref="U20" si="143">U6/Q6-1</f>
+        <f t="shared" ref="U20" si="156">U6/Q6-1</f>
         <v>0.32605500734830994</v>
       </c>
       <c r="V20" s="9">
-        <f t="shared" ref="V20" si="144">V6/R6-1</f>
+        <f t="shared" ref="V20" si="157">V6/R6-1</f>
         <v>0.35291858678955457</v>
       </c>
       <c r="W20" s="9">
-        <f t="shared" ref="W20" si="145">W6/S6-1</f>
+        <f t="shared" ref="W20" si="158">W6/S6-1</f>
         <v>0.48297094477583213</v>
       </c>
       <c r="X20" s="9">
-        <f t="shared" ref="X20" si="146">X6/T6-1</f>
+        <f t="shared" ref="X20" si="159">X6/T6-1</f>
         <v>0.42552493438320216</v>
       </c>
       <c r="Y20" s="9">
-        <f t="shared" ref="Y20" si="147">Y6/U6-1</f>
+        <f t="shared" ref="Y20" si="160">Y6/U6-1</f>
         <v>0.45186827105763139</v>
       </c>
       <c r="Z20" s="9">
-        <f t="shared" ref="Z20" si="148">Z6/V6-1</f>
+        <f t="shared" ref="Z20" si="161">Z6/V6-1</f>
         <v>0.38674425205790519</v>
       </c>
       <c r="AA20" s="9">
-        <f t="shared" ref="AA20" si="149">AA6/W6-1</f>
+        <f t="shared" ref="AA20" si="162">AA6/W6-1</f>
         <v>0.21720513818606468</v>
       </c>
       <c r="AB20" s="9">
-        <f t="shared" ref="AB20" si="150">AB6/X6-1</f>
+        <f t="shared" ref="AB20" si="163">AB6/X6-1</f>
         <v>7.5258918296893018E-2</v>
       </c>
       <c r="AC20" s="9">
-        <f t="shared" ref="AC20" si="151">AC6/Y6-1</f>
+        <f t="shared" ref="AC20" si="164">AC6/Y6-1</f>
         <v>7.7426390403489975E-3</v>
       </c>
       <c r="AD20" s="9">
-        <f t="shared" ref="AD20" si="152">AD6/Z6-1</f>
+        <f t="shared" ref="AD20" si="165">AD6/Z6-1</f>
         <v>7.6348377852829774E-2</v>
       </c>
       <c r="AE20" s="9">
-        <f t="shared" ref="AE20" si="153">AE6/AA6-1</f>
+        <f t="shared" ref="AE20" si="166">AE6/AA6-1</f>
         <v>6.3639270866645337E-2</v>
       </c>
       <c r="AF20" s="9">
-        <f t="shared" ref="AF20" si="154">AF6/AB6-1</f>
+        <f t="shared" ref="AF20" si="167">AF6/AB6-1</f>
         <v>0.12767551369863006</v>
       </c>
       <c r="AG20" s="9">
-        <f t="shared" ref="AG20" si="155">AG6/AC6-1</f>
+        <f t="shared" ref="AG20" si="168">AG6/AC6-1</f>
         <v>0.20950113624066669</v>
       </c>
       <c r="AH20" s="9">
-        <f t="shared" ref="AH20" si="156">AH6/AD6-1</f>
+        <f t="shared" ref="AH20" si="169">AH6/AD6-1</f>
         <v>0.15812494057240656</v>
       </c>
       <c r="AI20" s="9">
-        <f t="shared" ref="AI20" si="157">AI6/AE6-1</f>
+        <f t="shared" ref="AI20" si="170">AI6/AE6-1</f>
         <v>0.21767889356584491</v>
       </c>
       <c r="AJ20" s="9">
-        <f t="shared" ref="AJ20" si="158">AJ6/AF6-1</f>
+        <f t="shared" ref="AJ20" si="171">AJ6/AF6-1</f>
         <v>0.22824333301698774</v>
       </c>
       <c r="AK20" s="9">
-        <f t="shared" ref="AK20" si="159">AK6/AG6-1</f>
+        <f t="shared" ref="AK20" si="172">AK6/AG6-1</f>
         <v>0.35492529301243625</v>
       </c>
       <c r="AL20" s="9">
-        <f t="shared" ref="AL20" si="160">AL6/AH6-1</f>
+        <f t="shared" ref="AL20" si="173">AL6/AH6-1</f>
         <v>0.40689655172413786</v>
       </c>
-      <c r="AM20" s="9"/>
-      <c r="AN20" s="9"/>
-      <c r="AO20" s="9"/>
-      <c r="AP20" s="9"/>
+      <c r="AM20" s="9">
+        <f t="shared" ref="AM20" si="174">AM6/AI6-1</f>
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="AN20" s="9">
+        <f t="shared" ref="AN20" si="175">AN6/AJ6-1</f>
+        <v>0.39999999999999991</v>
+      </c>
+      <c r="AO20" s="9">
+        <f t="shared" ref="AO20" si="176">AO6/AK6-1</f>
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="AP20" s="9">
+        <f t="shared" ref="AP20" si="177">AP6/AL6-1</f>
+        <v>0.25</v>
+      </c>
       <c r="AQ20" s="9"/>
       <c r="AR20" s="9"/>
       <c r="AS20" s="9">
-        <f t="shared" ref="AS20" si="161">AS6/AR6-1</f>
+        <f t="shared" ref="AS20" si="178">AS6/AR6-1</f>
         <v>1.6944444444444446</v>
       </c>
       <c r="AT20" s="9">
-        <f t="shared" ref="AT20" si="162">AT6/AS6-1</f>
+        <f t="shared" ref="AT20" si="179">AT6/AS6-1</f>
         <v>2.6056701030927836</v>
       </c>
       <c r="AU20" s="9">
-        <f t="shared" ref="AU20" si="163">AU6/AT6-1</f>
+        <f t="shared" ref="AU20" si="180">AU6/AT6-1</f>
         <v>1.1436740528949274E-2</v>
       </c>
       <c r="AV20" s="9">
-        <f t="shared" ref="AV20" si="164">AV6/AU6-1</f>
+        <f t="shared" ref="AV20" si="181">AV6/AU6-1</f>
         <v>0.88409893992932864</v>
       </c>
       <c r="AW20" s="9">
-        <f t="shared" ref="AW20" si="165">AW6/AV6-1</f>
+        <f t="shared" ref="AW20" si="182">AW6/AV6-1</f>
         <v>0.80645161290322576</v>
       </c>
       <c r="AX20" s="9">
-        <f t="shared" ref="AX20" si="166">AX6/AW6-1</f>
+        <f t="shared" ref="AX20" si="183">AX6/AW6-1</f>
         <v>0.22902823920265791</v>
       </c>
       <c r="AY20" s="9">
-        <f t="shared" ref="AY20" si="167">AY6/AX6-1</f>
+        <f t="shared" ref="AY20" si="184">AY6/AX6-1</f>
         <v>0.31001858422030759</v>
       </c>
       <c r="AZ20" s="9">
-        <f t="shared" ref="AZ20:BL20" si="168">AZ6/AY6-1</f>
+        <f t="shared" ref="AZ20:BL20" si="185">AZ6/AY6-1</f>
         <v>0.3248645860201187</v>
       </c>
       <c r="BA20" s="9">
-        <f t="shared" si="168"/>
+        <f t="shared" si="185"/>
         <v>0.32385865861968277</v>
       </c>
       <c r="BB20" s="9">
-        <f t="shared" si="168"/>
+        <f t="shared" si="185"/>
         <v>0.35647058823529409</v>
       </c>
       <c r="BC20" s="9">
-        <f t="shared" si="168"/>
+        <f t="shared" si="185"/>
         <v>0.3364592367736341</v>
       </c>
       <c r="BD20" s="9">
-        <f t="shared" si="168"/>
+        <f t="shared" si="185"/>
         <v>0.43329953356317175</v>
       </c>
       <c r="BE20" s="9">
-        <f t="shared" si="168"/>
+        <f t="shared" si="185"/>
         <v>8.8997679551757303E-2</v>
       </c>
       <c r="BF20" s="9">
-        <f t="shared" si="168"/>
+        <f t="shared" si="185"/>
         <v>0.14003585999012547</v>
       </c>
       <c r="BG20" s="9">
-        <f t="shared" si="168"/>
+        <f t="shared" si="185"/>
         <v>0.30771334792122529</v>
       </c>
       <c r="BH20" s="9">
-        <f t="shared" si="168"/>
-        <v>0.1399999999999999</v>
+        <f t="shared" si="185"/>
+        <v>0.33939029491738126</v>
       </c>
       <c r="BI20" s="9">
-        <f t="shared" si="168"/>
-        <v>6.0000000000000053E-2</v>
+        <f t="shared" si="185"/>
+        <v>0.16999999999999993</v>
       </c>
       <c r="BJ20" s="9">
-        <f t="shared" si="168"/>
+        <f t="shared" si="185"/>
+        <v>8.0000000000000071E-2</v>
+      </c>
+      <c r="BK20" s="9">
+        <f t="shared" si="185"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="BK20" s="9">
-        <f t="shared" si="168"/>
+      <c r="BL20" s="9">
+        <f t="shared" si="185"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="BL20" s="9">
-        <f t="shared" si="168"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
       <c r="BM20" s="9">
-        <f t="shared" ref="BM20" si="169">BM6/BL6-1</f>
+        <f t="shared" ref="BM20" si="186">BM6/BL6-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BN20" s="9">
-        <f t="shared" ref="BN20" si="170">BN6/BM6-1</f>
+        <f t="shared" ref="BN20" si="187">BN6/BM6-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BO20" s="9">
-        <f t="shared" ref="BO20" si="171">BO6/BN6-1</f>
+        <f t="shared" ref="BO20" si="188">BO6/BN6-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BP20" s="9">
-        <f t="shared" ref="BP20" si="172">BP6/BO6-1</f>
+        <f t="shared" ref="BP20" si="189">BP6/BO6-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BQ20" s="9">
-        <f t="shared" ref="BQ20" si="173">BQ6/BP6-1</f>
+        <f t="shared" ref="BQ20" si="190">BQ6/BP6-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BS20" t="s">
@@ -6444,7 +6645,7 @@
       </c>
       <c r="BT20" s="20">
         <f>NPV(BT19,BH13:FT13)</f>
-        <v>2036350.4827568533</v>
+        <v>2047684.3471044214</v>
       </c>
     </row>
     <row r="21" spans="2:72">
@@ -6456,253 +6657,265 @@
         <v>0.13159860557768924</v>
       </c>
       <c r="D21" s="9">
-        <f t="shared" ref="D21:R21" si="174">D7/D3</f>
+        <f t="shared" ref="D21:R21" si="191">D7/D3</f>
         <v>0.12058791975109967</v>
       </c>
       <c r="E21" s="9">
-        <f t="shared" si="174"/>
+        <f t="shared" si="191"/>
         <v>0.11328427575522851</v>
       </c>
       <c r="F21" s="9">
-        <f t="shared" si="174"/>
+        <f t="shared" si="191"/>
         <v>0.1059204440333025</v>
       </c>
       <c r="G21" s="9">
-        <f t="shared" si="174"/>
+        <f t="shared" si="191"/>
         <v>0.13329433394618084</v>
       </c>
       <c r="H21" s="9">
-        <f t="shared" si="174"/>
+        <f t="shared" si="191"/>
         <v>0.14020104300506386</v>
       </c>
       <c r="I21" s="9">
-        <f t="shared" si="174"/>
+        <f t="shared" si="191"/>
         <v>0.14045312158519704</v>
       </c>
       <c r="J21" s="9">
-        <f t="shared" si="174"/>
+        <f t="shared" si="191"/>
         <v>0.14585550431595129</v>
       </c>
       <c r="K21" s="9">
-        <f t="shared" si="174"/>
+        <f t="shared" si="191"/>
         <v>0.13397890827087616</v>
       </c>
       <c r="L21" s="9">
-        <f t="shared" si="174"/>
+        <f t="shared" si="191"/>
         <v>0.14312818688485712</v>
       </c>
       <c r="M21" s="9">
-        <f t="shared" si="174"/>
+        <f t="shared" si="191"/>
         <v>0.13686834353047814</v>
       </c>
       <c r="N21" s="9">
-        <f t="shared" si="174"/>
+        <f t="shared" si="191"/>
         <v>0.14353476899724885</v>
       </c>
       <c r="O21" s="9">
-        <f t="shared" si="174"/>
+        <f t="shared" si="191"/>
         <v>0.15712916502226984</v>
       </c>
       <c r="P21" s="9">
-        <f t="shared" si="174"/>
+        <f t="shared" si="191"/>
         <v>0.15197731042971049</v>
       </c>
       <c r="Q21" s="9">
-        <f t="shared" si="174"/>
+        <f t="shared" si="191"/>
         <v>0.12496506753609687</v>
       </c>
       <c r="R21" s="9">
-        <f t="shared" si="174"/>
+        <f t="shared" si="191"/>
         <v>0.11684240524365916</v>
       </c>
       <c r="S21" s="9">
-        <f t="shared" ref="S21:V21" si="175">S7/S3</f>
+        <f t="shared" ref="S21:V21" si="192">S7/S3</f>
         <v>0.10863169156700164</v>
       </c>
       <c r="T21" s="9">
-        <f t="shared" si="175"/>
+        <f t="shared" si="192"/>
         <v>0.1120817140695395</v>
       </c>
       <c r="U21" s="9">
-        <f t="shared" si="175"/>
+        <f t="shared" si="192"/>
         <v>0.1225094794898311</v>
       </c>
       <c r="V21" s="9">
-        <f t="shared" si="175"/>
+        <f t="shared" si="192"/>
         <v>0.13029016067238872</v>
       </c>
       <c r="W21" s="9">
-        <f t="shared" ref="W21:AE21" si="176">W7/W3</f>
+        <f t="shared" ref="W21:AE21" si="193">W7/W3</f>
         <v>0.11867564855955282</v>
       </c>
       <c r="X21" s="9">
-        <f t="shared" si="176"/>
+        <f t="shared" si="193"/>
         <v>0.12473110818125044</v>
       </c>
       <c r="Y21" s="9">
-        <f t="shared" si="176"/>
+        <f t="shared" si="193"/>
         <v>0.13639315869235766</v>
       </c>
       <c r="Z21" s="9">
-        <f t="shared" si="176"/>
+        <f t="shared" si="193"/>
         <v>0.142204259288046</v>
       </c>
       <c r="AA21" s="9">
-        <f t="shared" si="176"/>
+        <f t="shared" si="193"/>
         <v>0.10626636411241054</v>
       </c>
       <c r="AB21" s="9">
-        <f t="shared" si="176"/>
+        <f t="shared" si="193"/>
         <v>9.8565580174380454E-2</v>
       </c>
       <c r="AC21" s="9">
-        <f t="shared" si="176"/>
+        <f t="shared" si="193"/>
         <v>8.3594839609483967E-2</v>
       </c>
       <c r="AD21" s="9">
-        <f t="shared" si="176"/>
+        <f t="shared" si="193"/>
         <v>8.0426815586746775E-2</v>
       </c>
       <c r="AE21" s="9">
-        <f t="shared" si="176"/>
+        <f t="shared" si="193"/>
         <v>7.0333287614867651E-2</v>
       </c>
       <c r="AF21" s="9">
-        <f t="shared" ref="AF21:AH21" si="177">AF7/AF3</f>
+        <f t="shared" ref="AF21:AH21" si="194">AF7/AF3</f>
         <v>6.9642445803793099E-2</v>
       </c>
       <c r="AG21" s="9">
-        <f t="shared" si="177"/>
+        <f t="shared" si="194"/>
         <v>6.9526226317475182E-2</v>
       </c>
       <c r="AH21" s="9">
-        <f t="shared" si="177"/>
+        <f t="shared" si="194"/>
         <v>6.6962901725741444E-2</v>
       </c>
       <c r="AI21" s="9">
-        <f t="shared" ref="AI21:AL21" si="178">AI7/AI3</f>
+        <f t="shared" ref="AI21:AL21" si="195">AI7/AI3</f>
         <v>6.5155740416883295E-2</v>
       </c>
       <c r="AJ21" s="9">
-        <f t="shared" si="178"/>
+        <f t="shared" si="195"/>
         <v>6.269467126862531E-2</v>
       </c>
       <c r="AK21" s="9">
-        <f t="shared" si="178"/>
+        <f t="shared" si="195"/>
         <v>5.5520861793060379E-2</v>
       </c>
       <c r="AL21" s="9">
-        <f t="shared" si="178"/>
+        <f t="shared" si="195"/>
         <v>5.6934867179803984E-2</v>
       </c>
-      <c r="AM21" s="9"/>
-      <c r="AN21" s="9"/>
-      <c r="AO21" s="9"/>
-      <c r="AP21" s="9"/>
+      <c r="AM21" s="9">
+        <f t="shared" ref="AM21:AP21" si="196">AM7/AM3</f>
+        <v>0.06</v>
+      </c>
+      <c r="AN21" s="9">
+        <f t="shared" si="196"/>
+        <v>0.06</v>
+      </c>
+      <c r="AO21" s="9">
+        <f t="shared" si="196"/>
+        <v>0.06</v>
+      </c>
+      <c r="AP21" s="9">
+        <f t="shared" si="196"/>
+        <v>5.9999999999999991E-2</v>
+      </c>
       <c r="AQ21" s="9"/>
       <c r="AR21" s="9">
-        <f t="shared" ref="AR21:AV21" si="179">AR7/AR3</f>
+        <f t="shared" ref="AR21:AV21" si="197">AR7/AR3</f>
         <v>8.4599797365754806E-2</v>
       </c>
       <c r="AS21" s="9">
-        <f t="shared" si="179"/>
+        <f t="shared" si="197"/>
         <v>0.1059013742926435</v>
       </c>
       <c r="AT21" s="9">
-        <f t="shared" si="179"/>
+        <f t="shared" si="197"/>
         <v>0.17606602475928473</v>
       </c>
       <c r="AU21" s="9">
-        <f t="shared" si="179"/>
+        <f t="shared" si="197"/>
         <v>0.12665142276422764</v>
       </c>
       <c r="AV21" s="9">
-        <f t="shared" si="179"/>
+        <f t="shared" si="197"/>
         <v>0.13476656505695492</v>
       </c>
       <c r="AW21" s="9">
-        <f t="shared" ref="AW21:AY21" si="180">AW7/AW3</f>
+        <f t="shared" ref="AW21:AY21" si="198">AW7/AW3</f>
         <v>0.15199687639446677</v>
       </c>
       <c r="AX21" s="9">
-        <f t="shared" si="180"/>
+        <f t="shared" si="198"/>
         <v>0.13647876112598595</v>
       </c>
       <c r="AY21" s="9">
-        <f t="shared" si="180"/>
+        <f t="shared" si="198"/>
         <v>0.1162275846800974</v>
       </c>
       <c r="AZ21" s="9">
-        <f t="shared" ref="AZ21:BL21" si="181">AZ7/AZ3</f>
+        <f t="shared" ref="AZ21:BL21" si="199">AZ7/AZ3</f>
         <v>0.14049571976073641</v>
       </c>
       <c r="BA21" s="9">
-        <f t="shared" si="181"/>
+        <f t="shared" si="199"/>
         <v>0.13973428413769684</v>
       </c>
       <c r="BB21" s="9">
-        <f t="shared" si="181"/>
+        <f t="shared" si="199"/>
         <v>0.13482074308447525</v>
       </c>
       <c r="BC21" s="9">
-        <f t="shared" si="181"/>
+        <f t="shared" si="199"/>
         <v>0.11908012448167965</v>
       </c>
       <c r="BD21" s="9">
-        <f t="shared" si="181"/>
+        <f t="shared" si="199"/>
         <v>0.13087326021147597</v>
       </c>
       <c r="BE21" s="9">
-        <f t="shared" si="181"/>
+        <f t="shared" si="199"/>
         <v>9.1003247738050325E-2</v>
       </c>
       <c r="BF21" s="9">
-        <f t="shared" si="181"/>
+        <f t="shared" si="199"/>
         <v>6.8978723404255315E-2</v>
       </c>
       <c r="BG21" s="9">
-        <f t="shared" si="181"/>
+        <f t="shared" si="199"/>
         <v>5.9667106212524572E-2</v>
       </c>
       <c r="BH21" s="9">
-        <f t="shared" si="181"/>
-        <v>6.5000000000000002E-2</v>
+        <f t="shared" si="199"/>
+        <v>0.06</v>
       </c>
       <c r="BI21" s="9">
-        <f t="shared" si="181"/>
-        <v>6.5000000000000002E-2</v>
+        <f t="shared" si="199"/>
+        <v>0.06</v>
       </c>
       <c r="BJ21" s="9">
-        <f t="shared" si="181"/>
-        <v>6.5000000000000002E-2</v>
+        <f t="shared" si="199"/>
+        <v>0.06</v>
       </c>
       <c r="BK21" s="9">
-        <f t="shared" si="181"/>
-        <v>6.5000000000000002E-2</v>
+        <f t="shared" si="199"/>
+        <v>0.06</v>
       </c>
       <c r="BL21" s="9">
-        <f t="shared" si="181"/>
-        <v>6.5000000000000002E-2</v>
+        <f t="shared" si="199"/>
+        <v>6.0000000000000005E-2</v>
       </c>
       <c r="BM21" s="9">
-        <f t="shared" ref="BM21:BQ21" si="182">BM7/BM3</f>
-        <v>6.5000000000000002E-2</v>
+        <f t="shared" ref="BM21:BQ21" si="200">BM7/BM3</f>
+        <v>5.9999999999999991E-2</v>
       </c>
       <c r="BN21" s="9">
-        <f t="shared" si="182"/>
-        <v>6.5000000000000002E-2</v>
+        <f t="shared" si="200"/>
+        <v>0.06</v>
       </c>
       <c r="BO21" s="9">
-        <f t="shared" si="182"/>
-        <v>6.5000000000000002E-2</v>
+        <f t="shared" si="200"/>
+        <v>5.9999999999999991E-2</v>
       </c>
       <c r="BP21" s="9">
-        <f t="shared" si="182"/>
-        <v>6.5000000000000002E-2</v>
+        <f t="shared" si="200"/>
+        <v>0.06</v>
       </c>
       <c r="BQ21" s="9">
-        <f t="shared" si="182"/>
-        <v>6.5000000000000002E-2</v>
+        <f t="shared" si="200"/>
+        <v>0.06</v>
       </c>
       <c r="BS21" t="s">
         <v>46</v>
@@ -6721,237 +6934,249 @@
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
       <c r="G22" s="9">
-        <f t="shared" ref="G22" si="183">G8/C8-1</f>
+        <f t="shared" ref="G22" si="201">G8/C8-1</f>
         <v>0.1557251908396946</v>
       </c>
       <c r="H22" s="9">
-        <f t="shared" ref="H22" si="184">H8/D8-1</f>
+        <f t="shared" ref="H22" si="202">H8/D8-1</f>
         <v>0.21249999999999991</v>
       </c>
       <c r="I22" s="9">
-        <f t="shared" ref="I22" si="185">I8/E8-1</f>
+        <f t="shared" ref="I22" si="203">I8/E8-1</f>
         <v>0.75932835820895517</v>
       </c>
       <c r="J22" s="9">
-        <f t="shared" ref="J22" si="186">J8/F8-1</f>
+        <f t="shared" ref="J22" si="204">J8/F8-1</f>
         <v>0.42274052478134116</v>
       </c>
       <c r="K22" s="9">
-        <f t="shared" ref="K22" si="187">K8/G8-1</f>
+        <f t="shared" ref="K22" si="205">K8/G8-1</f>
         <v>4.3685601056803174</v>
       </c>
       <c r="L22" s="9">
-        <f t="shared" ref="L22" si="188">L8/H8-1</f>
+        <f t="shared" ref="L22" si="206">L8/H8-1</f>
         <v>3.1546391752577323</v>
       </c>
       <c r="M22" s="9">
-        <f t="shared" ref="M22" si="189">M8/I8-1</f>
+        <f t="shared" ref="M22" si="207">M8/I8-1</f>
         <v>0.42948038176033942</v>
       </c>
       <c r="N22" s="9">
-        <f t="shared" ref="N22" si="190">N8/J8-1</f>
+        <f t="shared" ref="N22" si="208">N8/J8-1</f>
         <v>0.87397540983606548</v>
       </c>
       <c r="O22" s="9">
-        <f t="shared" ref="O22" si="191">O8/K8-1</f>
+        <f t="shared" ref="O22" si="209">O8/K8-1</f>
         <v>-0.6104822834645669</v>
       </c>
       <c r="P22" s="9">
-        <f t="shared" ref="P22" si="192">P8/L8-1</f>
+        <f t="shared" ref="P22" si="210">P8/L8-1</f>
         <v>-0.50589330024813894</v>
       </c>
       <c r="Q22" s="9">
-        <f t="shared" ref="Q22" si="193">Q8/M8-1</f>
+        <f t="shared" ref="Q22" si="211">Q8/M8-1</f>
         <v>0.32789317507418403</v>
       </c>
       <c r="R22" s="9">
-        <f t="shared" ref="R22" si="194">R8/N8-1</f>
+        <f t="shared" ref="R22" si="212">R8/N8-1</f>
         <v>-0.12575177692728268</v>
       </c>
       <c r="S22" s="9">
-        <f t="shared" ref="S22" si="195">S8/O8-1</f>
+        <f t="shared" ref="S22" si="213">S8/O8-1</f>
         <v>2.4636765634870494E-2</v>
       </c>
       <c r="T22" s="9">
-        <f t="shared" ref="T22" si="196">T8/P8-1</f>
+        <f t="shared" ref="T22" si="214">T8/P8-1</f>
         <v>0.22787193973634645</v>
       </c>
       <c r="U22" s="9">
-        <f t="shared" ref="U22" si="197">U8/Q8-1</f>
+        <f t="shared" ref="U22" si="215">U8/Q8-1</f>
         <v>0.64581005586592188</v>
       </c>
       <c r="V22" s="9">
-        <f t="shared" ref="V22" si="198">V8/R8-1</f>
+        <f t="shared" ref="V22" si="216">V8/R8-1</f>
         <v>1.0669168230143842</v>
       </c>
       <c r="W22" s="9">
-        <f t="shared" ref="W22" si="199">W8/S8-1</f>
+        <f t="shared" ref="W22" si="217">W8/S8-1</f>
         <v>0.45499383477188649</v>
       </c>
       <c r="X22" s="9">
-        <f t="shared" ref="X22" si="200">X8/T8-1</f>
+        <f t="shared" ref="X22" si="218">X8/T8-1</f>
         <v>0.52709611451942751</v>
       </c>
       <c r="Y22" s="9">
-        <f t="shared" ref="Y22" si="201">Y8/U8-1</f>
+        <f t="shared" ref="Y22" si="219">Y8/U8-1</f>
         <v>0.14867617107942976</v>
       </c>
       <c r="Z22" s="9">
-        <f t="shared" ref="Z22" si="202">Z8/V8-1</f>
+        <f t="shared" ref="Z22" si="220">Z8/V8-1</f>
         <v>-6.656580937972767E-2</v>
       </c>
       <c r="AA22" s="9">
-        <f t="shared" ref="AA22" si="203">AA8/W8-1</f>
+        <f t="shared" ref="AA22" si="221">AA8/W8-1</f>
         <v>0.22245762711864403</v>
       </c>
       <c r="AB22" s="9">
-        <f t="shared" ref="AB22" si="204">AB8/X8-1</f>
+        <f t="shared" ref="AB22" si="222">AB8/X8-1</f>
         <v>0.39404084365584202</v>
       </c>
       <c r="AC22" s="9">
-        <f t="shared" ref="AC22" si="205">AC8/Y8-1</f>
+        <f t="shared" ref="AC22" si="223">AC8/Y8-1</f>
         <v>-0.38829787234042556</v>
       </c>
       <c r="AD22" s="9">
-        <f t="shared" ref="AD22" si="206">AD8/Z8-1</f>
+        <f t="shared" ref="AD22" si="224">AD8/Z8-1</f>
         <v>-0.25802269043760129</v>
       </c>
       <c r="AE22" s="9">
-        <f t="shared" ref="AE22" si="207">AE8/AA8-1</f>
+        <f t="shared" ref="AE22" si="225">AE8/AA8-1</f>
         <v>0.19757365684575401</v>
       </c>
       <c r="AF22" s="9">
-        <f t="shared" ref="AF22" si="208">AF8/AB8-1</f>
+        <f t="shared" ref="AF22" si="226">AF8/AB8-1</f>
         <v>-0.12151777137367914</v>
       </c>
       <c r="AG22" s="9">
-        <f t="shared" ref="AG22" si="209">AG8/AC8-1</f>
+        <f t="shared" ref="AG22" si="227">AG8/AC8-1</f>
         <v>-9.9033816425120769E-2</v>
       </c>
       <c r="AH22" s="9">
-        <f t="shared" ref="AH22" si="210">AH8/AD8-1</f>
+        <f t="shared" ref="AH22" si="228">AH8/AD8-1</f>
         <v>9.6111839231105556E-3</v>
       </c>
       <c r="AI22" s="9">
-        <f t="shared" ref="AI22" si="211">AI8/AE8-1</f>
+        <f t="shared" ref="AI22" si="229">AI8/AE8-1</f>
         <v>-0.34008683068017365</v>
       </c>
       <c r="AJ22" s="9">
-        <f t="shared" ref="AJ22" si="212">AJ8/AF8-1</f>
+        <f t="shared" ref="AJ22" si="230">AJ8/AF8-1</f>
         <v>-0.27200656096227449</v>
       </c>
       <c r="AK22" s="9">
-        <f t="shared" ref="AK22" si="213">AK8/AG8-1</f>
+        <f t="shared" ref="AK22" si="231">AK8/AG8-1</f>
         <v>0.88310991957104568</v>
       </c>
       <c r="AL22" s="9">
-        <f t="shared" ref="AL22" si="214">AL8/AH8-1</f>
+        <f t="shared" ref="AL22" si="232">AL8/AH8-1</f>
         <v>0.59974037213327569</v>
       </c>
-      <c r="AM22" s="9"/>
-      <c r="AN22" s="9"/>
-      <c r="AO22" s="9"/>
-      <c r="AP22" s="9"/>
+      <c r="AM22" s="9">
+        <f t="shared" ref="AM22" si="233">AM8/AI8-1</f>
+        <v>0.5</v>
+      </c>
+      <c r="AN22" s="9">
+        <f t="shared" ref="AN22" si="234">AN8/AJ8-1</f>
+        <v>0.5</v>
+      </c>
+      <c r="AO22" s="9">
+        <f t="shared" ref="AO22" si="235">AO8/AK8-1</f>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="AP22" s="9">
+        <f t="shared" ref="AP22" si="236">AP8/AL8-1</f>
+        <v>0.19999999999999996</v>
+      </c>
       <c r="AQ22" s="9"/>
       <c r="AR22" s="9"/>
       <c r="AS22" s="9">
-        <f t="shared" ref="AS22" si="215">AS8/AR8-1</f>
+        <f t="shared" ref="AS22" si="237">AS8/AR8-1</f>
         <v>1.2753623188405796</v>
       </c>
       <c r="AT22" s="9">
-        <f t="shared" ref="AT22" si="216">AT8/AS8-1</f>
+        <f t="shared" ref="AT22" si="238">AT8/AS8-1</f>
         <v>1.8407643312101909</v>
       </c>
       <c r="AU22" s="9">
-        <f t="shared" ref="AU22" si="217">AU8/AT8-1</f>
+        <f t="shared" ref="AU22" si="239">AU8/AT8-1</f>
         <v>-0.12443946188340804</v>
       </c>
       <c r="AV22" s="9">
-        <f t="shared" ref="AV22" si="218">AV8/AU8-1</f>
+        <f t="shared" ref="AV22" si="240">AV8/AU8-1</f>
         <v>0.24583866837387958</v>
       </c>
       <c r="AW22" s="9">
-        <f t="shared" ref="AW22" si="219">AW8/AV8-1</f>
+        <f t="shared" ref="AW22" si="241">AW8/AV8-1</f>
         <v>0.33093525179856109</v>
       </c>
       <c r="AX22" s="9">
-        <f t="shared" ref="AX22" si="220">AX8/AW8-1</f>
+        <f t="shared" ref="AX22" si="242">AX8/AW8-1</f>
         <v>0.33667953667953676</v>
       </c>
       <c r="AY22" s="9">
-        <f t="shared" ref="AY22" si="221">AY8/AX8-1</f>
+        <f t="shared" ref="AY22" si="243">AY8/AX8-1</f>
         <v>0.45407279029462733</v>
       </c>
       <c r="AZ22" s="9">
-        <f t="shared" ref="AZ22:BL22" si="222">AZ8/AY8-1</f>
+        <f t="shared" ref="AZ22:BL22" si="244">AZ8/AY8-1</f>
         <v>0.37147397695669437</v>
       </c>
       <c r="BA22" s="9">
-        <f t="shared" si="222"/>
+        <f t="shared" si="244"/>
         <v>2.0315758980301273</v>
       </c>
       <c r="BB22" s="9">
-        <f t="shared" si="222"/>
+        <f t="shared" si="244"/>
         <v>-0.37267080745341619</v>
       </c>
       <c r="BC22" s="9">
-        <f t="shared" si="222"/>
+        <f t="shared" si="244"/>
         <v>0.49718202589489713</v>
       </c>
       <c r="BD22" s="9">
-        <f t="shared" si="222"/>
+        <f t="shared" si="244"/>
         <v>0.20215688269406851</v>
       </c>
       <c r="BE22" s="9">
-        <f t="shared" si="222"/>
+        <f t="shared" si="244"/>
         <v>-3.4529451591063021E-2</v>
       </c>
       <c r="BF22" s="9">
-        <f t="shared" si="222"/>
+        <f t="shared" si="244"/>
         <v>-1.0431276297335201E-2</v>
       </c>
       <c r="BG22" s="9">
-        <f t="shared" si="222"/>
+        <f t="shared" si="244"/>
         <v>7.6446097971476723E-2</v>
       </c>
       <c r="BH22" s="9">
-        <f t="shared" si="222"/>
-        <v>0.1399999999999999</v>
+        <f t="shared" si="244"/>
+        <v>0.32202929558920346</v>
       </c>
       <c r="BI22" s="9">
-        <f t="shared" si="222"/>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="244"/>
+        <v>0.15999999999999992</v>
       </c>
       <c r="BJ22" s="9">
-        <f t="shared" si="222"/>
+        <f t="shared" si="244"/>
+        <v>8.0000000000000071E-2</v>
+      </c>
+      <c r="BK22" s="9">
+        <f t="shared" si="244"/>
+        <v>4.0000000000000036E-2</v>
+      </c>
+      <c r="BL22" s="9">
+        <f t="shared" si="244"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="BK22" s="9">
-        <f t="shared" si="222"/>
+      <c r="BM22" s="9">
+        <f t="shared" ref="BM22" si="245">BM8/BL8-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BL22" s="9">
-        <f t="shared" si="222"/>
+      <c r="BN22" s="9">
+        <f t="shared" ref="BN22" si="246">BN8/BM8-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BM22" s="9">
-        <f t="shared" ref="BM22" si="223">BM8/BL8-1</f>
+      <c r="BO22" s="9">
+        <f t="shared" ref="BO22" si="247">BO8/BN8-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BN22" s="9">
-        <f t="shared" ref="BN22" si="224">BN8/BM8-1</f>
+      <c r="BP22" s="9">
+        <f t="shared" ref="BP22" si="248">BP8/BO8-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BO22" s="9">
-        <f t="shared" ref="BO22" si="225">BO8/BN8-1</f>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="BP22" s="9">
-        <f t="shared" ref="BP22" si="226">BP8/BO8-1</f>
-        <v>2.0000000000000018E-2</v>
-      </c>
       <c r="BQ22" s="9">
-        <f t="shared" ref="BQ22" si="227">BQ8/BP8-1</f>
+        <f t="shared" ref="BQ22" si="249">BQ8/BP8-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BS22" t="s">
@@ -6959,7 +7184,7 @@
       </c>
       <c r="BT22" s="20">
         <f>BT20+BT21</f>
-        <v>2086722.4827568533</v>
+        <v>2098056.3471044214</v>
       </c>
     </row>
     <row r="23" spans="2:72">
@@ -6971,525 +7196,549 @@
         <v>0.10240610328638497</v>
       </c>
       <c r="D23" s="9">
-        <f t="shared" ref="D23:R23" si="228">D12/D11</f>
+        <f t="shared" ref="D23:R23" si="250">D12/D11</f>
         <v>0.13324420677361853</v>
       </c>
       <c r="E23" s="9">
-        <f t="shared" si="228"/>
+        <f t="shared" si="250"/>
         <v>0.10103132161955691</v>
       </c>
       <c r="F23" s="9">
-        <f t="shared" si="228"/>
+        <f t="shared" si="250"/>
         <v>0.52452425623157328</v>
       </c>
       <c r="G23" s="9">
-        <f t="shared" si="228"/>
+        <f t="shared" si="250"/>
         <v>0.11105169340463458</v>
       </c>
       <c r="H23" s="9">
-        <f t="shared" si="228"/>
+        <f t="shared" si="250"/>
         <v>0.12985685071574643</v>
       </c>
       <c r="I23" s="9">
-        <f t="shared" si="228"/>
+        <f t="shared" si="250"/>
         <v>0.13108930987821379</v>
       </c>
       <c r="J23" s="9">
-        <f t="shared" si="228"/>
+        <f t="shared" si="250"/>
         <v>0.13662024840045164</v>
       </c>
       <c r="K23" s="9">
-        <f t="shared" si="228"/>
+        <f t="shared" si="250"/>
         <v>0.30241240666283747</v>
       </c>
       <c r="L23" s="9">
-        <f t="shared" si="228"/>
+        <f t="shared" si="250"/>
         <v>0.46051537822111388</v>
       </c>
       <c r="M23" s="9">
-        <f t="shared" si="228"/>
+        <f t="shared" si="250"/>
         <v>0.16891799699822621</v>
       </c>
       <c r="N23" s="9">
-        <f t="shared" si="228"/>
+        <f t="shared" si="250"/>
         <v>0.19849492856363835</v>
       </c>
       <c r="O23" s="9">
-        <f t="shared" si="228"/>
+        <f t="shared" si="250"/>
         <v>0.16362395495649207</v>
       </c>
       <c r="P23" s="9">
-        <f t="shared" si="228"/>
+        <f t="shared" si="250"/>
         <v>0.15543956940140272</v>
       </c>
       <c r="Q23" s="9">
-        <f t="shared" si="228"/>
+        <f t="shared" si="250"/>
         <v>3.5288331488995447E-2</v>
       </c>
       <c r="R23" s="9">
-        <f t="shared" si="228"/>
+        <f t="shared" si="250"/>
         <v>0.14063577173496744</v>
       </c>
       <c r="S23" s="9">
-        <f t="shared" ref="S23:V23" si="229">S12/S11</f>
+        <f t="shared" ref="S23:V23" si="251">S12/S11</f>
         <v>0.17438928975049986</v>
       </c>
       <c r="T23" s="9">
-        <f t="shared" si="229"/>
+        <f t="shared" si="251"/>
         <v>0.16934388236234316</v>
       </c>
       <c r="U23" s="9">
-        <f t="shared" si="229"/>
+        <f t="shared" si="251"/>
         <v>0.12976810222432561</v>
       </c>
       <c r="V23" s="9">
-        <f t="shared" si="229"/>
+        <f t="shared" si="251"/>
         <v>0.19028499448905684</v>
       </c>
       <c r="W23" s="9">
-        <f t="shared" ref="W23:AE23" si="230">W12/W11</f>
+        <f t="shared" ref="W23:AE23" si="252">W12/W11</f>
         <v>0.1619892231701841</v>
       </c>
       <c r="X23" s="9">
-        <f t="shared" si="230"/>
+        <f t="shared" si="252"/>
         <v>0.18311751771316884</v>
       </c>
       <c r="Y23" s="9">
-        <f t="shared" si="230"/>
+        <f t="shared" si="252"/>
         <v>0.21180057388809181</v>
       </c>
       <c r="Z23" s="9">
-        <f t="shared" si="230"/>
+        <f t="shared" si="252"/>
         <v>0.24345422019840623</v>
       </c>
       <c r="AA23" s="9">
-        <f t="shared" si="230"/>
+        <f t="shared" si="252"/>
         <v>0.21869440262761736</v>
       </c>
       <c r="AB23" s="9">
-        <f t="shared" si="230"/>
+        <f t="shared" si="252"/>
         <v>0.16194985472936618</v>
       </c>
       <c r="AC23" s="9">
-        <f t="shared" si="230"/>
+        <f t="shared" si="252"/>
         <v>0.17053883834849545</v>
       </c>
       <c r="AD23" s="9">
-        <f t="shared" si="230"/>
+        <f t="shared" si="252"/>
         <v>0.16605188005711566</v>
       </c>
       <c r="AE23" s="9">
-        <f t="shared" si="230"/>
+        <f t="shared" si="252"/>
         <v>0.12789959811041388</v>
       </c>
       <c r="AF23" s="9">
-        <f t="shared" ref="AF23:AH23" si="231">AF12/AF11</f>
+        <f t="shared" ref="AF23:AH23" si="253">AF12/AF11</f>
         <v>0.10863233152389778</v>
       </c>
       <c r="AG23" s="9">
-        <f t="shared" si="231"/>
+        <f t="shared" si="253"/>
         <v>0.11973964762652901</v>
       </c>
       <c r="AH23" s="9">
-        <f t="shared" si="231"/>
+        <f t="shared" si="253"/>
         <v>0.12339226469117848</v>
       </c>
       <c r="AI23" s="9">
-        <f t="shared" ref="AI23:AL23" si="232">AI12/AI11</f>
+        <f t="shared" ref="AI23:AL23" si="254">AI12/AI11</f>
         <v>9.4549015341094556E-2</v>
       </c>
       <c r="AJ23" s="9">
-        <f t="shared" si="232"/>
+        <f t="shared" si="254"/>
         <v>0.10699327943897925</v>
       </c>
       <c r="AK23" s="9">
-        <f t="shared" si="232"/>
+        <f t="shared" si="254"/>
         <v>0.13959285417532197</v>
       </c>
       <c r="AL23" s="9">
-        <f t="shared" si="232"/>
+        <f t="shared" si="254"/>
         <v>0.10199574031710973</v>
       </c>
-      <c r="AM23" s="9"/>
-      <c r="AN23" s="9"/>
-      <c r="AO23" s="9"/>
-      <c r="AP23" s="9"/>
+      <c r="AM23" s="9">
+        <f t="shared" ref="AM23:AP23" si="255">AM12/AM11</f>
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="AN23" s="9">
+        <f t="shared" si="255"/>
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="AO23" s="9">
+        <f t="shared" si="255"/>
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="AP23" s="9">
+        <f t="shared" si="255"/>
+        <v>0.14000000000000001</v>
+      </c>
       <c r="AQ23" s="9"/>
       <c r="AR23" s="9">
-        <f t="shared" ref="AR23:AV23" si="233">AR12/AR11</f>
+        <f t="shared" ref="AR23:AV23" si="256">AR12/AR11</f>
         <v>0.39880952380952384</v>
       </c>
       <c r="AS23" s="9">
-        <f t="shared" si="233"/>
+        <f t="shared" si="256"/>
         <v>0.41002949852507375</v>
       </c>
       <c r="AT23" s="9">
-        <f t="shared" si="233"/>
+        <f t="shared" si="256"/>
         <v>0.89271255060728749</v>
       </c>
       <c r="AU23" s="9">
-        <f t="shared" si="233"/>
+        <f t="shared" si="256"/>
         <v>0.45533769063180829</v>
       </c>
       <c r="AV23" s="9">
-        <f t="shared" si="233"/>
+        <f t="shared" si="256"/>
         <v>0.40122199592668023</v>
       </c>
       <c r="AW23" s="9">
-        <f t="shared" ref="AW23:AY23" si="234">AW12/AW11</f>
+        <f t="shared" ref="AW23:AY23" si="257">AW12/AW11</f>
         <v>0.4045850823377462</v>
       </c>
       <c r="AX23" s="9">
-        <f t="shared" si="234"/>
+        <f t="shared" si="257"/>
         <v>0.18381530595941845</v>
       </c>
       <c r="AY23" s="9">
-        <f t="shared" si="234"/>
+        <f t="shared" si="257"/>
         <v>0.26172671651937457</v>
       </c>
       <c r="AZ23" s="9">
-        <f t="shared" ref="AZ23:BL23" si="235">AZ12/AZ11</f>
+        <f t="shared" ref="AZ23:BL23" si="258">AZ12/AZ11</f>
         <v>0.12811009029612397</v>
       </c>
       <c r="BA23" s="9">
-        <f t="shared" si="235"/>
+        <f t="shared" si="258"/>
         <v>0.25520329138431752</v>
       </c>
       <c r="BB23" s="9">
-        <f t="shared" si="235"/>
+        <f t="shared" si="258"/>
         <v>0.12160940325497288</v>
       </c>
       <c r="BC23" s="9">
-        <f t="shared" si="235"/>
+        <f t="shared" si="258"/>
         <v>0.1673540173000867</v>
       </c>
       <c r="BD23" s="9">
-        <f t="shared" si="235"/>
+        <f t="shared" si="258"/>
         <v>0.19501023630243935</v>
       </c>
       <c r="BE23" s="9">
-        <f t="shared" si="235"/>
+        <f t="shared" si="258"/>
         <v>0.17466141137993207</v>
       </c>
       <c r="BF23" s="9">
-        <f t="shared" si="235"/>
+        <f t="shared" si="258"/>
         <v>0.1201493185172324</v>
       </c>
       <c r="BG23" s="9">
-        <f t="shared" si="235"/>
+        <f t="shared" si="258"/>
         <v>0.11107451942378567</v>
       </c>
       <c r="BH23" s="9">
-        <f t="shared" si="235"/>
+        <f t="shared" si="258"/>
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="BI23" s="9">
+        <f t="shared" si="258"/>
+        <v>0.11999999999999998</v>
+      </c>
+      <c r="BJ23" s="9">
+        <f t="shared" si="258"/>
         <v>0.12</v>
       </c>
-      <c r="BI23" s="9">
-        <f t="shared" si="235"/>
+      <c r="BK23" s="9">
+        <f t="shared" si="258"/>
         <v>0.12</v>
       </c>
-      <c r="BJ23" s="9">
-        <f t="shared" si="235"/>
+      <c r="BL23" s="9">
+        <f t="shared" si="258"/>
         <v>0.12</v>
       </c>
-      <c r="BK23" s="9">
-        <f t="shared" si="235"/>
+      <c r="BM23" s="9">
+        <f t="shared" ref="BM23:BQ23" si="259">BM12/BM11</f>
         <v>0.12</v>
       </c>
-      <c r="BL23" s="9">
-        <f t="shared" si="235"/>
+      <c r="BN23" s="9">
+        <f t="shared" si="259"/>
         <v>0.12</v>
       </c>
-      <c r="BM23" s="9">
-        <f t="shared" ref="BM23:BQ23" si="236">BM12/BM11</f>
+      <c r="BO23" s="9">
+        <f t="shared" si="259"/>
         <v>0.12</v>
       </c>
-      <c r="BN23" s="9">
-        <f t="shared" si="236"/>
+      <c r="BP23" s="9">
+        <f t="shared" si="259"/>
         <v>0.12</v>
       </c>
-      <c r="BO23" s="9">
-        <f t="shared" si="236"/>
-        <v>0.12</v>
-      </c>
-      <c r="BP23" s="9">
-        <f t="shared" si="236"/>
-        <v>0.12</v>
-      </c>
       <c r="BQ23" s="9">
-        <f t="shared" si="236"/>
-        <v>0.12000000000000001</v>
+        <f t="shared" si="259"/>
+        <v>0.11999999999999998</v>
       </c>
       <c r="BS23" t="s">
         <v>48</v>
       </c>
       <c r="BT23" s="5">
         <f>BT22/BL14</f>
-        <v>829.05144328838037</v>
+        <v>833.55436913167318</v>
       </c>
     </row>
     <row r="24" spans="2:72">
       <c r="B24" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C24" s="9">
         <f>C13/C3</f>
         <v>0.38085159362549803</v>
       </c>
       <c r="D24" s="9">
-        <f t="shared" ref="D24:AL24" si="237">D13/D3</f>
+        <f t="shared" ref="D24:AL24" si="260">D13/D3</f>
         <v>0.41733719557987342</v>
       </c>
       <c r="E24" s="9">
-        <f t="shared" si="237"/>
+        <f t="shared" si="260"/>
         <v>0.4557513555383424</v>
       </c>
       <c r="F24" s="9">
-        <f t="shared" si="237"/>
+        <f t="shared" si="260"/>
         <v>0.2735121800801727</v>
       </c>
       <c r="G24" s="9">
-        <f t="shared" si="237"/>
+        <f t="shared" si="260"/>
         <v>0.41676416513454789</v>
       </c>
       <c r="H24" s="9">
-        <f t="shared" si="237"/>
+        <f t="shared" si="260"/>
         <v>0.38591187363011109</v>
       </c>
       <c r="I24" s="9">
-        <f t="shared" si="237"/>
+        <f t="shared" si="260"/>
         <v>0.37422597799956292</v>
       </c>
       <c r="J24" s="9">
-        <f t="shared" si="237"/>
+        <f t="shared" si="260"/>
         <v>0.40688187300461154</v>
       </c>
       <c r="K24" s="9">
-        <f t="shared" si="237"/>
+        <f t="shared" si="260"/>
         <v>0.16110632088611793</v>
       </c>
       <c r="L24" s="9">
-        <f t="shared" si="237"/>
+        <f t="shared" si="260"/>
         <v>0.15391912723823076</v>
       </c>
       <c r="M24" s="9">
-        <f t="shared" si="237"/>
+        <f t="shared" si="260"/>
         <v>0.34506004985270788</v>
       </c>
       <c r="N24" s="9">
-        <f t="shared" si="237"/>
+        <f t="shared" si="260"/>
         <v>0.34859121525471964</v>
       </c>
       <c r="O24" s="9">
-        <f t="shared" si="237"/>
+        <f t="shared" si="260"/>
         <v>0.27637142696059086</v>
       </c>
       <c r="P24" s="9">
-        <f t="shared" si="237"/>
+        <f t="shared" si="260"/>
         <v>0.27709102584684542</v>
       </c>
       <c r="Q24" s="9">
-        <f t="shared" si="237"/>
+        <f t="shared" si="260"/>
         <v>0.3654401490451793</v>
       </c>
       <c r="R24" s="9">
-        <f t="shared" si="237"/>
+        <f t="shared" si="260"/>
         <v>0.39965089769165002</v>
       </c>
       <c r="S24" s="9">
-        <f t="shared" si="237"/>
+        <f t="shared" si="260"/>
         <v>0.36288257995491191</v>
       </c>
       <c r="T24" s="9">
-        <f t="shared" si="237"/>
+        <f t="shared" si="260"/>
         <v>0.35746466279189737</v>
       </c>
       <c r="U24" s="9">
-        <f t="shared" si="237"/>
+        <f t="shared" si="260"/>
         <v>0.31692519820751464</v>
       </c>
       <c r="V24" s="9">
-        <f t="shared" si="237"/>
+        <f t="shared" si="260"/>
         <v>0.30545573342045085</v>
       </c>
       <c r="W24" s="9">
-        <f t="shared" si="237"/>
+        <f t="shared" si="260"/>
         <v>0.26748602551239786</v>
       </c>
       <c r="X24" s="9">
-        <f t="shared" si="237"/>
+        <f t="shared" si="260"/>
         <v>0.23201026993269031</v>
       </c>
       <c r="Y24" s="9">
-        <f t="shared" si="237"/>
+        <f t="shared" si="260"/>
         <v>0.15858410911452694</v>
       </c>
       <c r="Z24" s="9">
-        <f t="shared" si="237"/>
+        <f t="shared" si="260"/>
         <v>0.1446292554018343</v>
       </c>
       <c r="AA24" s="9">
-        <f t="shared" si="237"/>
+        <f t="shared" si="260"/>
         <v>0.19930179787048349</v>
       </c>
       <c r="AB24" s="9">
-        <f t="shared" si="237"/>
+        <f t="shared" si="260"/>
         <v>0.24338260570642833</v>
       </c>
       <c r="AC24" s="9">
-        <f t="shared" si="237"/>
+        <f t="shared" si="260"/>
         <v>0.34440376569037656</v>
       </c>
       <c r="AD24" s="9">
-        <f t="shared" si="237"/>
+        <f t="shared" si="260"/>
         <v>0.34945526164892421</v>
       </c>
       <c r="AE24" s="9">
-        <f t="shared" si="237"/>
+        <f t="shared" si="260"/>
         <v>0.33929502125908656</v>
       </c>
       <c r="AF24" s="9">
-        <f t="shared" si="237"/>
+        <f t="shared" si="260"/>
         <v>0.34462900872770086</v>
       </c>
       <c r="AG24" s="9">
-        <f t="shared" si="237"/>
+        <f t="shared" si="260"/>
         <v>0.38650865998176848</v>
       </c>
       <c r="AH24" s="9">
-        <f t="shared" si="237"/>
+        <f t="shared" si="260"/>
         <v>0.39863594089077192</v>
       </c>
       <c r="AI24" s="9">
-        <f t="shared" si="237"/>
+        <f t="shared" si="260"/>
         <v>0.39334499220116276</v>
       </c>
       <c r="AJ24" s="9">
-        <f t="shared" si="237"/>
+        <f t="shared" si="260"/>
         <v>0.38591211381429413</v>
       </c>
       <c r="AK24" s="9">
-        <f t="shared" si="237"/>
+        <f t="shared" si="260"/>
         <v>0.36374458452051051</v>
       </c>
       <c r="AL24" s="9">
-        <f t="shared" si="237"/>
+        <f t="shared" si="260"/>
         <v>0.3801445911876179</v>
       </c>
-      <c r="AM24" s="9"/>
-      <c r="AN24" s="9"/>
-      <c r="AO24" s="9"/>
-      <c r="AP24" s="9"/>
+      <c r="AM24" s="9">
+        <f t="shared" ref="AM24:AP24" si="261">AM13/AM3</f>
+        <v>0.32492870370370375</v>
+      </c>
+      <c r="AN24" s="9">
+        <f t="shared" si="261"/>
+        <v>0.33920589275191504</v>
+      </c>
+      <c r="AO24" s="9">
+        <f t="shared" si="261"/>
+        <v>0.32490843188530233</v>
+      </c>
+      <c r="AP24" s="9">
+        <f t="shared" si="261"/>
+        <v>0.33575050172808169</v>
+      </c>
       <c r="AQ24" s="9"/>
       <c r="AR24" s="9">
-        <f t="shared" ref="AR24:AV24" si="238">AR13/AR3</f>
+        <f t="shared" ref="AR24:AV24" si="262">AR13/AR3</f>
         <v>0.30699088145896658</v>
       </c>
       <c r="AS24" s="9">
-        <f t="shared" si="238"/>
+        <f t="shared" si="262"/>
         <v>0.2694691457828079</v>
       </c>
       <c r="AT24" s="9">
-        <f t="shared" si="238"/>
+        <f t="shared" si="262"/>
         <v>1.0414619768127334E-2</v>
       </c>
       <c r="AU24" s="9">
-        <f t="shared" si="238"/>
+        <f t="shared" si="262"/>
         <v>0.19054878048780488</v>
       </c>
       <c r="AV24" s="9">
-        <f t="shared" si="238"/>
+        <f t="shared" si="262"/>
         <v>0.2358414888496711</v>
       </c>
       <c r="AW24" s="9">
-        <f t="shared" ref="AW24:AY24" si="239">AW13/AW3</f>
+        <f t="shared" ref="AW24:AY24" si="263">AW13/AW3</f>
         <v>0.20571173583221777</v>
       </c>
       <c r="AX24" s="9">
-        <f t="shared" si="239"/>
+        <f t="shared" si="263"/>
         <v>0.36967219046240685</v>
       </c>
       <c r="AY24" s="9">
-        <f t="shared" si="239"/>
+        <f t="shared" si="263"/>
         <v>0.37399453914840231</v>
       </c>
       <c r="AZ24" s="9">
-        <f t="shared" ref="AZ24:BQ24" si="240">AZ13/AZ3</f>
+        <f t="shared" ref="AZ24:BQ24" si="264">AZ13/AZ3</f>
         <v>0.39600272216053584</v>
       </c>
       <c r="BA24" s="9">
-        <f t="shared" si="240"/>
+        <f t="shared" si="264"/>
         <v>0.26125896684918715</v>
       </c>
       <c r="BB24" s="9">
-        <f t="shared" si="240"/>
+        <f t="shared" si="264"/>
         <v>0.33902938370983876</v>
       </c>
       <c r="BC24" s="9">
-        <f t="shared" si="240"/>
+        <f t="shared" si="264"/>
         <v>0.33384494059985248</v>
       </c>
       <c r="BD24" s="9">
-        <f t="shared" si="240"/>
+        <f t="shared" si="264"/>
         <v>0.19894690804311846</v>
       </c>
       <c r="BE24" s="9">
-        <f t="shared" si="240"/>
+        <f t="shared" si="264"/>
         <v>0.29123850530069317</v>
       </c>
       <c r="BF24" s="9">
-        <f t="shared" si="240"/>
+        <f t="shared" si="264"/>
         <v>0.36966565349544073</v>
       </c>
       <c r="BG24" s="9">
-        <f t="shared" si="240"/>
+        <f t="shared" si="264"/>
         <v>0.38010748140223416</v>
       </c>
       <c r="BH24" s="9">
-        <f t="shared" si="240"/>
-        <v>0.36842787974111868</v>
+        <f t="shared" si="264"/>
+        <v>0.33146014534237955</v>
       </c>
       <c r="BI24" s="9">
-        <f t="shared" si="240"/>
-        <v>0.37469170524028322</v>
+        <f t="shared" si="264"/>
+        <v>0.3301919118055589</v>
       </c>
       <c r="BJ24" s="9">
-        <f t="shared" si="240"/>
-        <v>0.38097228109804726</v>
+        <f t="shared" si="264"/>
+        <v>0.32729343981866116</v>
       </c>
       <c r="BK24" s="9">
-        <f t="shared" si="240"/>
-        <v>0.38446245478925212</v>
+        <f t="shared" si="264"/>
+        <v>0.33065247631079864</v>
       </c>
       <c r="BL24" s="9">
-        <f t="shared" si="240"/>
-        <v>0.38505919509626035</v>
+        <f t="shared" si="264"/>
+        <v>0.33406624122282019</v>
       </c>
       <c r="BM24" s="9">
-        <f t="shared" si="240"/>
-        <v>0.38513389821859845</v>
+        <f t="shared" si="264"/>
+        <v>0.33748306937432643</v>
       </c>
       <c r="BN24" s="9">
-        <f t="shared" si="240"/>
-        <v>0.38513518721365053</v>
+        <f t="shared" si="264"/>
+        <v>0.3375979902949296</v>
       </c>
       <c r="BO24" s="9">
-        <f t="shared" si="240"/>
-        <v>0.38513520945513374</v>
+        <f t="shared" si="264"/>
+        <v>0.33759997324414792</v>
       </c>
       <c r="BP24" s="9">
-        <f t="shared" si="240"/>
-        <v>0.38513520983890842</v>
+        <f t="shared" si="264"/>
+        <v>0.33760000745974239</v>
       </c>
       <c r="BQ24" s="9">
-        <f t="shared" si="240"/>
-        <v>0.38513520984553046</v>
+        <f t="shared" si="264"/>
+        <v>0.33760000805012896</v>
       </c>
       <c r="BS24" t="s">
         <v>49</v>
       </c>
       <c r="BT24" s="5">
         <f>Main!D3</f>
-        <v>726.51</v>
+        <v>635.1</v>
       </c>
     </row>
     <row r="25" spans="2:72">
@@ -7501,7 +7750,7 @@
       </c>
       <c r="BT25" s="10">
         <f>BT23/BT24-1</f>
-        <v>0.14114250772650117</v>
+        <v>0.31247735652916564</v>
       </c>
     </row>
     <row r="26" spans="2:72">
@@ -7509,14 +7758,15 @@
         <v>67</v>
       </c>
       <c r="BT26" s="3" t="s">
-        <v>92</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -7530,7 +7780,7 @@
   <sheetData>
     <row r="2" spans="2:23">
       <c r="B2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="2:23">
@@ -7556,7 +7806,7 @@
         <v>2027</v>
       </c>
       <c r="J4" s="21" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K4" s="22">
         <v>2022</v>
@@ -7579,46 +7829,46 @@
     </row>
     <row r="5" spans="2:23">
       <c r="B5" s="24" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D5" s="25" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E5" s="25" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F5" s="25" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G5" s="26" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J5" s="24" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K5" s="25" t="s">
+        <v>129</v>
+      </c>
+      <c r="L5" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="M5" s="25" t="s">
+        <v>144</v>
+      </c>
+      <c r="N5" s="25" t="s">
+        <v>145</v>
+      </c>
+      <c r="O5" s="26" t="s">
         <v>130</v>
       </c>
-      <c r="L5" s="25" t="s">
-        <v>137</v>
-      </c>
-      <c r="M5" s="25" t="s">
-        <v>145</v>
-      </c>
-      <c r="N5" s="25" t="s">
-        <v>146</v>
-      </c>
-      <c r="O5" s="26" t="s">
-        <v>131</v>
-      </c>
       <c r="P5" s="27" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="R5" s="25" t="str">
         <f>LEFT(K5,4)</f>
@@ -7647,46 +7897,46 @@
     </row>
     <row r="6" spans="2:23">
       <c r="B6" s="28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E6" s="29" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F6" s="29" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G6" s="30" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H6" s="31" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J6" s="28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K6" s="29" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L6" s="29" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="M6" s="29" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="N6" s="29" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O6" s="30" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P6" s="31" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="R6" s="25" t="str">
         <f t="shared" ref="R6:R8" si="5">LEFT(K6,4)</f>
@@ -7715,46 +7965,46 @@
     </row>
     <row r="7" spans="2:23">
       <c r="B7" s="28" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C7" s="29" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D7" s="29" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E7" s="29" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F7" s="30" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G7" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H7" s="31" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J7" s="28" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K7" s="29" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L7" s="29" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="M7" s="29" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="N7" s="30" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O7" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P7" s="31" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="R7" s="25" t="str">
         <f t="shared" si="5"/>
@@ -7783,46 +8033,46 @@
     </row>
     <row r="8" spans="2:23">
       <c r="B8" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="C8" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="D8" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="E8" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="F8" s="30" t="s">
+        <v>116</v>
+      </c>
+      <c r="G8" s="30" t="s">
+        <v>124</v>
+      </c>
+      <c r="H8" s="32" t="s">
         <v>98</v>
       </c>
-      <c r="C8" s="29" t="s">
-        <v>104</v>
-      </c>
-      <c r="D8" s="29" t="s">
-        <v>113</v>
-      </c>
-      <c r="E8" s="29" t="s">
-        <v>121</v>
-      </c>
-      <c r="F8" s="30" t="s">
-        <v>117</v>
-      </c>
-      <c r="G8" s="30" t="s">
-        <v>125</v>
-      </c>
-      <c r="H8" s="32" t="s">
-        <v>99</v>
-      </c>
       <c r="J8" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="K8" s="29" t="s">
+        <v>135</v>
+      </c>
+      <c r="L8" s="29" t="s">
+        <v>138</v>
+      </c>
+      <c r="M8" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="N8" s="30" t="s">
+        <v>132</v>
+      </c>
+      <c r="O8" s="30" t="s">
+        <v>150</v>
+      </c>
+      <c r="P8" s="32" t="s">
         <v>98</v>
-      </c>
-      <c r="K8" s="29" t="s">
-        <v>136</v>
-      </c>
-      <c r="L8" s="29" t="s">
-        <v>139</v>
-      </c>
-      <c r="M8" s="29" t="s">
-        <v>142</v>
-      </c>
-      <c r="N8" s="30" t="s">
-        <v>133</v>
-      </c>
-      <c r="O8" s="30" t="s">
-        <v>151</v>
-      </c>
-      <c r="P8" s="32" t="s">
-        <v>99</v>
       </c>
       <c r="R8" s="25" t="str">
         <f t="shared" si="5"/>
@@ -7867,51 +8117,51 @@
     </row>
     <row r="10" spans="2:23">
       <c r="B10" s="33" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C10" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="D10" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="D10" s="34" t="s">
+      <c r="E10" s="34" t="s">
         <v>106</v>
       </c>
-      <c r="E10" s="34" t="s">
+      <c r="F10" s="35" t="s">
         <v>107</v>
       </c>
-      <c r="F10" s="35" t="s">
+      <c r="G10" s="35" t="s">
         <v>108</v>
       </c>
-      <c r="G10" s="35" t="s">
-        <v>109</v>
-      </c>
       <c r="H10" s="36" t="s">
+        <v>98</v>
+      </c>
+      <c r="J10" s="33" t="s">
         <v>99</v>
       </c>
-      <c r="J10" s="33" t="s">
-        <v>100</v>
-      </c>
       <c r="K10" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="L10" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="L10" s="34" t="s">
+      <c r="M10" s="34" t="s">
         <v>106</v>
       </c>
-      <c r="M10" s="34" t="s">
+      <c r="N10" s="35" t="s">
         <v>107</v>
       </c>
-      <c r="N10" s="35" t="s">
+      <c r="O10" s="35" t="s">
         <v>108</v>
       </c>
-      <c r="O10" s="35" t="s">
-        <v>109</v>
-      </c>
       <c r="P10" s="36" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12" spans="2:23">
       <c r="J12" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K12" s="45">
         <v>-0.21340000000000001</v>
@@ -7939,7 +8189,7 @@
     </row>
     <row r="13" spans="2:23">
       <c r="J13" s="28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K13" s="42">
         <v>-0.35699999999999998</v>
@@ -7967,7 +8217,7 @@
     </row>
     <row r="14" spans="2:23">
       <c r="J14" s="28" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K14" s="42">
         <v>-0.52200000000000002</v>
@@ -7996,7 +8246,7 @@
     </row>
     <row r="15" spans="2:23">
       <c r="J15" s="28" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K15" s="42">
         <v>-0.54800000000000004</v>
@@ -8018,7 +8268,7 @@
         <v>8.7804878048780566E-2</v>
       </c>
       <c r="P15" s="49" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" spans="2:23">
@@ -8032,7 +8282,7 @@
     </row>
     <row r="17" spans="10:16">
       <c r="J17" s="33" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K17" s="43">
         <v>-0.41399999999999998</v>
@@ -8050,7 +8300,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
       <c r="P17" s="36" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18" spans="10:16">
